--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -25814,22 +25814,22 @@
       </c>
       <c r="I346" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>ustawienie po stronie GitHuba (Settings → Branches → Add rule), nie da się go zapisać w repo</t>
+          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="K346" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L346" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M346" s="11" t="inlineStr">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="N346" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01 — nie spełnia żadnego z czterech warunków blokera. Do zrobienia ręcznie przez PM: reguła na main z wymaganym statusem joba CI. Procedura krok po kroku: docs/zadania/X-02-status-wymagany-do-merge.md. Bez tego bramka testowa jest dobrowolna.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$354</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$355</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$354,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$355,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$354,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$355,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$354,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$355,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$354,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$355,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$354,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$355,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$354,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$355,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$354,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$355,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$354,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$355,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$354,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$355,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$354,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$355,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"A",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"A",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"A",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"A",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"B",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"B",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"B",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"B",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"C",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"C",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"C",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"C",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"D",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"D",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"D",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"D",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"E",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"E",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"E",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"E",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"F",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"F",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"F",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"F",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"G",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"G",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"G",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"G",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"H",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"H",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"H",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"H",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"I",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"I",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"I",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"I",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"J",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"J",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"J",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"J",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"K",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"K",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"K",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"K",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"L",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"L",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"L",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"L",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"M",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"M",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"M",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"M",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"N",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"N",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"N",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"N",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"O",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"O",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"O",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"O",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"P",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"P",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"P",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"P",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Q",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"Q",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Q",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Q",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"X",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"X",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"X",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"X",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$354,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$355,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Z",Macierz!$K$2:$K$354,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$354,"Z",Macierz!$K$2:$K$354,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Z",Macierz!$K$2:$K$354,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$354,"Z",Macierz!$L$2:$L$354,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N354"/>
+  <dimension ref="A1:N355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20699,7 +20699,7 @@
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit fcf58db). Dwie warstwy: walidacja DTO i twardy warunek w serwisie. Osiem przypadków testowych, sprawdzone też w drugą stronę — na starym kodzie test świeci na czerwono. Dodatkowo @RateLimit 10/h na POST /subscriptions. Pełne D2 po pierwszym zielonym przebiegu CI. Dokumentacja: docs/zadania/Z-02-blokada-zamowienia-uslugi-bez-oplaty.md</t>
+          <t>Zamknięte 2026-08-21 (commit fcf58db). Dwie warstwy: walidacja DTO i twardy warunek w serwisie. Osiem przypadków testowych, sprawdzone też w drugą stronę — na starym kodzie test świeci na czerwono. Dodatkowo @RateLimit 10/h na POST /subscriptions. D2 potwierdzone w CI #18 (2026-08-21): 194 testy zielone, w tym 8 przypadków tego zadania. Dokumentacja: docs/zadania/Z-02-blokada-zamowienia-uslugi-bez-oplaty.md</t>
         </is>
       </c>
     </row>
@@ -25742,7 +25742,7 @@
       </c>
       <c r="I345" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J345" s="12" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="K345" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L345" s="11" t="inlineStr">
@@ -25767,7 +25767,7 @@
       </c>
       <c r="N345" s="12" t="inlineStr">
         <is>
-          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Stan CZĘŚCIOWE do pierwszego zielonego przebiegu — dopiero on daje D2.</t>
+          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
         </is>
       </c>
     </row>
@@ -26411,9 +26411,81 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="11" t="inlineStr">
+        <is>
+          <t>X-11</t>
+        </is>
+      </c>
+      <c r="B355" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C355" s="11" t="inlineStr">
+        <is>
+          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
+        </is>
+      </c>
+      <c r="D355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I355" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J355" s="12" t="inlineStr">
+        <is>
+          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
+        </is>
+      </c>
+      <c r="K355" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L355" s="11" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="M355" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N355" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N354"/>
-  <conditionalFormatting sqref="D2:D354">
+  <autoFilter ref="A1:N355"/>
+  <conditionalFormatting sqref="D2:D355">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26430,7 +26502,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E354">
+  <conditionalFormatting sqref="E2:E355">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26447,7 +26519,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F354">
+  <conditionalFormatting sqref="F2:F355">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26464,7 +26536,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G354">
+  <conditionalFormatting sqref="G2:G355">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26481,7 +26553,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H354">
+  <conditionalFormatting sqref="H2:H355">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26498,7 +26570,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I354">
+  <conditionalFormatting sqref="I2:I355">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26518,7 +26590,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K354">
+  <conditionalFormatting sqref="K2:K355">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26535,7 +26607,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L354">
+  <conditionalFormatting sqref="L2:L355">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$356</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$355,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$356,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$355,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$356,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$355,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$356,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$355,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$356,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$355,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$356,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$355,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$356,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$355,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$356,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$355,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$356,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$355,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$356,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$355,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$356,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"A",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"B",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"C",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"D",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"E",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"F",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"G",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"H",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"I",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"J",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"K",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"L",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"M",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"N",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"O",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"P",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Q",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"X",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$355,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$356,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$K$2:$K$355,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$355,"Z",Macierz!$L$2:$L$355,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N355"/>
+  <dimension ref="A1:N356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12426,22 +12426,22 @@
       </c>
       <c r="I156" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>node-migration-worker.sh:250,253 — eval z interpolacją ${db}; :217 lftp -e z ${spath}; dto/migration.dto.ts:88-89 remotePath tylko @MaxLength, :108-109 database tylko @MaxLength, :95-96 protocol bez @IsIn; wartości przekazywane bez zmian (migration-orchestrator.service.ts:643,1277); skrypt działa jako root</t>
+          <t>dto/migration.dto.ts — MIGRACJA_WZORCE + @Matches na 17 polach; ops/scripts/lib/migration-input-guard.sh — vg_require; node-migration-worker.sh — fail-closed source + zero eval</t>
         </is>
       </c>
       <c r="K156" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L156" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="N156" s="12" t="inlineStr">
         <is>
-          <t>Wykonanie dowolnego polecenia jako root na węźle hostingowym, z formularza migracji w panelu klienta. Jeden klient przejmuje węzeł i wszystkie konta pozostałych. Ta sama klasa błędu w node-wp-install.sh:132 i node-app-install.sh:46,64 (tam bez eskalacji uprawnień).</t>
+          <t>Zamknięte 2026-08-21. Trzy wektory: eval z nazwą bazy, łańcuch poleceń lftp ze ścieżką zdalną, eval przy imporcie — wszystkie usunięte, plus allowlista znaków na obu warstwach (DTO i węzeł). Worker startuje fail-closed bez biblioteki walidacji (kod 78), sprawdzone zachowaniem w teście. 70 przypadków testowych, 48 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy dostępu. Dokumentacja: docs/zadania/Z-03-walidacja-danych-migracji.md</t>
         </is>
       </c>
     </row>
@@ -20994,75 +20994,79 @@
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>N-01</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B278" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>System zgłoszeń dla klienta</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="D278" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E278" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F278" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G278" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H278" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J278" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:92,98</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
       <c r="K278" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L278" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M278" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N278" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N278" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-03. Walidacja znaków nie mówi nic o tym, DOKĄD worker się łączy. Klient może podać 127.0.0.1 albo adres z sieci wewnętrznej węzła i użyć workera jako sondy. Do zrobienia: odrzucanie adresów prywatnych i loopbacka po rozwiązaniu nazwy, z uwzględnieniem rebindingu DNS (sprawdzenie przy każdym połączeniu, nie tylko przy walidacji formularza).</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>N-02</t>
+          <t>N-01</t>
         </is>
       </c>
       <c r="B279" s="12" t="inlineStr">
@@ -21072,7 +21076,7 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>Załączniki w zgłoszeniu</t>
+          <t>System zgłoszeń dla klienta</t>
         </is>
       </c>
       <c r="D279" s="11" t="inlineStr">
@@ -21087,7 +21091,7 @@
       </c>
       <c r="F279" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G279" s="11" t="inlineStr">
@@ -21107,7 +21111,7 @@
       </c>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:98,245</t>
+          <t>tickets.controller.ts:92,98</t>
         </is>
       </c>
       <c r="K279" s="11" t="inlineStr">
@@ -21130,7 +21134,7 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>N-03</t>
+          <t>N-02</t>
         </is>
       </c>
       <c r="B280" s="12" t="inlineStr">
@@ -21140,7 +21144,7 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Ocena obsługi (CSAT)</t>
+          <t>Załączniki w zgłoszeniu</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
@@ -21155,17 +21159,17 @@
       </c>
       <c r="F280" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H280" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I280" s="11" t="inlineStr">
@@ -21175,12 +21179,12 @@
       </c>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:279</t>
+          <t>tickets.controller.ts:98,245</t>
         </is>
       </c>
       <c r="K280" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L280" s="11" t="inlineStr">
@@ -21198,7 +21202,7 @@
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>N-04</t>
+          <t>N-03</t>
         </is>
       </c>
       <c r="B281" s="12" t="inlineStr">
@@ -21208,7 +21212,7 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy po polsku</t>
+          <t>Ocena obsługi (CSAT)</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
@@ -21228,12 +21232,12 @@
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H281" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I281" s="11" t="inlineStr">
@@ -21243,12 +21247,12 @@
       </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>kb.public.controller.ts:226</t>
+          <t>tickets.controller.ts:279</t>
         </is>
       </c>
       <c r="K281" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L281" s="11" t="inlineStr">
@@ -21266,7 +21270,7 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>N-04</t>
         </is>
       </c>
       <c r="B282" s="12" t="inlineStr">
@@ -21276,7 +21280,7 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Baza wiedzy po polsku</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
@@ -21296,37 +21300,37 @@
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>kb.public.controller.ts:226</t>
         </is>
       </c>
       <c r="K282" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L282" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M282" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N282" s="12" t="inlineStr"/>
@@ -21334,7 +21338,7 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>N-06</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B283" s="12" t="inlineStr">
@@ -21344,7 +21348,7 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>Publiczna strona statusu usług</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="D283" s="11" t="inlineStr">
@@ -21364,49 +21368,45 @@
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H283" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H283" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I283" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>probes-admin.controller.ts:33; apps/status-page</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
       <c r="K283" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L283" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M283" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N283" s="12" t="inlineStr">
-        <is>
-          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N283" s="12" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>N-06</t>
         </is>
       </c>
       <c r="B284" s="12" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Publiczna strona statusu usług</t>
         </is>
       </c>
       <c r="D284" s="11" t="inlineStr">
@@ -21446,39 +21446,39 @@
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>probes-admin.controller.ts:33; apps/status-page</t>
         </is>
       </c>
       <c r="K284" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L284" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M284" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N284" s="12" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>N-08</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B285" s="12" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Edycja i zamknięcie incydentu</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="D285" s="11" t="inlineStr">
@@ -21518,35 +21518,39 @@
       </c>
       <c r="I285" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>status/actions.ts:158,177</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="K285" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L285" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M285" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N285" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N285" s="12" t="inlineStr">
+        <is>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>N-09</t>
+          <t>N-08</t>
         </is>
       </c>
       <c r="B286" s="12" t="inlineStr">
@@ -21556,7 +21560,7 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienia w panelu (dzwonek)</t>
+          <t>Edycja i zamknięcie incydentu</t>
         </is>
       </c>
       <c r="D286" s="11" t="inlineStr">
@@ -21566,19 +21570,19 @@
       </c>
       <c r="E286" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F286" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G286" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F286" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G286" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H286" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -21591,7 +21595,7 @@
       </c>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>notifications.controller.ts:12,20,26</t>
+          <t>status/actions.ts:158,177</t>
         </is>
       </c>
       <c r="K286" s="11" t="inlineStr">
@@ -21614,7 +21618,7 @@
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-09</t>
         </is>
       </c>
       <c r="B287" s="12" t="inlineStr">
@@ -21624,7 +21628,7 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Powiadomienia w panelu (dzwonek)</t>
         </is>
       </c>
       <c r="D287" s="11" t="inlineStr">
@@ -21654,39 +21658,35 @@
       </c>
       <c r="I287" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>notifications.controller.ts:12,20,26</t>
         </is>
       </c>
       <c r="K287" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L287" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M287" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N287" s="12" t="inlineStr">
-        <is>
-          <t>sterowalne są tylko zgody marketingowe</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N287" s="12" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B288" s="12" t="inlineStr">
@@ -21696,69 +21696,69 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E288" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E288" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="F288" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G288" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G288" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H288" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J288" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
       <c r="K288" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L288" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M288" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N288" s="12" t="inlineStr">
         <is>
-          <t>cały panel Product Ops/NOC jest read-only</t>
+          <t>sterowalne są tylko zgody marketingowe</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B289" s="12" t="inlineStr">
@@ -21768,32 +21768,32 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E289" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F289" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F289" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G289" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H289" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I289" s="11" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
       <c r="K289" s="11" t="inlineStr">
@@ -21813,20 +21813,24 @@
       </c>
       <c r="L289" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M289" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N289" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N289" s="12" t="inlineStr">
+        <is>
+          <t>cały panel Product Ops/NOC jest read-only</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B290" s="12" t="inlineStr">
@@ -21836,42 +21840,42 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E290" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F290" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G290" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H290" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
       <c r="K290" s="11" t="inlineStr">
@@ -21881,24 +21885,20 @@
       </c>
       <c r="L290" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M290" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N290" s="12" t="inlineStr">
-        <is>
-          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N290" s="12" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B291" s="12" t="inlineStr">
@@ -21908,42 +21908,42 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E291" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F291" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E291" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F291" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I291" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
       <c r="K291" s="11" t="inlineStr">
@@ -21958,19 +21958,19 @@
       </c>
       <c r="M291" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N291" s="12" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>N-15</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B292" s="12" t="inlineStr">
@@ -21980,69 +21980,69 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E292" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F292" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>cockpit migracji + kreator klienta</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="K292" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L292" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M292" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N292" s="12" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>N-15</t>
         </is>
       </c>
       <c r="B293" s="12" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
         </is>
       </c>
       <c r="D293" s="11" t="inlineStr">
@@ -22072,49 +22072,49 @@
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H293" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H293" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="I293" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>cockpit migracji + kreator klienta</t>
         </is>
       </c>
       <c r="K293" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L293" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M293" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N293" s="12" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>N-17</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B294" s="12" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Szablony odpowiedzi obsługi</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
@@ -22139,50 +22139,54 @@
       </c>
       <c r="F294" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G294" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G294" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H294" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J294" s="12" t="inlineStr">
         <is>
-          <t>settings/canned-responses/actions.ts:23</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="K294" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L294" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M294" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N294" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N294" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>N-18</t>
+          <t>N-17</t>
         </is>
       </c>
       <c r="B295" s="12" t="inlineStr">
@@ -22192,7 +22196,7 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>CRM klienta 360 dla obsługi</t>
+          <t>Szablony odpowiedzi obsługi</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
@@ -22207,7 +22211,7 @@
       </c>
       <c r="F295" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G295" s="11" t="inlineStr">
@@ -22227,12 +22231,12 @@
       </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
+          <t>settings/canned-responses/actions.ts:23</t>
         </is>
       </c>
       <c r="K295" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L295" s="11" t="inlineStr">
@@ -22250,7 +22254,7 @@
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>N-19</t>
+          <t>N-18</t>
         </is>
       </c>
       <c r="B296" s="12" t="inlineStr">
@@ -22260,7 +22264,7 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
+          <t>CRM klienta 360 dla obsługi</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
@@ -22280,12 +22284,12 @@
       </c>
       <c r="G296" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H296" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I296" s="11" t="inlineStr">
@@ -22295,7 +22299,7 @@
       </c>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>ai-chat.service.ts (223 l.)</t>
+          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
         </is>
       </c>
       <c r="K296" s="11" t="inlineStr">
@@ -22313,16 +22317,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N296" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
-        </is>
-      </c>
+      <c r="N296" s="12" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-19</t>
         </is>
       </c>
       <c r="B297" s="12" t="inlineStr">
@@ -22332,65 +22332,69 @@
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
         </is>
       </c>
       <c r="D297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H297" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I297" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>ai-chat.service.ts (223 l.)</t>
         </is>
       </c>
       <c r="K297" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L297" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M297" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N297" s="12" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N297" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B298" s="12" t="inlineStr">
@@ -22400,42 +22404,42 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E298" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F298" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J298" s="12" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
       <c r="K298" s="11" t="inlineStr">
@@ -22450,74 +22454,70 @@
       </c>
       <c r="M298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N298" s="12" t="inlineStr">
-        <is>
-          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N298" s="12" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B299" s="12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Subkonta z uprawnieniami (IAM)</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E299" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F299" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G299" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H299" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G299" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H299" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I299" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:42,53,63,69</t>
+          <t>poza produktem</t>
         </is>
       </c>
       <c r="K299" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M299" s="11" t="inlineStr">
@@ -22527,14 +22527,14 @@
       </c>
       <c r="N299" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="B300" s="12" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Aktywacja subkonta z zaproszenia</t>
+          <t>Subkonta z uprawnieniami (IAM)</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
@@ -22579,12 +22579,12 @@
       </c>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:47</t>
+          <t>customer-iam.controller.ts:42,53,63,69</t>
         </is>
       </c>
       <c r="K300" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L300" s="11" t="inlineStr">
@@ -22597,12 +22597,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N300" s="12" t="inlineStr"/>
+      <c r="N300" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>O-02</t>
         </is>
       </c>
       <c r="B301" s="12" t="inlineStr">
@@ -22612,69 +22616,65 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Aktywacja subkonta z zaproszenia</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F301" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E301" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F301" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G301" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H301" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I301" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>customer-iam.controller.ts:47</t>
         </is>
       </c>
       <c r="K301" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L301" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M301" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N301" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N301" s="12" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B302" s="12" t="inlineStr">
@@ -22684,12 +22684,12 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Egzekwowanie uprawnień w nawigacji i API</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E302" s="11" t="inlineStr">
@@ -22699,50 +22699,54 @@
       </c>
       <c r="F302" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G302" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H302" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G302" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
       <c r="K302" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L302" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M302" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N302" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N302" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-04</t>
         </is>
       </c>
       <c r="B303" s="12" t="inlineStr">
@@ -22752,7 +22756,7 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Egzekwowanie uprawnień w nawigacji i API</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
@@ -22767,42 +22771,42 @@
       </c>
       <c r="F303" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
         </is>
       </c>
       <c r="K303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L303" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M303" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
@@ -22810,7 +22814,7 @@
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B304" s="12" t="inlineStr">
@@ -22820,7 +22824,7 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
@@ -22850,17 +22854,17 @@
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
       <c r="K304" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L304" s="11" t="inlineStr">
@@ -22873,16 +22877,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N304" s="12" t="inlineStr">
-        <is>
-          <t>bez tego reseller nie jest produktem</t>
-        </is>
-      </c>
+      <c r="N304" s="12" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B305" s="12" t="inlineStr">
@@ -22892,7 +22892,7 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
@@ -22922,35 +22922,39 @@
       </c>
       <c r="I305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L305" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M305" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N305" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N305" s="12" t="inlineStr">
+        <is>
+          <t>bez tego reseller nie jest produktem</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B306" s="12" t="inlineStr">
@@ -22960,47 +22964,47 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E306" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F306" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G306" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E306" s="11" t="inlineStr">
+      <c r="H306" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F306" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G306" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H306" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
       <c r="K306" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L306" s="11" t="inlineStr">
@@ -23013,16 +23017,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N306" s="12" t="inlineStr">
-        <is>
-          <t>strona sprzedażowa bez operacji zapisu</t>
-        </is>
-      </c>
+      <c r="N306" s="12" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B307" s="12" t="inlineStr">
@@ -23032,22 +23032,22 @@
       </c>
       <c r="C307" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="D307" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E307" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F307" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G307" s="11" t="inlineStr">
@@ -23062,17 +23062,17 @@
       </c>
       <c r="I307" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
       <c r="K307" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L307" s="11" t="inlineStr">
@@ -23082,19 +23082,19 @@
       </c>
       <c r="M307" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N307" s="12" t="inlineStr">
         <is>
-          <t>seohost to reklamuje jako wyróżnik</t>
+          <t>strona sprzedażowa bez operacji zapisu</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>O-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B308" s="12" t="inlineStr">
@@ -23104,7 +23104,7 @@
       </c>
       <c r="C308" s="11" t="inlineStr">
         <is>
-          <t>Role i uprawnienia operatorów</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="D308" s="11" t="inlineStr">
@@ -23124,45 +23124,49 @@
       </c>
       <c r="G308" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H308" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:31,36,41</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
       <c r="K308" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L308" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M308" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N308" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N308" s="12" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje jako wyróżnik</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>O-11</t>
+          <t>O-10</t>
         </is>
       </c>
       <c r="B309" s="12" t="inlineStr">
@@ -23172,7 +23176,7 @@
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>Zarządzanie operatorami</t>
+          <t>Role i uprawnienia operatorów</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
@@ -23207,7 +23211,7 @@
       </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:51,56,61</t>
+          <t>staff-roles.admin.controller.ts:31,36,41</t>
         </is>
       </c>
       <c r="K309" s="11" t="inlineStr">
@@ -23230,7 +23234,7 @@
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>O-12</t>
+          <t>O-11</t>
         </is>
       </c>
       <c r="B310" s="12" t="inlineStr">
@@ -23240,32 +23244,32 @@
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Program partnerski / afiliacyjny</t>
+          <t>Zarządzanie operatorami</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E310" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F310" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H310" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I310" s="11" t="inlineStr">
@@ -23275,7 +23279,7 @@
       </c>
       <c r="J310" s="12" t="inlineStr">
         <is>
-          <t>partners.controller.ts:18,28,34</t>
+          <t>staff-roles.admin.controller.ts:51,56,61</t>
         </is>
       </c>
       <c r="K310" s="11" t="inlineStr">
@@ -23293,16 +23297,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N310" s="12" t="inlineStr">
-        <is>
-          <t>wypłata na portfel lub IBAN</t>
-        </is>
-      </c>
+      <c r="N310" s="12" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>Z-04</t>
+          <t>O-12</t>
         </is>
       </c>
       <c r="B311" s="12" t="inlineStr">
@@ -23312,29 +23312,29 @@
       </c>
       <c r="C311" s="11" t="inlineStr">
         <is>
-          <t>Guard uprawnień subkont — domyślna odmowa</t>
+          <t>Program partnerski / afiliacyjny</t>
         </is>
       </c>
       <c r="D311" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E311" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F311" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G311" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G311" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H311" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -23342,66 +23342,66 @@
       </c>
       <c r="I311" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>customer-permissions.guard.ts:75 — inferCustomerRoutePermissions kończy się return [] (zezwól) dla trasy niedopasowanej; addons/* i vps nie pasują do żadnej gałęzi; addon.service.ts:105 i vps.service.ts:174 zdejmują środki z portfela; jwt.strategy.ts:94 ustawia userId = customerOwnerId</t>
+          <t>partners.controller.ts:18,28,34</t>
         </is>
       </c>
       <c r="K311" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L311" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M311" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N311" s="12" t="inlineStr">
         <is>
-          <t>Subkonto zaproszone wyłącznie z uprawnieniem TICKETS_READ może wydawać środki z portfela właściciela i kupować VPS na jego rachunek. Guard musi domyślnie odmawiać, nie zezwalać.</t>
+          <t>wypłata na portfel lub IBAN</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>Z-04</t>
         </is>
       </c>
       <c r="B312" s="12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C312" s="11" t="inlineStr">
         <is>
-          <t>Eksport danych osobowych (art. 20)</t>
+          <t>Guard uprawnień subkont — domyślna odmowa</t>
         </is>
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E312" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F312" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F312" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G312" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
@@ -23409,44 +23409,44 @@
       </c>
       <c r="H312" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I312" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
+          <t>customer-permissions.guard.ts:75 — inferCustomerRoutePermissions kończy się return [] (zezwól) dla trasy niedopasowanej; addons/* i vps nie pasują do żadnej gałęzi; addon.service.ts:105 i vps.service.ts:174 zdejmują środki z portfela; jwt.strategy.ts:94 ustawia userId = customerOwnerId</t>
         </is>
       </c>
       <c r="K312" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L312" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="M312" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N312" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>Subkonto zaproszone wyłącznie z uprawnieniem TICKETS_READ może wydawać środki z portfela właściciela i kupować VPS na jego rachunek. Guard musi domyślnie odmawiać, nie zezwalać.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B313" s="12" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="C313" s="11" t="inlineStr">
         <is>
-          <t>Żądanie usunięcia konta (art. 17)</t>
+          <t>Eksport danych osobowych (art. 20)</t>
         </is>
       </c>
       <c r="D313" s="11" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.service.ts:29,308,383-432</t>
+          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
         </is>
       </c>
       <c r="K313" s="11" t="inlineStr">
@@ -23501,7 +23501,7 @@
       </c>
       <c r="L313" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M313" s="11" t="inlineStr">
@@ -23511,14 +23511,14 @@
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
+          <t>ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B314" s="12" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="C314" s="11" t="inlineStr">
         <is>
-          <t>Wycofanie żądania usunięcia</t>
+          <t>Żądanie usunięcia konta (art. 17)</t>
         </is>
       </c>
       <c r="D314" s="11" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="E314" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F314" s="11" t="inlineStr">
@@ -23548,12 +23548,12 @@
       </c>
       <c r="G314" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H314" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I314" s="11" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.controller.ts:62</t>
+          <t>account-deletion.service.ts:29,308,383-432</t>
         </is>
       </c>
       <c r="K314" s="11" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="L314" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M314" s="11" t="inlineStr">
@@ -23583,14 +23583,14 @@
       </c>
       <c r="N314" s="12" t="inlineStr">
         <is>
-          <t>karencja 14 dni</t>
+          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B315" s="12" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Historia zgód klienta</t>
+          <t>Wycofanie żądania usunięcia</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E315" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F315" s="11" t="inlineStr">
@@ -23620,12 +23620,12 @@
       </c>
       <c r="G315" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H315" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I315" s="11" t="inlineStr">
@@ -23635,12 +23635,12 @@
       </c>
       <c r="J315" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:70</t>
+          <t>account-deletion.controller.ts:62</t>
         </is>
       </c>
       <c r="K315" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L315" s="11" t="inlineStr">
@@ -23653,12 +23653,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N315" s="12" t="inlineStr"/>
+      <c r="N315" s="12" t="inlineStr">
+        <is>
+          <t>karencja 14 dni</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="B316" s="12" t="inlineStr">
@@ -23668,7 +23672,7 @@
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>Ponowna akceptacja przy zmianie regulaminu</t>
+          <t>Historia zgód klienta</t>
         </is>
       </c>
       <c r="D316" s="11" t="inlineStr">
@@ -23678,7 +23682,7 @@
       </c>
       <c r="E316" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F316" s="11" t="inlineStr">
@@ -23703,12 +23707,12 @@
       </c>
       <c r="J316" s="12" t="inlineStr">
         <is>
-          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
+          <t>consents.controller.ts:70</t>
         </is>
       </c>
       <c r="K316" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L316" s="11" t="inlineStr">
@@ -23726,7 +23730,7 @@
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="B317" s="12" t="inlineStr">
@@ -23736,7 +23740,7 @@
       </c>
       <c r="C317" s="11" t="inlineStr">
         <is>
-          <t>Umowa powierzenia (DPA) do pobrania</t>
+          <t>Ponowna akceptacja przy zmianie regulaminu</t>
         </is>
       </c>
       <c r="D317" s="11" t="inlineStr">
@@ -23746,24 +23750,24 @@
       </c>
       <c r="E317" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F317" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G317" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F317" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G317" s="11" t="inlineStr">
+      <c r="H317" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H317" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I317" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -23771,7 +23775,7 @@
       </c>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
+          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
         </is>
       </c>
       <c r="K317" s="11" t="inlineStr">
@@ -23794,7 +23798,7 @@
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="B318" s="12" t="inlineStr">
@@ -23804,7 +23808,7 @@
       </c>
       <c r="C318" s="11" t="inlineStr">
         <is>
-          <t>Dokumenty prawne z historią wersji</t>
+          <t>Umowa powierzenia (DPA) do pobrania</t>
         </is>
       </c>
       <c r="D318" s="11" t="inlineStr">
@@ -23814,7 +23818,7 @@
       </c>
       <c r="E318" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F318" s="11" t="inlineStr">
@@ -23839,7 +23843,7 @@
       </c>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>legal-documents.controller.ts:36,49</t>
+          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
         </is>
       </c>
       <c r="K318" s="11" t="inlineStr">
@@ -23857,16 +23861,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N318" s="12" t="inlineStr">
-        <is>
-          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
-        </is>
-      </c>
+      <c r="N318" s="12" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="B319" s="12" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Retencja i anonimizacja logów</t>
+          <t>Dokumenty prawne z historią wersji</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
@@ -23886,22 +23886,22 @@
       </c>
       <c r="E319" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F319" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G319" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F319" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G319" s="11" t="inlineStr">
-        <is>
-          <t>b.d.</t>
-        </is>
-      </c>
       <c r="H319" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I319" s="11" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="J319" s="12" t="inlineStr">
         <is>
-          <t>retention.scheduler.ts:29,30,87,95</t>
+          <t>legal-documents.controller.ts:36,49</t>
         </is>
       </c>
       <c r="K319" s="11" t="inlineStr">
@@ -23931,14 +23931,14 @@
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B320" s="12" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Zgody marketingowe (opt-in/out)</t>
+          <t>Retencja i anonimizacja logów</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="E320" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F320" s="11" t="inlineStr">
@@ -23968,12 +23968,12 @@
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H320" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I320" s="11" t="inlineStr">
@@ -23983,12 +23983,12 @@
       </c>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:99</t>
+          <t>retention.scheduler.ts:29,30,87,95</t>
         </is>
       </c>
       <c r="K320" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L320" s="11" t="inlineStr">
@@ -24001,12 +24001,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N320" s="12" t="inlineStr"/>
+      <c r="N320" s="12" t="inlineStr">
+        <is>
+          <t>ZERO testów</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B321" s="12" t="inlineStr">
@@ -24016,7 +24020,7 @@
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Baner zgody na cookies</t>
+          <t>Zgody marketingowe (opt-in/out)</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
@@ -24051,7 +24055,7 @@
       </c>
       <c r="J321" s="12" t="inlineStr">
         <is>
-          <t>cookie-consent.tsx</t>
+          <t>consents.controller.ts:99</t>
         </is>
       </c>
       <c r="K321" s="11" t="inlineStr">
@@ -24074,7 +24078,7 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="B322" s="12" t="inlineStr">
@@ -24084,7 +24088,7 @@
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Baner zgody na cookies</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
@@ -24104,49 +24108,45 @@
       </c>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H322" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I322" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>cookie-consent.tsx</t>
         </is>
       </c>
       <c r="K322" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L322" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M322" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N322" s="12" t="inlineStr">
-        <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N322" s="12" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B323" s="12" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="C323" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="D323" s="11" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="E323" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F323" s="11" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
       <c r="K323" s="11" t="inlineStr">
@@ -24206,19 +24206,19 @@
       </c>
       <c r="M323" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N323" s="12" t="inlineStr">
         <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B324" s="12" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C324" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="D324" s="11" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="E324" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F324" s="11" t="inlineStr">
@@ -24248,27 +24248,27 @@
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H324" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I324" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
       <c r="K324" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L324" s="11" t="inlineStr">
@@ -24278,19 +24278,19 @@
       </c>
       <c r="M324" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N324" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to eksponuje</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B325" s="12" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="C325" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="D325" s="11" t="inlineStr">
@@ -24320,49 +24320,49 @@
       </c>
       <c r="G325" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H325" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H325" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I325" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>poza kodem</t>
         </is>
       </c>
       <c r="K325" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L325" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M325" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>wszystkie 5 hostingów PL to eksponuje</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B326" s="12" t="inlineStr">
@@ -24372,32 +24372,32 @@
       </c>
       <c r="C326" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="D326" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E326" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F326" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H326" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I326" s="11" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="J326" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K326" s="11" t="inlineStr">
@@ -24417,96 +24417,96 @@
       </c>
       <c r="L326" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M326" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N326" s="12" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>Q-01</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B327" s="12" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Program eko / punkty za oszczędność</t>
+          <t>Podpisane DPA z subprocesorami</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E327" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F327" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H327" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I327" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
         <is>
-          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="K327" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="M327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
-          <t>nikt na rynku PL</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>Q-02</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="B328" s="12" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Raport energetyczny usługi</t>
+          <t>Program eko / punkty za oszczędność</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
@@ -24546,12 +24546,12 @@
       </c>
       <c r="I328" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J328" s="12" t="inlineStr">
         <is>
-          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
+          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
         </is>
       </c>
       <c r="K328" s="11" t="inlineStr">
@@ -24571,14 +24571,14 @@
       </c>
       <c r="N328" s="12" t="inlineStr">
         <is>
-          <t>metodologia opisana — uczciwe podejście</t>
+          <t>nikt na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>Q-03</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="B329" s="12" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Badge eko do osadzenia na stronie klienta</t>
+          <t>Raport energetyczny usługi</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="I329" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
         <is>
-          <t>eco-public.controller.ts:32,74; test D1</t>
+          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
         </is>
       </c>
       <c r="K329" s="11" t="inlineStr">
@@ -24643,14 +24643,14 @@
       </c>
       <c r="N329" s="12" t="inlineStr">
         <is>
-          <t>4 warianty + pixel odsłon</t>
+          <t>metodologia opisana — uczciwe podejście</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>Q-04</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="B330" s="12" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Tryb eko usługi</t>
+          <t>Badge eko do osadzenia na stronie klienta</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
@@ -24695,7 +24695,7 @@
       </c>
       <c r="J330" s="12" t="inlineStr">
         <is>
-          <t>subscriptions.controller.ts:73</t>
+          <t>eco-public.controller.ts:32,74; test D1</t>
         </is>
       </c>
       <c r="K330" s="11" t="inlineStr">
@@ -24715,14 +24715,14 @@
       </c>
       <c r="N330" s="12" t="inlineStr">
         <is>
-          <t>wpływa m.in. na politykę backupów</t>
+          <t>4 warianty + pixel odsłon</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>Q-05</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="B331" s="12" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>E-mail marketing wbudowany w panel</t>
+          <t>Tryb eko usługi</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="G331" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H331" s="11" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="J331" s="12" t="inlineStr">
         <is>
-          <t>email-marketing.controller.ts:36,81,119,139</t>
+          <t>subscriptions.controller.ts:73</t>
         </is>
       </c>
       <c r="K331" s="11" t="inlineStr">
@@ -24787,14 +24787,14 @@
       </c>
       <c r="N331" s="12" t="inlineStr">
         <is>
-          <t>double opt-in + cordon antyspamowy</t>
+          <t>wpływa m.in. na politykę backupów</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>Q-05</t>
         </is>
       </c>
       <c r="B332" s="12" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>E-mail marketing wbudowany w panel</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
@@ -24824,49 +24824,49 @@
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H332" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I332" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J332" s="12" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>email-marketing.controller.ts:36,81,119,139</t>
         </is>
       </c>
       <c r="K332" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L332" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M332" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N332" s="12" t="inlineStr">
         <is>
-          <t>bez tokenu menu prowadzi do pustego stanu</t>
+          <t>double opt-in + cordon antyspamowy</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B333" s="12" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C333" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="D333" s="11" t="inlineStr">
@@ -24896,32 +24896,32 @@
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H333" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I333" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
         </is>
       </c>
       <c r="K333" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L333" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M333" s="11" t="inlineStr">
@@ -24929,12 +24929,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N333" s="12" t="inlineStr"/>
+      <c r="N333" s="12" t="inlineStr">
+        <is>
+          <t>bez tokenu menu prowadzi do pustego stanu</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B334" s="12" t="inlineStr">
@@ -24944,7 +24948,7 @@
       </c>
       <c r="C334" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="D334" s="11" t="inlineStr">
@@ -24969,7 +24973,7 @@
       </c>
       <c r="H334" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I334" s="11" t="inlineStr">
@@ -25002,7 +25006,7 @@
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B335" s="12" t="inlineStr">
@@ -25012,29 +25016,29 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E335" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F335" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G335" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E335" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F335" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G335" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H335" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -25042,22 +25046,22 @@
       </c>
       <c r="I335" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K335" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L335" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M335" s="11" t="inlineStr">
@@ -25065,16 +25069,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N335" s="12" t="inlineStr">
-        <is>
-          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
-        </is>
-      </c>
+      <c r="N335" s="12" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>Q-10</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B336" s="12" t="inlineStr">
@@ -25084,22 +25084,22 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>Natywna aplikacja mobilna</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E336" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F336" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G336" s="11" t="inlineStr">
@@ -25109,44 +25109,44 @@
       </c>
       <c r="H336" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I336" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J336" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
       <c r="K336" s="11" t="inlineStr">
         <is>
-          <t>POZA ZAKRESEM</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L336" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M336" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N336" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl (iOS)</t>
+          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>Q-11</t>
+          <t>Q-10</t>
         </is>
       </c>
       <c r="B337" s="12" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Tryb prosty / zaawansowany panelu</t>
+          <t>Natywna aplikacja mobilna</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="G337" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H337" s="11" t="inlineStr">
@@ -25186,22 +25186,22 @@
       </c>
       <c r="I337" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
         <is>
-          <t>page.tsx:139 — ukrywa 7 zakładek</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K337" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>POZA ZAKRESEM</t>
         </is>
       </c>
       <c r="L337" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M337" s="11" t="inlineStr">
@@ -25209,12 +25209,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N337" s="12" t="inlineStr"/>
+      <c r="N337" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl (iOS)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>Q-12</t>
+          <t>Q-11</t>
         </is>
       </c>
       <c r="B338" s="12" t="inlineStr">
@@ -25224,7 +25228,7 @@
       </c>
       <c r="C338" s="11" t="inlineStr">
         <is>
-          <t>Kreator pierwszych kroków (onboarding)</t>
+          <t>Tryb prosty / zaawansowany panelu</t>
         </is>
       </c>
       <c r="D338" s="11" t="inlineStr">
@@ -25234,24 +25238,24 @@
       </c>
       <c r="E338" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F338" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G338" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H338" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F338" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G338" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H338" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I338" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -25259,12 +25263,12 @@
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>onboarding-wizard.tsx:52</t>
+          <t>page.tsx:139 — ukrywa 7 zakładek</t>
         </is>
       </c>
       <c r="K338" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L338" s="11" t="inlineStr">
@@ -25277,16 +25281,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N338" s="12" t="inlineStr">
-        <is>
-          <t>tylko nawigacja</t>
-        </is>
-      </c>
+      <c r="N338" s="12" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>Q-13</t>
+          <t>Q-12</t>
         </is>
       </c>
       <c r="B339" s="12" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Command palette dla operatora</t>
+          <t>Kreator pierwszych kroków (onboarding)</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="E339" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F339" s="11" t="inlineStr">
@@ -25316,12 +25316,12 @@
       </c>
       <c r="G339" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H339" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I339" s="11" t="inlineStr">
@@ -25331,12 +25331,12 @@
       </c>
       <c r="J339" s="12" t="inlineStr">
         <is>
-          <t>command-palette-actions.ts</t>
+          <t>onboarding-wizard.tsx:52</t>
         </is>
       </c>
       <c r="K339" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L339" s="11" t="inlineStr">
@@ -25349,12 +25349,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N339" s="12" t="inlineStr"/>
+      <c r="N339" s="12" t="inlineStr">
+        <is>
+          <t>tylko nawigacja</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-13</t>
         </is>
       </c>
       <c r="B340" s="12" t="inlineStr">
@@ -25364,22 +25368,22 @@
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>Command palette dla operatora</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E340" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F340" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G340" s="11" t="inlineStr">
@@ -25394,39 +25398,35 @@
       </c>
       <c r="I340" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J340" s="12" t="inlineStr">
         <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
+          <t>command-palette-actions.ts</t>
         </is>
       </c>
       <c r="K340" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L340" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M340" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N340" s="12" t="inlineStr">
-        <is>
-          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N340" s="12" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>Q-15</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B341" s="12" t="inlineStr">
@@ -25436,22 +25436,22 @@
       </c>
       <c r="C341" s="11" t="inlineStr">
         <is>
-          <t>Live-readiness (checklista przed startem)</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E341" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F341" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G341" s="11" t="inlineStr">
@@ -25466,39 +25466,39 @@
       </c>
       <c r="I341" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
         <is>
-          <t>live-readiness.service.ts — 14 checków</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
       <c r="K341" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L341" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M341" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N341" s="12" t="inlineStr">
         <is>
-          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>Q-16</t>
+          <t>Q-15</t>
         </is>
       </c>
       <c r="B342" s="12" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="C342" s="11" t="inlineStr">
         <is>
-          <t>Metryki biznesowe (MRR, churn)</t>
+          <t>Live-readiness (checklista przed startem)</t>
         </is>
       </c>
       <c r="D342" s="11" t="inlineStr">
@@ -25543,12 +25543,12 @@
       </c>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>business-metrics.admin.controller.ts:15; test D1</t>
+          <t>live-readiness.service.ts — 14 checków</t>
         </is>
       </c>
       <c r="K342" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L342" s="11" t="inlineStr">
@@ -25561,12 +25561,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N342" s="12" t="inlineStr"/>
+      <c r="N342" s="12" t="inlineStr">
+        <is>
+          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>Q-17</t>
+          <t>Q-16</t>
         </is>
       </c>
       <c r="B343" s="12" t="inlineStr">
@@ -25576,7 +25580,7 @@
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Grafana SSO dla operatora</t>
+          <t>Metryki biznesowe (MRR, churn)</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
@@ -25586,7 +25590,7 @@
       </c>
       <c r="E343" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F343" s="11" t="inlineStr">
@@ -25611,12 +25615,12 @@
       </c>
       <c r="J343" s="12" t="inlineStr">
         <is>
-          <t>grafana-auth.controller.ts</t>
+          <t>business-metrics.admin.controller.ts:15; test D1</t>
         </is>
       </c>
       <c r="K343" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L343" s="11" t="inlineStr">
@@ -25634,7 +25638,7 @@
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>Q-18</t>
+          <t>Q-17</t>
         </is>
       </c>
       <c r="B344" s="12" t="inlineStr">
@@ -25644,7 +25648,7 @@
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>VPN WireGuard dla dostępu operatorskiego</t>
+          <t>Grafana SSO dla operatora</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
@@ -25654,7 +25658,7 @@
       </c>
       <c r="E344" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F344" s="11" t="inlineStr">
@@ -25679,7 +25683,7 @@
       </c>
       <c r="J344" s="12" t="inlineStr">
         <is>
-          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
+          <t>grafana-auth.controller.ts</t>
         </is>
       </c>
       <c r="K344" s="11" t="inlineStr">
@@ -25702,32 +25706,32 @@
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>Q-18</t>
         </is>
       </c>
       <c r="B345" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C345" s="11" t="inlineStr">
         <is>
-          <t>CI uruchamiające testy</t>
+          <t>VPN WireGuard dla dostępu operatorskiego</t>
         </is>
       </c>
       <c r="D345" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E345" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F345" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G345" s="11" t="inlineStr">
@@ -25747,12 +25751,12 @@
       </c>
       <c r="J345" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
+          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
         </is>
       </c>
       <c r="K345" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L345" s="11" t="inlineStr">
@@ -25762,19 +25766,15 @@
       </c>
       <c r="M345" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N345" s="12" t="inlineStr">
-        <is>
-          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N345" s="12" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B346" s="12" t="inlineStr">
@@ -25784,7 +25784,7 @@
       </c>
       <c r="C346" s="11" t="inlineStr">
         <is>
-          <t>Status wymagany do merge</t>
+          <t>CI uruchamiające testy</t>
         </is>
       </c>
       <c r="D346" s="11" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
+          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
         </is>
       </c>
       <c r="K346" s="11" t="inlineStr">
@@ -25839,14 +25839,14 @@
       </c>
       <c r="N346" s="12" t="inlineStr">
         <is>
-          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
+          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B347" s="12" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>Testy uruchamiane przed wdrożeniem</t>
+          <t>Status wymagany do merge</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
@@ -25886,22 +25886,22 @@
       </c>
       <c r="I347" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
+          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="K347" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L347" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M347" s="11" t="inlineStr">
@@ -25911,14 +25911,14 @@
       </c>
       <c r="N347" s="12" t="inlineStr">
         <is>
-          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B348" s="12" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Testy uruchamiane przed wdrożeniem</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
@@ -25958,17 +25958,17 @@
       </c>
       <c r="I348" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
         </is>
       </c>
       <c r="K348" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L348" s="11" t="inlineStr">
@@ -25978,19 +25978,19 @@
       </c>
       <c r="M348" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N348" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B349" s="12" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="C349" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="D349" s="11" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
       <c r="K349" s="11" t="inlineStr">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="L349" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M349" s="11" t="inlineStr">
@@ -26053,12 +26053,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N349" s="12" t="inlineStr"/>
+      <c r="N349" s="12" t="inlineStr">
+        <is>
+          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B350" s="12" t="inlineStr">
@@ -26068,7 +26072,7 @@
       </c>
       <c r="C350" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="D350" s="11" t="inlineStr">
@@ -26103,7 +26107,7 @@
       </c>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
       <c r="K350" s="11" t="inlineStr">
@@ -26113,24 +26117,20 @@
       </c>
       <c r="L350" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M350" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N350" s="12" t="inlineStr">
-        <is>
-          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N350" s="12" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B351" s="12" t="inlineStr">
@@ -26140,7 +26140,7 @@
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
       <c r="K351" s="11" t="inlineStr">
@@ -26195,14 +26195,14 @@
       </c>
       <c r="N351" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01.</t>
+          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B352" s="12" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
       <c r="K352" s="11" t="inlineStr">
@@ -26267,14 +26267,14 @@
       </c>
       <c r="N352" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+          <t>Reklasyfikacja jak X-01.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B353" s="12" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="C353" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="D353" s="11" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="J353" s="12" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
       <c r="K353" s="11" t="inlineStr">
@@ -26334,15 +26334,19 @@
       </c>
       <c r="M353" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N353" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N353" s="12" t="inlineStr">
+        <is>
+          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B354" s="12" t="inlineStr">
@@ -26352,7 +26356,7 @@
       </c>
       <c r="C354" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="D354" s="11" t="inlineStr">
@@ -26382,12 +26386,12 @@
       </c>
       <c r="I354" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
       <c r="K354" s="11" t="inlineStr">
@@ -26402,90 +26406,158 @@
       </c>
       <c r="M354" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N354" s="12" t="inlineStr">
-        <is>
-          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N354" s="12" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B355" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C355" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="D355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H355" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I355" s="11" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="J355" s="12" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+      <c r="K355" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L355" s="11" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="M355" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N355" s="12" t="inlineStr">
+        <is>
+          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="11" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B355" s="12" t="inlineStr">
+      <c r="B356" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C355" s="11" t="inlineStr">
+      <c r="C356" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="D355" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E355" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F355" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G355" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H355" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I355" s="11" t="inlineStr">
+      <c r="D356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I356" s="11" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="J355" s="12" t="inlineStr">
+      <c r="J356" s="12" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
-      <c r="K355" s="11" t="inlineStr">
+      <c r="K356" s="11" t="inlineStr">
         <is>
           <t>LUKA</t>
         </is>
       </c>
-      <c r="L355" s="11" t="inlineStr">
+      <c r="L356" s="11" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="M355" s="11" t="inlineStr">
+      <c r="M356" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N355" s="12" t="inlineStr">
+      <c r="N356" s="12" t="inlineStr">
         <is>
           <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N355"/>
-  <conditionalFormatting sqref="D2:D355">
+  <autoFilter ref="A1:N356"/>
+  <conditionalFormatting sqref="D2:D356">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26502,7 +26574,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E355">
+  <conditionalFormatting sqref="E2:E356">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26519,7 +26591,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F355">
+  <conditionalFormatting sqref="F2:F356">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26536,7 +26608,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G355">
+  <conditionalFormatting sqref="G2:G356">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26553,7 +26625,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H355">
+  <conditionalFormatting sqref="H2:H356">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26570,7 +26642,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I355">
+  <conditionalFormatting sqref="I2:I356">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26590,7 +26662,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K355">
+  <conditionalFormatting sqref="K2:K356">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26607,7 +26679,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L355">
+  <conditionalFormatting sqref="L2:L356">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$357</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$356,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$357,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$356,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$357,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$356,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$357,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$356,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$357,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$356,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$357,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$356,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$357,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$356,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$357,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$356,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$357,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$356,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$357,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$356,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$357,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"A",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"B",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"C",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"D",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"E",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"F",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"G",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"H",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"I",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"J",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"K",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"L",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"M",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"N",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"O",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"P",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Q",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"X",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$356,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$357,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$K$2:$K$356,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$356,"Z",Macierz!$L$2:$L$356,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21066,37 +21066,37 @@
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>N-01</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B279" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>System zgłoszeń dla klienta</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="D279" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E279" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F279" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G279" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H279" s="11" t="inlineStr">
@@ -21106,35 +21106,39 @@
       </c>
       <c r="I279" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:92,98</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
       <c r="K279" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L279" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M279" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N279" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N279" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-04. Strażnik uprawnień odpowiada na pytanie „czy subkonto może wykonać ten RODZAJ operacji", nie „czy ten konkretny rekord należy do właściciela sesji". To drugie robi każdy serwis po swojemu i nikt tego nie przejrzał całościowo. Przy okazji: odmowa dla subkonta nie trafia do dziennika audytu, a jest sygnałem operacyjnym w obie strony (próba nadużycia albo za ostra klasyfikacja trasy).</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>N-02</t>
+          <t>N-01</t>
         </is>
       </c>
       <c r="B280" s="12" t="inlineStr">
@@ -21144,7 +21148,7 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Załączniki w zgłoszeniu</t>
+          <t>System zgłoszeń dla klienta</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
@@ -21159,7 +21163,7 @@
       </c>
       <c r="F280" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G280" s="11" t="inlineStr">
@@ -21179,7 +21183,7 @@
       </c>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:98,245</t>
+          <t>tickets.controller.ts:92,98</t>
         </is>
       </c>
       <c r="K280" s="11" t="inlineStr">
@@ -21202,7 +21206,7 @@
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>N-03</t>
+          <t>N-02</t>
         </is>
       </c>
       <c r="B281" s="12" t="inlineStr">
@@ -21212,7 +21216,7 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Ocena obsługi (CSAT)</t>
+          <t>Załączniki w zgłoszeniu</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
@@ -21227,17 +21231,17 @@
       </c>
       <c r="F281" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H281" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I281" s="11" t="inlineStr">
@@ -21247,12 +21251,12 @@
       </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:279</t>
+          <t>tickets.controller.ts:98,245</t>
         </is>
       </c>
       <c r="K281" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L281" s="11" t="inlineStr">
@@ -21270,7 +21274,7 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>N-04</t>
+          <t>N-03</t>
         </is>
       </c>
       <c r="B282" s="12" t="inlineStr">
@@ -21280,7 +21284,7 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy po polsku</t>
+          <t>Ocena obsługi (CSAT)</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
@@ -21300,12 +21304,12 @@
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I282" s="11" t="inlineStr">
@@ -21315,12 +21319,12 @@
       </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>kb.public.controller.ts:226</t>
+          <t>tickets.controller.ts:279</t>
         </is>
       </c>
       <c r="K282" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L282" s="11" t="inlineStr">
@@ -21338,7 +21342,7 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>N-04</t>
         </is>
       </c>
       <c r="B283" s="12" t="inlineStr">
@@ -21348,7 +21352,7 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Baza wiedzy po polsku</t>
         </is>
       </c>
       <c r="D283" s="11" t="inlineStr">
@@ -21368,37 +21372,37 @@
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H283" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I283" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>kb.public.controller.ts:226</t>
         </is>
       </c>
       <c r="K283" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L283" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M283" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N283" s="12" t="inlineStr"/>
@@ -21406,7 +21410,7 @@
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>N-06</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B284" s="12" t="inlineStr">
@@ -21416,7 +21420,7 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>Publiczna strona statusu usług</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="D284" s="11" t="inlineStr">
@@ -21436,49 +21440,45 @@
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H284" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H284" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>probes-admin.controller.ts:33; apps/status-page</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
       <c r="K284" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L284" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M284" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N284" s="12" t="inlineStr">
-        <is>
-          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N284" s="12" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>N-06</t>
         </is>
       </c>
       <c r="B285" s="12" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Publiczna strona statusu usług</t>
         </is>
       </c>
       <c r="D285" s="11" t="inlineStr">
@@ -21518,39 +21518,39 @@
       </c>
       <c r="I285" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>probes-admin.controller.ts:33; apps/status-page</t>
         </is>
       </c>
       <c r="K285" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L285" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M285" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>N-08</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B286" s="12" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Edycja i zamknięcie incydentu</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="D286" s="11" t="inlineStr">
@@ -21590,35 +21590,39 @@
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>status/actions.ts:158,177</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="K286" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L286" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M286" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N286" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N286" s="12" t="inlineStr">
+        <is>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>N-09</t>
+          <t>N-08</t>
         </is>
       </c>
       <c r="B287" s="12" t="inlineStr">
@@ -21628,7 +21632,7 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienia w panelu (dzwonek)</t>
+          <t>Edycja i zamknięcie incydentu</t>
         </is>
       </c>
       <c r="D287" s="11" t="inlineStr">
@@ -21638,19 +21642,19 @@
       </c>
       <c r="E287" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F287" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G287" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F287" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G287" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H287" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -21663,7 +21667,7 @@
       </c>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>notifications.controller.ts:12,20,26</t>
+          <t>status/actions.ts:158,177</t>
         </is>
       </c>
       <c r="K287" s="11" t="inlineStr">
@@ -21686,7 +21690,7 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-09</t>
         </is>
       </c>
       <c r="B288" s="12" t="inlineStr">
@@ -21696,7 +21700,7 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Powiadomienia w panelu (dzwonek)</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
@@ -21726,39 +21730,35 @@
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J288" s="12" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>notifications.controller.ts:12,20,26</t>
         </is>
       </c>
       <c r="K288" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L288" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M288" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N288" s="12" t="inlineStr">
-        <is>
-          <t>sterowalne są tylko zgody marketingowe</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N288" s="12" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B289" s="12" t="inlineStr">
@@ -21768,69 +21768,69 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E289" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E289" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="F289" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G289" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G289" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H289" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I289" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
       <c r="K289" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L289" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M289" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
-          <t>cały panel Product Ops/NOC jest read-only</t>
+          <t>sterowalne są tylko zgody marketingowe</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B290" s="12" t="inlineStr">
@@ -21840,32 +21840,32 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E290" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F290" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F290" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G290" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H290" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I290" s="11" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
       <c r="K290" s="11" t="inlineStr">
@@ -21885,20 +21885,24 @@
       </c>
       <c r="L290" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M290" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N290" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N290" s="12" t="inlineStr">
+        <is>
+          <t>cały panel Product Ops/NOC jest read-only</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B291" s="12" t="inlineStr">
@@ -21908,42 +21912,42 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E291" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F291" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I291" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
       <c r="K291" s="11" t="inlineStr">
@@ -21953,24 +21957,20 @@
       </c>
       <c r="L291" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M291" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N291" s="12" t="inlineStr">
-        <is>
-          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N291" s="12" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B292" s="12" t="inlineStr">
@@ -21980,42 +21980,42 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E292" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F292" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E292" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F292" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
       <c r="K292" s="11" t="inlineStr">
@@ -22030,19 +22030,19 @@
       </c>
       <c r="M292" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N292" s="12" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>N-15</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B293" s="12" t="inlineStr">
@@ -22052,69 +22052,69 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E293" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F293" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H293" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I293" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>cockpit migracji + kreator klienta</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="K293" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L293" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M293" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N293" s="12" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>N-15</t>
         </is>
       </c>
       <c r="B294" s="12" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
@@ -22144,49 +22144,49 @@
       </c>
       <c r="G294" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H294" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H294" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J294" s="12" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>cockpit migracji + kreator klienta</t>
         </is>
       </c>
       <c r="K294" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L294" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M294" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N294" s="12" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>N-17</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B295" s="12" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Szablony odpowiedzi obsługi</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
@@ -22211,50 +22211,54 @@
       </c>
       <c r="F295" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G295" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G295" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H295" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I295" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>settings/canned-responses/actions.ts:23</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="K295" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L295" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M295" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N295" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N295" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>N-18</t>
+          <t>N-17</t>
         </is>
       </c>
       <c r="B296" s="12" t="inlineStr">
@@ -22264,7 +22268,7 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>CRM klienta 360 dla obsługi</t>
+          <t>Szablony odpowiedzi obsługi</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
@@ -22279,7 +22283,7 @@
       </c>
       <c r="F296" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G296" s="11" t="inlineStr">
@@ -22299,12 +22303,12 @@
       </c>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
+          <t>settings/canned-responses/actions.ts:23</t>
         </is>
       </c>
       <c r="K296" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L296" s="11" t="inlineStr">
@@ -22322,7 +22326,7 @@
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>N-19</t>
+          <t>N-18</t>
         </is>
       </c>
       <c r="B297" s="12" t="inlineStr">
@@ -22332,7 +22336,7 @@
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
+          <t>CRM klienta 360 dla obsługi</t>
         </is>
       </c>
       <c r="D297" s="11" t="inlineStr">
@@ -22352,12 +22356,12 @@
       </c>
       <c r="G297" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H297" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I297" s="11" t="inlineStr">
@@ -22367,7 +22371,7 @@
       </c>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>ai-chat.service.ts (223 l.)</t>
+          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
         </is>
       </c>
       <c r="K297" s="11" t="inlineStr">
@@ -22385,16 +22389,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N297" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
-        </is>
-      </c>
+      <c r="N297" s="12" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-19</t>
         </is>
       </c>
       <c r="B298" s="12" t="inlineStr">
@@ -22404,65 +22404,69 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J298" s="12" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>ai-chat.service.ts (223 l.)</t>
         </is>
       </c>
       <c r="K298" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L298" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M298" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N298" s="12" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N298" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B299" s="12" t="inlineStr">
@@ -22472,42 +22476,42 @@
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E299" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F299" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I299" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
       <c r="K299" s="11" t="inlineStr">
@@ -22522,74 +22526,70 @@
       </c>
       <c r="M299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N299" s="12" t="inlineStr">
-        <is>
-          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N299" s="12" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B300" s="12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Subkonta z uprawnieniami (IAM)</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E300" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F300" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G300" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H300" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G300" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H300" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:42,53,63,69</t>
+          <t>poza produktem</t>
         </is>
       </c>
       <c r="K300" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L300" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M300" s="11" t="inlineStr">
@@ -22599,14 +22599,14 @@
       </c>
       <c r="N300" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="B301" s="12" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Aktywacja subkonta z zaproszenia</t>
+          <t>Subkonta z uprawnieniami (IAM)</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
@@ -22651,12 +22651,12 @@
       </c>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:47</t>
+          <t>customer-iam.controller.ts:42,53,63,69</t>
         </is>
       </c>
       <c r="K301" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L301" s="11" t="inlineStr">
@@ -22669,12 +22669,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N301" s="12" t="inlineStr"/>
+      <c r="N301" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>O-02</t>
         </is>
       </c>
       <c r="B302" s="12" t="inlineStr">
@@ -22684,69 +22688,65 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Aktywacja subkonta z zaproszenia</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E302" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F302" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E302" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F302" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G302" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H302" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>customer-iam.controller.ts:47</t>
         </is>
       </c>
       <c r="K302" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L302" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M302" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N302" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N302" s="12" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B303" s="12" t="inlineStr">
@@ -22756,12 +22756,12 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Egzekwowanie uprawnień w nawigacji i API</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E303" s="11" t="inlineStr">
@@ -22771,50 +22771,54 @@
       </c>
       <c r="F303" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G303" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H303" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G303" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H303" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I303" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
         <is>
-          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
       <c r="K303" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L303" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M303" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N303" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N303" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-04</t>
         </is>
       </c>
       <c r="B304" s="12" t="inlineStr">
@@ -22824,7 +22828,7 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Egzekwowanie uprawnień w nawigacji i API</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
@@ -22839,42 +22843,42 @@
       </c>
       <c r="F304" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G304" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H304" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
         </is>
       </c>
       <c r="K304" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L304" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M304" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N304" s="12" t="inlineStr"/>
@@ -22882,7 +22886,7 @@
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B305" s="12" t="inlineStr">
@@ -22892,7 +22896,7 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
@@ -22922,17 +22926,17 @@
       </c>
       <c r="I305" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
       <c r="K305" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L305" s="11" t="inlineStr">
@@ -22945,16 +22949,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N305" s="12" t="inlineStr">
-        <is>
-          <t>bez tego reseller nie jest produktem</t>
-        </is>
-      </c>
+      <c r="N305" s="12" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B306" s="12" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
@@ -22994,35 +22994,39 @@
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K306" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L306" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M306" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N306" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N306" s="12" t="inlineStr">
+        <is>
+          <t>bez tego reseller nie jest produktem</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B307" s="12" t="inlineStr">
@@ -23032,47 +23036,47 @@
       </c>
       <c r="C307" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="D307" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E307" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F307" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G307" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E307" s="11" t="inlineStr">
+      <c r="H307" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F307" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G307" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H307" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I307" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
       <c r="K307" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L307" s="11" t="inlineStr">
@@ -23085,16 +23089,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N307" s="12" t="inlineStr">
-        <is>
-          <t>strona sprzedażowa bez operacji zapisu</t>
-        </is>
-      </c>
+      <c r="N307" s="12" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B308" s="12" t="inlineStr">
@@ -23104,22 +23104,22 @@
       </c>
       <c r="C308" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="D308" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E308" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F308" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G308" s="11" t="inlineStr">
@@ -23134,17 +23134,17 @@
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
       <c r="K308" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L308" s="11" t="inlineStr">
@@ -23154,19 +23154,19 @@
       </c>
       <c r="M308" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N308" s="12" t="inlineStr">
         <is>
-          <t>seohost to reklamuje jako wyróżnik</t>
+          <t>strona sprzedażowa bez operacji zapisu</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>O-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B309" s="12" t="inlineStr">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>Role i uprawnienia operatorów</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
@@ -23196,45 +23196,49 @@
       </c>
       <c r="G309" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H309" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I309" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:31,36,41</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
       <c r="K309" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L309" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M309" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N309" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N309" s="12" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje jako wyróżnik</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>O-11</t>
+          <t>O-10</t>
         </is>
       </c>
       <c r="B310" s="12" t="inlineStr">
@@ -23244,7 +23248,7 @@
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Zarządzanie operatorami</t>
+          <t>Role i uprawnienia operatorów</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
@@ -23279,7 +23283,7 @@
       </c>
       <c r="J310" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:51,56,61</t>
+          <t>staff-roles.admin.controller.ts:31,36,41</t>
         </is>
       </c>
       <c r="K310" s="11" t="inlineStr">
@@ -23302,7 +23306,7 @@
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>O-12</t>
+          <t>O-11</t>
         </is>
       </c>
       <c r="B311" s="12" t="inlineStr">
@@ -23312,32 +23316,32 @@
       </c>
       <c r="C311" s="11" t="inlineStr">
         <is>
-          <t>Program partnerski / afiliacyjny</t>
+          <t>Zarządzanie operatorami</t>
         </is>
       </c>
       <c r="D311" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E311" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F311" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G311" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H311" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I311" s="11" t="inlineStr">
@@ -23347,7 +23351,7 @@
       </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>partners.controller.ts:18,28,34</t>
+          <t>staff-roles.admin.controller.ts:51,56,61</t>
         </is>
       </c>
       <c r="K311" s="11" t="inlineStr">
@@ -23365,16 +23369,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N311" s="12" t="inlineStr">
-        <is>
-          <t>wypłata na portfel lub IBAN</t>
-        </is>
-      </c>
+      <c r="N311" s="12" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>Z-04</t>
+          <t>O-12</t>
         </is>
       </c>
       <c r="B312" s="12" t="inlineStr">
@@ -23384,29 +23384,29 @@
       </c>
       <c r="C312" s="11" t="inlineStr">
         <is>
-          <t>Guard uprawnień subkont — domyślna odmowa</t>
+          <t>Program partnerski / afiliacyjny</t>
         </is>
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E312" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F312" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G312" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G312" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H312" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -23414,66 +23414,66 @@
       </c>
       <c r="I312" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>customer-permissions.guard.ts:75 — inferCustomerRoutePermissions kończy się return [] (zezwól) dla trasy niedopasowanej; addons/* i vps nie pasują do żadnej gałęzi; addon.service.ts:105 i vps.service.ts:174 zdejmują środki z portfela; jwt.strategy.ts:94 ustawia userId = customerOwnerId</t>
+          <t>partners.controller.ts:18,28,34</t>
         </is>
       </c>
       <c r="K312" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L312" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M312" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N312" s="12" t="inlineStr">
         <is>
-          <t>Subkonto zaproszone wyłącznie z uprawnieniem TICKETS_READ może wydawać środki z portfela właściciela i kupować VPS na jego rachunek. Guard musi domyślnie odmawiać, nie zezwalać.</t>
+          <t>wypłata na portfel lub IBAN</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>Z-04</t>
         </is>
       </c>
       <c r="B313" s="12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C313" s="11" t="inlineStr">
         <is>
-          <t>Eksport danych osobowych (art. 20)</t>
+          <t>Guard uprawnień subkont — domyślna odmowa</t>
         </is>
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E313" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F313" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F313" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G313" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
@@ -23481,7 +23481,7 @@
       </c>
       <c r="H313" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I313" s="11" t="inlineStr">
@@ -23491,12 +23491,12 @@
       </c>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
+          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
         </is>
       </c>
       <c r="K313" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L313" s="11" t="inlineStr">
@@ -23506,19 +23506,19 @@
       </c>
       <c r="M313" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B314" s="12" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="C314" s="11" t="inlineStr">
         <is>
-          <t>Żądanie usunięcia konta (art. 17)</t>
+          <t>Eksport danych osobowych (art. 20)</t>
         </is>
       </c>
       <c r="D314" s="11" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.service.ts:29,308,383-432</t>
+          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
         </is>
       </c>
       <c r="K314" s="11" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="L314" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M314" s="11" t="inlineStr">
@@ -23583,14 +23583,14 @@
       </c>
       <c r="N314" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
+          <t>ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B315" s="12" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Wycofanie żądania usunięcia</t>
+          <t>Żądanie usunięcia konta (art. 17)</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E315" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F315" s="11" t="inlineStr">
@@ -23620,12 +23620,12 @@
       </c>
       <c r="G315" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H315" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I315" s="11" t="inlineStr">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="J315" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.controller.ts:62</t>
+          <t>account-deletion.service.ts:29,308,383-432</t>
         </is>
       </c>
       <c r="K315" s="11" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="L315" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M315" s="11" t="inlineStr">
@@ -23655,14 +23655,14 @@
       </c>
       <c r="N315" s="12" t="inlineStr">
         <is>
-          <t>karencja 14 dni</t>
+          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B316" s="12" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>Historia zgód klienta</t>
+          <t>Wycofanie żądania usunięcia</t>
         </is>
       </c>
       <c r="D316" s="11" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="E316" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F316" s="11" t="inlineStr">
@@ -23692,12 +23692,12 @@
       </c>
       <c r="G316" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H316" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I316" s="11" t="inlineStr">
@@ -23707,12 +23707,12 @@
       </c>
       <c r="J316" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:70</t>
+          <t>account-deletion.controller.ts:62</t>
         </is>
       </c>
       <c r="K316" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L316" s="11" t="inlineStr">
@@ -23725,12 +23725,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N316" s="12" t="inlineStr"/>
+      <c r="N316" s="12" t="inlineStr">
+        <is>
+          <t>karencja 14 dni</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="B317" s="12" t="inlineStr">
@@ -23740,7 +23744,7 @@
       </c>
       <c r="C317" s="11" t="inlineStr">
         <is>
-          <t>Ponowna akceptacja przy zmianie regulaminu</t>
+          <t>Historia zgód klienta</t>
         </is>
       </c>
       <c r="D317" s="11" t="inlineStr">
@@ -23750,7 +23754,7 @@
       </c>
       <c r="E317" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F317" s="11" t="inlineStr">
@@ -23775,12 +23779,12 @@
       </c>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
+          <t>consents.controller.ts:70</t>
         </is>
       </c>
       <c r="K317" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L317" s="11" t="inlineStr">
@@ -23798,7 +23802,7 @@
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="B318" s="12" t="inlineStr">
@@ -23808,7 +23812,7 @@
       </c>
       <c r="C318" s="11" t="inlineStr">
         <is>
-          <t>Umowa powierzenia (DPA) do pobrania</t>
+          <t>Ponowna akceptacja przy zmianie regulaminu</t>
         </is>
       </c>
       <c r="D318" s="11" t="inlineStr">
@@ -23818,24 +23822,24 @@
       </c>
       <c r="E318" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F318" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G318" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F318" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G318" s="11" t="inlineStr">
+      <c r="H318" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H318" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I318" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -23843,7 +23847,7 @@
       </c>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
+          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
         </is>
       </c>
       <c r="K318" s="11" t="inlineStr">
@@ -23866,7 +23870,7 @@
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="B319" s="12" t="inlineStr">
@@ -23876,7 +23880,7 @@
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Dokumenty prawne z historią wersji</t>
+          <t>Umowa powierzenia (DPA) do pobrania</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
@@ -23886,7 +23890,7 @@
       </c>
       <c r="E319" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F319" s="11" t="inlineStr">
@@ -23911,7 +23915,7 @@
       </c>
       <c r="J319" s="12" t="inlineStr">
         <is>
-          <t>legal-documents.controller.ts:36,49</t>
+          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
         </is>
       </c>
       <c r="K319" s="11" t="inlineStr">
@@ -23929,16 +23933,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N319" s="12" t="inlineStr">
-        <is>
-          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
-        </is>
-      </c>
+      <c r="N319" s="12" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="B320" s="12" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Retencja i anonimizacja logów</t>
+          <t>Dokumenty prawne z historią wersji</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
@@ -23958,22 +23958,22 @@
       </c>
       <c r="E320" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F320" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G320" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F320" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G320" s="11" t="inlineStr">
-        <is>
-          <t>b.d.</t>
-        </is>
-      </c>
       <c r="H320" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I320" s="11" t="inlineStr">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>retention.scheduler.ts:29,30,87,95</t>
+          <t>legal-documents.controller.ts:36,49</t>
         </is>
       </c>
       <c r="K320" s="11" t="inlineStr">
@@ -24003,14 +24003,14 @@
       </c>
       <c r="N320" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B321" s="12" t="inlineStr">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Zgody marketingowe (opt-in/out)</t>
+          <t>Retencja i anonimizacja logów</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="E321" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F321" s="11" t="inlineStr">
@@ -24040,12 +24040,12 @@
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H321" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I321" s="11" t="inlineStr">
@@ -24055,12 +24055,12 @@
       </c>
       <c r="J321" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:99</t>
+          <t>retention.scheduler.ts:29,30,87,95</t>
         </is>
       </c>
       <c r="K321" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L321" s="11" t="inlineStr">
@@ -24073,12 +24073,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N321" s="12" t="inlineStr"/>
+      <c r="N321" s="12" t="inlineStr">
+        <is>
+          <t>ZERO testów</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B322" s="12" t="inlineStr">
@@ -24088,7 +24092,7 @@
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Baner zgody na cookies</t>
+          <t>Zgody marketingowe (opt-in/out)</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
@@ -24123,7 +24127,7 @@
       </c>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>cookie-consent.tsx</t>
+          <t>consents.controller.ts:99</t>
         </is>
       </c>
       <c r="K322" s="11" t="inlineStr">
@@ -24146,7 +24150,7 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="B323" s="12" t="inlineStr">
@@ -24156,7 +24160,7 @@
       </c>
       <c r="C323" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Baner zgody na cookies</t>
         </is>
       </c>
       <c r="D323" s="11" t="inlineStr">
@@ -24176,49 +24180,45 @@
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H323" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I323" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>cookie-consent.tsx</t>
         </is>
       </c>
       <c r="K323" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L323" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M323" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N323" s="12" t="inlineStr">
-        <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N323" s="12" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B324" s="12" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C324" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="D324" s="11" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="E324" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F324" s="11" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
       <c r="K324" s="11" t="inlineStr">
@@ -24278,19 +24278,19 @@
       </c>
       <c r="M324" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N324" s="12" t="inlineStr">
         <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B325" s="12" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="C325" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="D325" s="11" t="inlineStr">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="E325" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F325" s="11" t="inlineStr">
@@ -24320,27 +24320,27 @@
       </c>
       <c r="G325" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H325" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I325" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
       <c r="K325" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L325" s="11" t="inlineStr">
@@ -24350,19 +24350,19 @@
       </c>
       <c r="M325" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to eksponuje</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B326" s="12" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="C326" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="D326" s="11" t="inlineStr">
@@ -24392,49 +24392,49 @@
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H326" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H326" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I326" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J326" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>poza kodem</t>
         </is>
       </c>
       <c r="K326" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L326" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M326" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N326" s="12" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>wszystkie 5 hostingów PL to eksponuje</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B327" s="12" t="inlineStr">
@@ -24444,32 +24444,32 @@
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H327" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I327" s="11" t="inlineStr">
@@ -24479,7 +24479,7 @@
       </c>
       <c r="J327" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K327" s="11" t="inlineStr">
@@ -24489,96 +24489,96 @@
       </c>
       <c r="L327" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M327" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>Q-01</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B328" s="12" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Program eko / punkty za oszczędność</t>
+          <t>Podpisane DPA z subprocesorami</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E328" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F328" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H328" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I328" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J328" s="12" t="inlineStr">
         <is>
-          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="K328" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="M328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N328" s="12" t="inlineStr">
         <is>
-          <t>nikt na rynku PL</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>Q-02</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="B329" s="12" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Raport energetyczny usługi</t>
+          <t>Program eko / punkty za oszczędność</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="I329" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
         <is>
-          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
+          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
         </is>
       </c>
       <c r="K329" s="11" t="inlineStr">
@@ -24643,14 +24643,14 @@
       </c>
       <c r="N329" s="12" t="inlineStr">
         <is>
-          <t>metodologia opisana — uczciwe podejście</t>
+          <t>nikt na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>Q-03</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="B330" s="12" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Badge eko do osadzenia na stronie klienta</t>
+          <t>Raport energetyczny usługi</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
@@ -24690,12 +24690,12 @@
       </c>
       <c r="I330" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J330" s="12" t="inlineStr">
         <is>
-          <t>eco-public.controller.ts:32,74; test D1</t>
+          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
         </is>
       </c>
       <c r="K330" s="11" t="inlineStr">
@@ -24715,14 +24715,14 @@
       </c>
       <c r="N330" s="12" t="inlineStr">
         <is>
-          <t>4 warianty + pixel odsłon</t>
+          <t>metodologia opisana — uczciwe podejście</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>Q-04</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="B331" s="12" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>Tryb eko usługi</t>
+          <t>Badge eko do osadzenia na stronie klienta</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="J331" s="12" t="inlineStr">
         <is>
-          <t>subscriptions.controller.ts:73</t>
+          <t>eco-public.controller.ts:32,74; test D1</t>
         </is>
       </c>
       <c r="K331" s="11" t="inlineStr">
@@ -24787,14 +24787,14 @@
       </c>
       <c r="N331" s="12" t="inlineStr">
         <is>
-          <t>wpływa m.in. na politykę backupów</t>
+          <t>4 warianty + pixel odsłon</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>Q-05</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="B332" s="12" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>E-mail marketing wbudowany w panel</t>
+          <t>Tryb eko usługi</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H332" s="11" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="J332" s="12" t="inlineStr">
         <is>
-          <t>email-marketing.controller.ts:36,81,119,139</t>
+          <t>subscriptions.controller.ts:73</t>
         </is>
       </c>
       <c r="K332" s="11" t="inlineStr">
@@ -24859,14 +24859,14 @@
       </c>
       <c r="N332" s="12" t="inlineStr">
         <is>
-          <t>double opt-in + cordon antyspamowy</t>
+          <t>wpływa m.in. na politykę backupów</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>Q-05</t>
         </is>
       </c>
       <c r="B333" s="12" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C333" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>E-mail marketing wbudowany w panel</t>
         </is>
       </c>
       <c r="D333" s="11" t="inlineStr">
@@ -24896,49 +24896,49 @@
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H333" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I333" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>email-marketing.controller.ts:36,81,119,139</t>
         </is>
       </c>
       <c r="K333" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L333" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M333" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
-          <t>bez tokenu menu prowadzi do pustego stanu</t>
+          <t>double opt-in + cordon antyspamowy</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B334" s="12" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="C334" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="D334" s="11" t="inlineStr">
@@ -24968,32 +24968,32 @@
       </c>
       <c r="G334" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H334" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I334" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J334" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
         </is>
       </c>
       <c r="K334" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L334" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M334" s="11" t="inlineStr">
@@ -25001,12 +25001,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N334" s="12" t="inlineStr"/>
+      <c r="N334" s="12" t="inlineStr">
+        <is>
+          <t>bez tokenu menu prowadzi do pustego stanu</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B335" s="12" t="inlineStr">
@@ -25016,7 +25020,7 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
@@ -25041,7 +25045,7 @@
       </c>
       <c r="H335" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I335" s="11" t="inlineStr">
@@ -25074,7 +25078,7 @@
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B336" s="12" t="inlineStr">
@@ -25084,29 +25088,29 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E336" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F336" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G336" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E336" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F336" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G336" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H336" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -25114,22 +25118,22 @@
       </c>
       <c r="I336" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J336" s="12" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K336" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L336" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M336" s="11" t="inlineStr">
@@ -25137,16 +25141,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N336" s="12" t="inlineStr">
-        <is>
-          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
-        </is>
-      </c>
+      <c r="N336" s="12" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>Q-10</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B337" s="12" t="inlineStr">
@@ -25156,22 +25156,22 @@
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Natywna aplikacja mobilna</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E337" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F337" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G337" s="11" t="inlineStr">
@@ -25181,44 +25181,44 @@
       </c>
       <c r="H337" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I337" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
       <c r="K337" s="11" t="inlineStr">
         <is>
-          <t>POZA ZAKRESEM</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L337" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M337" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N337" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl (iOS)</t>
+          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>Q-11</t>
+          <t>Q-10</t>
         </is>
       </c>
       <c r="B338" s="12" t="inlineStr">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="C338" s="11" t="inlineStr">
         <is>
-          <t>Tryb prosty / zaawansowany panelu</t>
+          <t>Natywna aplikacja mobilna</t>
         </is>
       </c>
       <c r="D338" s="11" t="inlineStr">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="G338" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H338" s="11" t="inlineStr">
@@ -25258,22 +25258,22 @@
       </c>
       <c r="I338" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>page.tsx:139 — ukrywa 7 zakładek</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K338" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>POZA ZAKRESEM</t>
         </is>
       </c>
       <c r="L338" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M338" s="11" t="inlineStr">
@@ -25281,12 +25281,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N338" s="12" t="inlineStr"/>
+      <c r="N338" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl (iOS)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>Q-12</t>
+          <t>Q-11</t>
         </is>
       </c>
       <c r="B339" s="12" t="inlineStr">
@@ -25296,7 +25300,7 @@
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Kreator pierwszych kroków (onboarding)</t>
+          <t>Tryb prosty / zaawansowany panelu</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
@@ -25306,24 +25310,24 @@
       </c>
       <c r="E339" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F339" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G339" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H339" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F339" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G339" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H339" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I339" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -25331,12 +25335,12 @@
       </c>
       <c r="J339" s="12" t="inlineStr">
         <is>
-          <t>onboarding-wizard.tsx:52</t>
+          <t>page.tsx:139 — ukrywa 7 zakładek</t>
         </is>
       </c>
       <c r="K339" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L339" s="11" t="inlineStr">
@@ -25349,16 +25353,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N339" s="12" t="inlineStr">
-        <is>
-          <t>tylko nawigacja</t>
-        </is>
-      </c>
+      <c r="N339" s="12" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>Q-13</t>
+          <t>Q-12</t>
         </is>
       </c>
       <c r="B340" s="12" t="inlineStr">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Command palette dla operatora</t>
+          <t>Kreator pierwszych kroków (onboarding)</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="E340" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F340" s="11" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="G340" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H340" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I340" s="11" t="inlineStr">
@@ -25403,12 +25403,12 @@
       </c>
       <c r="J340" s="12" t="inlineStr">
         <is>
-          <t>command-palette-actions.ts</t>
+          <t>onboarding-wizard.tsx:52</t>
         </is>
       </c>
       <c r="K340" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L340" s="11" t="inlineStr">
@@ -25421,12 +25421,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N340" s="12" t="inlineStr"/>
+      <c r="N340" s="12" t="inlineStr">
+        <is>
+          <t>tylko nawigacja</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-13</t>
         </is>
       </c>
       <c r="B341" s="12" t="inlineStr">
@@ -25436,22 +25440,22 @@
       </c>
       <c r="C341" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>Command palette dla operatora</t>
         </is>
       </c>
       <c r="D341" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E341" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F341" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G341" s="11" t="inlineStr">
@@ -25466,39 +25470,35 @@
       </c>
       <c r="I341" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
         <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
+          <t>command-palette-actions.ts</t>
         </is>
       </c>
       <c r="K341" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L341" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M341" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N341" s="12" t="inlineStr">
-        <is>
-          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N341" s="12" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>Q-15</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B342" s="12" t="inlineStr">
@@ -25508,22 +25508,22 @@
       </c>
       <c r="C342" s="11" t="inlineStr">
         <is>
-          <t>Live-readiness (checklista przed startem)</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="D342" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E342" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F342" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G342" s="11" t="inlineStr">
@@ -25538,39 +25538,39 @@
       </c>
       <c r="I342" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>live-readiness.service.ts — 14 checków</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
       <c r="K342" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L342" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M342" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N342" s="12" t="inlineStr">
         <is>
-          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>Q-16</t>
+          <t>Q-15</t>
         </is>
       </c>
       <c r="B343" s="12" t="inlineStr">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Metryki biznesowe (MRR, churn)</t>
+          <t>Live-readiness (checklista przed startem)</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
@@ -25615,12 +25615,12 @@
       </c>
       <c r="J343" s="12" t="inlineStr">
         <is>
-          <t>business-metrics.admin.controller.ts:15; test D1</t>
+          <t>live-readiness.service.ts — 14 checków</t>
         </is>
       </c>
       <c r="K343" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L343" s="11" t="inlineStr">
@@ -25633,12 +25633,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N343" s="12" t="inlineStr"/>
+      <c r="N343" s="12" t="inlineStr">
+        <is>
+          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>Q-17</t>
+          <t>Q-16</t>
         </is>
       </c>
       <c r="B344" s="12" t="inlineStr">
@@ -25648,7 +25652,7 @@
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>Grafana SSO dla operatora</t>
+          <t>Metryki biznesowe (MRR, churn)</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
@@ -25658,7 +25662,7 @@
       </c>
       <c r="E344" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F344" s="11" t="inlineStr">
@@ -25683,12 +25687,12 @@
       </c>
       <c r="J344" s="12" t="inlineStr">
         <is>
-          <t>grafana-auth.controller.ts</t>
+          <t>business-metrics.admin.controller.ts:15; test D1</t>
         </is>
       </c>
       <c r="K344" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L344" s="11" t="inlineStr">
@@ -25706,7 +25710,7 @@
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>Q-18</t>
+          <t>Q-17</t>
         </is>
       </c>
       <c r="B345" s="12" t="inlineStr">
@@ -25716,7 +25720,7 @@
       </c>
       <c r="C345" s="11" t="inlineStr">
         <is>
-          <t>VPN WireGuard dla dostępu operatorskiego</t>
+          <t>Grafana SSO dla operatora</t>
         </is>
       </c>
       <c r="D345" s="11" t="inlineStr">
@@ -25726,7 +25730,7 @@
       </c>
       <c r="E345" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F345" s="11" t="inlineStr">
@@ -25751,7 +25755,7 @@
       </c>
       <c r="J345" s="12" t="inlineStr">
         <is>
-          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
+          <t>grafana-auth.controller.ts</t>
         </is>
       </c>
       <c r="K345" s="11" t="inlineStr">
@@ -25774,32 +25778,32 @@
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>Q-18</t>
         </is>
       </c>
       <c r="B346" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C346" s="11" t="inlineStr">
         <is>
-          <t>CI uruchamiające testy</t>
+          <t>VPN WireGuard dla dostępu operatorskiego</t>
         </is>
       </c>
       <c r="D346" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E346" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F346" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G346" s="11" t="inlineStr">
@@ -25819,12 +25823,12 @@
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
+          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
         </is>
       </c>
       <c r="K346" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L346" s="11" t="inlineStr">
@@ -25834,19 +25838,15 @@
       </c>
       <c r="M346" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N346" s="12" t="inlineStr">
-        <is>
-          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N346" s="12" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B347" s="12" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>Status wymagany do merge</t>
+          <t>CI uruchamiające testy</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="J347" s="12" t="inlineStr">
         <is>
-          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
+          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
         </is>
       </c>
       <c r="K347" s="11" t="inlineStr">
@@ -25911,14 +25911,14 @@
       </c>
       <c r="N347" s="12" t="inlineStr">
         <is>
-          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
+          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B348" s="12" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Testy uruchamiane przed wdrożeniem</t>
+          <t>Status wymagany do merge</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
@@ -25958,22 +25958,22 @@
       </c>
       <c r="I348" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
+          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="K348" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L348" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M348" s="11" t="inlineStr">
@@ -25983,14 +25983,14 @@
       </c>
       <c r="N348" s="12" t="inlineStr">
         <is>
-          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B349" s="12" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="C349" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Testy uruchamiane przed wdrożeniem</t>
         </is>
       </c>
       <c r="D349" s="11" t="inlineStr">
@@ -26030,17 +26030,17 @@
       </c>
       <c r="I349" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
         </is>
       </c>
       <c r="K349" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L349" s="11" t="inlineStr">
@@ -26050,19 +26050,19 @@
       </c>
       <c r="M349" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N349" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B350" s="12" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C350" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="D350" s="11" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
       <c r="K350" s="11" t="inlineStr">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="L350" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M350" s="11" t="inlineStr">
@@ -26125,12 +26125,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N350" s="12" t="inlineStr"/>
+      <c r="N350" s="12" t="inlineStr">
+        <is>
+          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B351" s="12" t="inlineStr">
@@ -26140,7 +26144,7 @@
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
@@ -26175,7 +26179,7 @@
       </c>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
       <c r="K351" s="11" t="inlineStr">
@@ -26185,24 +26189,20 @@
       </c>
       <c r="L351" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M351" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N351" s="12" t="inlineStr">
-        <is>
-          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N351" s="12" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B352" s="12" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
       <c r="K352" s="11" t="inlineStr">
@@ -26267,14 +26267,14 @@
       </c>
       <c r="N352" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01.</t>
+          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B353" s="12" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="C353" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="D353" s="11" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="J353" s="12" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
       <c r="K353" s="11" t="inlineStr">
@@ -26339,14 +26339,14 @@
       </c>
       <c r="N353" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+          <t>Reklasyfikacja jak X-01.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B354" s="12" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="C354" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="D354" s="11" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
       <c r="K354" s="11" t="inlineStr">
@@ -26406,15 +26406,19 @@
       </c>
       <c r="M354" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N354" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N354" s="12" t="inlineStr">
+        <is>
+          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B355" s="12" t="inlineStr">
@@ -26424,7 +26428,7 @@
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="D355" s="11" t="inlineStr">
@@ -26454,12 +26458,12 @@
       </c>
       <c r="I355" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J355" s="12" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
       <c r="K355" s="11" t="inlineStr">
@@ -26474,90 +26478,158 @@
       </c>
       <c r="M355" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N355" s="12" t="inlineStr">
-        <is>
-          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N355" s="12" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B356" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C356" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="D356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H356" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I356" s="11" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="J356" s="12" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+      <c r="K356" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L356" s="11" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="M356" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N356" s="12" t="inlineStr">
+        <is>
+          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="11" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B356" s="12" t="inlineStr">
+      <c r="B357" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C356" s="11" t="inlineStr">
+      <c r="C357" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="D356" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E356" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F356" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G356" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H356" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I356" s="11" t="inlineStr">
+      <c r="D357" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E357" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F357" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G357" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I357" s="11" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="J356" s="12" t="inlineStr">
+      <c r="J357" s="12" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
-      <c r="K356" s="11" t="inlineStr">
+      <c r="K357" s="11" t="inlineStr">
         <is>
           <t>LUKA</t>
         </is>
       </c>
-      <c r="L356" s="11" t="inlineStr">
+      <c r="L357" s="11" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="M356" s="11" t="inlineStr">
+      <c r="M357" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N356" s="12" t="inlineStr">
+      <c r="N357" s="12" t="inlineStr">
         <is>
           <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N356"/>
-  <conditionalFormatting sqref="D2:D356">
+  <autoFilter ref="A1:N357"/>
+  <conditionalFormatting sqref="D2:D357">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26574,7 +26646,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E356">
+  <conditionalFormatting sqref="E2:E357">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26591,7 +26663,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F356">
+  <conditionalFormatting sqref="F2:F357">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26608,7 +26680,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G356">
+  <conditionalFormatting sqref="G2:G357">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26625,7 +26697,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H356">
+  <conditionalFormatting sqref="H2:H357">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26642,7 +26714,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I356">
+  <conditionalFormatting sqref="I2:I357">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26662,7 +26734,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K356">
+  <conditionalFormatting sqref="K2:K357">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26679,7 +26751,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L356">
+  <conditionalFormatting sqref="L2:L357">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$358</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$357,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$358,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$357,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$358,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$357,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$358,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$357,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$358,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$357,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$358,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$357,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$358,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$357,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$358,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$357,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$358,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$357,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$358,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$357,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$358,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"A",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"B",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"C",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"D",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"E",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"F",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"G",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"H",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"I",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"J",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"K",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"L",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"M",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"N",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"O",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"P",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Q",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"X",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$357,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$358,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$K$2:$K$357,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$357,"Z",Macierz!$L$2:$L$357,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N357"/>
+  <dimension ref="A1:N358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>kolejka PHP_APPLY</t>
+          <t>KOREKTA: pozycja miała stan DZIAŁA na podstawie kodu i kolejki PHP_APPLY. Odkryte 2026-08-21 przy przeglądzie Dockerfile.api: loadery skryptów w API czytają plik z dysku i rzucają wyjątkiem, gdy go nie ma, a obraz produkcyjny kopiował tylko 7 z 10 potrzebnych skryptów. Endpoint /agent/tasks/php-apply/script zwracał 500, więc agent nie miał czego uruchomić — zadanie PHP_APPLY nie mogło się wykonać na produkcji ani razu. Naprawione (COPY + test apps/api/src/test/dockerfile-scripts.spec.ts), ale do czasu potwierdzenia na produkcji stan to CZĘŚCIOWE: kod i testy były zielone przez cały czas, więc D1 i D2 nic tu nie dowodzą — potrzebny D3.</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="N180" s="12" t="inlineStr">
         <is>
-          <t>Softaculous/Installatron ma ~400 aplikacji; my mamy Nextcloud i PrestaShop</t>
+          <t>Softaculous/Installatron ma ~400 aplikacji; my mamy Nextcloud i PrestaShop | KOREKTA 2026-08-21: niezależnie od ubogiego katalogu, ścieżka wykonania była przerwana — node-app-install.sh nie był kopiowany do obrazu, więc /agent/tasks/app-install/script zwracał 500 i zadanie APP_INSTALL nie mogło się wykonać na produkcji. Naprawione razem z B-01.</t>
         </is>
       </c>
     </row>
@@ -26627,9 +26627,81 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="11" t="inlineStr">
+        <is>
+          <t>X-12</t>
+        </is>
+      </c>
+      <c r="B358" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C358" s="11" t="inlineStr">
+        <is>
+          <t>Skrypty węzła serwowane przez API obecne w obrazie produkcyjnym</t>
+        </is>
+      </c>
+      <c r="D358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I358" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J358" s="12" t="inlineStr">
+        <is>
+          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts porównuje loadery z listą COPY</t>
+        </is>
+      </c>
+      <c r="K358" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L358" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M358" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N358" s="12" t="inlineStr">
+        <is>
+          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N357"/>
-  <conditionalFormatting sqref="D2:D357">
+  <autoFilter ref="A1:N358"/>
+  <conditionalFormatting sqref="D2:D358">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26646,7 +26718,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E357">
+  <conditionalFormatting sqref="E2:E358">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26663,7 +26735,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F357">
+  <conditionalFormatting sqref="F2:F358">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26680,7 +26752,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G357">
+  <conditionalFormatting sqref="G2:G358">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26697,7 +26769,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H357">
+  <conditionalFormatting sqref="H2:H358">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26714,7 +26786,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I357">
+  <conditionalFormatting sqref="I2:I358">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26734,7 +26806,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K357">
+  <conditionalFormatting sqref="K2:K358">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26751,7 +26823,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L357">
+  <conditionalFormatting sqref="L2:L358">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -25963,7 +25963,7 @@
       </c>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
+          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="K348" s="11" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="N348" s="12" t="inlineStr">
         <is>
-          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Rozszerzony 2026-08-21 na live-release-readiness — to z niej idą realne wdrożenia, więc ochrona samego main nie pilnowała niczego, co trafia na serwer. Konsekwencja: scalanie na gałąź wdrożeniową przez PR albo fast-forward; lokalny merge commit zostanie zablokowany, bo nie ma własnego przebiegu CI. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$359</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$358,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$359,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$358,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$359,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$358,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$359,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$358,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$359,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$358,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$359,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$358,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$359,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$358,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$359,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$358,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$359,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$358,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$359,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$358,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$359,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"A",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"B",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"C",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"D",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"E",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"F",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"G",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"H",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"I",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"J",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"K",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"L",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"M",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"N",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"O",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"P",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Q",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"X",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$358,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$359,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$K$2:$K$358,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$358,"Z",Macierz!$L$2:$L$358,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N358"/>
+  <dimension ref="A1:N359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26699,9 +26699,81 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="11" t="inlineStr">
+        <is>
+          <t>X-13</t>
+        </is>
+      </c>
+      <c r="B359" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C359" s="11" t="inlineStr">
+        <is>
+          <t>Jedna gałąź wdrożeniowa — main</t>
+        </is>
+      </c>
+      <c r="D359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I359" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J359" s="12" t="inlineStr">
+        <is>
+          <t>.github/workflows/deploy.yml — on.push.branches: [main]</t>
+        </is>
+      </c>
+      <c r="K359" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M359" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N359" s="12" t="inlineStr">
+        <is>
+          <t>Do 2026-08-21 wdrożenie wyzwalały trzy gałęzie: main, master i live-release-readiness. Realne wdrożenia szły z live-release-readiness, master w repozytorium nie istniał, a main stał od czerwca. Trzy wyzwalacze to trzy odpowiedzi na pytanie „co jest na produkcji" — czyli brak odpowiedzi. Decyzja PM-a: zostaje sam main, chroniony rulesetem z X-02 i bramką testową z X-03. Konsekwencja: live-release-readiness przestaje być gałęzią wdrożeniową i zostaje jako zapis historii do czasu wycofania.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N358"/>
-  <conditionalFormatting sqref="D2:D358">
+  <autoFilter ref="A1:N359"/>
+  <conditionalFormatting sqref="D2:D359">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26718,7 +26790,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E358">
+  <conditionalFormatting sqref="E2:E359">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26735,7 +26807,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F358">
+  <conditionalFormatting sqref="F2:F359">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26752,7 +26824,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G358">
+  <conditionalFormatting sqref="G2:G359">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26769,7 +26841,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H358">
+  <conditionalFormatting sqref="H2:H359">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26786,7 +26858,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I358">
+  <conditionalFormatting sqref="I2:I359">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26806,7 +26878,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K358">
+  <conditionalFormatting sqref="K2:K359">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26823,7 +26895,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L358">
+  <conditionalFormatting sqref="L2:L359">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -3619,7 +3619,7 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>KOREKTA: pozycja miała stan DZIAŁA na podstawie kodu i kolejki PHP_APPLY. Odkryte 2026-08-21 przy przeglądzie Dockerfile.api: loadery skryptów w API czytają plik z dysku i rzucają wyjątkiem, gdy go nie ma, a obraz produkcyjny kopiował tylko 7 z 10 potrzebnych skryptów. Endpoint /agent/tasks/php-apply/script zwracał 500, więc agent nie miał czego uruchomić — zadanie PHP_APPLY nie mogło się wykonać na produkcji ani razu. Naprawione (COPY + test apps/api/src/test/dockerfile-scripts.spec.ts), ale do czasu potwierdzenia na produkcji stan to CZĘŚCIOWE: kod i testy były zielone przez cały czas, więc D1 i D2 nic tu nie dowodzą — potrzebny D3.</t>
+          <t>KOREKTA: pozycja miała stan DZIAŁA na podstawie kodu i kolejki PHP_APPLY. Odkryte 2026-08-21 przy przeglądzie Dockerfile.api: loadery skryptów w API czytają plik z dysku i rzucają wyjątkiem, gdy go nie ma, a obraz produkcyjny kopiował tylko 7 z 10 potrzebnych skryptów. Endpoint /agent/tasks/php-apply/script zwracał 500, więc agent nie miał czego uruchomić — zadanie PHP_APPLY nie mogło się wykonać na produkcji ani razu. Naprawione (COPY + test apps/api/src/test/dockerfile-scripts.spec.ts), ale do czasu potwierdzenia na produkcji stan to CZĘŚCIOWE: kod i testy były zielone przez cały czas, więc D1 i D2 nic tu nie dowodzą — potrzebny D3. | 2026-08-21 21:57: przyczyna wdrożeniowa USUNIĘTA — node-php-apply.sh jest już w obrazie (potwierdzone na serwerze, X-12 D3). Pozycja zostaje CZĘŚCIOWE, bo jej własny dowód wymaga wykonania zadania PHP_APPLY na żywym węźle, a węzła jeszcze nie ma. Do przejścia z części B checklisty D3.</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts porównuje loadery z listą COPY</t>
+          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts; D3: 2026-08-21 21:57 — `docker exec &lt;api&gt; ls -la ops/scripts/` na control-plane pokazuje 10 plików, w tym node-php-apply.sh, node-app-install.sh i node-account-restore.sh</t>
         </is>
       </c>
       <c r="K358" s="11" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="N358" s="12" t="inlineStr">
         <is>
-          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę.</t>
+          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę. | D3 OSIĄGNIĘTE 2026-08-21 21:57 po wdrożeniu #62: wszystkie dziesięć skryptów obecne w obrazie na serwerze. To pierwsza pozycja w tym audycie z dowodem poziomu D3.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$359,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$360,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$359,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$360,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$359,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$360,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$359,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$360,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$359,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$360,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$359,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$360,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$359,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$360,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$359,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$360,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$359,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$360,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$359,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$360,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"A",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"B",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"C",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"D",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"E",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"F",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"G",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"H",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"I",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"J",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"K",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"L",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"M",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"N",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"O",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"P",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Q",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"X",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$359,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$360,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$K$2:$K$359,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$359,"Z",Macierz!$L$2:$L$359,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N359"/>
+  <dimension ref="A1:N360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20818,22 +20818,22 @@
       </c>
       <c r="I275" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J275" s="12" t="inlineStr">
         <is>
-          <t>addon.service.ts:110 — idempotencyKey zawiera Date.now(), więc mechanizm z wallet-ledger.service.ts:94-105 nigdy nie zadziała; addon.controller.ts:17 dopuszcza 10 wywołań na godzinę</t>
+          <t>addon.service.ts — kluczIdempotencji + sprawdzenie duplikatu przed obciążeniem + obsługa P2002; schema.prisma — PurchasedAddon.idempotencyKey @unique; migracja 20260821220000_addon_idempotency</t>
         </is>
       </c>
       <c r="K275" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L275" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M275" s="11" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="N275" s="12" t="inlineStr">
         <is>
-          <t>Podwójne kliknięcie, ponowienie przeglądarki albo timeout = do 10 obciążeń za ten sam dodatek w godzinę. Bez ścieżki zwrotu w systemie, bo nie ma ani refundu, ani korekty faktury.</t>
+          <t>Zamknięte 2026-08-21. Mechanizm idempotencji w księdze portfela był poprawny — nie miał czego porównywać, bo Date.now() w kluczu dawał inny klucz przy każdym kliknięciu. Poprawka na dwóch drogach: klucz od klienta (panel, useRef, jeden na decyzję zakupu) i okno czasu jako zapas. Sprawdzenie duplikatu idzie PRZED obciążeniem, więc nie powtarzają się też skutki uboczne — bez tego klient dostawałby dziesięć zgłoszeń do BOK-u przy jednym obciążeniu. Wyścig domyka unikalny indeks w bazie. 20 testów, 10 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy pieniędzy. Dokumentacja: docs/zadania/Z-06-klucz-idempotencji-dodatku.md</t>
         </is>
       </c>
     </row>
@@ -21138,75 +21138,79 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>N-01</t>
+          <t>Z-11</t>
         </is>
       </c>
       <c r="B280" s="12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>System zgłoszeń dla klienta</t>
+          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
         </is>
       </c>
       <c r="D280" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E280" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F280" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H280" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J280" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:92,98</t>
+          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
         </is>
       </c>
       <c r="K280" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L280" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M280" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N280" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N280" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-06. Sprawdziłem, że Date.now() w kluczu idempotencji występował tylko w jednym miejscu — ale to sprawdzenie odpowiada wyłącznie na pytanie „czy klucz jest zmienny", nie na pytanie „czy klucz identyfikuje właściwą operację". Klucz może być stabilny i jednocześnie zły: za szeroki (blokuje legalne powtórzenie) albo za wąski (nie łapie duplikatu). Do przejścia po wszystkich wywołaniach wallet.debit/credit i handlerach webhooków.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>N-02</t>
+          <t>N-01</t>
         </is>
       </c>
       <c r="B281" s="12" t="inlineStr">
@@ -21216,7 +21220,7 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Załączniki w zgłoszeniu</t>
+          <t>System zgłoszeń dla klienta</t>
         </is>
       </c>
       <c r="D281" s="11" t="inlineStr">
@@ -21231,7 +21235,7 @@
       </c>
       <c r="F281" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G281" s="11" t="inlineStr">
@@ -21251,7 +21255,7 @@
       </c>
       <c r="J281" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:98,245</t>
+          <t>tickets.controller.ts:92,98</t>
         </is>
       </c>
       <c r="K281" s="11" t="inlineStr">
@@ -21274,7 +21278,7 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>N-03</t>
+          <t>N-02</t>
         </is>
       </c>
       <c r="B282" s="12" t="inlineStr">
@@ -21284,7 +21288,7 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Ocena obsługi (CSAT)</t>
+          <t>Załączniki w zgłoszeniu</t>
         </is>
       </c>
       <c r="D282" s="11" t="inlineStr">
@@ -21299,17 +21303,17 @@
       </c>
       <c r="F282" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I282" s="11" t="inlineStr">
@@ -21319,12 +21323,12 @@
       </c>
       <c r="J282" s="12" t="inlineStr">
         <is>
-          <t>tickets.controller.ts:279</t>
+          <t>tickets.controller.ts:98,245</t>
         </is>
       </c>
       <c r="K282" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L282" s="11" t="inlineStr">
@@ -21342,7 +21346,7 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>N-04</t>
+          <t>N-03</t>
         </is>
       </c>
       <c r="B283" s="12" t="inlineStr">
@@ -21352,7 +21356,7 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy po polsku</t>
+          <t>Ocena obsługi (CSAT)</t>
         </is>
       </c>
       <c r="D283" s="11" t="inlineStr">
@@ -21372,12 +21376,12 @@
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H283" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I283" s="11" t="inlineStr">
@@ -21387,12 +21391,12 @@
       </c>
       <c r="J283" s="12" t="inlineStr">
         <is>
-          <t>kb.public.controller.ts:226</t>
+          <t>tickets.controller.ts:279</t>
         </is>
       </c>
       <c r="K283" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L283" s="11" t="inlineStr">
@@ -21410,7 +21414,7 @@
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>N-04</t>
         </is>
       </c>
       <c r="B284" s="12" t="inlineStr">
@@ -21420,7 +21424,7 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Baza wiedzy po polsku</t>
         </is>
       </c>
       <c r="D284" s="11" t="inlineStr">
@@ -21440,37 +21444,37 @@
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H284" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>kb.public.controller.ts:226</t>
         </is>
       </c>
       <c r="K284" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L284" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M284" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N284" s="12" t="inlineStr"/>
@@ -21478,7 +21482,7 @@
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>N-06</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B285" s="12" t="inlineStr">
@@ -21488,7 +21492,7 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Publiczna strona statusu usług</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="D285" s="11" t="inlineStr">
@@ -21508,49 +21512,45 @@
       </c>
       <c r="G285" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H285" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H285" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I285" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
         <is>
-          <t>probes-admin.controller.ts:33; apps/status-page</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
       <c r="K285" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L285" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M285" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N285" s="12" t="inlineStr">
-        <is>
-          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N285" s="12" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>N-06</t>
         </is>
       </c>
       <c r="B286" s="12" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Publiczna strona statusu usług</t>
         </is>
       </c>
       <c r="D286" s="11" t="inlineStr">
@@ -21590,39 +21590,39 @@
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J286" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>probes-admin.controller.ts:33; apps/status-page</t>
         </is>
       </c>
       <c r="K286" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L286" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M286" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N286" s="12" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>tylko cyber_Folks i dhosting mają na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>N-08</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B287" s="12" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Edycja i zamknięcie incydentu</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="D287" s="11" t="inlineStr">
@@ -21662,35 +21662,39 @@
       </c>
       <c r="I287" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
         <is>
-          <t>status/actions.ts:158,177</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="K287" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L287" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M287" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N287" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N287" s="12" t="inlineStr">
+        <is>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>N-09</t>
+          <t>N-08</t>
         </is>
       </c>
       <c r="B288" s="12" t="inlineStr">
@@ -21700,7 +21704,7 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienia w panelu (dzwonek)</t>
+          <t>Edycja i zamknięcie incydentu</t>
         </is>
       </c>
       <c r="D288" s="11" t="inlineStr">
@@ -21710,19 +21714,19 @@
       </c>
       <c r="E288" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F288" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G288" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F288" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G288" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H288" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -21735,7 +21739,7 @@
       </c>
       <c r="J288" s="12" t="inlineStr">
         <is>
-          <t>notifications.controller.ts:12,20,26</t>
+          <t>status/actions.ts:158,177</t>
         </is>
       </c>
       <c r="K288" s="11" t="inlineStr">
@@ -21758,7 +21762,7 @@
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-09</t>
         </is>
       </c>
       <c r="B289" s="12" t="inlineStr">
@@ -21768,7 +21772,7 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Powiadomienia w panelu (dzwonek)</t>
         </is>
       </c>
       <c r="D289" s="11" t="inlineStr">
@@ -21798,39 +21802,35 @@
       </c>
       <c r="I289" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>notifications.controller.ts:12,20,26</t>
         </is>
       </c>
       <c r="K289" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L289" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M289" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N289" s="12" t="inlineStr">
-        <is>
-          <t>sterowalne są tylko zgody marketingowe</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N289" s="12" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B290" s="12" t="inlineStr">
@@ -21840,69 +21840,69 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="D290" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E290" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E290" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="F290" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G290" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G290" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H290" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J290" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
       <c r="K290" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L290" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M290" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N290" s="12" t="inlineStr">
         <is>
-          <t>cały panel Product Ops/NOC jest read-only</t>
+          <t>sterowalne są tylko zgody marketingowe</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B291" s="12" t="inlineStr">
@@ -21912,32 +21912,32 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="D291" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E291" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F291" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F291" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G291" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H291" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I291" s="11" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="J291" s="12" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
       <c r="K291" s="11" t="inlineStr">
@@ -21957,20 +21957,24 @@
       </c>
       <c r="L291" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M291" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N291" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N291" s="12" t="inlineStr">
+        <is>
+          <t>cały panel Product Ops/NOC jest read-only</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B292" s="12" t="inlineStr">
@@ -21980,42 +21984,42 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="D292" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E292" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F292" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G292" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J292" s="12" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
       <c r="K292" s="11" t="inlineStr">
@@ -22025,24 +22029,20 @@
       </c>
       <c r="L292" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M292" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N292" s="12" t="inlineStr">
-        <is>
-          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N292" s="12" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B293" s="12" t="inlineStr">
@@ -22052,42 +22052,42 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="D293" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E293" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F293" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E293" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F293" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H293" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I293" s="11" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
       <c r="K293" s="11" t="inlineStr">
@@ -22102,19 +22102,19 @@
       </c>
       <c r="M293" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N293" s="12" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>Skorygowane: powierzchnia abuse częściowo istnieje — outbound-cordon.admin.controller.ts:25,31, uprawnienie ABUSE_MANAGE (staff-permissions.catalog.ts:21), zarezerwowany adres abuse@, throttling na węźle. Brakuje kolejki i procesu, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>N-15</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B294" s="12" t="inlineStr">
@@ -22124,69 +22124,69 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="D294" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E294" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F294" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G294" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H294" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="J294" s="12" t="inlineStr">
         <is>
-          <t>cockpit migracji + kreator klienta</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="K294" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L294" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M294" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N294" s="12" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>N-15</t>
         </is>
       </c>
       <c r="B295" s="12" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Migracja z innego hostingu wykonywana przez dostawcę</t>
         </is>
       </c>
       <c r="D295" s="11" t="inlineStr">
@@ -22216,49 +22216,49 @@
       </c>
       <c r="G295" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H295" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H295" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="I295" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>cockpit migracji + kreator klienta</t>
         </is>
       </c>
       <c r="K295" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L295" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M295" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N295" s="12" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>4 z 5 hostingów PL robi ręcznie; u nas to produkt</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>N-17</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B296" s="12" t="inlineStr">
@@ -22268,7 +22268,7 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Szablony odpowiedzi obsługi</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="D296" s="11" t="inlineStr">
@@ -22283,50 +22283,54 @@
       </c>
       <c r="F296" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G296" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G296" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H296" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I296" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J296" s="12" t="inlineStr">
         <is>
-          <t>settings/canned-responses/actions.ts:23</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="K296" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L296" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M296" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N296" s="12" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N296" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>N-18</t>
+          <t>N-17</t>
         </is>
       </c>
       <c r="B297" s="12" t="inlineStr">
@@ -22336,7 +22340,7 @@
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>CRM klienta 360 dla obsługi</t>
+          <t>Szablony odpowiedzi obsługi</t>
         </is>
       </c>
       <c r="D297" s="11" t="inlineStr">
@@ -22351,7 +22355,7 @@
       </c>
       <c r="F297" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G297" s="11" t="inlineStr">
@@ -22371,12 +22375,12 @@
       </c>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
+          <t>settings/canned-responses/actions.ts:23</t>
         </is>
       </c>
       <c r="K297" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L297" s="11" t="inlineStr">
@@ -22394,7 +22398,7 @@
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>N-19</t>
+          <t>N-18</t>
         </is>
       </c>
       <c r="B298" s="12" t="inlineStr">
@@ -22404,7 +22408,7 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
+          <t>CRM klienta 360 dla obsługi</t>
         </is>
       </c>
       <c r="D298" s="11" t="inlineStr">
@@ -22424,12 +22428,12 @@
       </c>
       <c r="G298" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I298" s="11" t="inlineStr">
@@ -22439,7 +22443,7 @@
       </c>
       <c r="J298" s="12" t="inlineStr">
         <is>
-          <t>ai-chat.service.ts (223 l.)</t>
+          <t>crm-profile-data.ts; users.admin.controller.ts:109,120</t>
         </is>
       </c>
       <c r="K298" s="11" t="inlineStr">
@@ -22457,16 +22461,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N298" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
-        </is>
-      </c>
+      <c r="N298" s="12" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-19</t>
         </is>
       </c>
       <c r="B299" s="12" t="inlineStr">
@@ -22476,65 +22476,69 @@
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>Sugestia AI odpowiedzi na zgłoszenie</t>
         </is>
       </c>
       <c r="D299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I299" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>ai-chat.service.ts (223 l.)</t>
         </is>
       </c>
       <c r="K299" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L299" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M299" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N299" s="12" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N299" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: wynik renderowany jako surowy JSON.stringify w &lt;pre&gt; (ticket-detail-panel.tsx:346-349), bez możliwości wstawienia do odpowiedzi.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B300" s="12" t="inlineStr">
@@ -22544,42 +22548,42 @@
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="D300" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E300" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F300" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G300" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J300" s="12" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
       <c r="K300" s="11" t="inlineStr">
@@ -22594,74 +22598,70 @@
       </c>
       <c r="M300" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N300" s="12" t="inlineStr">
-        <is>
-          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
-        </is>
-      </c>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N300" s="12" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>Subkonta z uprawnieniami (IAM)</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="D301" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E301" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F301" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G301" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H301" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G301" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H301" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I301" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:42,53,63,69</t>
+          <t>poza produktem</t>
         </is>
       </c>
       <c r="K301" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L301" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M301" s="11" t="inlineStr">
@@ -22671,14 +22671,14 @@
       </c>
       <c r="N301" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+          <t>home.pl i nazwa.pl mają telefon 24/7 — decyzja operacyjna, nie produktowa</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="B302" s="12" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Aktywacja subkonta z zaproszenia</t>
+          <t>Subkonta z uprawnieniami (IAM)</t>
         </is>
       </c>
       <c r="D302" s="11" t="inlineStr">
@@ -22723,12 +22723,12 @@
       </c>
       <c r="J302" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:47</t>
+          <t>customer-iam.controller.ts:42,53,63,69</t>
         </is>
       </c>
       <c r="K302" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L302" s="11" t="inlineStr">
@@ -22741,12 +22741,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N302" s="12" t="inlineStr"/>
+      <c r="N302" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl ma coś podobnego na rynku PL</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>O-02</t>
         </is>
       </c>
       <c r="B303" s="12" t="inlineStr">
@@ -22756,69 +22760,65 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Aktywacja subkonta z zaproszenia</t>
         </is>
       </c>
       <c r="D303" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E303" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F303" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E303" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F303" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G303" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>customer-iam.controller.ts:47</t>
         </is>
       </c>
       <c r="K303" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L303" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M303" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N303" s="12" t="inlineStr">
-        <is>
-          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N303" s="12" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B304" s="12" t="inlineStr">
@@ -22828,12 +22828,12 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Egzekwowanie uprawnień w nawigacji i API</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="D304" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E304" s="11" t="inlineStr">
@@ -22843,50 +22843,54 @@
       </c>
       <c r="F304" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G304" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H304" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G304" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H304" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
         <is>
-          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
       <c r="K304" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L304" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M304" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N304" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N304" s="12" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: customer-iam.service.ts:72-88 filtruje action startsWith CUSTOMER_IAM_ — istnieje 5 takich akcji. To dziennik zarządzania subkontami, nie ich działań.</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-04</t>
         </is>
       </c>
       <c r="B305" s="12" t="inlineStr">
@@ -22896,7 +22900,7 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Egzekwowanie uprawnień w nawigacji i API</t>
         </is>
       </c>
       <c r="D305" s="11" t="inlineStr">
@@ -22911,42 +22915,42 @@
       </c>
       <c r="F305" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>middleware.ts:39; customer-permissions.guard.ts:9; test D1</t>
         </is>
       </c>
       <c r="K305" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L305" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M305" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N305" s="12" t="inlineStr"/>
@@ -22954,7 +22958,7 @@
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B306" s="12" t="inlineStr">
@@ -22964,7 +22968,7 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="D306" s="11" t="inlineStr">
@@ -22994,17 +22998,17 @@
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
       <c r="K306" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L306" s="11" t="inlineStr">
@@ -23017,16 +23021,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N306" s="12" t="inlineStr">
-        <is>
-          <t>bez tego reseller nie jest produktem</t>
-        </is>
-      </c>
+      <c r="N306" s="12" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B307" s="12" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="C307" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="D307" s="11" t="inlineStr">
@@ -23066,35 +23066,39 @@
       </c>
       <c r="I307" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K307" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L307" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M307" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N307" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N307" s="12" t="inlineStr">
+        <is>
+          <t>bez tego reseller nie jest produktem</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B308" s="12" t="inlineStr">
@@ -23104,47 +23108,47 @@
       </c>
       <c r="C308" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="D308" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E308" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F308" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G308" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E308" s="11" t="inlineStr">
+      <c r="H308" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F308" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G308" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H308" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
       <c r="K308" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L308" s="11" t="inlineStr">
@@ -23157,16 +23161,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N308" s="12" t="inlineStr">
-        <is>
-          <t>strona sprzedażowa bez operacji zapisu</t>
-        </is>
-      </c>
+      <c r="N308" s="12" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B309" s="12" t="inlineStr">
@@ -23176,22 +23176,22 @@
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="D309" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E309" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F309" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G309" s="11" t="inlineStr">
@@ -23206,17 +23206,17 @@
       </c>
       <c r="I309" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
       <c r="K309" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L309" s="11" t="inlineStr">
@@ -23226,19 +23226,19 @@
       </c>
       <c r="M309" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N309" s="12" t="inlineStr">
         <is>
-          <t>seohost to reklamuje jako wyróżnik</t>
+          <t>strona sprzedażowa bez operacji zapisu</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>O-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B310" s="12" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>Role i uprawnienia operatorów</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="D310" s="11" t="inlineStr">
@@ -23268,45 +23268,49 @@
       </c>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H310" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I310" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J310" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:31,36,41</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
       <c r="K310" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L310" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M310" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N310" s="12" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N310" s="12" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje jako wyróżnik</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>O-11</t>
+          <t>O-10</t>
         </is>
       </c>
       <c r="B311" s="12" t="inlineStr">
@@ -23316,7 +23320,7 @@
       </c>
       <c r="C311" s="11" t="inlineStr">
         <is>
-          <t>Zarządzanie operatorami</t>
+          <t>Role i uprawnienia operatorów</t>
         </is>
       </c>
       <c r="D311" s="11" t="inlineStr">
@@ -23351,7 +23355,7 @@
       </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>staff-roles.admin.controller.ts:51,56,61</t>
+          <t>staff-roles.admin.controller.ts:31,36,41</t>
         </is>
       </c>
       <c r="K311" s="11" t="inlineStr">
@@ -23374,7 +23378,7 @@
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>O-12</t>
+          <t>O-11</t>
         </is>
       </c>
       <c r="B312" s="12" t="inlineStr">
@@ -23384,32 +23388,32 @@
       </c>
       <c r="C312" s="11" t="inlineStr">
         <is>
-          <t>Program partnerski / afiliacyjny</t>
+          <t>Zarządzanie operatorami</t>
         </is>
       </c>
       <c r="D312" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E312" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F312" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G312" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I312" s="11" t="inlineStr">
@@ -23419,7 +23423,7 @@
       </c>
       <c r="J312" s="12" t="inlineStr">
         <is>
-          <t>partners.controller.ts:18,28,34</t>
+          <t>staff-roles.admin.controller.ts:51,56,61</t>
         </is>
       </c>
       <c r="K312" s="11" t="inlineStr">
@@ -23437,16 +23441,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N312" s="12" t="inlineStr">
-        <is>
-          <t>wypłata na portfel lub IBAN</t>
-        </is>
-      </c>
+      <c r="N312" s="12" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>Z-04</t>
+          <t>O-12</t>
         </is>
       </c>
       <c r="B313" s="12" t="inlineStr">
@@ -23456,29 +23456,29 @@
       </c>
       <c r="C313" s="11" t="inlineStr">
         <is>
-          <t>Guard uprawnień subkont — domyślna odmowa</t>
+          <t>Program partnerski / afiliacyjny</t>
         </is>
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E313" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F313" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G313" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="G313" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H313" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="J313" s="12" t="inlineStr">
         <is>
-          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
+          <t>partners.controller.ts:18,28,34</t>
         </is>
       </c>
       <c r="K313" s="11" t="inlineStr">
@@ -23506,46 +23506,46 @@
       </c>
       <c r="M313" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
+          <t>wypłata na portfel lub IBAN</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>Z-04</t>
         </is>
       </c>
       <c r="B314" s="12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C314" s="11" t="inlineStr">
         <is>
-          <t>Eksport danych osobowych (art. 20)</t>
+          <t>Guard uprawnień subkont — domyślna odmowa</t>
         </is>
       </c>
       <c r="D314" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E314" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F314" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F314" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
       <c r="G314" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="H314" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I314" s="11" t="inlineStr">
@@ -23563,12 +23563,12 @@
       </c>
       <c r="J314" s="12" t="inlineStr">
         <is>
-          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
+          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
         </is>
       </c>
       <c r="K314" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L314" s="11" t="inlineStr">
@@ -23578,19 +23578,19 @@
       </c>
       <c r="M314" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N314" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B315" s="12" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Żądanie usunięcia konta (art. 17)</t>
+          <t>Eksport danych osobowych (art. 20)</t>
         </is>
       </c>
       <c r="D315" s="11" t="inlineStr">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="J315" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.service.ts:29,308,383-432</t>
+          <t>data-export.service.ts:43-76 (ZIP, 12 sekcji, 13 tabel, TTL 7 dni)</t>
         </is>
       </c>
       <c r="K315" s="11" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="L315" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M315" s="11" t="inlineStr">
@@ -23655,14 +23655,14 @@
       </c>
       <c r="N315" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
+          <t>ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B316" s="12" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>Wycofanie żądania usunięcia</t>
+          <t>Żądanie usunięcia konta (art. 17)</t>
         </is>
       </c>
       <c r="D316" s="11" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="E316" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F316" s="11" t="inlineStr">
@@ -23692,12 +23692,12 @@
       </c>
       <c r="G316" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H316" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I316" s="11" t="inlineStr">
@@ -23707,7 +23707,7 @@
       </c>
       <c r="J316" s="12" t="inlineStr">
         <is>
-          <t>account-deletion.controller.ts:62</t>
+          <t>account-deletion.service.ts:29,308,383-432</t>
         </is>
       </c>
       <c r="K316" s="11" t="inlineStr">
@@ -23717,7 +23717,7 @@
       </c>
       <c r="L316" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M316" s="11" t="inlineStr">
@@ -23727,14 +23727,14 @@
       </c>
       <c r="N316" s="12" t="inlineStr">
         <is>
-          <t>karencja 14 dni</t>
+          <t>ZERO testów na operacji NIEODWRACALNEJ (twarde kasowanie konta DA)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B317" s="12" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="C317" s="11" t="inlineStr">
         <is>
-          <t>Historia zgód klienta</t>
+          <t>Wycofanie żądania usunięcia</t>
         </is>
       </c>
       <c r="D317" s="11" t="inlineStr">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="E317" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F317" s="11" t="inlineStr">
@@ -23764,12 +23764,12 @@
       </c>
       <c r="G317" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H317" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I317" s="11" t="inlineStr">
@@ -23779,12 +23779,12 @@
       </c>
       <c r="J317" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:70</t>
+          <t>account-deletion.controller.ts:62</t>
         </is>
       </c>
       <c r="K317" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L317" s="11" t="inlineStr">
@@ -23797,12 +23797,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N317" s="12" t="inlineStr"/>
+      <c r="N317" s="12" t="inlineStr">
+        <is>
+          <t>karencja 14 dni</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="B318" s="12" t="inlineStr">
@@ -23812,7 +23816,7 @@
       </c>
       <c r="C318" s="11" t="inlineStr">
         <is>
-          <t>Ponowna akceptacja przy zmianie regulaminu</t>
+          <t>Historia zgód klienta</t>
         </is>
       </c>
       <c r="D318" s="11" t="inlineStr">
@@ -23822,7 +23826,7 @@
       </c>
       <c r="E318" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F318" s="11" t="inlineStr">
@@ -23847,12 +23851,12 @@
       </c>
       <c r="J318" s="12" t="inlineStr">
         <is>
-          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
+          <t>consents.controller.ts:70</t>
         </is>
       </c>
       <c r="K318" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L318" s="11" t="inlineStr">
@@ -23870,7 +23874,7 @@
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="B319" s="12" t="inlineStr">
@@ -23880,7 +23884,7 @@
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Umowa powierzenia (DPA) do pobrania</t>
+          <t>Ponowna akceptacja przy zmianie regulaminu</t>
         </is>
       </c>
       <c r="D319" s="11" t="inlineStr">
@@ -23890,24 +23894,24 @@
       </c>
       <c r="E319" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F319" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G319" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F319" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G319" s="11" t="inlineStr">
+      <c r="H319" s="11" t="inlineStr">
         <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H319" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I319" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -23915,7 +23919,7 @@
       </c>
       <c r="J319" s="12" t="inlineStr">
         <is>
-          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
+          <t>reconsent-modal.tsx:169; consents.controller.ts:76</t>
         </is>
       </c>
       <c r="K319" s="11" t="inlineStr">
@@ -23938,7 +23942,7 @@
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="B320" s="12" t="inlineStr">
@@ -23948,7 +23952,7 @@
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Dokumenty prawne z historią wersji</t>
+          <t>Umowa powierzenia (DPA) do pobrania</t>
         </is>
       </c>
       <c r="D320" s="11" t="inlineStr">
@@ -23958,7 +23962,7 @@
       </c>
       <c r="E320" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F320" s="11" t="inlineStr">
@@ -23983,7 +23987,7 @@
       </c>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>legal-documents.controller.ts:36,49</t>
+          <t>dpa.controller.ts:23; dpa-pdf.service.ts</t>
         </is>
       </c>
       <c r="K320" s="11" t="inlineStr">
@@ -24001,16 +24005,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N320" s="12" t="inlineStr">
-        <is>
-          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
-        </is>
-      </c>
+      <c r="N320" s="12" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="B321" s="12" t="inlineStr">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Retencja i anonimizacja logów</t>
+          <t>Dokumenty prawne z historią wersji</t>
         </is>
       </c>
       <c r="D321" s="11" t="inlineStr">
@@ -24030,22 +24030,22 @@
       </c>
       <c r="E321" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F321" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G321" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F321" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G321" s="11" t="inlineStr">
-        <is>
-          <t>b.d.</t>
-        </is>
-      </c>
       <c r="H321" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I321" s="11" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="J321" s="12" t="inlineStr">
         <is>
-          <t>retention.scheduler.ts:29,30,87,95</t>
+          <t>legal-documents.controller.ts:36,49</t>
         </is>
       </c>
       <c r="K321" s="11" t="inlineStr">
@@ -24075,14 +24075,14 @@
       </c>
       <c r="N321" s="12" t="inlineStr">
         <is>
-          <t>ZERO testów</t>
+          <t>brakujący dokument → „Dokument w przygotowaniu”</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B322" s="12" t="inlineStr">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>Zgody marketingowe (opt-in/out)</t>
+          <t>Retencja i anonimizacja logów</t>
         </is>
       </c>
       <c r="D322" s="11" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="E322" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F322" s="11" t="inlineStr">
@@ -24112,12 +24112,12 @@
       </c>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H322" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I322" s="11" t="inlineStr">
@@ -24127,12 +24127,12 @@
       </c>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>consents.controller.ts:99</t>
+          <t>retention.scheduler.ts:29,30,87,95</t>
         </is>
       </c>
       <c r="K322" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L322" s="11" t="inlineStr">
@@ -24145,12 +24145,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N322" s="12" t="inlineStr"/>
+      <c r="N322" s="12" t="inlineStr">
+        <is>
+          <t>ZERO testów</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B323" s="12" t="inlineStr">
@@ -24160,7 +24164,7 @@
       </c>
       <c r="C323" s="11" t="inlineStr">
         <is>
-          <t>Baner zgody na cookies</t>
+          <t>Zgody marketingowe (opt-in/out)</t>
         </is>
       </c>
       <c r="D323" s="11" t="inlineStr">
@@ -24195,7 +24199,7 @@
       </c>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>cookie-consent.tsx</t>
+          <t>consents.controller.ts:99</t>
         </is>
       </c>
       <c r="K323" s="11" t="inlineStr">
@@ -24218,7 +24222,7 @@
     <row r="324">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="B324" s="12" t="inlineStr">
@@ -24228,7 +24232,7 @@
       </c>
       <c r="C324" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Baner zgody na cookies</t>
         </is>
       </c>
       <c r="D324" s="11" t="inlineStr">
@@ -24248,49 +24252,45 @@
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H324" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I324" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>cookie-consent.tsx</t>
         </is>
       </c>
       <c r="K324" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L324" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M324" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N324" s="12" t="inlineStr">
-        <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N324" s="12" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B325" s="12" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="C325" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="D325" s="11" t="inlineStr">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="E325" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F325" s="11" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="J325" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
       <c r="K325" s="11" t="inlineStr">
@@ -24350,19 +24350,19 @@
       </c>
       <c r="M325" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
-          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak encji i widoku” był mylący. Art. 30 wymaga formy pisemnej lub elektronicznej — dokument ją spełnia. Do pilnowania zostaje dyscyplina przeglądów i dat.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B326" s="12" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="C326" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="D326" s="11" t="inlineStr">
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E326" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F326" s="11" t="inlineStr">
@@ -24392,27 +24392,27 @@
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="H326" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="I326" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J326" s="12" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
       <c r="K326" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L326" s="11" t="inlineStr">
@@ -24422,19 +24422,19 @@
       </c>
       <c r="M326" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N326" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to eksponuje</t>
+          <t>KOREKTA DOWODU: wcześniejszy zapis „brak audytu w repo” był FAŁSZYWY. Audyt istnieje. Dokument powołuje się na zwolnienie mikroprzedsiębiorcy (art. 4 ust. 2 ustawy z 26.04.2024) — warto potwierdzić z prawnikiem i pilnować progów 10 osób / 2 mln EUR.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B327" s="12" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="D327" s="11" t="inlineStr">
@@ -24464,49 +24464,49 @@
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H327" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="H327" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="I327" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>poza kodem</t>
         </is>
       </c>
       <c r="K327" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L327" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M327" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>wszystkie 5 hostingów PL to eksponuje</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B328" s="12" t="inlineStr">
@@ -24516,32 +24516,32 @@
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="D328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H328" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I328" s="11" t="inlineStr">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="J328" s="12" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K328" s="11" t="inlineStr">
@@ -24561,96 +24561,96 @@
       </c>
       <c r="L328" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M328" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N328" s="12" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>Q-01</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B329" s="12" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Program eko / punkty za oszczędność</t>
+          <t>Podpisane DPA z subprocesorami</t>
         </is>
       </c>
       <c r="D329" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E329" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F329" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G329" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H329" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I329" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
         <is>
-          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="K329" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L329" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="M329" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N329" s="12" t="inlineStr">
         <is>
-          <t>nikt na rynku PL</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>Q-02</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="B330" s="12" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>Raport energetyczny usługi</t>
+          <t>Program eko / punkty za oszczędność</t>
         </is>
       </c>
       <c r="D330" s="11" t="inlineStr">
@@ -24690,12 +24690,12 @@
       </c>
       <c r="I330" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J330" s="12" t="inlineStr">
         <is>
-          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
+          <t>users.controller.ts:58,91; FEATURE_ECO domyślnie true</t>
         </is>
       </c>
       <c r="K330" s="11" t="inlineStr">
@@ -24715,14 +24715,14 @@
       </c>
       <c r="N330" s="12" t="inlineStr">
         <is>
-          <t>metodologia opisana — uczciwe podejście</t>
+          <t>nikt na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>Q-03</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="B331" s="12" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>Badge eko do osadzenia na stronie klienta</t>
+          <t>Raport energetyczny usługi</t>
         </is>
       </c>
       <c r="D331" s="11" t="inlineStr">
@@ -24762,12 +24762,12 @@
       </c>
       <c r="I331" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
         <is>
-          <t>eco-public.controller.ts:32,74; test D1</t>
+          <t>eco-report.service.ts:9 — jawnie deklarowany jako szacunek</t>
         </is>
       </c>
       <c r="K331" s="11" t="inlineStr">
@@ -24787,14 +24787,14 @@
       </c>
       <c r="N331" s="12" t="inlineStr">
         <is>
-          <t>4 warianty + pixel odsłon</t>
+          <t>metodologia opisana — uczciwe podejście</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>Q-04</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="B332" s="12" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>Tryb eko usługi</t>
+          <t>Badge eko do osadzenia na stronie klienta</t>
         </is>
       </c>
       <c r="D332" s="11" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="J332" s="12" t="inlineStr">
         <is>
-          <t>subscriptions.controller.ts:73</t>
+          <t>eco-public.controller.ts:32,74; test D1</t>
         </is>
       </c>
       <c r="K332" s="11" t="inlineStr">
@@ -24859,14 +24859,14 @@
       </c>
       <c r="N332" s="12" t="inlineStr">
         <is>
-          <t>wpływa m.in. na politykę backupów</t>
+          <t>4 warianty + pixel odsłon</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>Q-05</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="B333" s="12" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C333" s="11" t="inlineStr">
         <is>
-          <t>E-mail marketing wbudowany w panel</t>
+          <t>Tryb eko usługi</t>
         </is>
       </c>
       <c r="D333" s="11" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="H333" s="11" t="inlineStr">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="J333" s="12" t="inlineStr">
         <is>
-          <t>email-marketing.controller.ts:36,81,119,139</t>
+          <t>subscriptions.controller.ts:73</t>
         </is>
       </c>
       <c r="K333" s="11" t="inlineStr">
@@ -24931,14 +24931,14 @@
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
-          <t>double opt-in + cordon antyspamowy</t>
+          <t>wpływa m.in. na politykę backupów</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>Q-05</t>
         </is>
       </c>
       <c r="B334" s="12" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="C334" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>E-mail marketing wbudowany w panel</t>
         </is>
       </c>
       <c r="D334" s="11" t="inlineStr">
@@ -24968,49 +24968,49 @@
       </c>
       <c r="G334" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H334" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="I334" s="11" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J334" s="12" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>email-marketing.controller.ts:36,81,119,139</t>
         </is>
       </c>
       <c r="K334" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L334" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M334" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N334" s="12" t="inlineStr">
         <is>
-          <t>bez tokenu menu prowadzi do pustego stanu</t>
+          <t>double opt-in + cordon antyspamowy</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B335" s="12" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="D335" s="11" t="inlineStr">
@@ -25040,32 +25040,32 @@
       </c>
       <c r="G335" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H335" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I335" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
         </is>
       </c>
       <c r="K335" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L335" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M335" s="11" t="inlineStr">
@@ -25073,12 +25073,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N335" s="12" t="inlineStr"/>
+      <c r="N335" s="12" t="inlineStr">
+        <is>
+          <t>bez tokenu menu prowadzi do pustego stanu</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="11" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B336" s="12" t="inlineStr">
@@ -25088,7 +25092,7 @@
       </c>
       <c r="C336" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="D336" s="11" t="inlineStr">
@@ -25113,7 +25117,7 @@
       </c>
       <c r="H336" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="I336" s="11" t="inlineStr">
@@ -25146,7 +25150,7 @@
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B337" s="12" t="inlineStr">
@@ -25156,29 +25160,29 @@
       </c>
       <c r="C337" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="D337" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E337" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F337" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G337" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="E337" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="F337" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="G337" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
       <c r="H337" s="11" t="inlineStr">
         <is>
           <t>TAK</t>
@@ -25186,22 +25190,22 @@
       </c>
       <c r="I337" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K337" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L337" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M337" s="11" t="inlineStr">
@@ -25209,16 +25213,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="N337" s="12" t="inlineStr">
-        <is>
-          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
-        </is>
-      </c>
+      <c r="N337" s="12" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t>Q-10</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B338" s="12" t="inlineStr">
@@ -25228,22 +25228,22 @@
       </c>
       <c r="C338" s="11" t="inlineStr">
         <is>
-          <t>Natywna aplikacja mobilna</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="D338" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="E338" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F338" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="G338" s="11" t="inlineStr">
@@ -25253,44 +25253,44 @@
       </c>
       <c r="H338" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I338" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
       <c r="K338" s="11" t="inlineStr">
         <is>
-          <t>POZA ZAKRESEM</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L338" s="11" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M338" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N338" s="12" t="inlineStr">
         <is>
-          <t>tylko home.pl (iOS)</t>
+          <t>twardy wymóg zapisany w decyzji brandingowej DA</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t>Q-11</t>
+          <t>Q-10</t>
         </is>
       </c>
       <c r="B339" s="12" t="inlineStr">
@@ -25300,7 +25300,7 @@
       </c>
       <c r="C339" s="11" t="inlineStr">
         <is>
-          <t>Tryb prosty / zaawansowany panelu</t>
+          <t>Natywna aplikacja mobilna</t>
         </is>
       </c>
       <c r="D339" s="11" t="inlineStr">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="G339" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H339" s="11" t="inlineStr">
@@ -25330,22 +25330,22 @@
       </c>
       <c r="I339" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
         <is>
-          <t>page.tsx:139 — ukrywa 7 zakładek</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K339" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>POZA ZAKRESEM</t>
         </is>
       </c>
       <c r="L339" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="M339" s="11" t="inlineStr">
@@ -25353,12 +25353,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N339" s="12" t="inlineStr"/>
+      <c r="N339" s="12" t="inlineStr">
+        <is>
+          <t>tylko home.pl (iOS)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t>Q-12</t>
+          <t>Q-11</t>
         </is>
       </c>
       <c r="B340" s="12" t="inlineStr">
@@ -25368,7 +25372,7 @@
       </c>
       <c r="C340" s="11" t="inlineStr">
         <is>
-          <t>Kreator pierwszych kroków (onboarding)</t>
+          <t>Tryb prosty / zaawansowany panelu</t>
         </is>
       </c>
       <c r="D340" s="11" t="inlineStr">
@@ -25378,24 +25382,24 @@
       </c>
       <c r="E340" s="11" t="inlineStr">
         <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F340" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G340" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="H340" s="11" t="inlineStr">
+        <is>
           <t>CZĘŚĆ</t>
         </is>
       </c>
-      <c r="F340" s="11" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="G340" s="11" t="inlineStr">
-        <is>
-          <t>CZĘŚĆ</t>
-        </is>
-      </c>
-      <c r="H340" s="11" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
       <c r="I340" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
@@ -25403,12 +25407,12 @@
       </c>
       <c r="J340" s="12" t="inlineStr">
         <is>
-          <t>onboarding-wizard.tsx:52</t>
+          <t>page.tsx:139 — ukrywa 7 zakładek</t>
         </is>
       </c>
       <c r="K340" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L340" s="11" t="inlineStr">
@@ -25421,16 +25425,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N340" s="12" t="inlineStr">
-        <is>
-          <t>tylko nawigacja</t>
-        </is>
-      </c>
+      <c r="N340" s="12" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t>Q-13</t>
+          <t>Q-12</t>
         </is>
       </c>
       <c r="B341" s="12" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="C341" s="11" t="inlineStr">
         <is>
-          <t>Command palette dla operatora</t>
+          <t>Kreator pierwszych kroków (onboarding)</t>
         </is>
       </c>
       <c r="D341" s="11" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="E341" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F341" s="11" t="inlineStr">
@@ -25460,12 +25460,12 @@
       </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="H341" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I341" s="11" t="inlineStr">
@@ -25475,12 +25475,12 @@
       </c>
       <c r="J341" s="12" t="inlineStr">
         <is>
-          <t>command-palette-actions.ts</t>
+          <t>onboarding-wizard.tsx:52</t>
         </is>
       </c>
       <c r="K341" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L341" s="11" t="inlineStr">
@@ -25493,12 +25493,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N341" s="12" t="inlineStr"/>
+      <c r="N341" s="12" t="inlineStr">
+        <is>
+          <t>tylko nawigacja</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-13</t>
         </is>
       </c>
       <c r="B342" s="12" t="inlineStr">
@@ -25508,22 +25512,22 @@
       </c>
       <c r="C342" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>Command palette dla operatora</t>
         </is>
       </c>
       <c r="D342" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E342" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F342" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G342" s="11" t="inlineStr">
@@ -25538,39 +25542,35 @@
       </c>
       <c r="I342" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
+          <t>command-palette-actions.ts</t>
         </is>
       </c>
       <c r="K342" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L342" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M342" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N342" s="12" t="inlineStr">
-        <is>
-          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N342" s="12" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t>Q-15</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B343" s="12" t="inlineStr">
@@ -25580,22 +25580,22 @@
       </c>
       <c r="C343" s="11" t="inlineStr">
         <is>
-          <t>Live-readiness (checklista przed startem)</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="D343" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="E343" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="F343" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G343" s="11" t="inlineStr">
@@ -25610,39 +25610,39 @@
       </c>
       <c r="I343" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
         <is>
-          <t>live-readiness.service.ts — 14 checków</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
       <c r="K343" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L343" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M343" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N343" s="12" t="inlineStr">
         <is>
-          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+          <t>w tym brakuje kroku konfiguracji backupu — patrz H-19</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="11" t="inlineStr">
         <is>
-          <t>Q-16</t>
+          <t>Q-15</t>
         </is>
       </c>
       <c r="B344" s="12" t="inlineStr">
@@ -25652,7 +25652,7 @@
       </c>
       <c r="C344" s="11" t="inlineStr">
         <is>
-          <t>Metryki biznesowe (MRR, churn)</t>
+          <t>Live-readiness (checklista przed startem)</t>
         </is>
       </c>
       <c r="D344" s="11" t="inlineStr">
@@ -25687,12 +25687,12 @@
       </c>
       <c r="J344" s="12" t="inlineStr">
         <is>
-          <t>business-metrics.admin.controller.ts:15; test D1</t>
+          <t>live-readiness.service.ts — 14 checków</t>
         </is>
       </c>
       <c r="K344" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L344" s="11" t="inlineStr">
@@ -25705,12 +25705,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N344" s="12" t="inlineStr"/>
+      <c r="N344" s="12" t="inlineStr">
+        <is>
+          <t>dobre narzędzie; nie sprawdza odtwarzalności kopii</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="11" t="inlineStr">
         <is>
-          <t>Q-17</t>
+          <t>Q-16</t>
         </is>
       </c>
       <c r="B345" s="12" t="inlineStr">
@@ -25720,7 +25724,7 @@
       </c>
       <c r="C345" s="11" t="inlineStr">
         <is>
-          <t>Grafana SSO dla operatora</t>
+          <t>Metryki biznesowe (MRR, churn)</t>
         </is>
       </c>
       <c r="D345" s="11" t="inlineStr">
@@ -25730,7 +25734,7 @@
       </c>
       <c r="E345" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚĆ</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F345" s="11" t="inlineStr">
@@ -25755,12 +25759,12 @@
       </c>
       <c r="J345" s="12" t="inlineStr">
         <is>
-          <t>grafana-auth.controller.ts</t>
+          <t>business-metrics.admin.controller.ts:15; test D1</t>
         </is>
       </c>
       <c r="K345" s="11" t="inlineStr">
         <is>
-          <t>PRZEWAGA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L345" s="11" t="inlineStr">
@@ -25778,7 +25782,7 @@
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t>Q-18</t>
+          <t>Q-17</t>
         </is>
       </c>
       <c r="B346" s="12" t="inlineStr">
@@ -25788,7 +25792,7 @@
       </c>
       <c r="C346" s="11" t="inlineStr">
         <is>
-          <t>VPN WireGuard dla dostępu operatorskiego</t>
+          <t>Grafana SSO dla operatora</t>
         </is>
       </c>
       <c r="D346" s="11" t="inlineStr">
@@ -25798,7 +25802,7 @@
       </c>
       <c r="E346" s="11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>CZĘŚĆ</t>
         </is>
       </c>
       <c r="F346" s="11" t="inlineStr">
@@ -25823,7 +25827,7 @@
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
+          <t>grafana-auth.controller.ts</t>
         </is>
       </c>
       <c r="K346" s="11" t="inlineStr">
@@ -25846,32 +25850,32 @@
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>Q-18</t>
         </is>
       </c>
       <c r="B347" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>CI uruchamiające testy</t>
+          <t>VPN WireGuard dla dostępu operatorskiego</t>
         </is>
       </c>
       <c r="D347" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="E347" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F347" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G347" s="11" t="inlineStr">
@@ -25891,12 +25895,12 @@
       </c>
       <c r="J347" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
+          <t>vpn.admin.controller.ts:29; vpn.service.ts:14-25</t>
         </is>
       </c>
       <c r="K347" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>PRZEWAGA</t>
         </is>
       </c>
       <c r="L347" s="11" t="inlineStr">
@@ -25906,19 +25910,15 @@
       </c>
       <c r="M347" s="11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="N347" s="12" t="inlineStr">
-        <is>
-          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N347" s="12" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B348" s="12" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>Status wymagany do merge</t>
+          <t>CI uruchamiające testy</t>
         </is>
       </c>
       <c r="D348" s="11" t="inlineStr">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="J348" s="12" t="inlineStr">
         <is>
-          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
+          <t>.github/workflows/ci.yml — typecheck, testy API, build, smoke migracji Prisma, gitleaks, pnpm audit, Trivy, dependabot</t>
         </is>
       </c>
       <c r="K348" s="11" t="inlineStr">
@@ -25983,14 +25983,14 @@
       </c>
       <c r="N348" s="12" t="inlineStr">
         <is>
-          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Rozszerzony 2026-08-21 na live-release-readiness — to z niej idą realne wdrożenia, więc ochrona samego main nie pilnowała niczego, co trafia na serwer. Konsekwencja: scalanie na gałąź wdrożeniową przez PR albo fast-forward; lokalny merge commit zostanie zablokowany, bo nie ma własnego przebiegu CI. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
+          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B349" s="12" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="C349" s="11" t="inlineStr">
         <is>
-          <t>Testy uruchamiane przed wdrożeniem</t>
+          <t>Status wymagany do merge</t>
         </is>
       </c>
       <c r="D349" s="11" t="inlineStr">
@@ -26030,22 +26030,22 @@
       </c>
       <c r="I349" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
+          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="K349" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L349" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M349" s="11" t="inlineStr">
@@ -26055,14 +26055,14 @@
       </c>
       <c r="N349" s="12" t="inlineStr">
         <is>
-          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Rozszerzony 2026-08-21 na live-release-readiness — to z niej idą realne wdrożenia, więc ochrona samego main nie pilnowała niczego, co trafia na serwer. Konsekwencja: scalanie na gałąź wdrożeniową przez PR albo fast-forward; lokalny merge commit zostanie zablokowany, bo nie ma własnego przebiegu CI. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B350" s="12" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C350" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Testy uruchamiane przed wdrożeniem</t>
         </is>
       </c>
       <c r="D350" s="11" t="inlineStr">
@@ -26102,17 +26102,17 @@
       </c>
       <c r="I350" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>.github/workflows/deploy.yml — job test-gate (typecheck + pnpm --filter api test), build-push ma needs: test-gate</t>
         </is>
       </c>
       <c r="K350" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L350" s="11" t="inlineStr">
@@ -26122,19 +26122,19 @@
       </c>
       <c r="M350" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N350" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+          <t>Ścieżka automatyczna (push → build → deploy) od 2026-08-21 nie przepuszcza czerwonych testów. Ścieżka ręczna ops/scripts/prod-deploy-ghcr.sh nadal nie uruchamia żadnych testów — dlatego CZĘŚCIOWE, nie DZIAŁA.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B351" s="12" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="D351" s="11" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
       <c r="K351" s="11" t="inlineStr">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="L351" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M351" s="11" t="inlineStr">
@@ -26197,12 +26197,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="N351" s="12" t="inlineStr"/>
+      <c r="N351" s="12" t="inlineStr">
+        <is>
+          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="11" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B352" s="12" t="inlineStr">
@@ -26212,7 +26216,7 @@
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="D352" s="11" t="inlineStr">
@@ -26247,7 +26251,7 @@
       </c>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
       <c r="K352" s="11" t="inlineStr">
@@ -26257,24 +26261,20 @@
       </c>
       <c r="L352" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M352" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N352" s="12" t="inlineStr">
-        <is>
-          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N352" s="12" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B353" s="12" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="C353" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="D353" s="11" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="J353" s="12" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
       <c r="K353" s="11" t="inlineStr">
@@ -26339,14 +26339,14 @@
       </c>
       <c r="N353" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01.</t>
+          <t>Reklasyfikacja jak X-01 — z zastrzeżeniem, że po ustaleniach Z-02 i Z-04 to właśnie moduł auth i guardy są miejscem, gdzie brak testów już zamienił się w realne luki.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="11" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B354" s="12" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="C354" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="D354" s="11" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
       <c r="K354" s="11" t="inlineStr">
@@ -26411,14 +26411,14 @@
       </c>
       <c r="N354" s="12" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+          <t>Reklasyfikacja jak X-01.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B355" s="12" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="D355" s="11" t="inlineStr">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="J355" s="12" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
       <c r="K355" s="11" t="inlineStr">
@@ -26478,15 +26478,19 @@
       </c>
       <c r="M355" s="11" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N355" s="12" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N355" s="12" t="inlineStr">
+        <is>
+          <t>Reklasyfikacja jak X-01 — ale patrz Z-03: brak testów walidacji wejścia migracji to nie jest kwestia jakości, tylko przyczyna luki wykonania kodu.</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B356" s="12" t="inlineStr">
@@ -26496,7 +26500,7 @@
       </c>
       <c r="C356" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="D356" s="11" t="inlineStr">
@@ -26526,12 +26530,12 @@
       </c>
       <c r="I356" s="11" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J356" s="12" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
       <c r="K356" s="11" t="inlineStr">
@@ -26546,19 +26550,15 @@
       </c>
       <c r="M356" s="11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N356" s="12" t="inlineStr">
-        <is>
-          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
-        </is>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N356" s="12" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="11" t="inlineStr">
         <is>
-          <t>X-11</t>
+          <t>X-10</t>
         </is>
       </c>
       <c r="B357" s="12" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="C357" s="11" t="inlineStr">
         <is>
-          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
         </is>
       </c>
       <c r="D357" s="11" t="inlineStr">
@@ -26598,12 +26598,12 @@
       </c>
       <c r="I357" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
         <is>
-          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
         </is>
       </c>
       <c r="K357" s="11" t="inlineStr">
@@ -26613,24 +26613,24 @@
       </c>
       <c r="L357" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M357" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N357" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
+          <t>pokrycie pozorne w najdroższym możliwym miejscu</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="11" t="inlineStr">
         <is>
-          <t>X-12</t>
+          <t>X-11</t>
         </is>
       </c>
       <c r="B358" s="12" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="C358" s="11" t="inlineStr">
         <is>
-          <t>Skrypty węzła serwowane przez API obecne w obrazie produkcyjnym</t>
+          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
       <c r="D358" s="11" t="inlineStr">
@@ -26670,22 +26670,22 @@
       </c>
       <c r="I358" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts; D3: 2026-08-21 21:57 — `docker exec &lt;api&gt; ls -la ops/scripts/` na control-plane pokazuje 10 plików, w tym node-php-apply.sh, node-app-install.sh i node-account-restore.sh</t>
+          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
       <c r="K358" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L358" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M358" s="11" t="inlineStr">
@@ -26695,85 +26695,157 @@
       </c>
       <c r="N358" s="12" t="inlineStr">
         <is>
-          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę. | D3 OSIĄGNIĘTE 2026-08-21 21:57 po wdrożeniu #62: wszystkie dziesięć skryptów obecne w obrazie na serwerze. To pierwsza pozycja w tym audycie z dowodem poziomu D3.</t>
+          <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
         <is>
+          <t>X-12</t>
+        </is>
+      </c>
+      <c r="B359" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C359" s="11" t="inlineStr">
+        <is>
+          <t>Skrypty węzła serwowane przez API obecne w obrazie produkcyjnym</t>
+        </is>
+      </c>
+      <c r="D359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I359" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J359" s="12" t="inlineStr">
+        <is>
+          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts; D3: 2026-08-21 21:57 — `docker exec &lt;api&gt; ls -la ops/scripts/` na control-plane pokazuje 10 plików, w tym node-php-apply.sh, node-app-install.sh i node-account-restore.sh</t>
+        </is>
+      </c>
+      <c r="K359" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L359" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M359" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N359" s="12" t="inlineStr">
+        <is>
+          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę. | D3 OSIĄGNIĘTE 2026-08-21 21:57 po wdrożeniu #62: wszystkie dziesięć skryptów obecne w obrazie na serwerze. To pierwsza pozycja w tym audycie z dowodem poziomu D3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="11" t="inlineStr">
+        <is>
           <t>X-13</t>
         </is>
       </c>
-      <c r="B359" s="12" t="inlineStr">
+      <c r="B360" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C359" s="11" t="inlineStr">
+      <c r="C360" s="11" t="inlineStr">
         <is>
           <t>Jedna gałąź wdrożeniowa — main</t>
         </is>
       </c>
-      <c r="D359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I359" s="11" t="inlineStr">
+      <c r="D360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I360" s="11" t="inlineStr">
         <is>
           <t>DZIAŁA</t>
         </is>
       </c>
-      <c r="J359" s="12" t="inlineStr">
+      <c r="J360" s="12" t="inlineStr">
         <is>
           <t>.github/workflows/deploy.yml — on.push.branches: [main]</t>
         </is>
       </c>
-      <c r="K359" s="11" t="inlineStr">
+      <c r="K360" s="11" t="inlineStr">
         <is>
           <t>PARYTET</t>
         </is>
       </c>
-      <c r="L359" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M359" s="11" t="inlineStr">
+      <c r="L360" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M360" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N359" s="12" t="inlineStr">
+      <c r="N360" s="12" t="inlineStr">
         <is>
           <t>Do 2026-08-21 wdrożenie wyzwalały trzy gałęzie: main, master i live-release-readiness. Realne wdrożenia szły z live-release-readiness, master w repozytorium nie istniał, a main stał od czerwca. Trzy wyzwalacze to trzy odpowiedzi na pytanie „co jest na produkcji" — czyli brak odpowiedzi. Decyzja PM-a: zostaje sam main, chroniony rulesetem z X-02 i bramką testową z X-03. Konsekwencja: live-release-readiness przestaje być gałęzią wdrożeniową i zostaje jako zapis historii do czasu wycofania.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N359"/>
-  <conditionalFormatting sqref="D2:D359">
+  <autoFilter ref="A1:N360"/>
+  <conditionalFormatting sqref="D2:D360">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26790,7 +26862,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E359">
+  <conditionalFormatting sqref="E2:E360">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26807,7 +26879,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F359">
+  <conditionalFormatting sqref="F2:F360">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26824,7 +26896,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G359">
+  <conditionalFormatting sqref="G2:G360">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26841,7 +26913,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H359">
+  <conditionalFormatting sqref="H2:H360">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26858,7 +26930,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I359">
+  <conditionalFormatting sqref="I2:I360">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26878,7 +26950,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K359">
+  <conditionalFormatting sqref="K2:K360">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26895,7 +26967,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L359">
+  <conditionalFormatting sqref="L2:L360">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowane 2026-08-21 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
+          <t>Wygenerowane 2026-08-22 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
         </is>
       </c>
     </row>
@@ -26670,22 +26670,22 @@
       </c>
       <c r="I358" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
+          <t>.github/workflows/ci.yml — osobny job api-tests o nazwie „API unit tests"</t>
         </is>
       </c>
       <c r="K358" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L358" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M358" s="11" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="N358" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy pierwszym przebiegu CI (#17, 2026-08-21). Testy stoją w tym samym jobie co lint i typecheck, w kroku PO nich — więc błąd typów w dowolnym z sześciu workspace’ów kasuje jedyny krok dający poziom dowodu D2. Dokładnie tak było w #17: CI działało, typecheck padał na apps/www, a pnpm --filter api test nie uruchomiło się ani razu. Zasada na przyszłość: krok, który dowodzi, nie może stać za krokiem, który tylko sprawdza higienę. Po rozdzieleniu trzeba dopisać nowy check do rulesetu z X-02.</t>
+          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. UWAGA: nowy check trzeba dopisać do rulesetu z X-02, inaczej nie jest wymagany do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -26035,7 +26035,7 @@
       </c>
       <c r="J349" s="12" t="inlineStr">
         <is>
-          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
+          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 4 checki z ci.yml</t>
         </is>
       </c>
       <c r="K349" s="11" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="N358" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. UWAGA: nowy check trzeba dopisać do rulesetu z X-02, inaczej nie jest wymagany do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md</t>
+          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. Check „API unit tests" dopisany do rulesetu z X-02 tego samego dnia — bez tego rozdzielenie jobów otwierałoby dziurę: testy widoczne, ale niewymagane do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$360,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$363,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$360,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$363,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$360,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$363,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$360,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$363,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$360,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$363,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$360,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$363,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$360,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$363,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$360,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$363,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$360,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$363,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$360,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$363,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"A",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"B",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"C",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"D",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"E",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"F",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"G",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"H",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"I",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"J",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"K",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"L",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"M",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"N",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"O",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"P",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Q",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"X",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$360,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$363,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$K$2:$K$360,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$360,"Z",Macierz!$L$2:$L$360,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N360"/>
+  <dimension ref="A1:N363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26843,9 +26843,225 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="11" t="inlineStr">
+        <is>
+          <t>Z-12</t>
+        </is>
+      </c>
+      <c r="B361" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C361" s="11" t="inlineStr">
+        <is>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+        </is>
+      </c>
+      <c r="D361" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E361" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F361" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G361" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H361" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I361" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J361" s="12" t="inlineStr">
+        <is>
+          <t>provisioning.service.ts:299-301 zwiększa allocatedCpu/allocatedMemory/allocatedDisk o pełne limity planu; node-selector.service.ts:109-115 wpuszcza konto tylko gdy total-allocated ≥ limit planu + headroom; schema.prisma:474 reservedHeadroomPercent Int @default(0)</t>
+        </is>
+      </c>
+      <c r="K361" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L361" s="11" t="inlineStr">
+        <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="M361" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N361" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy PB-01. Węzeł księguje 8 GB RAM i 2 vCPU na każde konto, mimo że w LVE to sufity burst, a nie rezerwacje. Skutek arytmetyczny: 128 GB / 8 GB = 16 kont na węzeł i selektor przestaje wpuszczać kolejne. Próg rentowności przy cenie 45 zł to 58 kont. Oznacza to, że przy dzisiejszym kodzie każdy węzeł domyka się na stracie ok. 1 074 zł/mies. i nie da się tego naprawić sprzedażą — selektor po prostu odmówi provisioningu. To nie jest optymalizacja kosztu, to warunek istnienia oferty. Do zrobienia: współczynniki nadsubskrypcji per węzeł (overcommitCpu/Ram/Disk) użyte w node-selector, oddzielenie księgowania 'sprzedane' od 'realnie zajęte', alarm gdy realne zużycie zbliża się do pojemności. Dysk traktować ostrożniej niż RAM i CPU: quota dyskowa jest realnie egzekwowana i klient może ją wypełnić w całości. Model: docs/strategy/PB-01_unit_economics_wezla.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="11" t="inlineStr">
+        <is>
+          <t>Z-13</t>
+        </is>
+      </c>
+      <c r="B362" s="12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C362" s="11" t="inlineStr">
+        <is>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+        </is>
+      </c>
+      <c r="D362" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E362" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F362" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G362" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H362" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I362" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J362" s="12" t="inlineStr">
+        <is>
+          <t>seed.ts:40-112 zawiera wyłącznie starter/pro/business (19,99/49,99/99,99 zł); apps/www/.../Pricing.tsx:120 sprzedaje 45 zł/399 zł, hosting/page.tsx:77 opisuje bazę 50 GB / 8 GB / 2 vCPU — planu o takich limitach nie ma w żadnym seedzie ani migracji</t>
+        </is>
+      </c>
+      <c r="K362" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L362" s="11" t="inlineStr">
+        <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="M362" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N362" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy PB-01. Strona sprzedaje pakiet, którego nie ma po stronie produktu. Trzy plany w seedzie to próbki z czasów prototypu i mają inne ceny oraz inne limity niż cokolwiek, co Verris ogłasza publicznie. Dopóki plan nie istnieje jako rekord z cpuLimit/ramLimitMb/diskLimitMb, nie działa ani wycena, ani placement, ani synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh czyta limity z Planu). Do zrobienia: migracja tworząca plan produkcyjny z limitami zgodnymi z treścią oferty, wycofanie planów próbnych z isPublic, test sprawdzający, że każda cena widoczna na www ma odpowiadający jej aktywny plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="11" t="inlineStr">
+        <is>
+          <t>Z-14</t>
+        </is>
+      </c>
+      <c r="B363" s="12" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C363" s="11" t="inlineStr">
+        <is>
+          <t>Treść oferty nie obiecuje zasobów, których nie da się dotrzymać jednocześnie</t>
+        </is>
+      </c>
+      <c r="D363" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E363" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F363" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G363" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H363" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I363" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J363" s="12" t="inlineStr">
+        <is>
+          <t>apps/www/src/app/(frontend)/hosting/page.tsx — „do 8 GB RAM, do 2 vCPU”; apps/www/src/app/(frontend)/components/Pricing.tsx — ta sama zmiana w karcie pakietu</t>
+        </is>
+      </c>
+      <c r="K363" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L363" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M363" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N363" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. Strona pisała „Baza w cenie: 50 GB NVMe, 8 GB RAM, 2 vCPU”. Przy gęstości, przy której węzeł w ogóle się domyka (51 kont), oznaczałoby to 408 GB RAM obiecane na maszynie ze 128 GB. Sformułowanie „w cenie” to obietnica rezerwacji; RAM i CPU są w LVE sufitami burst, więc poprawne jest „do”. Dysk zostaje bez zmiany — quota dyskowa jest realnie egzekwowana i 50 GB to faktyczna alokacja. To ten sam typ błędu, który audyt wychwycił w oferta.md: zdanie prawdziwe dla jednego klienta i nieprawdziwe dla wszystkich naraz. Decyzja PM-a z 2026-08-22. Dokumentacja: docs/strategy/DECYZJA_CENOWA_2026-08.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N360"/>
-  <conditionalFormatting sqref="D2:D360">
+  <autoFilter ref="A1:N363"/>
+  <conditionalFormatting sqref="D2:D363">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26862,7 +27078,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E360">
+  <conditionalFormatting sqref="E2:E363">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26879,7 +27095,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F360">
+  <conditionalFormatting sqref="F2:F363">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26896,7 +27112,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G360">
+  <conditionalFormatting sqref="G2:G363">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26913,7 +27129,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H360">
+  <conditionalFormatting sqref="H2:H363">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -26930,7 +27146,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I360">
+  <conditionalFormatting sqref="I2:I363">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -26950,7 +27166,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K360">
+  <conditionalFormatting sqref="K2:K363">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -26967,7 +27183,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L360">
+  <conditionalFormatting sqref="L2:L363">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$363,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$364,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$363,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$364,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$363,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$364,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$363,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$364,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$363,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$364,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$363,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$364,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$363,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$364,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$363,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$364,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$363,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$364,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$363,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$364,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"A",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"B",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"C",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"D",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"E",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"F",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"G",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"H",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"I",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"J",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"K",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"L",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"M",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"N",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"O",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"P",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Q",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"X",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$363,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$364,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$K$2:$K$363,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$363,"Z",Macierz!$L$2:$L$363,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N363"/>
+  <dimension ref="A1:N364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26886,22 +26886,22 @@
       </c>
       <c r="I361" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J361" s="12" t="inlineStr">
         <is>
-          <t>provisioning.service.ts:299-301 zwiększa allocatedCpu/allocatedMemory/allocatedDisk o pełne limity planu; node-selector.service.ts:109-115 wpuszcza konto tylko gdy total-allocated ≥ limit planu + headroom; schema.prisma:474 reservedHeadroomPercent Int @default(0)</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="K361" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L361" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M361" s="11" t="inlineStr">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="N361" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy PB-01. Węzeł księguje 8 GB RAM i 2 vCPU na każde konto, mimo że w LVE to sufity burst, a nie rezerwacje. Skutek arytmetyczny: 128 GB / 8 GB = 16 kont na węzeł i selektor przestaje wpuszczać kolejne. Próg rentowności przy cenie 45 zł to 58 kont. Oznacza to, że przy dzisiejszym kodzie każdy węzeł domyka się na stracie ok. 1 074 zł/mies. i nie da się tego naprawić sprzedażą — selektor po prostu odmówi provisioningu. To nie jest optymalizacja kosztu, to warunek istnienia oferty. Do zrobienia: współczynniki nadsubskrypcji per węzeł (overcommitCpu/Ram/Disk) użyte w node-selector, oddzielenie księgowania 'sprzedane' od 'realnie zajęte', alarm gdy realne zużycie zbliża się do pojemności. Dysk traktować ostrożniej niż RAM i CPU: quota dyskowa jest realnie egzekwowana i klient może ją wypełnić w całości. Model: docs/strategy/PB-01_unit_economics_wezla.xlsx</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
     </row>
@@ -27059,9 +27059,81 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="11" t="inlineStr">
+        <is>
+          <t>Z-15</t>
+        </is>
+      </c>
+      <c r="B364" s="12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="inlineStr">
+        <is>
+          <t>Alert wyprzedzający, gdy realne zużycie węzła zbliża się do progu</t>
+        </is>
+      </c>
+      <c r="D364" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E364" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F364" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚĆ</t>
+        </is>
+      </c>
+      <c r="G364" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚĆ</t>
+        </is>
+      </c>
+      <c r="H364" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I364" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J364" s="12" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — bramka fizyczna odmawia po przekroczeniu progu, nie przed</t>
+        </is>
+      </c>
+      <c r="K364" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L364" s="11" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="M364" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N364" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-12. Bramka realnego zużycia działa poprawnie, ale odzywa się dopiero wtedy, gdy węzeł jest już pełny — a operator dowiaduje się o tym z nieudanej sprzedaży. To jest ten sam wzorzec co przy X-12: mechanizm działa, tylko informacja dociera po fakcie. Do zrobienia: próg ostrzegawczy (np. 70% pojemności fizycznej) podpięty pod istniejący ops-watchdog.scheduler.ts, który już liczy procenty wykorzystania i wysyła alerty. Przy okazji: nikt nie liczy sumy nadsubskrypcji po całej flocie — przy jednym węźle bez znaczenia, przy pięciu już nie.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N363"/>
-  <conditionalFormatting sqref="D2:D363">
+  <autoFilter ref="A1:N364"/>
+  <conditionalFormatting sqref="D2:D364">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27078,7 +27150,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E363">
+  <conditionalFormatting sqref="E2:E364">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27095,7 +27167,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F363">
+  <conditionalFormatting sqref="F2:F364">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27112,7 +27184,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G363">
+  <conditionalFormatting sqref="G2:G364">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27129,7 +27201,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H363">
+  <conditionalFormatting sqref="H2:H364">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27146,7 +27218,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I363">
+  <conditionalFormatting sqref="I2:I364">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27166,7 +27238,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K363">
+  <conditionalFormatting sqref="K2:K364">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27183,7 +27255,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L363">
+  <conditionalFormatting sqref="L2:L364">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$364,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$365,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$364,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$365,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$364,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$365,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$364,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$365,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$364,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$365,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$364,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$365,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$364,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$365,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$364,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$365,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$364,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$365,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$364,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$365,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"A",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"B",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"C",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"D",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"E",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"F",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"G",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"H",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"I",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"J",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"K",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"L",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"M",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"N",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"O",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"P",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Q",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"X",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$364,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$365,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$K$2:$K$364,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$364,"Z",Macierz!$L$2:$L$364,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N364"/>
+  <dimension ref="A1:N365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26958,22 +26958,22 @@
       </c>
       <c r="I362" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J362" s="12" t="inlineStr">
         <is>
-          <t>seed.ts:40-112 zawiera wyłącznie starter/pro/business (19,99/49,99/99,99 zł); apps/www/.../Pricing.tsx:120 sprzedaje 45 zł/399 zł, hosting/page.tsx:77 opisuje bazę 50 GB / 8 GB / 2 vCPU — planu o takich limitach nie ma w żadnym seedzie ani migracji</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="K362" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L362" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M362" s="11" t="inlineStr">
@@ -26983,7 +26983,7 @@
       </c>
       <c r="N362" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy PB-01. Strona sprzedaje pakiet, którego nie ma po stronie produktu. Trzy plany w seedzie to próbki z czasów prototypu i mają inne ceny oraz inne limity niż cokolwiek, co Verris ogłasza publicznie. Dopóki plan nie istnieje jako rekord z cpuLimit/ramLimitMb/diskLimitMb, nie działa ani wycena, ani placement, ani synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh czyta limity z Planu). Do zrobienia: migracja tworząca plan produkcyjny z limitami zgodnymi z treścią oferty, wycofanie planów próbnych z isPublic, test sprawdzający, że każda cena widoczna na www ma odpowiadający jej aktywny plan.</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
     </row>
@@ -27131,9 +27131,81 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" s="11" t="inlineStr">
+        <is>
+          <t>Z-16</t>
+        </is>
+      </c>
+      <c r="B365" s="12" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C365" s="11" t="inlineStr">
+        <is>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+        </is>
+      </c>
+      <c r="D365" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="E365" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="F365" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚĆ</t>
+        </is>
+      </c>
+      <c r="G365" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚĆ</t>
+        </is>
+      </c>
+      <c r="H365" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I365" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J365" s="12" t="inlineStr">
+        <is>
+          <t>autoscaling-engine.service.ts:287 — Math.min(value, 10) przycina krotność niezależnie od planu, więc sufit CPU (12×) i dysku (20×) z oferty jest nieosiągalny; w całym pliku nie ma ani jednego odwołania do Server/allocated — silnik skaluje konto bez pytania węzła o pojemność i bez aktualizacji allocatedCpu/Memory/Disk</t>
+        </is>
+      </c>
+      <c r="K365" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L365" s="11" t="inlineStr">
+        <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="M365" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N365" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-13. Dwie rzeczy, jedna przyczyna — silnik autoskalowania nie wie nic o węźle, na którym stoi konto. | PIERWSZA: oferta obiecuje skalowanie do 24 vCPU i 1000 GB, a przycięcie do 10× daje realnie 20 vCPU i 500 GB. Klient płacący za nadwyżkę godzinowo nie dostanie tego, za co zapłacił, i będzie miał rację w reklamacji. | DRUGA i groźniejsza: silnik podnosi limity konta w DirectAdminie, nie sprawdzając, czy węzeł ma te zasoby, i nie zapisując ich w allocated*. Po Z-12 znaczy to, że dwie warstwy nadsubskrybują niezależnie od siebie i żadna nie widzi drugiej: placement liczy sprzedane limity BAZOWE, autoskalowanie dokłada do nich nadwyżkę poza księgą. Jedno konto może urosnąć do 1000 GB na węźle 1,92 TB — połowa dysku dla jednego klienta, o czym selektor się nie dowie. | Do zrobienia: sprawdzenie pojemności węzła przed skalowaniem w górę (ten sam node-capacity.ts), skalowanie częściowe zamiast odmowy, zapis nadwyżki w allocated* albo osobnej kolumnie, podniesienie progu 10× po dołożeniu tego zabezpieczenia — w tej kolejności, nie odwrotnie. | Rozbieżność sufitu jest utrwalona testem plan-produkcyjny.spec.ts, który zapali się przy zmianie progu i wymusi przejrzenie oferty.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N364"/>
-  <conditionalFormatting sqref="D2:D364">
+  <autoFilter ref="A1:N365"/>
+  <conditionalFormatting sqref="D2:D365">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27150,7 +27222,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E364">
+  <conditionalFormatting sqref="E2:E365">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27167,7 +27239,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F364">
+  <conditionalFormatting sqref="F2:F365">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27184,7 +27256,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G364">
+  <conditionalFormatting sqref="G2:G365">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27201,7 +27273,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H364">
+  <conditionalFormatting sqref="H2:H365">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27218,7 +27290,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I364">
+  <conditionalFormatting sqref="I2:I365">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27238,7 +27310,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K364">
+  <conditionalFormatting sqref="K2:K365">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27255,7 +27327,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L364">
+  <conditionalFormatting sqref="L2:L365">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$365,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$366,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$365,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$366,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$365,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$366,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$365,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$366,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$365,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$366,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$365,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$366,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$365,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$366,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$365,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$366,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$365,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$366,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$365,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$366,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"A",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"B",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"C",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"D",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"E",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"F",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"G",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"H",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"I",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"J",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"K",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"L",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"M",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"N",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"O",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"P",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Q",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"X",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$365,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$366,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$K$2:$K$365,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$365,"Z",Macierz!$L$2:$L$365,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N365"/>
+  <dimension ref="A1:N366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27174,38 +27174,110 @@
       </c>
       <c r="I365" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
         <is>
-          <t>autoscaling-engine.service.ts:287 — Math.min(value, 10) przycina krotność niezależnie od planu, więc sufit CPU (12×) i dysku (20×) z oferty jest nieosiągalny; w całym pliku nie ma ani jednego odwołania do Server/allocated — silnik skaluje konto bez pytania węzła o pojemność i bez aktualizacji allocatedCpu/Memory/Disk</t>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
         </is>
       </c>
       <c r="K365" s="11" t="inlineStr">
         <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L365" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M365" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N365" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="11" t="inlineStr">
+        <is>
+          <t>Z-17</t>
+        </is>
+      </c>
+      <c r="B366" s="12" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C366" s="11" t="inlineStr">
+        <is>
+          <t>Klient widzi, że autoskalowanie dało mu mniej, niż potrzebował</t>
+        </is>
+      </c>
+      <c r="D366" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="E366" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="F366" s="11" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G366" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚĆ</t>
+        </is>
+      </c>
+      <c r="H366" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I366" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J366" s="12" t="inlineStr">
+        <is>
+          <t>autoscaling-engine.service.ts — obcięcie zostawia wpis w dzienniku audytu i warn w logu, ale panel klienta nie pokazuje niczego</t>
+        </is>
+      </c>
+      <c r="K366" s="11" t="inlineStr">
+        <is>
           <t>LUKA</t>
         </is>
       </c>
-      <c r="L365" s="11" t="inlineStr">
-        <is>
-          <t>BLOKER STARTU</t>
-        </is>
-      </c>
-      <c r="M365" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N365" s="12" t="inlineStr">
-        <is>
-          <t>Odkryte przy zamykaniu Z-13. Dwie rzeczy, jedna przyczyna — silnik autoskalowania nie wie nic o węźle, na którym stoi konto. | PIERWSZA: oferta obiecuje skalowanie do 24 vCPU i 1000 GB, a przycięcie do 10× daje realnie 20 vCPU i 500 GB. Klient płacący za nadwyżkę godzinowo nie dostanie tego, za co zapłacił, i będzie miał rację w reklamacji. | DRUGA i groźniejsza: silnik podnosi limity konta w DirectAdminie, nie sprawdzając, czy węzeł ma te zasoby, i nie zapisując ich w allocated*. Po Z-12 znaczy to, że dwie warstwy nadsubskrybują niezależnie od siebie i żadna nie widzi drugiej: placement liczy sprzedane limity BAZOWE, autoskalowanie dokłada do nich nadwyżkę poza księgą. Jedno konto może urosnąć do 1000 GB na węźle 1,92 TB — połowa dysku dla jednego klienta, o czym selektor się nie dowie. | Do zrobienia: sprawdzenie pojemności węzła przed skalowaniem w górę (ten sam node-capacity.ts), skalowanie częściowe zamiast odmowy, zapis nadwyżki w allocated* albo osobnej kolumnie, podniesienie progu 10× po dołożeniu tego zabezpieczenia — w tej kolejności, nie odwrotnie. | Rozbieżność sufitu jest utrwalona testem plan-produkcyjny.spec.ts, który zapali się przy zmianie progu i wymusi przejrzenie oferty.</t>
+      <c r="L366" s="11" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="M366" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N366" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy zamykaniu Z-16. Gdy węzeł nie ma pełnej nadwyżki, konto dostaje tyle, ile się da — i to jest właściwe zachowanie. Ale klient płaci za autoskalowanie godzinowo i nie dowiaduje się, że w szczycie dostał połowę tego, czego strona potrzebowała. Widzi wolną stronę i nie wie dlaczego. | To nie jest kosmetyka interfejsu: przy usłudze rozliczanej za realne użycie informacja o tym, że usługa nie dowiozła, jest częścią usługi. Bez niej pierwsze zgłoszenie do BOK-u brzmi „strona muliła w Black Friday”, a odpowiedź wymaga grzebania w dzienniku audytu. | Do zrobienia: wpis w historii autoskalowania widoczny w panelu klienta plus, przy powtarzających się obcięciach, sygnał od nas — bo to my mamy za mało węzłów, nie on za mały pakiet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N365"/>
-  <conditionalFormatting sqref="D2:D365">
+  <autoFilter ref="A1:N366"/>
+  <conditionalFormatting sqref="D2:D366">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27222,7 +27294,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E365">
+  <conditionalFormatting sqref="E2:E366">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27239,7 +27311,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F365">
+  <conditionalFormatting sqref="F2:F366">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27256,7 +27328,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G365">
+  <conditionalFormatting sqref="G2:G366">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27273,7 +27345,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H365">
+  <conditionalFormatting sqref="H2:H366">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27290,7 +27362,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I365">
+  <conditionalFormatting sqref="I2:I366">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27310,7 +27382,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K365">
+  <conditionalFormatting sqref="K2:K366">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27327,7 +27399,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L365">
+  <conditionalFormatting sqref="L2:L366">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$368</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$366,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$368,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$366,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$368,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$366,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$368,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$366,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$368,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$366,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$368,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$366,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$368,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$366,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$368,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$366,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$368,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$366,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$368,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$366,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$368,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"A",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"B",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"C",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"D",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"E",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"F",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"G",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"H",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"I",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"J",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"K",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"L",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"M",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"N",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"O",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"P",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Q",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"X",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$366,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$368,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$K$2:$K$366,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$366,"Z",Macierz!$L$2:$L$366,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N366"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27275,9 +27275,153 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="11" t="inlineStr">
+        <is>
+          <t>X-14</t>
+        </is>
+      </c>
+      <c r="B367" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C367" s="11" t="inlineStr">
+        <is>
+          <t>CI sprawdza DANE po migracji, nie tylko czy migracja się wykonała</t>
+        </is>
+      </c>
+      <c r="D367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I367" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J367" s="12" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml — job migrations: kroki „Seed reference data” i „Verify migrated data (Z-12, Z-13, Z-16)”; ops/sql/sprawdz-baze-po-migracji.sql — 5 bloków asercji kończących się RAISE EXCEPTION</t>
+        </is>
+      </c>
+      <c r="K367" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L367" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M367" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N367" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. Job migrations sprawdzał wyłącznie, czy migracje dają się zastosować i czy schemat nie ma dryfu. Nie sprawdzał, czy DANE, które migracje wstawiają, tam są i mają właściwe wartości — a Z-12 i Z-13 to migracje danych, których poprawność testy jednostkowe potwierdzały wyłącznie przez czytanie SQL-a jako TEKSTU. | Teraz CI odpytuje bazę: czy plan verris-hosting istnieje z ceną 45,00 brutto i limitami 200/8192/51200, czy publiczny pakiet hostingowy jest dokładnie jeden, czy prototypy są wycofane ale nie zdezaktywowane, czy kolumny overcommit mają NEUTRALNĄ domyślną 1, czy księga pojemności zgadza się z sumą limitów kont żywych. | Sprawdzone na prawdziwym Postgresie 16 ze wszystkimi 100 migracjami: komplet przechodzi, a podmiana ceny na 49,00 i podniesienie domyślnej nadsubskrypcji do 4 wywalają job z kodem 3. | ODKRYTE PRZY TESTOWANIU: na bazie z samych migracji plany prototypowe w ogóle nie istnieją (tworzy je seed), więc asercja o ich wycofaniu przechodziła TRYWIALNIE — w logu CI wygląda to identycznie jak prawdziwe „wszystko w porządku”. Stąd krok seeda przed asercjami plus jawny warunek: zero znalezionych prototypów to błąd, nie sukces. Przy okazji CI po raz pierwszy weryfikuje, że seed w ogóle wykonuje się na świeżej bazie. | Dokumentacja: docs/zadania/X-14-asercje-danych-po-migracji.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="11" t="inlineStr">
+        <is>
+          <t>X-15</t>
+        </is>
+      </c>
+      <c r="B368" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C368" s="11" t="inlineStr">
+        <is>
+          <t>Niezmiennik księgi pojemności sprawdzany liczbowo, nie tekstowo</t>
+        </is>
+      </c>
+      <c r="D368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I368" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J368" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/src/subscriptions/ksiega-niezmiennik.spec.ts — 15 testów: losowe ciągi operacji (założenie konta, skalowanie w górę i w dół, zmiana planu, usunięcie) z porównaniem księgi z prawdą po KAŻDYM kroku; node-capacity.ts — deltaKsiegi/limityEfektywne/ksiegaUpdateData jako jedyna arytmetyka księgi w projekcie</t>
+        </is>
+      </c>
+      <c r="K368" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L368" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M368" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N368" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. Strażniki z Z-16 były statyczne — czytały tekst źródłowy. Złapią usunięcie linii (i złapały, gdy arytmetyka poszła do wspólnych funkcji), ale nie złapią błędu w ZNAKU delty ani pomylonych argumentów: deltaKsiegi(po, przed) zamiast deltaKsiegi(przed, po) przechodzi każdy test tekstowy i rozjeżdża księgę przy pierwszej operacji. | Test sprawdza jedyną rzecz, która musi być prawdziwa: allocated* równa się sumie limitów efektywnych kont żywych po dowolnym ciągu operacji. Deterministyczny generator, sześć ziaren, sprawdzenie po każdym kroku — żeby dwa błędy nie zniosły się nawzajem. | Uczciwość testu polega na tym, że symulator używa DOKŁADNIE tych samych funkcji co produkcja; gdyby liczył po swojemu, sprawdzałby siebie. Warunkiem było wyciągnięcie arytmetyki z czterech serwisów do node-capacity.ts — przy okazji piąty rozjazd nie ma już gdzie powstać. | Zweryfikowane: odwrócenie znaku w JEDNYM zasobie czerwieni 10 z 15 testów niezmiennika. Test statyczny tego nie widzi. | Czego to nie sprawdza: czy serwisy wołają te funkcje w odpowiednim momencie i z odpowiednimi argumentami — to jest rola X-04. Tu weryfikowana jest arytmetyka, tam okablowanie.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N366"/>
-  <conditionalFormatting sqref="D2:D366">
+  <autoFilter ref="A1:N368"/>
+  <conditionalFormatting sqref="D2:D368">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27294,7 +27438,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E366">
+  <conditionalFormatting sqref="E2:E368">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27311,7 +27455,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F366">
+  <conditionalFormatting sqref="F2:F368">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27328,7 +27472,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G366">
+  <conditionalFormatting sqref="G2:G368">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27345,7 +27489,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H366">
+  <conditionalFormatting sqref="H2:H368">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27362,7 +27506,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I366">
+  <conditionalFormatting sqref="I2:I368">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27382,7 +27526,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K366">
+  <conditionalFormatting sqref="K2:K368">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27399,7 +27543,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L366">
+  <conditionalFormatting sqref="L2:L368">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -26174,17 +26174,17 @@
       </c>
       <c r="I351" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>apps/api/test/integration/ — setup.ts (izolacja przez TRUNCATE CASCADE, fabryki, atrapy DirectAdmina/poczty/audytu), node-selector.int-spec.ts (9 testów placementu na prawdziwych zapytaniach), ksiega.int-spec.ts (6 testów cyklu życia księgi z prawdziwymi transakcjami); apps/api/jest.integration.cjs — maxWorkers 1, bo testy dzielą jedną bazę; .github/workflows/ci.yml — job „API integration tests” z Postgresem 16</t>
         </is>
       </c>
       <c r="K351" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L351" s="11" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="N351" s="12" t="inlineStr">
         <is>
-          <t>wszystkie 35 testów to jednostkowe z ręcznymi fake'ami</t>
+          <t>CZĘŚCIOWE od 2026-08-22 — pierwsze testy integracyjne w historii tego projektu. Do tej pory WSZYSTKIE testy API podstawiały fałszywą Prismę: dowodziły, że logika jest poprawna, nie że zapytanie zwraca to, czego się po nim spodziewamy. | Uruchomione naprawdę, nie tylko napisane: postawiłem Postgresa 16, zaaplikowałem 100 migracji, wygenerowałem klienta i puściłem pakiet — 15 testów zielonych. Sprawdzone, że czerwienią się na regresji: usunięcie zwolnienia pojemności z account-deletion czerwieni 4 z 6 testów księgi. | Co złapały, czego atrapy nie mogły: że Postgres zwraca Float (overcommit) jako number a nie Decimal, że groupBy z filtrem statusu faktycznie pomija konta DELETED, że okno świeżości telemetrii działa na prawdziwym ORDER BY, że wybór najnowszej próbki na subskrypcję nie sumuje okna. | ZAKRES: pokryty jest placement (NodeSelectorService) i cykl życia księgi pojemności (autoskalowanie, usunięcie konta). NIE są pokryte: ścieżki HTTP przez supertest, provisioning end-to-end, płatności, webhooki, KSeF. Dlatego CZĘŚCIOWE, nie DZIAŁA — pozycja opisuje testy integracyjne CAŁEGO API. | Job w CI celowo NIE jest jeszcze wymagany do scalenia (ruleset z X-02): dokładanie nieprzetestowanego w tym repo checka jako wymaganego zablokowałoby merge na ślepo. Do dopisania po pierwszym zielonym przebiegu na main. Poziom dowodu: D1 do czasu tego przebiegu, potem D2. | Ograniczenie warsztatu, warte zapisania: nie da się ich uruchomić ani na maszynie PM-a (klient Prismy zbudowany pod macOS, sandbox to Linux), ani domyślnie w kontenerze (binaries.prisma.sh poza listą dozwolonych hostów). Wymagało zbudowania środowiska od zera. CI jest jedynym miejscem, gdzie biegną rutynowo. Dokumentacja: docs/zadania/X-04-testy-integracyjne-api.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$369</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$368,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$369,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$368,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$369,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$368,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$369,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$368,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$369,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$368,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$369,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$368,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$369,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$368,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$369,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$368,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$369,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$368,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$369,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$368,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$369,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"A",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"B",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"C",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"D",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"E",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"F",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"G",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"H",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"I",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"J",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"K",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"L",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"M",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"N",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"O",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"P",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Q",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"X",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$368,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$369,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$K$2:$K$368,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$368,"Z",Macierz!$L$2:$L$368,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N368"/>
+  <dimension ref="A1:N369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="N358" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. Check „API unit tests" dopisany do rulesetu z X-02 tego samego dnia — bez tego rozdzielenie jobów otwierałoby dziurę: testy widoczne, ale niewymagane do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md</t>
+          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. Check „API unit tests" dopisany do rulesetu z X-02 tego samego dnia — bez tego rozdzielenie jobów otwierałoby dziurę: testy widoczne, ale niewymagane do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md | KOREKTA 2026-08-22: podział jobów zabrał testom budowanie bibliotek, które wcześniej działo się przy okazji przez pnpm typecheck (Turbo, dependsOn ^build). Job „API unit tests” był przez to CZERWONY od tego commita aż do X-17, mimo że zgłosiłem pozycję jako zamkniętą na podstawie zielonych testów lokalnych. Sam przebieg CI sprawdziłem dopiero przy #56. Wniosek zapisany w X-17: pozycja dotycząca CI nie może być zamknięta bez obejrzenia przebiegu, którego dotyczy.</t>
         </is>
       </c>
     </row>
@@ -27419,9 +27419,81 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="11" t="inlineStr">
+        <is>
+          <t>X-17</t>
+        </is>
+      </c>
+      <c r="B369" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C369" s="11" t="inlineStr">
+        <is>
+          <t>Joby CI budują zależności workspace'u zanim uruchomią testy</t>
+        </is>
+      </c>
+      <c r="D369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I369" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J369" s="12" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml — krok „Build workspace libraries” w jobie api-tests, „Generate Prisma client” w jobie migrations; turbo.json — zadanie test dostaje dependsOn ^build; apps/api/src/test/ci-joby.spec.ts — 6 testów strażnika</t>
+        </is>
+      </c>
+      <c r="K369" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L369" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M369" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N369" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N368"/>
-  <conditionalFormatting sqref="D2:D368">
+  <autoFilter ref="A1:N369"/>
+  <conditionalFormatting sqref="D2:D369">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27438,7 +27510,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E368">
+  <conditionalFormatting sqref="E2:E369">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27455,7 +27527,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F368">
+  <conditionalFormatting sqref="F2:F369">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27472,7 +27544,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G368">
+  <conditionalFormatting sqref="G2:G369">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27489,7 +27561,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H368">
+  <conditionalFormatting sqref="H2:H369">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27506,7 +27578,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I368">
+  <conditionalFormatting sqref="I2:I369">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27526,7 +27598,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K368">
+  <conditionalFormatting sqref="K2:K369">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27543,7 +27615,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L368">
+  <conditionalFormatting sqref="L2:L369">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$369</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$372</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$369,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$372,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$369,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$372,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$369,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$372,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$369,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$372,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$369,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$372,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$369,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$372,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$369,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$372,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$369,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$372,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$369,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$372,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$369,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$372,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"A",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"B",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"C",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"D",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"E",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"F",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"G",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"H",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"I",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"J",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"K",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"L",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"M",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"N",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"O",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"P",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Q",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"X",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$369,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$372,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$K$2:$K$369,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$369,"Z",Macierz!$L$2:$L$369,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N369"/>
+  <dimension ref="A1:N372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26199,7 +26199,7 @@
       </c>
       <c r="N351" s="12" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE od 2026-08-22 — pierwsze testy integracyjne w historii tego projektu. Do tej pory WSZYSTKIE testy API podstawiały fałszywą Prismę: dowodziły, że logika jest poprawna, nie że zapytanie zwraca to, czego się po nim spodziewamy. | Uruchomione naprawdę, nie tylko napisane: postawiłem Postgresa 16, zaaplikowałem 100 migracji, wygenerowałem klienta i puściłem pakiet — 15 testów zielonych. Sprawdzone, że czerwienią się na regresji: usunięcie zwolnienia pojemności z account-deletion czerwieni 4 z 6 testów księgi. | Co złapały, czego atrapy nie mogły: że Postgres zwraca Float (overcommit) jako number a nie Decimal, że groupBy z filtrem statusu faktycznie pomija konta DELETED, że okno świeżości telemetrii działa na prawdziwym ORDER BY, że wybór najnowszej próbki na subskrypcję nie sumuje okna. | ZAKRES: pokryty jest placement (NodeSelectorService) i cykl życia księgi pojemności (autoskalowanie, usunięcie konta). NIE są pokryte: ścieżki HTTP przez supertest, provisioning end-to-end, płatności, webhooki, KSeF. Dlatego CZĘŚCIOWE, nie DZIAŁA — pozycja opisuje testy integracyjne CAŁEGO API. | Job w CI celowo NIE jest jeszcze wymagany do scalenia (ruleset z X-02): dokładanie nieprzetestowanego w tym repo checka jako wymaganego zablokowałoby merge na ślepo. Do dopisania po pierwszym zielonym przebiegu na main. Poziom dowodu: D1 do czasu tego przebiegu, potem D2. | Ograniczenie warsztatu, warte zapisania: nie da się ich uruchomić ani na maszynie PM-a (klient Prismy zbudowany pod macOS, sandbox to Linux), ani domyślnie w kontenerze (binaries.prisma.sh poza listą dozwolonych hostów). Wymagało zbudowania środowiska od zera. CI jest jedynym miejscem, gdzie biegną rutynowo. Dokumentacja: docs/zadania/X-04-testy-integracyjne-api.md</t>
+          <t>CZĘŚCIOWE od 2026-08-22 — pierwsze testy integracyjne w historii tego projektu. Do tej pory WSZYSTKIE testy API podstawiały fałszywą Prismę: dowodziły, że logika jest poprawna, nie że zapytanie zwraca to, czego się po nim spodziewamy. | Uruchomione naprawdę, nie tylko napisane: postawiłem Postgresa 16, zaaplikowałem 100 migracji, wygenerowałem klienta i puściłem pakiet — 15 testów zielonych. Sprawdzone, że czerwienią się na regresji: usunięcie zwolnienia pojemności z account-deletion czerwieni 4 z 6 testów księgi. | Co złapały, czego atrapy nie mogły: że Postgres zwraca Float (overcommit) jako number a nie Decimal, że groupBy z filtrem statusu faktycznie pomija konta DELETED, że okno świeżości telemetrii działa na prawdziwym ORDER BY, że wybór najnowszej próbki na subskrypcję nie sumuje okna. | ZAKRES: pokryty jest placement (NodeSelectorService) i cykl życia księgi pojemności (autoskalowanie, usunięcie konta). NIE są pokryte: ścieżki HTTP przez supertest, provisioning end-to-end, płatności, webhooki, KSeF. Dlatego CZĘŚCIOWE, nie DZIAŁA — pozycja opisuje testy integracyjne CAŁEGO API. | Job w CI celowo NIE jest jeszcze wymagany do scalenia (ruleset z X-02): dokładanie nieprzetestowanego w tym repo checka jako wymaganego zablokowałoby merge na ślepo. Do dopisania po pierwszym zielonym przebiegu na main. Poziom dowodu: D1 do czasu tego przebiegu, potem D2. | Ograniczenie warsztatu, warte zapisania: nie da się ich uruchomić ani na maszynie PM-a (klient Prismy zbudowany pod macOS, sandbox to Linux), ani domyślnie w kontenerze (binaries.prisma.sh poza listą dozwolonych hostów). Wymagało zbudowania środowiska od zera. CI jest jedynym miejscem, gdzie biegną rutynowo. Dokumentacja: docs/zadania/X-04-testy-integracyjne-api.md | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #57 zielony w komplecie — sześć jobów, w tym „API integration tests" z Postgresem 16.</t>
         </is>
       </c>
     </row>
@@ -27487,13 +27487,229 @@
       </c>
       <c r="N369" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md</t>
+          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #57 zielony w komplecie — sześć jobów, w tym „API integration tests" z Postgresem 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="11" t="inlineStr">
+        <is>
+          <t>X-18</t>
+        </is>
+      </c>
+      <c r="B370" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C370" s="11" t="inlineStr">
+        <is>
+          <t>Zależności podniesione do najnowszych bezpiecznych wersji</t>
+        </is>
+      </c>
+      <c r="D370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I370" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J370" s="12" t="inlineStr">
+        <is>
+          <t>package.json — 16 pnpm.overrides na zależności przechodnie; apps/www next 15.4.4 → 16.3.2; wszystkie panele next 16.3.2; NestJS 11.2.1; React 19.2.8; Payload 3.88.0; recharts 3; @types/node 26; ioredis 6; bullmq 6; graphql 17; sharp 0.35.3; libs/typescript-config/nestjs.json target ES2022 + lib ES2023</t>
+        </is>
+      </c>
+      <c r="K370" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L370" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M370" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N370" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="11" t="inlineStr">
+        <is>
+          <t>X-19</t>
+        </is>
+      </c>
+      <c r="B371" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C371" s="11" t="inlineStr">
+        <is>
+          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
+        </is>
+      </c>
+      <c r="D371" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E371" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F371" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G371" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H371" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I371" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J371" s="12" t="inlineStr">
+        <is>
+          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
+        </is>
+      </c>
+      <c r="K371" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L371" s="11" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="M371" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N371" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy X-18. Next 16 usunęło komendę `next lint`, więc panele przeszły na płaską konfigurację i eslint wołany wprost. Nowszy eslint-config-next włącza reguły, których poprzednia konfiguracja nie egzekwowała — przede wszystkim rodzinę react-hooks z React Compilera. W panelu klienta odsłoniło to 105 znalezisk. | Osobno: apps/api i libs/directadmin-sdk wołały `eslint` BEZ ŻADNEJ konfiguracji w repozytorium — jedyny plik, libs/eslint-config/base.js, jest w starym formacie eslintrc i nic go nie importowało. Krok lintowania tych pakietów nie sprawdzał niczego. Dodana płaska konfiguracja node.mjs. | NAJWAŻNIEJSZE: nowe reguły wyłapały REALNY BUG. W admin-panel/autoscaling/pricing-table.tsx useMemo stał PO wczesnym return — przy pustej liście reguł hook nie wykonywał się wcale, a po dodaniu pierwszej stawki React widział inną liczbę hooków i komponent się wywalał. Czyli: panel cennika autoskalowania psuł się dokładnie w momencie dodania pierwszej reguły. Naprawione. Drugi: JSX konstruowany w try/catch w pulpicie admina — try nie chronił przed niczym, bo React renderuje zwrócony element po wyjściu z funkcji. | Reguły NIE są wyłączone, tylko obniżone do ostrzeżeń, z komentarzem wskazującym tę pozycję. Wracają na 'error' przy jej zamykaniu. | Wyjątek trwały: no-control-regex zostaje wyłączone — znaki sterujące w regexach walidacyjnych są zamierzone. no-useless-escape zostaje ostrzeżeniem świadomie: cztery wystąpienia siedzą w regexach walidujących wejście (kody promocyjne, ścieżki plików, załączniki), a zmiana regexa walidacyjnego przy okazji podnoszenia zależności to dokładnie ten rodzaj zmiany, który Z-03 kazał robić z testem na każdy przypadek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="11" t="inlineStr">
+        <is>
+          <t>X-20</t>
+        </is>
+      </c>
+      <c r="B372" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C372" s="11" t="inlineStr">
+        <is>
+          <t>Decyzja i migracja na Prismę 7</t>
+        </is>
+      </c>
+      <c r="D372" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E372" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F372" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G372" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H372" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I372" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J372" s="12" t="inlineStr">
+        <is>
+          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
+        </is>
+      </c>
+      <c r="K372" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L372" s="11" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="M372" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N372" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy X-18, świadomie odłożone. Prisma 7 nie jest podniesieniem wersji, tylko zmianą architektury dostępu do bazy: właściwość `url` znika z datasource w schemacie i przenosi się do prisma.config.ts, a PrismaClient wymaga przekazania driver adaptera (@prisma/adapter-pg) albo adresu Accelerate. Sprawdzone realnie — `prisma generate` na 7.9.1 kończy się błędem P1012. | Dotyka: prisma.service.ts, libs/database/src/index.ts, seed, jobów CI, testów integracyjnych i sposobu, w jaki produkcja dostaje DATABASE_URL. Czyli każdej ścieżki do bazy naraz. | Argument za zrobieniem: zamyka ostatnią wysoką podatność (deepmerge-ts). Argument za odłożeniem: zmiana w warstwie danych na dwa sprinty przed startem sprzedaży, przy siedmiu otwartych blokerach, której nie da się w pełni zweryfikować lokalnie — binaries.prisma.sh jest poza listą dozwolonych hostów w obu moich środowiskach, więc jedyną weryfikacją byłoby CI. | Do zrobienia po starcie, z własnym sprintem i testem integracyjnym na każdej ścieżce zapisu.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N369"/>
-  <conditionalFormatting sqref="D2:D369">
+  <autoFilter ref="A1:N372"/>
+  <conditionalFormatting sqref="D2:D372">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27510,7 +27726,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E369">
+  <conditionalFormatting sqref="E2:E372">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27527,7 +27743,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F369">
+  <conditionalFormatting sqref="F2:F372">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27544,7 +27760,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G369">
+  <conditionalFormatting sqref="G2:G372">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27561,7 +27777,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H369">
+  <conditionalFormatting sqref="H2:H372">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27578,7 +27794,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I369">
+  <conditionalFormatting sqref="I2:I372">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27598,7 +27814,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K369">
+  <conditionalFormatting sqref="K2:K372">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27615,7 +27831,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L369">
+  <conditionalFormatting sqref="L2:L372">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$375</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$372,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$375,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$372,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$375,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$372,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$375,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$372,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$375,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$372,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$375,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$372,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$375,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$372,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$375,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$372,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$375,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$372,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$375,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$372,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$375,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"A",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"B",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"C",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"D",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"E",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"F",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"G",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"H",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"I",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"J",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"K",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"L",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"M",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"N",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"O",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"P",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Q",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"X",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$372,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$375,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$K$2:$K$372,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$372,"Z",Macierz!$L$2:$L$372,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N372"/>
+  <dimension ref="A1:N375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="N370" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md</t>
+          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md | KOREKTA 2026-08-22 (X-21): graphql cofnięty z ^17.0.2 do ^16.14.2 — jedynym konsumentem jest Payload 3.88, który deklaruje peera ^16.8.1, a nasz kod nie importuje graphql ani razu. Podniosłem major pod biblioteką, która go nie wspiera, bo wersja była wyższa — na PUBLICZNEJ stronie. Build www przechodzi na 16, ostrzeżenie o peerze znikło. | Domknięty body-parser override'em ^2.3.0: podatności 2 → 1 (została deepmerge-ts, wysoka, tylko przez Prismę 6 — znika z X-20). | engines.node podniesione z "&gt;=22" do "&gt;=22.12" — patrz X-21.</t>
         </is>
       </c>
     </row>
@@ -27707,9 +27707,225 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="11" t="inlineStr">
+        <is>
+          <t>X-21</t>
+        </is>
+      </c>
+      <c r="B373" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C373" s="11" t="inlineStr">
+        <is>
+          <t>Deklaracje typów opisują tę wersję biblioteki, która jest zainstalowana</t>
+        </is>
+      </c>
+      <c r="D373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I373" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J373" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/package.json — @types/archiver ^8.0.0 przy archiver ^8.0.0; apps/api/src/test/typy-zgodne-z-runtime.spec.ts — 12 testów; package.json — engines.node "&gt;=22.12"</t>
+        </is>
+      </c>
+      <c r="K373" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L373" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M373" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N373" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. BŁĄD PRODUKCYJNY znaleziony przy X-18, siedzący w kodzie PRZED podniesieniem. apps/api/package.json deklarował jednocześnie archiver ^8.0.0 i @types/archiver ^7.0.0. Archiver 8 usunął fabrykę create() na rzecz klas per format — kod wołał archiver.create('zip'/'tar'), typecheck był ZIELONY, bo typy z linii 7 tę funkcję opisywały, a w runtime jej nie było. Sprawdzone realnie: Object.keys(require('archiver')) = ['Archiver','JsonArchive','TarArchive','ZipArchive'], create === undefined. | CO TO PSUŁO: (1) data-export.service.ts → buildZipToFile — eksport danych osobowych (RODO art. 20, prawo do przenoszenia) wywalał się przy KAŻDYM żądaniu; (2) default-hosting-page.assets.ts → buildDefaultHostingPageBundle — budowa paczki domyślnej strony wywalała się przy KAŻDYM provisioningu konta. Nie „czasem" — zawsze, od momentu podniesienia archivera. | DLACZEGO NIKT TEGO NIE ZOBACZYŁ: typecheck czytał typy opisujące nieistniejącą wersję, żaden test nie dotykał tych dwóch funkcji, lint nie ma reguły na „ta metoda nie istnieje w runtime". Typecheck jest bramką wdrożenia — jeżeli typy opisują inną wersję niż zainstalowana, bramka przepuszcza kod, który się nie uruchomi, i robi to cicho, na zielono. | DRUGIE DNO: archiver 8 jest czystym ESM-em ("type": "module", brak wejścia CJS), a API kompiluje się do CommonJS-a. Node obsługuje require(esm) bez flagi dopiero od 22.12, a engines.node stał na "&gt;=22". Obrazy używają taga node:22 (dziś 22.22), więc realnie nic się nie paliło, ale deklaracja pozwalała na konfigurację, która by się paliła — ERR_REQUIRE_ESM w tych samych dwóch ścieżkach. Podniesione do "&gt;=22.12". | STRAŻNIK NA CAŁĄ KLASĘ, nie na sam archiver: żadne @types/X w monorepo nie może opisywać innego majora niż zainstalowany X. Test runtime'u wywołuje osobny proces Node'a (execFileSync), bo transformacja jesta nie ładuje zależności ESM i sprawdzałaby ładowarkę jesta zamiast produkcji. | Czerwieni się na starym kodzie: cofnięcie wszystkich trzech rzeczy daje 3 czerwone z 12, każdy z wykonalnym komunikatem. | Strażnik po raz TRZECI w tym projekcie trafił sam w siebie — szukana fraza padała w treści jego własnego komunikatu błędu (ta sama pułapka co polskie „jest" w X-17). Pominięty __filename + osobny test na spreparowanym wejściu. | PRZY OKAZJI: body-parser (niska, DoS przy cichym wyłączeniu limitu rozmiaru) domknięty override'em ^2.3.0 — podatności 2 → 1; graphql cofnięty z ^17.0.2 do ^16.14.2, bo jedynym konsumentem jest Payload 3.88 deklarujący peera ^16.8.1, a nasz kod nie importuje graphql ani razu — to korekta mojego własnego błędu z X-18: podniosłem wersję, bo była wyższa, nie sprawdzając, kto z niej korzysta. | Weryfikacja: 433 testy jednostkowe, 15 integracyjnych, lint 7/7, typecheck 8/8, build www. Dokumentacja: docs/zadania/X-21-typy-klamaly-o-runtime.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="11" t="inlineStr">
+        <is>
+          <t>X-22</t>
+        </is>
+      </c>
+      <c r="B374" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C374" s="11" t="inlineStr">
+        <is>
+          <t>Eksport danych osobowych (RODO art. 20) sprawdzany testem end-to-end</t>
+        </is>
+      </c>
+      <c r="D374" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E374" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F374" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G374" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H374" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I374" s="11" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="J374" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/src/compliance/data-export.service.ts — buildZipToFile bez żadnego testu; apps/api/src/compliance/*.spec.ts — brak pokrycia tej ścieżki</t>
+        </is>
+      </c>
+      <c r="K374" s="11" t="inlineStr">
+        <is>
+          <t>LUKA</t>
+        </is>
+      </c>
+      <c r="L374" s="11" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="M374" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N374" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy X-21. Eksport danych osobowych wywalał się w runtime przy każdym żądaniu przez cały okres między podniesieniem archivera a 2026-08-22 i NIC tego nie zgłosiło — bo tej ścieżki nie dotyka żaden test. Strażnik z X-21 pilnuje teraz zgodności typów z runtime'em, ale to jest obejście od strony zależności, nie dowód, że eksport działa. | To jest OBOWIĄZEK USTAWOWY (RODO art. 20 — prawo do przenoszenia danych), z terminem miesiąca na odpowiedź. Ścieżka, której nie sprawdza nic, a której awaria jest naruszeniem, nie sprawdzeniem. | DO ZROBIENIA: test integracyjny, który zakłada konto z danymi w każdej sekcji (profil, subskrypcje, faktury, zgłoszenia, załączniki), wywołuje eksport, rozpakowuje wynikowy ZIP i sprawdza, że każda sekcja jest w środku i daje się sparsować. Plus ten sam wzorzec dla buildDefaultHostingPageBundle (tar.gz rozpakowany, index.html obecny). | Dopiero taki test daje D2. D3 wymaga wywołania eksportu na produkcji i obejrzenia pliku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="11" t="inlineStr">
+        <is>
+          <t>X-23</t>
+        </is>
+      </c>
+      <c r="B375" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C375" s="11" t="inlineStr">
+        <is>
+          <t>Bramka podatności zatrzymuje wdrożenie, a nie tylko dopisuje adnotację</t>
+        </is>
+      </c>
+      <c r="D375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I375" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J375" s="12" t="inlineStr">
+        <is>
+          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony</t>
+        </is>
+      </c>
+      <c r="K375" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L375" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M375" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N375" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N372"/>
-  <conditionalFormatting sqref="D2:D372">
+  <autoFilter ref="A1:N375"/>
+  <conditionalFormatting sqref="D2:D375">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27726,7 +27942,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E372">
+  <conditionalFormatting sqref="E2:E375">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27743,7 +27959,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F372">
+  <conditionalFormatting sqref="F2:F375">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27760,7 +27976,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G372">
+  <conditionalFormatting sqref="G2:G375">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27777,7 +27993,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H372">
+  <conditionalFormatting sqref="H2:H375">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27794,7 +28010,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I372">
+  <conditionalFormatting sqref="I2:I375">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -27814,7 +28030,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K372">
+  <conditionalFormatting sqref="K2:K375">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -27831,7 +28047,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L372">
+  <conditionalFormatting sqref="L2:L375">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -27899,7 +27899,7 @@
       </c>
       <c r="J375" s="12" t="inlineStr">
         <is>
-          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony</t>
+          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony; .github/dependabot.yml — 3 reguły ignore z terminem; apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów</t>
         </is>
       </c>
       <c r="K375" s="11" t="inlineStr">
@@ -27919,7 +27919,7 @@
       </c>
       <c r="N375" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md</t>
+          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -20746,22 +20746,22 @@
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J274" s="12" t="inlineStr">
         <is>
-          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="K274" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L274" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M274" s="11" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="N274" s="12" t="inlineStr">
         <is>
-          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
         </is>
       </c>
     </row>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="N375" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8.</t>
+          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #59 zielony w komplecie, sześć jobów, ZERO adnotacji błędu — krok „Bramka podatności" przeszedł bez continue-on-error, a adnotacja „Process completed with exit code 1", która towarzyszyła każdemu wcześniejszemu przebiegowi, zniknęła.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$376</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$375,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$376,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$375,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$376,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$375,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$376,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$375,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$376,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$375,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$376,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$375,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$376,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$375,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$376,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$375,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$376,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$375,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$376,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$375,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$376,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"A",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"B",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"C",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"D",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"E",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"F",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"G",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"H",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"I",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"J",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"K",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"L",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"M",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"N",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"O",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"P",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Q",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"X",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$375,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$376,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$K$2:$K$375,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$375,"Z",Macierz!$L$2:$L$375,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N375"/>
+  <dimension ref="A1:N376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20602,22 +20602,22 @@
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J272" s="12" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="K272" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L272" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M272" s="11" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="N272" s="12" t="inlineStr">
         <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
     </row>
@@ -27923,9 +27923,81 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="11" t="inlineStr">
+        <is>
+          <t>M-34</t>
+        </is>
+      </c>
+      <c r="B376" s="12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C376" s="11" t="inlineStr">
+        <is>
+          <t>Model prepaid potwierdzony z księgową — doładowanie bez faktury zaliczkowej</t>
+        </is>
+      </c>
+      <c r="D376" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E376" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F376" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G376" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="H376" s="11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I376" s="11" t="inlineStr">
+        <is>
+          <t>b.d.</t>
+        </is>
+      </c>
+      <c r="J376" s="12" t="inlineStr">
+        <is>
+          <t>faktura-za-portfel.ts — TYPY_SPRZEDAZY nie obejmuje TOPUP; billing.service.ts:handleCheckoutCompleted — doładowanie kredytuje portfel i nie tworzy dokumentu</t>
+        </is>
+      </c>
+      <c r="K376" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L376" s="11" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="M376" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N376" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy Z-01, decyzja podjęta 2026-08-22 i WYMAGA POTWIERDZENIA. Przyjęliśmy model prepaid: doładowanie portfela nie jest sprzedażą, tylko wpłatą na poczet usług, więc nie generuje faktury; VAT powstaje przy świadczeniu usługi, czyli przy obciążeniu portfela, i tam idzie dokument. Klient dostaje potwierdzenie wpłaty mailem, nie fakturę. | RYZYKO: jeżeli środki z portfela dałoby się wydać wyłącznie na konkretną, z góry określoną usługę, organ podatkowy może uznać wpłatę za zaliczkę wymagającą faktury zaliczkowej (art. 106b ust. 1 pkt 4 ustawy o VAT). U nas środki są uniwersalne — idą na abonament, domeny, VPS, autoskalowanie i monitoring — co przemawia za modelem prepaid, ale to jest argument, nie rozstrzygnięcie. | DO ZROBIENIA PRZED STARTEM SPRZEDAŻY: potwierdzić model z księgową na piśmie i zapisać decyzję w repo z datą. Jeżeli wyjdzie, że potrzebne są faktury zaliczkowe, to osobny sprint: faktura końcowa musi odwoływać się do zaliczkowej i odejmować rozliczoną kwotę, a KSeF ma na to osobny typ dokumentu. | NIE jest to bloker w sensie kodu — mechanizm działa i jest spójny. Jest to bloker w sensie decyzji: sprzedaż ruszająca przy nierozstrzygniętym modelu podatkowym generuje dług, który rośnie z każdą wpłatą.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N375"/>
-  <conditionalFormatting sqref="D2:D375">
+  <autoFilter ref="A1:N376"/>
+  <conditionalFormatting sqref="D2:D376">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27942,7 +28014,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E375">
+  <conditionalFormatting sqref="E2:E376">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27959,7 +28031,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F375">
+  <conditionalFormatting sqref="F2:F376">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27976,7 +28048,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G375">
+  <conditionalFormatting sqref="G2:G376">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -27993,7 +28065,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H375">
+  <conditionalFormatting sqref="H2:H376">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28010,7 +28082,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I375">
+  <conditionalFormatting sqref="I2:I376">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28030,7 +28102,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K375">
+  <conditionalFormatting sqref="K2:K376">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28047,7 +28119,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L375">
+  <conditionalFormatting sqref="L2:L376">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$377</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$376,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$377,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$376,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$377,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$376,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$377,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$376,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$377,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$376,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$377,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$376,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$377,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$376,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$377,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$376,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$377,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$376,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$377,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$376,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$377,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"A",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"B",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"C",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"D",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"E",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"F",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"G",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"H",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"I",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"J",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"K",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"L",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"M",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"N",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"O",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"P",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Q",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"X",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$376,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$377,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$K$2:$K$376,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$376,"Z",Macierz!$L$2:$L$376,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N376"/>
+  <dimension ref="A1:N377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18626,22 +18626,22 @@
       </c>
       <c r="I244" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J244" s="12" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="K244" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L244" s="11" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M244" s="11" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="N244" s="12" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
     </row>
@@ -27995,9 +27995,81 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="11" t="inlineStr">
+        <is>
+          <t>X-24</t>
+        </is>
+      </c>
+      <c r="B377" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C377" s="11" t="inlineStr">
+        <is>
+          <t>Panel admina woła ścieżki, które API naprawdę wystawia</t>
+        </is>
+      </c>
+      <c r="D377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I377" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J377" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/src/test/sciezki-panelu.spec.ts — 5 testów; porównuje wywołania adminApi() z panelu z trasami zadeklarowanymi w kontrolerach API</t>
+        </is>
+      </c>
+      <c r="K377" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L377" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M377" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N377" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy M-06. Formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna, a kontroler wystawia /admin/invoices/reczna. Kod się kompilował, testy jednostkowe przechodziły, panel się budował — 404 wyszłoby dopiero pod palcem operatora. | To ta sama rodzina co „bliźniacze miejsca", rozciągnięta na dwa pakiety: ścieżka zapisana dwa razy, w panelu i w kontrolerze, a nic ich nie łączy. Kompilator nie pomoże, bo po obu stronach to zwykły napis. | Strażnik wyciąga wywołania adminApi() z panelu i trasy z kontrolerów, porównuje kształt ścieżki i metodę HTTP. Segmenty dynamiczne (${id} w panelu, :id w kontrolerze) pasują do wszystkiego. | STRAŻNIK ZACZĄŁ OD JEDENASTU FAŁSZYWYCH ALARMÓW: (1) czytał 220 znaków po wywołaniu szukając `method:` i łapał metodę z NASTĘPNEGO wywołania — zwykły GET raportowany jako POST; (2) zamieniał wstawkę ${qs} na gwiazdkę w miejscu, produkując segment „webhooki*", który nie pasował do niczego; (3) grupował warianty ścieżki po wartości pochodnej zamiast po oryginale, więc wariant pełny zawsze zostawał sam i zawsze wyglądał na niepokryty. Jedenaście fałszywych alarmów przy dwóch prawdziwych znaleziskach. Strażnik, który tonie we własnym szumie, zostanie wyciszony — doprowadzenie do zera fałszywych alarmów było warunkiem działania, nie dopieszczaniem. | PIĄTE wystąpienie tej rodziny: „jest" (X-17), archiver.create (X-21), --audit-level (X-23), endsWith('billing.service.ts') (Z-05), teraz ścieżki panelu. | Czerwieni się na starym kodzie: przywrócenie błędnej ścieżki daje 1 czerwony z 5. | CZEGO NIE ROBI: nie sprawdza kształtu ciała żądania ani odpowiedzi — tylko ścieżkę i metodę; nie obejmuje panelu klienta ani panelu staff (te wołają inne bazowe adresy).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N376"/>
-  <conditionalFormatting sqref="D2:D376">
+  <autoFilter ref="A1:N377"/>
+  <conditionalFormatting sqref="D2:D377">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28014,7 +28086,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E376">
+  <conditionalFormatting sqref="E2:E377">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28031,7 +28103,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F376">
+  <conditionalFormatting sqref="F2:F377">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28048,7 +28120,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G376">
+  <conditionalFormatting sqref="G2:G377">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28065,7 +28137,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H376">
+  <conditionalFormatting sqref="H2:H377">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28082,7 +28154,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I376">
+  <conditionalFormatting sqref="I2:I377">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28102,7 +28174,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K376">
+  <conditionalFormatting sqref="K2:K377">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28119,7 +28191,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L376">
+  <conditionalFormatting sqref="L2:L377">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -13834,17 +13834,17 @@
       </c>
       <c r="I176" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
         <is>
-          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
+          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
         </is>
       </c>
       <c r="K176" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L176" s="11" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="N176" s="12" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
+          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$378</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$377,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$378,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$377,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$378,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$377,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$378,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$377,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$378,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$377,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$378,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$377,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$378,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$377,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$378,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$377,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$378,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$377,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$378,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$377,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$378,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"A",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"B",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"C",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"D",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"E",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"F",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"G",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"H",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"I",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"J",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"K",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"L",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"M",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"N",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"O",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"P",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Q",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"X",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$377,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$378,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$K$2:$K$377,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$377,"Z",Macierz!$L$2:$L$377,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N377"/>
+  <dimension ref="A1:N378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28067,9 +28067,81 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="11" t="inlineStr">
+        <is>
+          <t>X-25</t>
+        </is>
+      </c>
+      <c r="B378" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C378" s="11" t="inlineStr">
+        <is>
+          <t>Asercje po migracji biegną także na produkcji, z rollbackiem przy naruszeniu</t>
+        </is>
+      </c>
+      <c r="D378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I378" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J378" s="12" t="inlineStr">
+        <is>
+          <t>ops/sql/po-migracji-niezmienniki.sql — CI I PRODUKCJA, 14 RAISE EXCEPTION (Z-01, Z-05, Z-12, Z-13, Z-16, M-06); ops/sql/po-migracji-katalog.sql — tylko CI, wartości z oferty; ops/sql/po-migracji-historia.sql — raport, ZERO RAISE EXCEPTION w kodzie; ops/scripts/prod-deploy-ghcr.sh:79-133 — krok 3.5 (bramka + rollback) i 3.6 (raport); .github/workflows/ci.yml — cztery kroki po seedzie; ops/scripts/asercje-czerwienia-sie.sh — 10 naruszeń, każde na właściwej asercji; apps/api/src/test/asercje-po-migracji.spec.ts (36). Usunięte: ops/sql/sprawdz-baze-po-migracji.sql</t>
+        </is>
+      </c>
+      <c r="K378" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L378" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M378" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N378" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-22: ZAMKNIĘTE. Sześć zamkniętych blokerów zostawiło plik asercji o stanie bazy po migracjach. Plik był porządny i biegł w JEDNYM miejscu: w CI, na świeżej bazie testowej — czyli dokładnie tam, gdzie nie ma prawdziwych danych. Produkcja po `prisma migrate deploy` nie była sprawdzana NICZYM; `migrate deploy` kończy się zerem, gdy pliki SQL się wykonały, i nie mówi nic o tym, czy baza jest po nich w stanie, w którym kod policzy dobrze. | DLACZEGO NIE DAŁO SIĘ PO PROSTU DOPISAĆ TEGO PLIKU DO DEPLOYU: część twierdzeń wywaliłaby wdrożenie bez powodu. Asercja „są plany prototypowe" dotyczy rzeczy, które tworzy SEED, a seed na produkcji nie biegnie. Gorsza była druga: pilnowała, żeby verris-hosting kosztował dokładnie 45,00 — a cenę WOLNO zmienić z panelu (plans.service.ts, updatePlan). Pierwsza legalna podwyżka zamieniłaby każde kolejne wdrożenie w rollback, a wtedy ktoś słusznie wyłączyłby całe sprawdzanie. Tego nie zauważyłem od razu — zobaczyłem dopiero, gdy własny strażnik zapalił się na isPublic i zamiast go poluzować sprawdziłem, czy cena jest edytowalna. Była. | TRZY PLIKI, TRZY RÓŻNE ŻYCIA: niezmienniki (CI i produkcja, blokują) — twierdzenia, których nie unieważni żadna legalna zmiana biznesowa; katalog (TYLKO CI) — dzisiejsza decyzja handlowa, w CI zmienia się w jednym commicie razem z PLAN_PRODUKCYJNY i treścią strony; historia (CI i produkcja, tylko raport) — dane sprzed migracji, których migracja nie naprawia i nie miała naprawiać; wycofanie wdrożenia z tego powodu byłoby karą za przeszłość, nie ochroną przed błędem. | Z Z-13 do niezmienników przeszły dwa twierdzenia, których panel nie może naruszyć: istnienie wiersza o slugu verris-hosting (slug stoi na sztywno w plan-produkcyjny.ts) oraz reguła cennika, którą API wymusza przy zapisie (ceny dodatnie, rok &gt;= 6x miesiąc) — API pilnuje jej przy zapisie, baza nie pilnuje wcale, a migracja danych zapisuje Z POMINIĘCIEM API. | JEDNA REGUŁA, JEDNO MIEJSCE: blok M-06 sprawdzał sumy korekty, które obejmuje już Z-01 (korekta to wiersz w Invoice) — druga kopia nigdy by nie wystartowała, a przy zmianie zasad ktoś poprawiłby jedną z dwóch. Usunięta. | DWIE CICHE PUŁAPKI W SAMYM WYWOŁANIU: `psql -U "${POSTGRES_USER:?}"` — przy pustej zmiennej psql połączyłby się z bazą o nazwie użytkownika i asercje przeszłyby na PUSTEJ, NIEWŁAŚCIWEJ bazie; `sh -c` zamiast `sh -lc` — skrypt profilu czytający stdin zjadłby SQL i psql dostałby pusty plik. | ASERCJA, KTÓRA SIĘ NIE CZERWIENI, NIE JEST BRAMKĄ: ops/scripts/asercje-czerwienia-sie.sh psuje po jednym niezmienniku naraz w transakcji z ROLLBACK-iem i sprawdza DWIE rzeczy — kod wyjścia różny od zera ORAZ że powodem jest TA asercja. Drugi warunek nie jest ozdobą: w pierwszym przebiegu trzy przypadki M-06 świeciły na czerwono, a naprawdę odbijał je CHECK w bazie, zanim asercja zdążyła cokolwiek zobaczyć (ta sama lekcja co Z-01 i H-20). | Czerwieni się na starym kodzie: jeden plik + brak asercji w deployu → 11 z 36; `|| true` zamiast bramki → 1; RAISE EXCEPTION w pliku historii → 1; katalog wpuszczony na produkcję → 1. | CZEGO NIE ROBI: nie cofa schematu (rollback wraca do poprzedniego obrazu, migracje zostają); nie sprawdza katalogu na produkcji — cena może się tam rozjechać z PLAN_PRODUKCYJNY i deploy tego nie zauważy (to bliżej monitoringu niż bramki); asercje-czerwienia-sie.sh NIE WOLNO uruchamiać na produkcji, bo zdejmuje ograniczenia CHECK wewnątrz transakcji. | D3 powstanie przy pierwszym deployu na main, w logu wdrożenia, z datą. Dokumentacja: docs/zadania/X-25-asercje-po-migracji.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N377"/>
-  <conditionalFormatting sqref="D2:D377">
+  <autoFilter ref="A1:N378"/>
+  <conditionalFormatting sqref="D2:D378">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28086,7 +28158,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E377">
+  <conditionalFormatting sqref="E2:E378">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28103,7 +28175,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F377">
+  <conditionalFormatting sqref="F2:F378">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28120,7 +28192,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G377">
+  <conditionalFormatting sqref="G2:G378">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28137,7 +28209,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H377">
+  <conditionalFormatting sqref="H2:H378">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28154,7 +28226,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I377">
+  <conditionalFormatting sqref="I2:I378">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28174,7 +28246,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K377">
+  <conditionalFormatting sqref="K2:K378">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28191,7 +28263,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L377">
+  <conditionalFormatting sqref="L2:L378">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$378,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$379,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$378,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$379,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$378,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$379,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$378,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$379,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$378,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$379,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$378,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$379,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$378,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$379,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$378,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$379,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$378,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$379,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$378,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$379,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"A",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"B",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"C",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"D",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"E",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"F",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"G",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"H",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"I",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"J",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"K",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"L",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"M",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"N",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"O",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"P",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Q",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"X",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$378,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$379,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$K$2:$K$378,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$378,"Z",Macierz!$L$2:$L$378,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N378"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28139,9 +28139,81 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="11" t="inlineStr">
+        <is>
+          <t>X-26</t>
+        </is>
+      </c>
+      <c r="B379" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C379" s="11" t="inlineStr">
+        <is>
+          <t>Skrypty powłoki mają bit wykonywalności — także po świeżym git clone</t>
+        </is>
+      </c>
+      <c r="D379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I379" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J379" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/src/test/skrypty-wykonywalne.spec.ts (3) — żaden .sh w repozytorium bez bitu wykonywalności; 82 skrypty przestawione na tryb 100755 (16 z nich miało 100644, w tym restore-drill-isolated.sh z bramki startu i pięć uruchamianych na węzłach produkcyjnych); docs/ops/RESTORE_TEST.md — usunięte obejście `chmod +x` sprzed uruchomienia</t>
+        </is>
+      </c>
+      <c r="K379" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L379" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M379" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N379" s="12" t="inlineStr">
+        <is>
+          <t>Odkryte przy X-25, dzień po zamknięciu mechanizmu H-20. Runbook, dokumentacja zadania i MAIL PRZYPOMINAJĄCY do administratora mówią jednym głosem: `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "…"` — a plik miał w gicie tryb 100644. Na świeżym `git clone` to polecenie kończy się „Permission denied". Czyli procedura, którą właśnie zamieniliśmy w bramkę startu sprzedaży, nie dawała się wykonać w sposób, w jaki sama każe siebie wykonywać. | Szesnaście skryptów miało ten sam problem, w tym pięć uruchamianych na węzłach produkcyjnych (node-app-install, node-db-upgrade, node-offsite-backup, node-php-apply, node-wp-install). | ŚLAD PO TYM BŁĘDZIE LEŻAŁ W REPOZYTORIUM OD DAWNA: docs/ops/RESTORE_TEST.md kazał wpisać `chmod +x` PRZED uruchomieniem, a Dockerfile.api robi `chmod +x` na entrypoincie. Obejścia działały, więc nikt nie naprawił przyczyny — a każde z nich było zapisanym w repozytorium dowodem, że przyczyna istnieje. To jest ten sam kształt co „bramka, która raportuje zamiast bramkować": objaw obsłużony, przyczyna zostaje. | REGUŁA JEST BEZWYJĄTKOWA i to jest jej najważniejsza cecha. Lista „te skrypty wolno mieć nieuruchamialne, bo woła je bash" musiałaby być utrzymywana obok prawdziwych wywołań, czyli byłaby kolejnym wystąpieniem bliźniaczych miejsc (Z-12, Z-16, M-06, X-24). Skrypt wykonywalny działa pod `bash x.sh` tak samo dobrze, więc reguła bez wyjątków nic nie kosztuje. | Strażnik czyta TRYB Z DYSKU, nie z indeksu gita: liczy się to, co dostaje maszyna po `git clone`, a actions/checkout wypisuje pliki dokładnie z trybami z indeksu. Czytanie dysku działa też tam, gdzie kopia robocza nie jest repozytorium, i nie wymaga drugiej ścieżki kodu na wypadek braku gita. | Ma też kontrolę „strażnik w ogóle coś widzi" (ponad 50 skryptów, w tym ten z bramki startu) — bez niej cała reszta przechodziłaby trywialnie na pustej liście, gdyby `find` przestał trafiać. | Czerwieni się na starym kodzie: 1 z 3 testów, z wypisaną listą wszystkich szesnastu plików. | CZEGO NIE ROBI: nie sprawdza shebangów ani tego, czy skrypt w ogóle da się uruchomić — tylko bit wykonywalności.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N378"/>
-  <conditionalFormatting sqref="D2:D378">
+  <autoFilter ref="A1:N379"/>
+  <conditionalFormatting sqref="D2:D379">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28158,7 +28230,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E378">
+  <conditionalFormatting sqref="E2:E379">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28175,7 +28247,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F378">
+  <conditionalFormatting sqref="F2:F379">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28192,7 +28264,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G378">
+  <conditionalFormatting sqref="G2:G379">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28209,7 +28281,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H378">
+  <conditionalFormatting sqref="H2:H379">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28226,7 +28298,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I378">
+  <conditionalFormatting sqref="I2:I379">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28246,7 +28318,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K378">
+  <conditionalFormatting sqref="K2:K379">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28263,7 +28335,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L378">
+  <conditionalFormatting sqref="L2:L379">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$380</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$379,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$380,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$379,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$380,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$379,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$380,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$379,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$380,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$379,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$380,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$379,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$380,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$379,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$380,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$379,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$380,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$379,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$380,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$379,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$380,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"A",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"A",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"A",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"A",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"A",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"B",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"B",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"B",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"B",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"B",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"C",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"C",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"C",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"C",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"C",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"D",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"D",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"D",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"D",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"D",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"E",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"E",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"E",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"E",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"E",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"F",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"F",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"F",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"F",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"F",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"G",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"G",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"G",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"G",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"G",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"H",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"H",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"H",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"H",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"H",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"I",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"I",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"I",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"I",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"I",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"J",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"J",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"J",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"J",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"J",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"K",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"K",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"K",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"K",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"K",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"L",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"L",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"L",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"L",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"L",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"M",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"M",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"M",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"M",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"M",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"N",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"N",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"N",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"N",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"N",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"O",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"O",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"O",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"O",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"O",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"P",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"P",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"P",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"P",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"P",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Q",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"Q",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Q",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Q",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Q",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"X",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"X",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"X",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"X",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"X",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$379,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$380,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Z",Macierz!$K$2:$K$380,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$380,"Z",Macierz!$K$2:$K$380,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$K$2:$K$379,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Z",Macierz!$K$2:$K$380,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$379,"Z",Macierz!$L$2:$L$379,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$380,"Z",Macierz!$L$2:$L$380,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28211,9 +28211,81 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="11" t="inlineStr">
+        <is>
+          <t>X-27</t>
+        </is>
+      </c>
+      <c r="B380" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>Obraz, który trafia na serwer, buduje się przed scaleniem</t>
+        </is>
+      </c>
+      <c r="D380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I380" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J380" s="12" t="inlineStr">
+        <is>
+          <t>Dockerfile.api / Dockerfile.panel — ponowna instalacja PO `COPY libs libs`; package.json — pnpm.overrides @prisma/client 6.19.3 (drzewo znów ma jedną wersję); .github/workflows/ci.yml — job `Obraz API (build bez push)`; apps/api/src/test/obrazy-dockera.spec.ts (14). Przyczyna deployu #63: „Could not resolve @prisma/client"</t>
+        </is>
+      </c>
+      <c r="K380" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L380" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M380" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N380" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22, wykryte przez wdrożenie #63 — pierwsze po scaleniu sprintu 2. Wysypał się build obrazu verris-api, czyli krok PRZED dotknięciem serwera: produkcja została nietknięta, migracje nie poszły. | DWIE PRZYCZYNY, NIE JEDNA. (1) `COPY libs libs` w etapie budowania kładzie katalogi pakietów na te, które zostawił etap `deps`, i pakiet traci WŁASNE node_modules. Dopóki każda zależność lądowała w node_modules katalogu głównego (linker hoisted), nie było tego widać — założenie trzymało się PRZYPADKIEM. (2) Przestało być prawdą przy X-18: apps/www podniosło Payloada, jego adapter postgresowy ciągnie drizzle-orm, a to ma @prisma/client jako peer OPCJONALNY; pnpm dociąga takie peery samo (autoInstallPeers), więc w drzewie stanęły DWIE wersje — 7.9.1 na górze i nasza 6.19.3 w libs/database. Po COPY zostawała tylko ta z góry, a `prisma generate` z CLI 6.19.3 nie umie pracować z klientem 7.x. | Poprawki są dwie, bo błędy są dwa: pnpm.overrides sprowadza drzewo do jednej wersji klienta (to naprawia TEN przypadek i chroni też obraz runtime, który kopiuje node_modules katalogu głównego), a ponowna instalacja w obrazach znosi założenie o hoistowaniu (to chroni przed następnym pakietem w dwóch wersjach). Dockerfile.panel dostał tę samą poprawkę mimo że jeszcze nie wybuchł — naprawiona jedna kopia i zostawiona druga to wzorzec, który dał Z-12, Z-16 i X-24. | NAJWAŻNIEJSZE ZNALEZISKO STRUKTURALNE: obraz, który JAKO JEDYNY trafia na serwer, powstawał wyłącznie w workflow wdrożeniowym — czyli PO scaleniu do main. Bramka scalenia sprawdzała lint, typy, 605 testów, migracje i asercje bazy, i nie sprawdzała tej jednej rzeczy. `pnpm build` w repozytorium przechodzi, bo tam node_modules są kompletne; rozjeżdżało się wyłącznie w układzie plików wewnątrz obrazu. Dlatego CI dostało job budujący Dockerfile.api bez pushowania. | DWA RAZY UWIERZYŁEM W WYNIK, KTÓRY NICZEGO NIE DOWODZIŁ: raz pnpm nie przeliczył lockfile'a i override wyglądał na nieskuteczny; raz uproszczone repozytorium testowe nie zawierało package.json apps/www, czyli pakietu ciągnącego 7.9.1 — więc wynik wyglądał dobrze z niewłaściwego powodu. Rozstrzygnięte dopiero na pełnym drzewie zależności. Ta sama rodzina co Z-01 i H-20. | Czerwieni się na starym kodzie: 7 z 14. | CZEGO NIE ROBI: CI nie buduje obrazów paneli (własny Dockerfile, ~2,5 min każdy, bez Prismy) — jeżeli kiedyś wywali się panel, job dostanie drugą pozycję w macierzy, a nie listę wyjątków. Dokumentacja: docs/zadania/X-27-obraz-api-w-ci.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N379"/>
-  <conditionalFormatting sqref="D2:D379">
+  <autoFilter ref="A1:N380"/>
+  <conditionalFormatting sqref="D2:D380">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28230,7 +28302,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E379">
+  <conditionalFormatting sqref="E2:E380">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28247,7 +28319,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F379">
+  <conditionalFormatting sqref="F2:F380">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28264,7 +28336,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G379">
+  <conditionalFormatting sqref="G2:G380">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28281,7 +28353,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H379">
+  <conditionalFormatting sqref="H2:H380">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28298,7 +28370,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I379">
+  <conditionalFormatting sqref="I2:I380">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28318,7 +28390,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K379">
+  <conditionalFormatting sqref="K2:K380">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28335,7 +28407,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L379">
+  <conditionalFormatting sqref="L2:L380">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$382</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$381,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$382,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$381,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$382,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$381,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$382,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$381,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$382,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$381,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$382,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$381,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$382,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$381,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$382,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$381,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$382,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$381,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$382,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$381,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$382,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"A",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"A",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"A",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"A",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"B",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"B",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"B",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"B",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"C",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"C",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"C",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"C",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"D",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"D",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"D",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"D",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"E",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"E",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"E",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"E",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"F",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"F",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"F",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"F",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"G",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"G",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"G",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"G",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"H",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"H",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"H",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"H",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"I",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"I",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"I",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"I",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"J",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"J",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"J",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"J",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"K",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"K",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"K",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"K",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"L",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"L",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"L",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"L",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"M",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"M",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"M",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"M",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"N",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"N",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"N",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"N",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"O",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"O",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"O",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"O",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"P",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"P",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"P",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"P",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Q",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"Q",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Q",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Q",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"X",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"X",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"X",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"X",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$381,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$382,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Z",Macierz!$K$2:$K$381,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$381,"Z",Macierz!$K$2:$K$381,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Z",Macierz!$K$2:$K$381,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$381,"Z",Macierz!$L$2:$L$381,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N381"/>
+  <dimension ref="A1:N382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28355,9 +28355,81 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" s="11" t="inlineStr">
+        <is>
+          <t>X-28</t>
+        </is>
+      </c>
+      <c r="B382" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C382" s="11" t="inlineStr">
+        <is>
+          <t>Reguła alertowa ma odbiorcę, a nie tylko próg</t>
+        </is>
+      </c>
+      <c r="D382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I382" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J382" s="12" t="inlineStr">
+        <is>
+          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — 13 reguł, 2 grupy, provisionowane z repo; ops/observability/prometheus.yml — bez rule_files, z opisem dlaczego; ops/observability/grafana/provisioning/datasources/datasources.yml — uid: Prometheus; docker-compose.prod.yml — bez montowania usuniętego alerts.yml; ops/observability/grafana/migracja-regul-do-grafany.py — zapis, jak powstał wynik; apps/api/src/test/routing-alertow.spec.ts (31); docs/ops/GRAFANA_ALERTING.md</t>
+        </is>
+      </c>
+      <c r="K382" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L382" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M382" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N382" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N381"/>
-  <conditionalFormatting sqref="D2:D381">
+  <autoFilter ref="A1:N382"/>
+  <conditionalFormatting sqref="D2:D382">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28374,7 +28446,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E381">
+  <conditionalFormatting sqref="E2:E382">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28391,7 +28463,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F381">
+  <conditionalFormatting sqref="F2:F382">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28408,7 +28480,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G381">
+  <conditionalFormatting sqref="G2:G382">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28425,7 +28497,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H381">
+  <conditionalFormatting sqref="H2:H382">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28442,7 +28514,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I381">
+  <conditionalFormatting sqref="I2:I382">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28462,7 +28534,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K381">
+  <conditionalFormatting sqref="K2:K382">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28479,7 +28551,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L381">
+  <conditionalFormatting sqref="L2:L382">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$383</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowane 2026-08-22 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
+          <t>Wygenerowane 2026-08-23 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$382,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$383,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$382,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$383,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$382,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$383,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$382,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$383,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$382,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$383,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$382,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$383,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$382,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$383,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$382,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$383,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$382,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$383,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$382,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$383,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"A",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"B",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"C",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"D",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"E",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"F",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"G",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"H",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"I",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"J",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"K",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"L",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"M",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"N",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"O",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"P",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Q",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"X",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$382,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$383,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$K$2:$K$382,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$382,"Z",Macierz!$L$2:$L$382,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N382"/>
+  <dimension ref="A1:N383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28427,9 +28427,81 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="11" t="inlineStr">
+        <is>
+          <t>X-29</t>
+        </is>
+      </c>
+      <c r="B383" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C383" s="11" t="inlineStr">
+        <is>
+          <t>Wdrożenie dowozi konfigurację obserwowalności na serwer</t>
+        </is>
+      </c>
+      <c r="D383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I383" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J383" s="12" t="inlineStr">
+        <is>
+          <t>ops/scripts/prod-deploy-ghcr.sh — krok 4.5: OBS_SERVICES, promtool check config przed restartem, compose up -d + compose restart, sprawdzenie /api/health i /-/healthy po restarcie, exit 1 gdy nie wrócą; apps/api/src/test/wdrozenie-obserwowalnosci.spec.ts (8)</t>
+        </is>
+      </c>
+      <c r="K383" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L383" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M383" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N383" s="12" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-23. Wykryte przy X-28, pytaniem kontrolnym: co się właściwie stanie po wdrożeniu poprawki, która przenosi reguły alertowe do Grafany? Odpowiedź: NIC. | MECHANIZM: prod-deploy-ghcr.sh robi na serwerze checkout repozytorium do wdrażanego SHA, więc nowe pliki lądują na dysku — po czym restartuje wyłącznie APP_SERVICES="api client-panel staff-panel admin-panel status-page www". Prometheusa i Grafany na tej liście nie ma, a oba czytają konfigurację TYLKO przy starcie kontenera i oba mają ją podmontowaną z repozytorium. | ZASIĘG SZERSZY NIŻ ALERTY: tą samą drogą nie docierało na produkcję wszystko pod ops/observability/ — cele scrapowania i retencja w prometheus.yml, źródła danych, dwadzieścia kilka dashboardów Grafany, punkty kontaktowe i polityki. Każda zmiana w tych plikach od ostatniego RĘCZNEGO restartu Grafany istniała wyłącznie w repozytorium. | RODZINA: ten sam kształt co X-28 (alarm bez odbiorcy), X-14 i X-23 (kontrola, która melduje zamiast zatrzymywać) i H-20 (procedura bez dowodu wykonania) — COŚ WYGLĄDA NA ZROBIONE, BO ISTNIEJE. Zielone CI, zielony deploy, plik na dysku, pozycja zamknięta — i zero zmiany w działającym systemie. Różnica: tu zawodziło ostatnie ogniwo, nie budowa ani test, tylko DOSTARCZENIE. | POPRAWKA: krok 4.5, dwa polecenia zamiast jednego. `up -d` odtwarza kontener, gdy zmieniła się DEFINICJA usługi (X-28 usunęło montowanie alerts.yml); `restart` wymusza ponowne wczytanie, gdy zmieniła się tylko TREŚĆ podmontowanego pliku — tego compose nie widzi. | BEZWARUNKOWO, nie „gdy się zmieniło": porównanie z poprzednim SHA wymagałoby obu wersji w repozytorium na serwerze, a fetch jest tam płytki (--depth 1); nieudane porównanie skończyłoby się cichym „brak zmian → nie restartuj", czyli dokładnie tym błędem, który ta pozycja naprawia. Kilkanaście sekund przerwy w metrykach kontra miesiąc bez kopii bazy. | SPRAWDZENIE PRZED: promtool check config przez `compose run --rm --no-deps --entrypoint promtool`, a nie `exec` — świeży kontener z tą samą definicją, więc sprawdzenie działa także wtedy, gdy Prometheus akurat leży; przy `exec` padałoby w jedynym momencie, w którym naprawdę zależy nam na restarcie. Restart na zepsutej konfiguracji zdejmuje monitoring, a zauważyć to miał właśnie monitoring. | SPRAWDZENIE PO: „wydałem polecenie restartu" to nie to samo co „wróciły" — /api/health Grafany i /-/healthy Prometheusa (pytany Z KONTENERA Grafany, bo obraz Prometheusa nie ma czym wykonać zapytania HTTP), 20 prób co 3 s, potem exit 1. | KOLEJNOŚĆ W DWIE STRONY: krok jest PO bramce zdrowia i PO zapisaniu .last-good-image-tag, żeby awaria monitoringu nie wywróciła sprawnego wdrożenia; kończy się exit 1, a nie ostrzeżeniem, żeby wdrożenie nie uchodziło za skończone, zanim monitoring dostanie nową konfigurację. | Czerwieni się na starym kodzie: 6 z 8. Dwie przechodziły i przedtem — w tym ta o APP_SERVICES, bo Prometheusa i Grafany naprawdę tam nie było (tyle że nie było ich też nigdzie indziej). | CZEGO NIE DOWODZI: że po najbliższym wdrożeniu Grafana MA reguły — to obserwacja na produkcji (D3): Alerting → Alert rules powinno pokazać trzynaście reguł w folderze Verris. | Deploy #66 (scalenie X-28) poszedł jeszcze STARYM skryptem, więc pliki wjechały na serwer, a monitoring został z poprzednią konfiguracją; naprawia się to samo przy pierwszym wdrożeniu z tą zmianą. Dokumentacja: docs/zadania/X-29-obserwowalnosc-nie-docierala-na-produkcje.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N382"/>
-  <conditionalFormatting sqref="D2:D382">
+  <autoFilter ref="A1:N383"/>
+  <conditionalFormatting sqref="D2:D383">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28446,7 +28518,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E382">
+  <conditionalFormatting sqref="E2:E383">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28463,7 +28535,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F382">
+  <conditionalFormatting sqref="F2:F383">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28480,7 +28552,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G382">
+  <conditionalFormatting sqref="G2:G383">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28497,7 +28569,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H382">
+  <conditionalFormatting sqref="H2:H383">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28514,7 +28586,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I382">
+  <conditionalFormatting sqref="I2:I383">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28534,7 +28606,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K382">
+  <conditionalFormatting sqref="K2:K383">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28551,7 +28623,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L382">
+  <conditionalFormatting sqref="L2:L383">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -13834,17 +13834,17 @@
       </c>
       <c r="I176" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
         <is>
-          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
+          <t>DOWÓD D4 — wiersz w bazie PRODUKCYJNEJ, odczytany 2026-08-23: finishedAt=2026-08-22 23:19:45, result=OK, owner=Dominik Kowalski, durationSec=9, objectName=latest.sql.gz.age. W tabeli stoi też wiersz poprzedni: 2026-08-22 19:57:36 / FAILED / durationSec=1 / objectName=latest.sql.gz — próba sprzed H-24, która szła po nieistniejący obiekt. | MECHANIZM (D2): admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach, suma kontrolna, deszyfrowanie age, zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8)</t>
         </is>
       </c>
       <c r="K176" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L176" s="11" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="N176" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
+          <t>ZAMKNIĘTE 2026-08-23. Pierwsze w historii projektu odtworzenie bazy z kopii — i pierwszy dowód, że warstwa DR w ogóle działa. Przebieg: MinIO stat latest.sql.gz.age (4,3 MiB, 2026-08-22 21:24:12), suma kontrolna zgodna, deszyfrowanie kluczem operacyjnym, odtworzenie do izolowanej bazy verris_restore_drill w 9 sekund, progi wierszy na pięciu tabelach: Invoice 0 (min 0), Plan 5 (min 1), Account 3 (min 0), User 10 (min 1), Subscription 7 (min 0), baza drillowa skasowana, produkcyjna verris_db nietknięta. | DZIEWIĘĆ SEKUND TO REALNE RTO — dolne oszacowanie, bo drill biegnie na tym samym hoście. To jest liczba, którą trzeba znać PRZED awarią, nie w jej trakcie. | DWA WIERSZE W TABELI, NIE JEDEN — i to jest część dowodu. Pierwsza próba (19:57, FAILED, 1 s, latest.sql.gz) padła, bo skrypt pytał o obiekt, którego produkcja NIGDY nie tworzy; naprawione w H-24, druga próba (23:19, OK, 9 s, latest.sql.gz.age) przeszła. Mechanizm zapisał własną porażkę zamiast ją przemilczeć — dokładnie po to powstał wymóg, żeby ślad powstawał RÓWNIEŻ przy niepowodzeniu. Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna. | DOWÓD ODCZYTANY Z BAZY, NIE Z KOMUNIKATU SKRYPTU. Skrypt drukuje „ślad próby zapisany" — to jest zdanie o zamiarze, nie o wyniku. Cała ta pozycja i cała awaria kopii z H-23 wzięły się z ufania takim zdaniom. | DOWÓD SIĘ STARZEJE: termin ważności 30 dni (MAKS_WIEK_PROBY_DNI), czyli do 2026-09-21, potem gotowość do startu znów zwraca go: false. Przypomnienie idzie mailem 7 dni przed terminem. Odtworzenie sprzed schematu, którego już nie ma, nie dowodzi niczego o dzisiejszej kopii. | ZROBIONE POZA KOLEJNOŚCIĄ — pozycja planowana na sprint 9 (po postawieniu węzła produkcyjnego w sprincie 8), wykonana w sprincie 2, bo H-23 wymusiło odtworzenie kopii tu i teraz. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej; nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$384</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$383,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$384,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$383,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$384,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$383,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$384,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$383,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$384,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$383,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$384,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$383,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$384,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$383,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$384,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$383,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$384,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$383,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$384,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$383,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$384,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"A",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"B",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"C",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"D",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"E",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"F",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"G",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"H",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"I",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"J",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"K",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"L",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"M",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"N",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"O",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"P",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Q",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"X",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$383,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$384,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$K$2:$K$383,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$383,"Z",Macierz!$L$2:$L$383,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N383"/>
+  <dimension ref="A1:N384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28499,9 +28499,81 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="11" t="inlineStr">
+        <is>
+          <t>X-30</t>
+        </is>
+      </c>
+      <c r="B384" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C384" s="11" t="inlineStr">
+        <is>
+          <t>Reguły alertowe nie tylko są wczytane, ale się liczą</t>
+        </is>
+      </c>
+      <c r="D384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I384" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J384" s="12" t="inlineStr">
+        <is>
+          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). BRAK: zielonego wdrożenia z czystym logiem Grafany — dowód D3 jeszcze nie powstał.</t>
+        </is>
+      </c>
+      <c r="K384" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L384" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M384" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N384" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA do czasu zielonego wdrożenia z czystym logiem Grafany (D3). Wpisanie DZIAŁA teraz byłoby powtórzeniem dokładnie tego błędu, który ta pozycja opisuje. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N383"/>
-  <conditionalFormatting sqref="D2:D383">
+  <autoFilter ref="A1:N384"/>
+  <conditionalFormatting sqref="D2:D384">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28518,7 +28590,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E383">
+  <conditionalFormatting sqref="E2:E384">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28535,7 +28607,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F383">
+  <conditionalFormatting sqref="F2:F384">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28552,7 +28624,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G383">
+  <conditionalFormatting sqref="G2:G384">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28569,7 +28641,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H383">
+  <conditionalFormatting sqref="H2:H384">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28586,7 +28658,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I383">
+  <conditionalFormatting sqref="I2:I384">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28606,7 +28678,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K383">
+  <conditionalFormatting sqref="K2:K384">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28623,7 +28695,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L383">
+  <conditionalFormatting sqref="L2:L384">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$385</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$384,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$385,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$384,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$385,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$384,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$385,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$384,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$385,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$384,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$385,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$384,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$385,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$384,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$385,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$384,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$385,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$384,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$385,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$384,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$385,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"A",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"B",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"C",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"D",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"E",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"F",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"G",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"H",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"I",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"J",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"K",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"L",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"M",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"N",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"O",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"P",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Q",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"X",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$384,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$385,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$K$2:$K$384,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$384,"Z",Macierz!$L$2:$L$384,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N384"/>
+  <dimension ref="A1:N385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28423,7 +28423,7 @@
       </c>
       <c r="N382" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md</t>
+          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md | DOWÓD D3 DOSTARCZALNOŚCI — 2026-08-23, dostarczony przez awarię, nie przez test. Przy X-30 reguły z execErrState: Alerting zapaliły się na błędzie ewaluacji i DZIESIĘĆ maili dotarło na dominik@hvln.pl z tematami [FIRING:1] &lt;alertname&gt; &lt;severity&gt; (Verris). Droga Grafana → SMTP → Postfix na panelu → mail.hvln.pl → skrzynka jest potwierdzona na całej długości. | TEN PRZYPADEK POTWIERDZIŁ TRZY RZECZY, KTÓRYCH PLANOWANY TEST JEDNEGO ALERTU BY NIE POTWIERDZIŁ: (1) droga do skrzynki działa; (2) migracja nie pogubiła nazw ani wag — tematy pokazały critical przy VerrisRuntimeErrorsHigh, VerrisOpenMajorIncident, VerrisSecurityWatchFindings i VerrisProvisioningQueueFailed oraz warning przy pozostałych, dokładnie jak w usuniętym alerts.yml; (3) progi `for:` przetrwały migrację — zapaliło się DZIESIĘĆ z trzynastu, a nie zapaliły się dokładnie te trzy z najdłuższym for: VerrisPostgresBackupStale (30 m), VerrisStatusWebhookFailed (30 m) i VerrisSecurityWatchStale (20 m), bo od restartu nie minęło tyle czasu. Skrypt migracyjny mógł te wartości po cichu przekręcić i żaden test w CI by tego nie zobaczył — zobaczyła to skrzynka.</t>
         </is>
       </c>
     </row>
@@ -28571,9 +28571,81 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="11" t="inlineStr">
+        <is>
+          <t>X-31</t>
+        </is>
+      </c>
+      <c r="B385" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C385" s="11" t="inlineStr">
+        <is>
+          <t>Kanał alertów daje znak życia (dead man's switch)</t>
+        </is>
+      </c>
+      <c r="D385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I385" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J385" s="12" t="inlineStr">
+        <is>
+          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — grupa verris_kanal_alertow, reguła VerrisKanalAlertowZyje (vector(1), for: 0s, oba stany awaryjne na Alerting, etykieta kanal: heartbeat); policies.yaml — gałąź object_matchers kanal=heartbeat, repeat_interval 24h; apps/api/src/test/routing-alertow.spec.ts (5 asercji X-31); docs/ops/GRAFANA_ALERTING.md §4. BRAK: pierwszego maila [FIRING:1] VerrisKanalAlertowZyje — dowód D3 jeszcze nie powstał.</t>
+        </is>
+      </c>
+      <c r="K385" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M385" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N385" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 powstanie przy pierwszym mailu. Decyzja właściciela produktu: wariant „jeden mail na dobę". | PROBLEM: po naprawie X-30 alerty ucichną, a cisza będzie znaczyła „nic się nie pali" — i będzie wyglądała IDENTYCZNIE jak: Grafana padła, Postfix przestał przyjmować, mail.hvln.pl zaczął odrzucać albo wrzucać do spamu, ktoś zmienił adres w punkcie kontaktowym, polityka przestała pasować do etykiet. To dokładnie ta sama cisza, która przez miesiąc znaczyła „kopia bazy jest w porządku" (H-23) i kosztowała wszystkie kopie zapasowe. | ROZWIĄZANIE: VerrisKanalAlertowZyje — reguła vector(1), pali się ZAWSZE, jej BRAK jest sygnałem. for: 0s, noDataState: Alerting, execErrState: Alerting — nie da się jej „nie zapalić": normalnie warunek jest spełniony, a gdyby źródło danych przestało odpowiadać, oba stany awaryjne też prowadzą do Alerting. Milczenie ma znaczyć awarię, nigdy spokój. | JEDEN MAIL NA DOBĘ, NIE SZEŚĆ: osobna gałąź polityki na etykiecie kanal: heartbeat z repeat_interval 24h. Na domyślnej (4h) byłoby sześć dziennie, a alert przychodzący sześć razy dziennie przestaje być czytany po tygodniu — wtedy przestaje cokolwiek dawać, bo jego BRAK jest jedyną informacją, jaką niesie. Strażnik pilnuje osobno, że polityka domyślna NIE została przy okazji przestawiona na dobę: prawdziwy alarm ma się przypominać co cztery godziny. | HACZYK, KTÓRY TRZEBA NAZWAĆ: mail, którego się nie czyta, wraca do punktu wyjścia. Jeśli po tygodniu przestanie być zauważany, reguła przestaje działać — nie dlatego, że jest zepsuta, tylko dlatego, że przestała być czytana. Tego nie da się naprawić kodem. | CZEGO NIE OBEJMUJE: awarii całego serwera (heartbeat mieszka na tej samej maszynie co Grafana i milczy razem z nią — odporny byłby watchdog SPOZA naszej infrastruktury, pukany cronem; nie ma go i to świadoma decyzja, nie przeoczenie) ani poprawności pozostałych reguł (tego pilnuje bramka z X-30). | Czerwieni się na starym kodzie: 5 z 36. | Doszła lista DOPISANE_POZNIEJ, trzymana osobno od ALERTY: tamta odpowiada na pytanie „czy migracja czegoś nie zgubiła" i ma zostać zamrożona, ta na „czy ktoś czegoś po cichu nie dołożył". Dokumentacja: docs/zadania/X-31-znak-zycia-kanalu-alertow.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N384"/>
-  <conditionalFormatting sqref="D2:D384">
+  <autoFilter ref="A1:N385"/>
+  <conditionalFormatting sqref="D2:D385">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28590,7 +28662,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E384">
+  <conditionalFormatting sqref="E2:E385">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28607,7 +28679,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F384">
+  <conditionalFormatting sqref="F2:F385">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28624,7 +28696,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G384">
+  <conditionalFormatting sqref="G2:G385">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28641,7 +28713,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H384">
+  <conditionalFormatting sqref="H2:H385">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28658,7 +28730,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I384">
+  <conditionalFormatting sqref="I2:I385">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28678,7 +28750,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K384">
+  <conditionalFormatting sqref="K2:K385">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28695,7 +28767,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L384">
+  <conditionalFormatting sqref="L2:L385">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -28542,17 +28542,17 @@
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J384" s="12" t="inlineStr">
         <is>
-          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). BRAK: zielonego wdrożenia z czystym logiem Grafany — dowód D3 jeszcze nie powstał.</t>
+          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). DOWÓD D3: wdrożenie #68 zielone przez krok 4.6; log Grafany po restarcie 11:01:46 bez „Failed to build rule evaluator" (wszystkie wystąpienia 10:58–11:01:39, czyli sprzed restartu); „inserting datasource from configuration" name=Prometheus uid=Prometheus.</t>
         </is>
       </c>
       <c r="K384" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L384" s="11" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="N384" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA do czasu zielonego wdrożenia z czystym logiem Grafany (D3). Wpisanie DZIAŁA teraz byłoby powtórzeniem dokładnie tego błędu, który ta pozycja opisuje. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md</t>
+          <t>ZAMKNIĘTE 2026-08-23. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md | ZAMKNIĘTE 2026-08-23 — DOWÓD D3 Z LOGU PRODUKCYJNEJ GRAFANY. Wdrożenie #68 (2788011) przeszło przez nowy krok 4.6 i trwało 9m54s, czyli o te 75 sekund dłużej — krok przechodzi tylko wtedy, gdy Grafana ma reguły I licznik nieudanych ewaluacji nie urósł. W logu: 11:01:46 „deleted datasource based on configuration" name=Prometheus, zaraz po tym „inserting datasource from configuration" name=Prometheus uid=Prometheus. Wszystkie wpisy „Failed to build rule evaluator" mają znacznik 10:58–11:01:39, czyli SPRZED restartu; po 11:01:46 nie ma ANI JEDNEGO. Wpisy „Detected stale state entry ... reason=Error" o 11:02–11:03 to Grafana sprzątająca stare wpisy w stanie Alerting-z-powodu-błędu, stąd wiadomości [RESOLVED]. | POTWIERDZENIE UBOCZNE, MOCNIEJSZE OD SAMEGO LOGU: reguła VerrisProvisioningQueueFailed NIE ucichła po naprawie — wysyła alarm co minutę od 11:12, a ma for: 10m przy restarcie 11:01:46, więc pierwsze zapalenie o 11:12 zgadza się co do sekundy. To znaczy, że warunek verris_provisioning_queue_depth{state="failed"} &gt; 0 jest PRAWDZIWIE spełniony: alerting zaczął działać i w ciągu dziesięciu minut znalazł na produkcji coś realnego. Reguła, która zapala się z właściwego powodu, dowodzi więcej niż cisza. Osobna pozycja.</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$385</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$386</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$385,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$386,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$385,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$386,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$385,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$386,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$385,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$386,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$385,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$386,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$385,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$386,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$385,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$386,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$385,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$386,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$385,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$386,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$385,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$386,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"A",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"B",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"C",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"D",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"E",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"F",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"G",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"H",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"I",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"J",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"K",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"L",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"M",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"N",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"O",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"P",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Q",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"X",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$385,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$386,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$K$2:$K$385,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$385,"Z",Macierz!$L$2:$L$385,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N385"/>
+  <dimension ref="A1:N386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27350,17 +27350,17 @@
     <row r="368">
       <c r="A368" s="11" t="inlineStr">
         <is>
-          <t>X-14</t>
+          <t>Z-18</t>
         </is>
       </c>
       <c r="B368" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>CI sprawdza DANE po migracji, nie tylko czy migracja się wykonała</t>
+          <t>Prawdziwa przyczyna błędu provisioningu nie ginie po drodze</t>
         </is>
       </c>
       <c r="D368" s="11" t="inlineStr">
@@ -27390,22 +27390,22 @@
       </c>
       <c r="I368" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J368" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml — job migrations: kroki „Seed reference data” i „Verify migrated data (Z-12, Z-13, Z-16)”; ops/sql/sprawdz-baze-po-migracji.sql — 5 bloków asercji kończących się RAISE EXCEPTION</t>
+          <t>apps/api/src/subscriptions/provisioning-error.ts — BladEtapuProvisioningu (etap, przyczyna, message z doklejoną przyczyną); provisioning-queue.service.ts — kategoriaBledu(err), klasyfikacja obiektu zamiast napisu, pole przyczyna w audycie ponowienia i twardej porażki; provisioning.service.ts — trzy etapy DA (ensureUserPackage, createAccount, setAccountLimits) bez prania przyczyny; apps/api/src/test/blad-provisioningu-nie-klamie.spec.ts (18). BRAK: dowodu D3 — nie ma węzła obliczeniowego, więc ścieżki provisioningu nie da się dziś przejść na produkcji.</t>
         </is>
       </c>
       <c r="K368" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L368" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="M368" s="11" t="inlineStr">
@@ -27415,14 +27415,14 @@
       </c>
       <c r="N368" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Job migrations sprawdzał wyłącznie, czy migracje dają się zastosować i czy schemat nie ma dryfu. Nie sprawdzał, czy DANE, które migracje wstawiają, tam są i mają właściwe wartości — a Z-12 i Z-13 to migracje danych, których poprawność testy jednostkowe potwierdzały wyłącznie przez czytanie SQL-a jako TEKSTU. | Teraz CI odpytuje bazę: czy plan verris-hosting istnieje z ceną 45,00 brutto i limitami 200/8192/51200, czy publiczny pakiet hostingowy jest dokładnie jeden, czy prototypy są wycofane ale nie zdezaktywowane, czy kolumny overcommit mają NEUTRALNĄ domyślną 1, czy księga pojemności zgadza się z sumą limitów kont żywych. | Sprawdzone na prawdziwym Postgresie 16 ze wszystkimi 100 migracjami: komplet przechodzi, a podmiana ceny na 49,00 i podniesienie domyślnej nadsubskrypcji do 4 wywalają job z kodem 3. | ODKRYTE PRZY TESTOWANIU: na bazie z samych migracji plany prototypowe w ogóle nie istnieją (tworzy je seed), więc asercja o ich wycofaniu przechodziła TRYWIALNIE — w logu CI wygląda to identycznie jak prawdziwe „wszystko w porządku”. Stąd krok seeda przed asercjami plus jawny warunek: zero znalezionych prototypów to błąd, nie sukces. Przy okazji CI po raz pierwszy weryfikuje, że seed w ogóle wykonuje się na świeżej bazie. | Dokumentacja: docs/zadania/X-14-asercje-danych-po-migracji.md</t>
+          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA — bloker startu do czasu dowodu D3 na węźle #1 (sprint 8). Krytyczność nadana decyzją właściciela produktu 2026-08-23. | JAK TO WYSZŁO: X-30 naprawiło alerting i w ciągu dziesięciu minut zapaliła się pierwsza reguła z PRAWDZIWEGO powodu — VerrisProvisioningQueueFailed. W kolejce leżały cztery martwe joby, a w panelu operatora stało przy nich „DirectAdmin package "starter" is missing on the node and could not be created automatically". W audycie stało co innego: ensureUserPackage / connect ECONNREFUSED 62.238.0.223:2222 (2026-07-07 i 07-10) oraz createAccount / „DirectAdmin API Error: Unable to Create User — A valid IP was not provided" (2026-05-30). Węzeł nie przyjmował połączeń; z pakietem nie było nic nie tak. Same joby są nieszkodliwe — konto testowe właściciela, domeny test.pl/testowa.pl/hvln.pl, sprzed trzech miesięcy, z czasów gdy węzeł testowy jeszcze istniał (dziś nie ma go wcale). Ale komunikat doprowadził mnie do hipotezy o złym mapowaniu planów na pakiety DA — całkowicie chybionej. Na tym polega koszt takiego błędu: nie na tym, że coś nie działa, tylko że wszyscy patrzą nie tam. | MECHANIZM: provisioning.service.ts łapał prawdziwy błąd, zapisywał go do audytu i rzucał dalej STAŁY NAPIS. Prawda zostawała w bazie, w górę szła zmyślona przyczyna. A wyżej: const errCategory = categorizeProvisioningError(msg) — klasyfikator dostawał ten wyprany napis. Jest napisany POPRAWNIE, ma econnrefused na liście błędów przejściowych; tylko nigdy nie widzi tego słowa. | DLACZEGO DOTYKA PIENIĘDZY: przy kliencie i chwilowym zerwaniu sieci — próba 1 → ECONNREFUSED przebrany za brak pakietu → permanent → ścieżka twardej porażki JUŻ PRZY PIERWSZEJ PRÓBIE: subskrypcja na FAILED, ZWROT ŚRODKÓW do portfela, status PENDING_PAYMENT; potem throw err i BullMQ i tak ponawia (attempts: 3, backoff wykładniczy); próba 2 przechodzi, konto powstaje, provisioning.service.ts:299 ustawia subskrypcję na ACTIVE. Klient ma działający hosting i odzyskane pieniądze, a zwrot jest idempotentny (sub-{id}-initial-refund), więc nic go nie cofnie. Wada uśpiona — nie ma dowodu, że się zdarzyła (te joby padły do końca, węzeł był wyłączony na dobre) — ale leży dokładnie na ścieżce pierwszego płacącego klienta. | RODZINA, NOWY WARIANT: to NIE jest „kontrola, która melduje zamiast zatrzymywać" (X-14, X-23, H-19, X-27), gdzie mechanizm istniał i niczego nie bramkował. To POPRAWNA KONTROLA, KTÓREJ SIĘ KŁAMIE: guard dobry, decyzja dobra, lista wyjątków kompletna — a wejście wyprane po drodze. Blisko też rodzinie „strażnik dopasowuje własną prozę" (dziesiąte wystąpienie): jeden z trzech komunikatów był ułożony tak, żeby TRAFIĆ w listę przejściowych — 'CloudLinux LVE limits could not be applied on this node.' kontra lower.includes('cloudlinux lve limits could not be applied'). Działało przypadkiem, dopóki ktoś nie poprawiłby zdania. | POPRAWKA: BladEtapuProvisioningu(etap, przyczyna, komunikatDlaCzlowieka) — klasa niosąca ORYGINALNĄ treść błędu; kategoriaBledu(err) pyta obiekt o przyczynę i dopiero na niej odpala istniejący klasyfikator, a napis zostaje ścieżką zapasową. Przyczyna jest DOKLEJONA także do message, bo panel pokazuje job.failedReason z BullMQ (czyli Error.message), a failedCategory liczy się z tego samego napisu — gdyby przyczyna została tylko we właściwości, panel dalej opowiadałby zmyśloną historię. Audyt dostał osobne pole przyczyna obok error. | Czerwieni się na starym kodzie: 4 z 18. Czternaście przechodziło, bo dotyczą zachowania kategoriaBledu, której przed poprawką nie było — redness siedzi w asercjach strukturalnych. Mówię o tym wprost, żeby „4 z 18" nie wyglądało słabiej, niż jest. | CZEGO NIE OBEJMUJE: innych miejsc, gdzie prawdziwy błąd może być prany (Stripe, migracje, autoskalowanie mają własne bloki catch i nie były przeglądane pod tym kątem — warte osobnego przejścia); sensowności samego zwrotu przy twardej porażce (zwrot jest właściwy, gdy błąd NAPRAWDĘ jest trwały — ta pozycja naprawia rozpoznanie, nie decyzję); czterech martwych jobów w kolejce (sprzątane po tej poprawce, decyzją właściciela produktu, żeby czyścić już na kodzie zapisującym prawdziwą przyczynę). | JAK ZAMKNĄĆ: na węźle #1 uruchomić provisioning, przerwać połączenie do DA w trakcie i pokazać w audycie PONOWIENIE zamiast zwrotu środków, a potem konto założone przy drugiej próbie. Dokumentacja: docs/zadania/Z-18-blad-provisioningu-nie-klamie.md</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="11" t="inlineStr">
         <is>
-          <t>X-15</t>
+          <t>X-14</t>
         </is>
       </c>
       <c r="B369" s="12" t="inlineStr">
@@ -27432,7 +27432,7 @@
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>Niezmiennik księgi pojemności sprawdzany liczbowo, nie tekstowo</t>
+          <t>CI sprawdza DANE po migracji, nie tylko czy migracja się wykonała</t>
         </is>
       </c>
       <c r="D369" s="11" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="J369" s="12" t="inlineStr">
         <is>
-          <t>apps/api/src/subscriptions/ksiega-niezmiennik.spec.ts — 15 testów: losowe ciągi operacji (założenie konta, skalowanie w górę i w dół, zmiana planu, usunięcie) z porównaniem księgi z prawdą po KAŻDYM kroku; node-capacity.ts — deltaKsiegi/limityEfektywne/ksiegaUpdateData jako jedyna arytmetyka księgi w projekcie</t>
+          <t>.github/workflows/ci.yml — job migrations: kroki „Seed reference data” i „Verify migrated data (Z-12, Z-13, Z-16)”; ops/sql/sprawdz-baze-po-migracji.sql — 5 bloków asercji kończących się RAISE EXCEPTION</t>
         </is>
       </c>
       <c r="K369" s="11" t="inlineStr">
@@ -27487,14 +27487,14 @@
       </c>
       <c r="N369" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strażniki z Z-16 były statyczne — czytały tekst źródłowy. Złapią usunięcie linii (i złapały, gdy arytmetyka poszła do wspólnych funkcji), ale nie złapią błędu w ZNAKU delty ani pomylonych argumentów: deltaKsiegi(po, przed) zamiast deltaKsiegi(przed, po) przechodzi każdy test tekstowy i rozjeżdża księgę przy pierwszej operacji. | Test sprawdza jedyną rzecz, która musi być prawdziwa: allocated* równa się sumie limitów efektywnych kont żywych po dowolnym ciągu operacji. Deterministyczny generator, sześć ziaren, sprawdzenie po każdym kroku — żeby dwa błędy nie zniosły się nawzajem. | Uczciwość testu polega na tym, że symulator używa DOKŁADNIE tych samych funkcji co produkcja; gdyby liczył po swojemu, sprawdzałby siebie. Warunkiem było wyciągnięcie arytmetyki z czterech serwisów do node-capacity.ts — przy okazji piąty rozjazd nie ma już gdzie powstać. | Zweryfikowane: odwrócenie znaku w JEDNYM zasobie czerwieni 10 z 15 testów niezmiennika. Test statyczny tego nie widzi. | Czego to nie sprawdza: czy serwisy wołają te funkcje w odpowiednim momencie i z odpowiednimi argumentami — to jest rola X-04. Tu weryfikowana jest arytmetyka, tam okablowanie.</t>
+          <t>Zamknięte 2026-08-22. Job migrations sprawdzał wyłącznie, czy migracje dają się zastosować i czy schemat nie ma dryfu. Nie sprawdzał, czy DANE, które migracje wstawiają, tam są i mają właściwe wartości — a Z-12 i Z-13 to migracje danych, których poprawność testy jednostkowe potwierdzały wyłącznie przez czytanie SQL-a jako TEKSTU. | Teraz CI odpytuje bazę: czy plan verris-hosting istnieje z ceną 45,00 brutto i limitami 200/8192/51200, czy publiczny pakiet hostingowy jest dokładnie jeden, czy prototypy są wycofane ale nie zdezaktywowane, czy kolumny overcommit mają NEUTRALNĄ domyślną 1, czy księga pojemności zgadza się z sumą limitów kont żywych. | Sprawdzone na prawdziwym Postgresie 16 ze wszystkimi 100 migracjami: komplet przechodzi, a podmiana ceny na 49,00 i podniesienie domyślnej nadsubskrypcji do 4 wywalają job z kodem 3. | ODKRYTE PRZY TESTOWANIU: na bazie z samych migracji plany prototypowe w ogóle nie istnieją (tworzy je seed), więc asercja o ich wycofaniu przechodziła TRYWIALNIE — w logu CI wygląda to identycznie jak prawdziwe „wszystko w porządku”. Stąd krok seeda przed asercjami plus jawny warunek: zero znalezionych prototypów to błąd, nie sukces. Przy okazji CI po raz pierwszy weryfikuje, że seed w ogóle wykonuje się na świeżej bazie. | Dokumentacja: docs/zadania/X-14-asercje-danych-po-migracji.md</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="11" t="inlineStr">
         <is>
-          <t>X-17</t>
+          <t>X-15</t>
         </is>
       </c>
       <c r="B370" s="12" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>Joby CI budują zależności workspace'u zanim uruchomią testy</t>
+          <t>Niezmiennik księgi pojemności sprawdzany liczbowo, nie tekstowo</t>
         </is>
       </c>
       <c r="D370" s="11" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="J370" s="12" t="inlineStr">
         <is>
-          <t>.github/workflows/ci.yml — krok „Build workspace libraries” w jobie api-tests, „Generate Prisma client” w jobie migrations; turbo.json — zadanie test dostaje dependsOn ^build; apps/api/src/test/ci-joby.spec.ts — 6 testów strażnika</t>
+          <t>apps/api/src/subscriptions/ksiega-niezmiennik.spec.ts — 15 testów: losowe ciągi operacji (założenie konta, skalowanie w górę i w dół, zmiana planu, usunięcie) z porównaniem księgi z prawdą po KAŻDYM kroku; node-capacity.ts — deltaKsiegi/limityEfektywne/ksiegaUpdateData jako jedyna arytmetyka księgi w projekcie</t>
         </is>
       </c>
       <c r="K370" s="11" t="inlineStr">
@@ -27559,14 +27559,14 @@
       </c>
       <c r="N370" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #57 zielony w komplecie — sześć jobów, w tym „API integration tests" z Postgresem 16.</t>
+          <t>Zamknięte 2026-08-22. Strażniki z Z-16 były statyczne — czytały tekst źródłowy. Złapią usunięcie linii (i złapały, gdy arytmetyka poszła do wspólnych funkcji), ale nie złapią błędu w ZNAKU delty ani pomylonych argumentów: deltaKsiegi(po, przed) zamiast deltaKsiegi(przed, po) przechodzi każdy test tekstowy i rozjeżdża księgę przy pierwszej operacji. | Test sprawdza jedyną rzecz, która musi być prawdziwa: allocated* równa się sumie limitów efektywnych kont żywych po dowolnym ciągu operacji. Deterministyczny generator, sześć ziaren, sprawdzenie po każdym kroku — żeby dwa błędy nie zniosły się nawzajem. | Uczciwość testu polega na tym, że symulator używa DOKŁADNIE tych samych funkcji co produkcja; gdyby liczył po swojemu, sprawdzałby siebie. Warunkiem było wyciągnięcie arytmetyki z czterech serwisów do node-capacity.ts — przy okazji piąty rozjazd nie ma już gdzie powstać. | Zweryfikowane: odwrócenie znaku w JEDNYM zasobie czerwieni 10 z 15 testów niezmiennika. Test statyczny tego nie widzi. | Czego to nie sprawdza: czy serwisy wołają te funkcje w odpowiednim momencie i z odpowiednimi argumentami — to jest rola X-04. Tu weryfikowana jest arytmetyka, tam okablowanie.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="11" t="inlineStr">
         <is>
-          <t>X-18</t>
+          <t>X-17</t>
         </is>
       </c>
       <c r="B371" s="12" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>Zależności podniesione do najnowszych bezpiecznych wersji</t>
+          <t>Joby CI budują zależności workspace'u zanim uruchomią testy</t>
         </is>
       </c>
       <c r="D371" s="11" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="J371" s="12" t="inlineStr">
         <is>
-          <t>package.json — 16 pnpm.overrides na zależności przechodnie; apps/www next 15.4.4 → 16.3.2; wszystkie panele next 16.3.2; NestJS 11.2.1; React 19.2.8; Payload 3.88.0; recharts 3; @types/node 26; ioredis 6; bullmq 6; graphql 17; sharp 0.35.3; libs/typescript-config/nestjs.json target ES2022 + lib ES2023</t>
+          <t>.github/workflows/ci.yml — krok „Build workspace libraries” w jobie api-tests, „Generate Prisma client” w jobie migrations; turbo.json — zadanie test dostaje dependsOn ^build; apps/api/src/test/ci-joby.spec.ts — 6 testów strażnika</t>
         </is>
       </c>
       <c r="K371" s="11" t="inlineStr">
@@ -27626,19 +27626,19 @@
       </c>
       <c r="M371" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N371" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md | KOREKTA 2026-08-22 (X-21): graphql cofnięty z ^17.0.2 do ^16.14.2 — jedynym konsumentem jest Payload 3.88, który deklaruje peera ^16.8.1, a nasz kod nie importuje graphql ani razu. Podniosłem major pod biblioteką, która go nie wspiera, bo wersja była wyższa — na PUBLICZNEJ stronie. Build www przechodzi na 16, ostrzeżenie o peerze znikło. | Domknięty body-parser override'em ^2.3.0: podatności 2 → 1 (została deepmerge-ts, wysoka, tylko przez Prismę 6 — znika z X-20). | engines.node podniesione z "&gt;=22" do "&gt;=22.12" — patrz X-21.</t>
+          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #57 zielony w komplecie — sześć jobów, w tym „API integration tests" z Postgresem 16.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="11" t="inlineStr">
         <is>
-          <t>X-19</t>
+          <t>X-18</t>
         </is>
       </c>
       <c r="B372" s="12" t="inlineStr">
@@ -27648,7 +27648,7 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
+          <t>Zależności podniesione do najnowszych bezpiecznych wersji</t>
         </is>
       </c>
       <c r="D372" s="11" t="inlineStr">
@@ -27678,22 +27678,22 @@
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J372" s="12" t="inlineStr">
         <is>
-          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
+          <t>package.json — 16 pnpm.overrides na zależności przechodnie; apps/www next 15.4.4 → 16.3.2; wszystkie panele next 16.3.2; NestJS 11.2.1; React 19.2.8; Payload 3.88.0; recharts 3; @types/node 26; ioredis 6; bullmq 6; graphql 17; sharp 0.35.3; libs/typescript-config/nestjs.json target ES2022 + lib ES2023</t>
         </is>
       </c>
       <c r="K372" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L372" s="11" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M372" s="11" t="inlineStr">
@@ -27703,14 +27703,14 @@
       </c>
       <c r="N372" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy X-18. Next 16 usunęło komendę `next lint`, więc panele przeszły na płaską konfigurację i eslint wołany wprost. Nowszy eslint-config-next włącza reguły, których poprzednia konfiguracja nie egzekwowała — przede wszystkim rodzinę react-hooks z React Compilera. W panelu klienta odsłoniło to 105 znalezisk. | Osobno: apps/api i libs/directadmin-sdk wołały `eslint` BEZ ŻADNEJ konfiguracji w repozytorium — jedyny plik, libs/eslint-config/base.js, jest w starym formacie eslintrc i nic go nie importowało. Krok lintowania tych pakietów nie sprawdzał niczego. Dodana płaska konfiguracja node.mjs. | NAJWAŻNIEJSZE: nowe reguły wyłapały REALNY BUG. W admin-panel/autoscaling/pricing-table.tsx useMemo stał PO wczesnym return — przy pustej liście reguł hook nie wykonywał się wcale, a po dodaniu pierwszej stawki React widział inną liczbę hooków i komponent się wywalał. Czyli: panel cennika autoskalowania psuł się dokładnie w momencie dodania pierwszej reguły. Naprawione. Drugi: JSX konstruowany w try/catch w pulpicie admina — try nie chronił przed niczym, bo React renderuje zwrócony element po wyjściu z funkcji. | Reguły NIE są wyłączone, tylko obniżone do ostrzeżeń, z komentarzem wskazującym tę pozycję. Wracają na 'error' przy jej zamykaniu. | Wyjątek trwały: no-control-regex zostaje wyłączone — znaki sterujące w regexach walidacyjnych są zamierzone. no-useless-escape zostaje ostrzeżeniem świadomie: cztery wystąpienia siedzą w regexach walidujących wejście (kody promocyjne, ścieżki plików, załączniki), a zmiana regexa walidacyjnego przy okazji podnoszenia zależności to dokładnie ten rodzaj zmiany, który Z-03 kazał robić z testem na każdy przypadek.</t>
+          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md | KOREKTA 2026-08-22 (X-21): graphql cofnięty z ^17.0.2 do ^16.14.2 — jedynym konsumentem jest Payload 3.88, który deklaruje peera ^16.8.1, a nasz kod nie importuje graphql ani razu. Podniosłem major pod biblioteką, która go nie wspiera, bo wersja była wyższa — na PUBLICZNEJ stronie. Build www przechodzi na 16, ostrzeżenie o peerze znikło. | Domknięty body-parser override'em ^2.3.0: podatności 2 → 1 (została deepmerge-ts, wysoka, tylko przez Prismę 6 — znika z X-20). | engines.node podniesione z "&gt;=22" do "&gt;=22.12" — patrz X-21.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="11" t="inlineStr">
         <is>
-          <t>X-20</t>
+          <t>X-19</t>
         </is>
       </c>
       <c r="B373" s="12" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>Decyzja i migracja na Prismę 7</t>
+          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
         </is>
       </c>
       <c r="D373" s="11" t="inlineStr">
@@ -27750,17 +27750,17 @@
       </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J373" s="12" t="inlineStr">
         <is>
-          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
+          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
         </is>
       </c>
       <c r="K373" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L373" s="11" t="inlineStr">
@@ -27770,19 +27770,19 @@
       </c>
       <c r="M373" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N373" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy X-18, świadomie odłożone. Prisma 7 nie jest podniesieniem wersji, tylko zmianą architektury dostępu do bazy: właściwość `url` znika z datasource w schemacie i przenosi się do prisma.config.ts, a PrismaClient wymaga przekazania driver adaptera (@prisma/adapter-pg) albo adresu Accelerate. Sprawdzone realnie — `prisma generate` na 7.9.1 kończy się błędem P1012. | Dotyka: prisma.service.ts, libs/database/src/index.ts, seed, jobów CI, testów integracyjnych i sposobu, w jaki produkcja dostaje DATABASE_URL. Czyli każdej ścieżki do bazy naraz. | Argument za zrobieniem: zamyka ostatnią wysoką podatność (deepmerge-ts). Argument za odłożeniem: zmiana w warstwie danych na dwa sprinty przed startem sprzedaży, przy siedmiu otwartych blokerach, której nie da się w pełni zweryfikować lokalnie — binaries.prisma.sh jest poza listą dozwolonych hostów w obu moich środowiskach, więc jedyną weryfikacją byłoby CI. | Do zrobienia po starcie, z własnym sprintem i testem integracyjnym na każdej ścieżce zapisu.</t>
+          <t>Odkryte przy X-18. Next 16 usunęło komendę `next lint`, więc panele przeszły na płaską konfigurację i eslint wołany wprost. Nowszy eslint-config-next włącza reguły, których poprzednia konfiguracja nie egzekwowała — przede wszystkim rodzinę react-hooks z React Compilera. W panelu klienta odsłoniło to 105 znalezisk. | Osobno: apps/api i libs/directadmin-sdk wołały `eslint` BEZ ŻADNEJ konfiguracji w repozytorium — jedyny plik, libs/eslint-config/base.js, jest w starym formacie eslintrc i nic go nie importowało. Krok lintowania tych pakietów nie sprawdzał niczego. Dodana płaska konfiguracja node.mjs. | NAJWAŻNIEJSZE: nowe reguły wyłapały REALNY BUG. W admin-panel/autoscaling/pricing-table.tsx useMemo stał PO wczesnym return — przy pustej liście reguł hook nie wykonywał się wcale, a po dodaniu pierwszej stawki React widział inną liczbę hooków i komponent się wywalał. Czyli: panel cennika autoskalowania psuł się dokładnie w momencie dodania pierwszej reguły. Naprawione. Drugi: JSX konstruowany w try/catch w pulpicie admina — try nie chronił przed niczym, bo React renderuje zwrócony element po wyjściu z funkcji. | Reguły NIE są wyłączone, tylko obniżone do ostrzeżeń, z komentarzem wskazującym tę pozycję. Wracają na 'error' przy jej zamykaniu. | Wyjątek trwały: no-control-regex zostaje wyłączone — znaki sterujące w regexach walidacyjnych są zamierzone. no-useless-escape zostaje ostrzeżeniem świadomie: cztery wystąpienia siedzą w regexach walidujących wejście (kody promocyjne, ścieżki plików, załączniki), a zmiana regexa walidacyjnego przy okazji podnoszenia zależności to dokładnie ten rodzaj zmiany, który Z-03 kazał robić z testem na każdy przypadek.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="11" t="inlineStr">
         <is>
-          <t>X-21</t>
+          <t>X-20</t>
         </is>
       </c>
       <c r="B374" s="12" t="inlineStr">
@@ -27792,7 +27792,7 @@
       </c>
       <c r="C374" s="11" t="inlineStr">
         <is>
-          <t>Deklaracje typów opisują tę wersję biblioteki, która jest zainstalowana</t>
+          <t>Decyzja i migracja na Prismę 7</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
@@ -27822,39 +27822,39 @@
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J374" s="12" t="inlineStr">
         <is>
-          <t>apps/api/package.json — @types/archiver ^8.0.0 przy archiver ^8.0.0; apps/api/src/test/typy-zgodne-z-runtime.spec.ts — 12 testów; package.json — engines.node "&gt;=22.12"</t>
+          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
         </is>
       </c>
       <c r="K374" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L374" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="M374" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N374" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. BŁĄD PRODUKCYJNY znaleziony przy X-18, siedzący w kodzie PRZED podniesieniem. apps/api/package.json deklarował jednocześnie archiver ^8.0.0 i @types/archiver ^7.0.0. Archiver 8 usunął fabrykę create() na rzecz klas per format — kod wołał archiver.create('zip'/'tar'), typecheck był ZIELONY, bo typy z linii 7 tę funkcję opisywały, a w runtime jej nie było. Sprawdzone realnie: Object.keys(require('archiver')) = ['Archiver','JsonArchive','TarArchive','ZipArchive'], create === undefined. | CO TO PSUŁO: (1) data-export.service.ts → buildZipToFile — eksport danych osobowych (RODO art. 20, prawo do przenoszenia) wywalał się przy KAŻDYM żądaniu; (2) default-hosting-page.assets.ts → buildDefaultHostingPageBundle — budowa paczki domyślnej strony wywalała się przy KAŻDYM provisioningu konta. Nie „czasem" — zawsze, od momentu podniesienia archivera. | DLACZEGO NIKT TEGO NIE ZOBACZYŁ: typecheck czytał typy opisujące nieistniejącą wersję, żaden test nie dotykał tych dwóch funkcji, lint nie ma reguły na „ta metoda nie istnieje w runtime". Typecheck jest bramką wdrożenia — jeżeli typy opisują inną wersję niż zainstalowana, bramka przepuszcza kod, który się nie uruchomi, i robi to cicho, na zielono. | DRUGIE DNO: archiver 8 jest czystym ESM-em ("type": "module", brak wejścia CJS), a API kompiluje się do CommonJS-a. Node obsługuje require(esm) bez flagi dopiero od 22.12, a engines.node stał na "&gt;=22". Obrazy używają taga node:22 (dziś 22.22), więc realnie nic się nie paliło, ale deklaracja pozwalała na konfigurację, która by się paliła — ERR_REQUIRE_ESM w tych samych dwóch ścieżkach. Podniesione do "&gt;=22.12". | STRAŻNIK NA CAŁĄ KLASĘ, nie na sam archiver: żadne @types/X w monorepo nie może opisywać innego majora niż zainstalowany X. Test runtime'u wywołuje osobny proces Node'a (execFileSync), bo transformacja jesta nie ładuje zależności ESM i sprawdzałaby ładowarkę jesta zamiast produkcji. | Czerwieni się na starym kodzie: cofnięcie wszystkich trzech rzeczy daje 3 czerwone z 12, każdy z wykonalnym komunikatem. | Strażnik po raz TRZECI w tym projekcie trafił sam w siebie — szukana fraza padała w treści jego własnego komunikatu błędu (ta sama pułapka co polskie „jest" w X-17). Pominięty __filename + osobny test na spreparowanym wejściu. | PRZY OKAZJI: body-parser (niska, DoS przy cichym wyłączeniu limitu rozmiaru) domknięty override'em ^2.3.0 — podatności 2 → 1; graphql cofnięty z ^17.0.2 do ^16.14.2, bo jedynym konsumentem jest Payload 3.88 deklarujący peera ^16.8.1, a nasz kod nie importuje graphql ani razu — to korekta mojego własnego błędu z X-18: podniosłem wersję, bo była wyższa, nie sprawdzając, kto z niej korzysta. | Weryfikacja: 433 testy jednostkowe, 15 integracyjnych, lint 7/7, typecheck 8/8, build www. Dokumentacja: docs/zadania/X-21-typy-klamaly-o-runtime.md</t>
+          <t>Odkryte przy X-18, świadomie odłożone. Prisma 7 nie jest podniesieniem wersji, tylko zmianą architektury dostępu do bazy: właściwość `url` znika z datasource w schemacie i przenosi się do prisma.config.ts, a PrismaClient wymaga przekazania driver adaptera (@prisma/adapter-pg) albo adresu Accelerate. Sprawdzone realnie — `prisma generate` na 7.9.1 kończy się błędem P1012. | Dotyka: prisma.service.ts, libs/database/src/index.ts, seed, jobów CI, testów integracyjnych i sposobu, w jaki produkcja dostaje DATABASE_URL. Czyli każdej ścieżki do bazy naraz. | Argument za zrobieniem: zamyka ostatnią wysoką podatność (deepmerge-ts). Argument za odłożeniem: zmiana w warstwie danych na dwa sprinty przed startem sprzedaży, przy siedmiu otwartych blokerach, której nie da się w pełni zweryfikować lokalnie — binaries.prisma.sh jest poza listą dozwolonych hostów w obu moich środowiskach, więc jedyną weryfikacją byłoby CI. | Do zrobienia po starcie, z własnym sprintem i testem integracyjnym na każdej ścieżce zapisu.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="11" t="inlineStr">
         <is>
-          <t>X-22</t>
+          <t>X-21</t>
         </is>
       </c>
       <c r="B375" s="12" t="inlineStr">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>Eksport danych osobowych (RODO art. 20) sprawdzany testem end-to-end</t>
+          <t>Deklaracje typów opisują tę wersję biblioteki, która jest zainstalowana</t>
         </is>
       </c>
       <c r="D375" s="11" t="inlineStr">
@@ -27894,39 +27894,39 @@
       </c>
       <c r="I375" s="11" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
         <is>
-          <t>apps/api/src/compliance/data-export.service.ts — buildZipToFile bez żadnego testu; apps/api/src/compliance/*.spec.ts — brak pokrycia tej ścieżki</t>
+          <t>apps/api/package.json — @types/archiver ^8.0.0 przy archiver ^8.0.0; apps/api/src/test/typy-zgodne-z-runtime.spec.ts — 12 testów; package.json — engines.node "&gt;=22.12"</t>
         </is>
       </c>
       <c r="K375" s="11" t="inlineStr">
         <is>
-          <t>LUKA</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L375" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M375" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N375" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy X-21. Eksport danych osobowych wywalał się w runtime przy każdym żądaniu przez cały okres między podniesieniem archivera a 2026-08-22 i NIC tego nie zgłosiło — bo tej ścieżki nie dotyka żaden test. Strażnik z X-21 pilnuje teraz zgodności typów z runtime'em, ale to jest obejście od strony zależności, nie dowód, że eksport działa. | To jest OBOWIĄZEK USTAWOWY (RODO art. 20 — prawo do przenoszenia danych), z terminem miesiąca na odpowiedź. Ścieżka, której nie sprawdza nic, a której awaria jest naruszeniem, nie sprawdzeniem. | DO ZROBIENIA: test integracyjny, który zakłada konto z danymi w każdej sekcji (profil, subskrypcje, faktury, zgłoszenia, załączniki), wywołuje eksport, rozpakowuje wynikowy ZIP i sprawdza, że każda sekcja jest w środku i daje się sparsować. Plus ten sam wzorzec dla buildDefaultHostingPageBundle (tar.gz rozpakowany, index.html obecny). | Dopiero taki test daje D2. D3 wymaga wywołania eksportu na produkcji i obejrzenia pliku.</t>
+          <t>Zamknięte 2026-08-22. BŁĄD PRODUKCYJNY znaleziony przy X-18, siedzący w kodzie PRZED podniesieniem. apps/api/package.json deklarował jednocześnie archiver ^8.0.0 i @types/archiver ^7.0.0. Archiver 8 usunął fabrykę create() na rzecz klas per format — kod wołał archiver.create('zip'/'tar'), typecheck był ZIELONY, bo typy z linii 7 tę funkcję opisywały, a w runtime jej nie było. Sprawdzone realnie: Object.keys(require('archiver')) = ['Archiver','JsonArchive','TarArchive','ZipArchive'], create === undefined. | CO TO PSUŁO: (1) data-export.service.ts → buildZipToFile — eksport danych osobowych (RODO art. 20, prawo do przenoszenia) wywalał się przy KAŻDYM żądaniu; (2) default-hosting-page.assets.ts → buildDefaultHostingPageBundle — budowa paczki domyślnej strony wywalała się przy KAŻDYM provisioningu konta. Nie „czasem" — zawsze, od momentu podniesienia archivera. | DLACZEGO NIKT TEGO NIE ZOBACZYŁ: typecheck czytał typy opisujące nieistniejącą wersję, żaden test nie dotykał tych dwóch funkcji, lint nie ma reguły na „ta metoda nie istnieje w runtime". Typecheck jest bramką wdrożenia — jeżeli typy opisują inną wersję niż zainstalowana, bramka przepuszcza kod, który się nie uruchomi, i robi to cicho, na zielono. | DRUGIE DNO: archiver 8 jest czystym ESM-em ("type": "module", brak wejścia CJS), a API kompiluje się do CommonJS-a. Node obsługuje require(esm) bez flagi dopiero od 22.12, a engines.node stał na "&gt;=22". Obrazy używają taga node:22 (dziś 22.22), więc realnie nic się nie paliło, ale deklaracja pozwalała na konfigurację, która by się paliła — ERR_REQUIRE_ESM w tych samych dwóch ścieżkach. Podniesione do "&gt;=22.12". | STRAŻNIK NA CAŁĄ KLASĘ, nie na sam archiver: żadne @types/X w monorepo nie może opisywać innego majora niż zainstalowany X. Test runtime'u wywołuje osobny proces Node'a (execFileSync), bo transformacja jesta nie ładuje zależności ESM i sprawdzałaby ładowarkę jesta zamiast produkcji. | Czerwieni się na starym kodzie: cofnięcie wszystkich trzech rzeczy daje 3 czerwone z 12, każdy z wykonalnym komunikatem. | Strażnik po raz TRZECI w tym projekcie trafił sam w siebie — szukana fraza padała w treści jego własnego komunikatu błędu (ta sama pułapka co polskie „jest" w X-17). Pominięty __filename + osobny test na spreparowanym wejściu. | PRZY OKAZJI: body-parser (niska, DoS przy cichym wyłączeniu limitu rozmiaru) domknięty override'em ^2.3.0 — podatności 2 → 1; graphql cofnięty z ^17.0.2 do ^16.14.2, bo jedynym konsumentem jest Payload 3.88 deklarujący peera ^16.8.1, a nasz kod nie importuje graphql ani razu — to korekta mojego własnego błędu z X-18: podniosłem wersję, bo była wyższa, nie sprawdzając, kto z niej korzysta. | Weryfikacja: 433 testy jednostkowe, 15 integracyjnych, lint 7/7, typecheck 8/8, build www. Dokumentacja: docs/zadania/X-21-typy-klamaly-o-runtime.md</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="11" t="inlineStr">
         <is>
-          <t>X-23</t>
+          <t>X-22</t>
         </is>
       </c>
       <c r="B376" s="12" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="C376" s="11" t="inlineStr">
         <is>
-          <t>Bramka podatności zatrzymuje wdrożenie, a nie tylko dopisuje adnotację</t>
+          <t>Eksport danych osobowych (RODO art. 20) sprawdzany testem end-to-end</t>
         </is>
       </c>
       <c r="D376" s="11" t="inlineStr">
@@ -27966,49 +27966,49 @@
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="J376" s="12" t="inlineStr">
         <is>
-          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony; .github/dependabot.yml — 3 reguły ignore z terminem; apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów</t>
+          <t>apps/api/src/compliance/data-export.service.ts — buildZipToFile bez żadnego testu; apps/api/src/compliance/*.spec.ts — brak pokrycia tej ścieżki</t>
         </is>
       </c>
       <c r="K376" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>LUKA</t>
         </is>
       </c>
       <c r="L376" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M376" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N376" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #59 zielony w komplecie, sześć jobów, ZERO adnotacji błędu — krok „Bramka podatności" przeszedł bez continue-on-error, a adnotacja „Process completed with exit code 1", która towarzyszyła każdemu wcześniejszemu przebiegowi, zniknęła.</t>
+          <t>Odkryte przy X-21. Eksport danych osobowych wywalał się w runtime przy każdym żądaniu przez cały okres między podniesieniem archivera a 2026-08-22 i NIC tego nie zgłosiło — bo tej ścieżki nie dotyka żaden test. Strażnik z X-21 pilnuje teraz zgodności typów z runtime'em, ale to jest obejście od strony zależności, nie dowód, że eksport działa. | To jest OBOWIĄZEK USTAWOWY (RODO art. 20 — prawo do przenoszenia danych), z terminem miesiąca na odpowiedź. Ścieżka, której nie sprawdza nic, a której awaria jest naruszeniem, nie sprawdzeniem. | DO ZROBIENIA: test integracyjny, który zakłada konto z danymi w każdej sekcji (profil, subskrypcje, faktury, zgłoszenia, załączniki), wywołuje eksport, rozpakowuje wynikowy ZIP i sprawdza, że każda sekcja jest w środku i daje się sparsować. Plus ten sam wzorzec dla buildDefaultHostingPageBundle (tar.gz rozpakowany, index.html obecny). | Dopiero taki test daje D2. D3 wymaga wywołania eksportu na produkcji i obejrzenia pliku.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="11" t="inlineStr">
         <is>
-          <t>M-34</t>
+          <t>X-23</t>
         </is>
       </c>
       <c r="B377" s="12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C377" s="11" t="inlineStr">
         <is>
-          <t>Model prepaid potwierdzony z księgową — doładowanie bez faktury zaliczkowej</t>
+          <t>Bramka podatności zatrzymuje wdrożenie, a nie tylko dopisuje adnotację</t>
         </is>
       </c>
       <c r="D377" s="11" t="inlineStr">
@@ -28028,32 +28028,32 @@
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H377" s="11" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I377" s="11" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
         <is>
-          <t>faktura-za-portfel.ts — TYPY_SPRZEDAZY nie obejmuje TOPUP; billing.service.ts:handleCheckoutCompleted — doładowanie kredytuje portfel i nie tworzy dokumentu</t>
+          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony; .github/dependabot.yml — 3 reguły ignore z terminem; apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów</t>
         </is>
       </c>
       <c r="K377" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L377" s="11" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M377" s="11" t="inlineStr">
@@ -28063,24 +28063,24 @@
       </c>
       <c r="N377" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy Z-01, decyzja podjęta 2026-08-22 i WYMAGA POTWIERDZENIA. Przyjęliśmy model prepaid: doładowanie portfela nie jest sprzedażą, tylko wpłatą na poczet usług, więc nie generuje faktury; VAT powstaje przy świadczeniu usługi, czyli przy obciążeniu portfela, i tam idzie dokument. Klient dostaje potwierdzenie wpłaty mailem, nie fakturę. | RYZYKO: jeżeli środki z portfela dałoby się wydać wyłącznie na konkretną, z góry określoną usługę, organ podatkowy może uznać wpłatę za zaliczkę wymagającą faktury zaliczkowej (art. 106b ust. 1 pkt 4 ustawy o VAT). U nas środki są uniwersalne — idą na abonament, domeny, VPS, autoskalowanie i monitoring — co przemawia za modelem prepaid, ale to jest argument, nie rozstrzygnięcie. | DO ZROBIENIA PRZED STARTEM SPRZEDAŻY: potwierdzić model z księgową na piśmie i zapisać decyzję w repo z datą. Jeżeli wyjdzie, że potrzebne są faktury zaliczkowe, to osobny sprint: faktura końcowa musi odwoływać się do zaliczkowej i odejmować rozliczoną kwotę, a KSeF ma na to osobny typ dokumentu. | NIE jest to bloker w sensie kodu — mechanizm działa i jest spójny. Jest to bloker w sensie decyzji: sprzedaż ruszająca przy nierozstrzygniętym modelu podatkowym generuje dług, który rośnie z każdą wpłatą.</t>
+          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #59 zielony w komplecie, sześć jobów, ZERO adnotacji błędu — krok „Bramka podatności" przeszedł bez continue-on-error, a adnotacja „Process completed with exit code 1", która towarzyszyła każdemu wcześniejszemu przebiegowi, zniknęła.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="11" t="inlineStr">
         <is>
-          <t>X-24</t>
+          <t>M-34</t>
         </is>
       </c>
       <c r="B378" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C378" s="11" t="inlineStr">
         <is>
-          <t>Panel admina woła ścieżki, które API naprawdę wystawia</t>
+          <t>Model prepaid potwierdzony z księgową — doładowanie bez faktury zaliczkowej</t>
         </is>
       </c>
       <c r="D378" s="11" t="inlineStr">
@@ -28100,32 +28100,32 @@
       </c>
       <c r="G378" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="H378" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="J378" s="12" t="inlineStr">
         <is>
-          <t>apps/api/src/test/sciezki-panelu.spec.ts — 5 testów; porównuje wywołania adminApi() z panelu z trasami zadeklarowanymi w kontrolerach API</t>
+          <t>faktura-za-portfel.ts — TYPY_SPRZEDAZY nie obejmuje TOPUP; billing.service.ts:handleCheckoutCompleted — doładowanie kredytuje portfel i nie tworzy dokumentu</t>
         </is>
       </c>
       <c r="K378" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L378" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="M378" s="11" t="inlineStr">
@@ -28135,14 +28135,14 @@
       </c>
       <c r="N378" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy M-06. Formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna, a kontroler wystawia /admin/invoices/reczna. Kod się kompilował, testy jednostkowe przechodziły, panel się budował — 404 wyszłoby dopiero pod palcem operatora. | To ta sama rodzina co „bliźniacze miejsca", rozciągnięta na dwa pakiety: ścieżka zapisana dwa razy, w panelu i w kontrolerze, a nic ich nie łączy. Kompilator nie pomoże, bo po obu stronach to zwykły napis. | Strażnik wyciąga wywołania adminApi() z panelu i trasy z kontrolerów, porównuje kształt ścieżki i metodę HTTP. Segmenty dynamiczne (${id} w panelu, :id w kontrolerze) pasują do wszystkiego. | STRAŻNIK ZACZĄŁ OD JEDENASTU FAŁSZYWYCH ALARMÓW: (1) czytał 220 znaków po wywołaniu szukając `method:` i łapał metodę z NASTĘPNEGO wywołania — zwykły GET raportowany jako POST; (2) zamieniał wstawkę ${qs} na gwiazdkę w miejscu, produkując segment „webhooki*", który nie pasował do niczego; (3) grupował warianty ścieżki po wartości pochodnej zamiast po oryginale, więc wariant pełny zawsze zostawał sam i zawsze wyglądał na niepokryty. Jedenaście fałszywych alarmów przy dwóch prawdziwych znaleziskach. Strażnik, który tonie we własnym szumie, zostanie wyciszony — doprowadzenie do zera fałszywych alarmów było warunkiem działania, nie dopieszczaniem. | PIĄTE wystąpienie tej rodziny: „jest" (X-17), archiver.create (X-21), --audit-level (X-23), endsWith('billing.service.ts') (Z-05), teraz ścieżki panelu. | Czerwieni się na starym kodzie: przywrócenie błędnej ścieżki daje 1 czerwony z 5. | CZEGO NIE ROBI: nie sprawdza kształtu ciała żądania ani odpowiedzi — tylko ścieżkę i metodę; nie obejmuje panelu klienta ani panelu staff (te wołają inne bazowe adresy).</t>
+          <t>Odkryte przy Z-01, decyzja podjęta 2026-08-22 i WYMAGA POTWIERDZENIA. Przyjęliśmy model prepaid: doładowanie portfela nie jest sprzedażą, tylko wpłatą na poczet usług, więc nie generuje faktury; VAT powstaje przy świadczeniu usługi, czyli przy obciążeniu portfela, i tam idzie dokument. Klient dostaje potwierdzenie wpłaty mailem, nie fakturę. | RYZYKO: jeżeli środki z portfela dałoby się wydać wyłącznie na konkretną, z góry określoną usługę, organ podatkowy może uznać wpłatę za zaliczkę wymagającą faktury zaliczkowej (art. 106b ust. 1 pkt 4 ustawy o VAT). U nas środki są uniwersalne — idą na abonament, domeny, VPS, autoskalowanie i monitoring — co przemawia za modelem prepaid, ale to jest argument, nie rozstrzygnięcie. | DO ZROBIENIA PRZED STARTEM SPRZEDAŻY: potwierdzić model z księgową na piśmie i zapisać decyzję w repo z datą. Jeżeli wyjdzie, że potrzebne są faktury zaliczkowe, to osobny sprint: faktura końcowa musi odwoływać się do zaliczkowej i odejmować rozliczoną kwotę, a KSeF ma na to osobny typ dokumentu. | NIE jest to bloker w sensie kodu — mechanizm działa i jest spójny. Jest to bloker w sensie decyzji: sprzedaż ruszająca przy nierozstrzygniętym modelu podatkowym generuje dług, który rośnie z każdą wpłatą.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="11" t="inlineStr">
         <is>
-          <t>X-25</t>
+          <t>X-24</t>
         </is>
       </c>
       <c r="B379" s="12" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="C379" s="11" t="inlineStr">
         <is>
-          <t>Asercje po migracji biegną także na produkcji, z rollbackiem przy naruszeniu</t>
+          <t>Panel admina woła ścieżki, które API naprawdę wystawia</t>
         </is>
       </c>
       <c r="D379" s="11" t="inlineStr">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="J379" s="12" t="inlineStr">
         <is>
-          <t>ops/sql/po-migracji-niezmienniki.sql — CI I PRODUKCJA, 14 RAISE EXCEPTION (Z-01, Z-05, Z-12, Z-13, Z-16, M-06); ops/sql/po-migracji-katalog.sql — tylko CI, wartości z oferty; ops/sql/po-migracji-historia.sql — raport, ZERO RAISE EXCEPTION w kodzie; ops/scripts/prod-deploy-ghcr.sh:79-133 — krok 3.5 (bramka + rollback) i 3.6 (raport); .github/workflows/ci.yml — cztery kroki po seedzie; ops/scripts/asercje-czerwienia-sie.sh — 10 naruszeń, każde na właściwej asercji; apps/api/src/test/asercje-po-migracji.spec.ts (36). Usunięte: ops/sql/sprawdz-baze-po-migracji.sql</t>
+          <t>apps/api/src/test/sciezki-panelu.spec.ts — 5 testów; porównuje wywołania adminApi() z panelu z trasami zadeklarowanymi w kontrolerach API</t>
         </is>
       </c>
       <c r="K379" s="11" t="inlineStr">
@@ -28207,14 +28207,14 @@
       </c>
       <c r="N379" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: ZAMKNIĘTE. Sześć zamkniętych blokerów zostawiło plik asercji o stanie bazy po migracjach. Plik był porządny i biegł w JEDNYM miejscu: w CI, na świeżej bazie testowej — czyli dokładnie tam, gdzie nie ma prawdziwych danych. Produkcja po `prisma migrate deploy` nie była sprawdzana NICZYM; `migrate deploy` kończy się zerem, gdy pliki SQL się wykonały, i nie mówi nic o tym, czy baza jest po nich w stanie, w którym kod policzy dobrze. | DLACZEGO NIE DAŁO SIĘ PO PROSTU DOPISAĆ TEGO PLIKU DO DEPLOYU: część twierdzeń wywaliłaby wdrożenie bez powodu. Asercja „są plany prototypowe" dotyczy rzeczy, które tworzy SEED, a seed na produkcji nie biegnie. Gorsza była druga: pilnowała, żeby verris-hosting kosztował dokładnie 45,00 — a cenę WOLNO zmienić z panelu (plans.service.ts, updatePlan). Pierwsza legalna podwyżka zamieniłaby każde kolejne wdrożenie w rollback, a wtedy ktoś słusznie wyłączyłby całe sprawdzanie. Tego nie zauważyłem od razu — zobaczyłem dopiero, gdy własny strażnik zapalił się na isPublic i zamiast go poluzować sprawdziłem, czy cena jest edytowalna. Była. | TRZY PLIKI, TRZY RÓŻNE ŻYCIA: niezmienniki (CI i produkcja, blokują) — twierdzenia, których nie unieważni żadna legalna zmiana biznesowa; katalog (TYLKO CI) — dzisiejsza decyzja handlowa, w CI zmienia się w jednym commicie razem z PLAN_PRODUKCYJNY i treścią strony; historia (CI i produkcja, tylko raport) — dane sprzed migracji, których migracja nie naprawia i nie miała naprawiać; wycofanie wdrożenia z tego powodu byłoby karą za przeszłość, nie ochroną przed błędem. | Z Z-13 do niezmienników przeszły dwa twierdzenia, których panel nie może naruszyć: istnienie wiersza o slugu verris-hosting (slug stoi na sztywno w plan-produkcyjny.ts) oraz reguła cennika, którą API wymusza przy zapisie (ceny dodatnie, rok &gt;= 6x miesiąc) — API pilnuje jej przy zapisie, baza nie pilnuje wcale, a migracja danych zapisuje Z POMINIĘCIEM API. | JEDNA REGUŁA, JEDNO MIEJSCE: blok M-06 sprawdzał sumy korekty, które obejmuje już Z-01 (korekta to wiersz w Invoice) — druga kopia nigdy by nie wystartowała, a przy zmianie zasad ktoś poprawiłby jedną z dwóch. Usunięta. | DWIE CICHE PUŁAPKI W SAMYM WYWOŁANIU: `psql -U "${POSTGRES_USER:?}"` — przy pustej zmiennej psql połączyłby się z bazą o nazwie użytkownika i asercje przeszłyby na PUSTEJ, NIEWŁAŚCIWEJ bazie; `sh -c` zamiast `sh -lc` — skrypt profilu czytający stdin zjadłby SQL i psql dostałby pusty plik. | ASERCJA, KTÓRA SIĘ NIE CZERWIENI, NIE JEST BRAMKĄ: ops/scripts/asercje-czerwienia-sie.sh psuje po jednym niezmienniku naraz w transakcji z ROLLBACK-iem i sprawdza DWIE rzeczy — kod wyjścia różny od zera ORAZ że powodem jest TA asercja. Drugi warunek nie jest ozdobą: w pierwszym przebiegu trzy przypadki M-06 świeciły na czerwono, a naprawdę odbijał je CHECK w bazie, zanim asercja zdążyła cokolwiek zobaczyć (ta sama lekcja co Z-01 i H-20). | Czerwieni się na starym kodzie: jeden plik + brak asercji w deployu → 11 z 36; `|| true` zamiast bramki → 1; RAISE EXCEPTION w pliku historii → 1; katalog wpuszczony na produkcję → 1. | CZEGO NIE ROBI: nie cofa schematu (rollback wraca do poprzedniego obrazu, migracje zostają); nie sprawdza katalogu na produkcji — cena może się tam rozjechać z PLAN_PRODUKCYJNY i deploy tego nie zauważy (to bliżej monitoringu niż bramki); asercje-czerwienia-sie.sh NIE WOLNO uruchamiać na produkcji, bo zdejmuje ograniczenia CHECK wewnątrz transakcji. | D3 powstanie przy pierwszym deployu na main, w logu wdrożenia, z datą. Dokumentacja: docs/zadania/X-25-asercje-po-migracji.md</t>
+          <t>Odkryte przy M-06. Formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna, a kontroler wystawia /admin/invoices/reczna. Kod się kompilował, testy jednostkowe przechodziły, panel się budował — 404 wyszłoby dopiero pod palcem operatora. | To ta sama rodzina co „bliźniacze miejsca", rozciągnięta na dwa pakiety: ścieżka zapisana dwa razy, w panelu i w kontrolerze, a nic ich nie łączy. Kompilator nie pomoże, bo po obu stronach to zwykły napis. | Strażnik wyciąga wywołania adminApi() z panelu i trasy z kontrolerów, porównuje kształt ścieżki i metodę HTTP. Segmenty dynamiczne (${id} w panelu, :id w kontrolerze) pasują do wszystkiego. | STRAŻNIK ZACZĄŁ OD JEDENASTU FAŁSZYWYCH ALARMÓW: (1) czytał 220 znaków po wywołaniu szukając `method:` i łapał metodę z NASTĘPNEGO wywołania — zwykły GET raportowany jako POST; (2) zamieniał wstawkę ${qs} na gwiazdkę w miejscu, produkując segment „webhooki*", który nie pasował do niczego; (3) grupował warianty ścieżki po wartości pochodnej zamiast po oryginale, więc wariant pełny zawsze zostawał sam i zawsze wyglądał na niepokryty. Jedenaście fałszywych alarmów przy dwóch prawdziwych znaleziskach. Strażnik, który tonie we własnym szumie, zostanie wyciszony — doprowadzenie do zera fałszywych alarmów było warunkiem działania, nie dopieszczaniem. | PIĄTE wystąpienie tej rodziny: „jest" (X-17), archiver.create (X-21), --audit-level (X-23), endsWith('billing.service.ts') (Z-05), teraz ścieżki panelu. | Czerwieni się na starym kodzie: przywrócenie błędnej ścieżki daje 1 czerwony z 5. | CZEGO NIE ROBI: nie sprawdza kształtu ciała żądania ani odpowiedzi — tylko ścieżkę i metodę; nie obejmuje panelu klienta ani panelu staff (te wołają inne bazowe adresy).</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="11" t="inlineStr">
         <is>
-          <t>X-26</t>
+          <t>X-25</t>
         </is>
       </c>
       <c r="B380" s="12" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="C380" s="11" t="inlineStr">
         <is>
-          <t>Skrypty powłoki mają bit wykonywalności — także po świeżym git clone</t>
+          <t>Asercje po migracji biegną także na produkcji, z rollbackiem przy naruszeniu</t>
         </is>
       </c>
       <c r="D380" s="11" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="J380" s="12" t="inlineStr">
         <is>
-          <t>apps/api/src/test/skrypty-wykonywalne.spec.ts (3) — żaden .sh w repozytorium bez bitu wykonywalności; 82 skrypty przestawione na tryb 100755 (16 z nich miało 100644, w tym restore-drill-isolated.sh z bramki startu i pięć uruchamianych na węzłach produkcyjnych); docs/ops/RESTORE_TEST.md — usunięte obejście `chmod +x` sprzed uruchomienia</t>
+          <t>ops/sql/po-migracji-niezmienniki.sql — CI I PRODUKCJA, 14 RAISE EXCEPTION (Z-01, Z-05, Z-12, Z-13, Z-16, M-06); ops/sql/po-migracji-katalog.sql — tylko CI, wartości z oferty; ops/sql/po-migracji-historia.sql — raport, ZERO RAISE EXCEPTION w kodzie; ops/scripts/prod-deploy-ghcr.sh:79-133 — krok 3.5 (bramka + rollback) i 3.6 (raport); .github/workflows/ci.yml — cztery kroki po seedzie; ops/scripts/asercje-czerwienia-sie.sh — 10 naruszeń, każde na właściwej asercji; apps/api/src/test/asercje-po-migracji.spec.ts (36). Usunięte: ops/sql/sprawdz-baze-po-migracji.sql</t>
         </is>
       </c>
       <c r="K380" s="11" t="inlineStr">
@@ -28279,14 +28279,14 @@
       </c>
       <c r="N380" s="12" t="inlineStr">
         <is>
-          <t>Odkryte przy X-25, dzień po zamknięciu mechanizmu H-20. Runbook, dokumentacja zadania i MAIL PRZYPOMINAJĄCY do administratora mówią jednym głosem: `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "…"` — a plik miał w gicie tryb 100644. Na świeżym `git clone` to polecenie kończy się „Permission denied". Czyli procedura, którą właśnie zamieniliśmy w bramkę startu sprzedaży, nie dawała się wykonać w sposób, w jaki sama każe siebie wykonywać. | Szesnaście skryptów miało ten sam problem, w tym pięć uruchamianych na węzłach produkcyjnych (node-app-install, node-db-upgrade, node-offsite-backup, node-php-apply, node-wp-install). | ŚLAD PO TYM BŁĘDZIE LEŻAŁ W REPOZYTORIUM OD DAWNA: docs/ops/RESTORE_TEST.md kazał wpisać `chmod +x` PRZED uruchomieniem, a Dockerfile.api robi `chmod +x` na entrypoincie. Obejścia działały, więc nikt nie naprawił przyczyny — a każde z nich było zapisanym w repozytorium dowodem, że przyczyna istnieje. To jest ten sam kształt co „bramka, która raportuje zamiast bramkować": objaw obsłużony, przyczyna zostaje. | REGUŁA JEST BEZWYJĄTKOWA i to jest jej najważniejsza cecha. Lista „te skrypty wolno mieć nieuruchamialne, bo woła je bash" musiałaby być utrzymywana obok prawdziwych wywołań, czyli byłaby kolejnym wystąpieniem bliźniaczych miejsc (Z-12, Z-16, M-06, X-24). Skrypt wykonywalny działa pod `bash x.sh` tak samo dobrze, więc reguła bez wyjątków nic nie kosztuje. | Strażnik czyta TRYB Z DYSKU, nie z indeksu gita: liczy się to, co dostaje maszyna po `git clone`, a actions/checkout wypisuje pliki dokładnie z trybami z indeksu. Czytanie dysku działa też tam, gdzie kopia robocza nie jest repozytorium, i nie wymaga drugiej ścieżki kodu na wypadek braku gita. | Ma też kontrolę „strażnik w ogóle coś widzi" (ponad 50 skryptów, w tym ten z bramki startu) — bez niej cała reszta przechodziłaby trywialnie na pustej liście, gdyby `find` przestał trafiać. | Czerwieni się na starym kodzie: 1 z 3 testów, z wypisaną listą wszystkich szesnastu plików. | CZEGO NIE ROBI: nie sprawdza shebangów ani tego, czy skrypt w ogóle da się uruchomić — tylko bit wykonywalności.</t>
+          <t>Stan 2026-08-22: ZAMKNIĘTE. Sześć zamkniętych blokerów zostawiło plik asercji o stanie bazy po migracjach. Plik był porządny i biegł w JEDNYM miejscu: w CI, na świeżej bazie testowej — czyli dokładnie tam, gdzie nie ma prawdziwych danych. Produkcja po `prisma migrate deploy` nie była sprawdzana NICZYM; `migrate deploy` kończy się zerem, gdy pliki SQL się wykonały, i nie mówi nic o tym, czy baza jest po nich w stanie, w którym kod policzy dobrze. | DLACZEGO NIE DAŁO SIĘ PO PROSTU DOPISAĆ TEGO PLIKU DO DEPLOYU: część twierdzeń wywaliłaby wdrożenie bez powodu. Asercja „są plany prototypowe" dotyczy rzeczy, które tworzy SEED, a seed na produkcji nie biegnie. Gorsza była druga: pilnowała, żeby verris-hosting kosztował dokładnie 45,00 — a cenę WOLNO zmienić z panelu (plans.service.ts, updatePlan). Pierwsza legalna podwyżka zamieniłaby każde kolejne wdrożenie w rollback, a wtedy ktoś słusznie wyłączyłby całe sprawdzanie. Tego nie zauważyłem od razu — zobaczyłem dopiero, gdy własny strażnik zapalił się na isPublic i zamiast go poluzować sprawdziłem, czy cena jest edytowalna. Była. | TRZY PLIKI, TRZY RÓŻNE ŻYCIA: niezmienniki (CI i produkcja, blokują) — twierdzenia, których nie unieważni żadna legalna zmiana biznesowa; katalog (TYLKO CI) — dzisiejsza decyzja handlowa, w CI zmienia się w jednym commicie razem z PLAN_PRODUKCYJNY i treścią strony; historia (CI i produkcja, tylko raport) — dane sprzed migracji, których migracja nie naprawia i nie miała naprawiać; wycofanie wdrożenia z tego powodu byłoby karą za przeszłość, nie ochroną przed błędem. | Z Z-13 do niezmienników przeszły dwa twierdzenia, których panel nie może naruszyć: istnienie wiersza o slugu verris-hosting (slug stoi na sztywno w plan-produkcyjny.ts) oraz reguła cennika, którą API wymusza przy zapisie (ceny dodatnie, rok &gt;= 6x miesiąc) — API pilnuje jej przy zapisie, baza nie pilnuje wcale, a migracja danych zapisuje Z POMINIĘCIEM API. | JEDNA REGUŁA, JEDNO MIEJSCE: blok M-06 sprawdzał sumy korekty, które obejmuje już Z-01 (korekta to wiersz w Invoice) — druga kopia nigdy by nie wystartowała, a przy zmianie zasad ktoś poprawiłby jedną z dwóch. Usunięta. | DWIE CICHE PUŁAPKI W SAMYM WYWOŁANIU: `psql -U "${POSTGRES_USER:?}"` — przy pustej zmiennej psql połączyłby się z bazą o nazwie użytkownika i asercje przeszłyby na PUSTEJ, NIEWŁAŚCIWEJ bazie; `sh -c` zamiast `sh -lc` — skrypt profilu czytający stdin zjadłby SQL i psql dostałby pusty plik. | ASERCJA, KTÓRA SIĘ NIE CZERWIENI, NIE JEST BRAMKĄ: ops/scripts/asercje-czerwienia-sie.sh psuje po jednym niezmienniku naraz w transakcji z ROLLBACK-iem i sprawdza DWIE rzeczy — kod wyjścia różny od zera ORAZ że powodem jest TA asercja. Drugi warunek nie jest ozdobą: w pierwszym przebiegu trzy przypadki M-06 świeciły na czerwono, a naprawdę odbijał je CHECK w bazie, zanim asercja zdążyła cokolwiek zobaczyć (ta sama lekcja co Z-01 i H-20). | Czerwieni się na starym kodzie: jeden plik + brak asercji w deployu → 11 z 36; `|| true` zamiast bramki → 1; RAISE EXCEPTION w pliku historii → 1; katalog wpuszczony na produkcję → 1. | CZEGO NIE ROBI: nie cofa schematu (rollback wraca do poprzedniego obrazu, migracje zostają); nie sprawdza katalogu na produkcji — cena może się tam rozjechać z PLAN_PRODUKCYJNY i deploy tego nie zauważy (to bliżej monitoringu niż bramki); asercje-czerwienia-sie.sh NIE WOLNO uruchamiać na produkcji, bo zdejmuje ograniczenia CHECK wewnątrz transakcji. | D3 powstanie przy pierwszym deployu na main, w logu wdrożenia, z datą. Dokumentacja: docs/zadania/X-25-asercje-po-migracji.md</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="11" t="inlineStr">
         <is>
-          <t>X-27</t>
+          <t>X-26</t>
         </is>
       </c>
       <c r="B381" s="12" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="C381" s="11" t="inlineStr">
         <is>
-          <t>Obraz, który trafia na serwer, buduje się przed scaleniem</t>
+          <t>Skrypty powłoki mają bit wykonywalności — także po świeżym git clone</t>
         </is>
       </c>
       <c r="D381" s="11" t="inlineStr">
@@ -28331,7 +28331,7 @@
       </c>
       <c r="J381" s="12" t="inlineStr">
         <is>
-          <t>Dockerfile.api / Dockerfile.panel — ponowna instalacja PO `COPY libs libs`; package.json — pnpm.overrides @prisma/client 6.19.3 (drzewo znów ma jedną wersję); .github/workflows/ci.yml — job `Obraz API (build bez push)`; apps/api/src/test/obrazy-dockera.spec.ts (14). Przyczyna deployu #63: „Could not resolve @prisma/client"</t>
+          <t>apps/api/src/test/skrypty-wykonywalne.spec.ts (3) — żaden .sh w repozytorium bez bitu wykonywalności; 82 skrypty przestawione na tryb 100755 (16 z nich miało 100644, w tym restore-drill-isolated.sh z bramki startu i pięć uruchamianych na węzłach produkcyjnych); docs/ops/RESTORE_TEST.md — usunięte obejście `chmod +x` sprzed uruchomienia</t>
         </is>
       </c>
       <c r="K381" s="11" t="inlineStr">
@@ -28351,14 +28351,14 @@
       </c>
       <c r="N381" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, wykryte przez wdrożenie #63 — pierwsze po scaleniu sprintu 2. Wysypał się build obrazu verris-api, czyli krok PRZED dotknięciem serwera: produkcja została nietknięta, migracje nie poszły. | DWIE PRZYCZYNY, NIE JEDNA. (1) `COPY libs libs` w etapie budowania kładzie katalogi pakietów na te, które zostawił etap `deps`, i pakiet traci WŁASNE node_modules. Dopóki każda zależność lądowała w node_modules katalogu głównego (linker hoisted), nie było tego widać — założenie trzymało się PRZYPADKIEM. (2) Przestało być prawdą przy X-18: apps/www podniosło Payloada, jego adapter postgresowy ciągnie drizzle-orm, a to ma @prisma/client jako peer OPCJONALNY; pnpm dociąga takie peery samo (autoInstallPeers), więc w drzewie stanęły DWIE wersje — 7.9.1 na górze i nasza 6.19.3 w libs/database. Po COPY zostawała tylko ta z góry, a `prisma generate` z CLI 6.19.3 nie umie pracować z klientem 7.x. | Poprawki są dwie, bo błędy są dwa: pnpm.overrides sprowadza drzewo do jednej wersji klienta (to naprawia TEN przypadek i chroni też obraz runtime, który kopiuje node_modules katalogu głównego), a ponowna instalacja w obrazach znosi założenie o hoistowaniu (to chroni przed następnym pakietem w dwóch wersjach). Dockerfile.panel dostał tę samą poprawkę mimo że jeszcze nie wybuchł — naprawiona jedna kopia i zostawiona druga to wzorzec, który dał Z-12, Z-16 i X-24. | NAJWAŻNIEJSZE ZNALEZISKO STRUKTURALNE: obraz, który JAKO JEDYNY trafia na serwer, powstawał wyłącznie w workflow wdrożeniowym — czyli PO scaleniu do main. Bramka scalenia sprawdzała lint, typy, 605 testów, migracje i asercje bazy, i nie sprawdzała tej jednej rzeczy. `pnpm build` w repozytorium przechodzi, bo tam node_modules są kompletne; rozjeżdżało się wyłącznie w układzie plików wewnątrz obrazu. Dlatego CI dostało job budujący Dockerfile.api bez pushowania. | DWA RAZY UWIERZYŁEM W WYNIK, KTÓRY NICZEGO NIE DOWODZIŁ: raz pnpm nie przeliczył lockfile'a i override wyglądał na nieskuteczny; raz uproszczone repozytorium testowe nie zawierało package.json apps/www, czyli pakietu ciągnącego 7.9.1 — więc wynik wyglądał dobrze z niewłaściwego powodu. Rozstrzygnięte dopiero na pełnym drzewie zależności. Ta sama rodzina co Z-01 i H-20. | Czerwieni się na starym kodzie: 7 z 14. | CZEGO NIE ROBI: CI nie buduje obrazów paneli (własny Dockerfile, ~2,5 min każdy, bez Prismy) — jeżeli kiedyś wywali się panel, job dostanie drugą pozycję w macierzy, a nie listę wyjątków. Dokumentacja: docs/zadania/X-27-obraz-api-w-ci.md</t>
+          <t>Odkryte przy X-25, dzień po zamknięciu mechanizmu H-20. Runbook, dokumentacja zadania i MAIL PRZYPOMINAJĄCY do administratora mówią jednym głosem: `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "…"` — a plik miał w gicie tryb 100644. Na świeżym `git clone` to polecenie kończy się „Permission denied". Czyli procedura, którą właśnie zamieniliśmy w bramkę startu sprzedaży, nie dawała się wykonać w sposób, w jaki sama każe siebie wykonywać. | Szesnaście skryptów miało ten sam problem, w tym pięć uruchamianych na węzłach produkcyjnych (node-app-install, node-db-upgrade, node-offsite-backup, node-php-apply, node-wp-install). | ŚLAD PO TYM BŁĘDZIE LEŻAŁ W REPOZYTORIUM OD DAWNA: docs/ops/RESTORE_TEST.md kazał wpisać `chmod +x` PRZED uruchomieniem, a Dockerfile.api robi `chmod +x` na entrypoincie. Obejścia działały, więc nikt nie naprawił przyczyny — a każde z nich było zapisanym w repozytorium dowodem, że przyczyna istnieje. To jest ten sam kształt co „bramka, która raportuje zamiast bramkować": objaw obsłużony, przyczyna zostaje. | REGUŁA JEST BEZWYJĄTKOWA i to jest jej najważniejsza cecha. Lista „te skrypty wolno mieć nieuruchamialne, bo woła je bash" musiałaby być utrzymywana obok prawdziwych wywołań, czyli byłaby kolejnym wystąpieniem bliźniaczych miejsc (Z-12, Z-16, M-06, X-24). Skrypt wykonywalny działa pod `bash x.sh` tak samo dobrze, więc reguła bez wyjątków nic nie kosztuje. | Strażnik czyta TRYB Z DYSKU, nie z indeksu gita: liczy się to, co dostaje maszyna po `git clone`, a actions/checkout wypisuje pliki dokładnie z trybami z indeksu. Czytanie dysku działa też tam, gdzie kopia robocza nie jest repozytorium, i nie wymaga drugiej ścieżki kodu na wypadek braku gita. | Ma też kontrolę „strażnik w ogóle coś widzi" (ponad 50 skryptów, w tym ten z bramki startu) — bez niej cała reszta przechodziłaby trywialnie na pustej liście, gdyby `find` przestał trafiać. | Czerwieni się na starym kodzie: 1 z 3 testów, z wypisaną listą wszystkich szesnastu plików. | CZEGO NIE ROBI: nie sprawdza shebangów ani tego, czy skrypt w ogóle da się uruchomić — tylko bit wykonywalności.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="11" t="inlineStr">
         <is>
-          <t>X-28</t>
+          <t>X-27</t>
         </is>
       </c>
       <c r="B382" s="12" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C382" s="11" t="inlineStr">
         <is>
-          <t>Reguła alertowa ma odbiorcę, a nie tylko próg</t>
+          <t>Obraz, który trafia na serwer, buduje się przed scaleniem</t>
         </is>
       </c>
       <c r="D382" s="11" t="inlineStr">
@@ -28403,7 +28403,7 @@
       </c>
       <c r="J382" s="12" t="inlineStr">
         <is>
-          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — 13 reguł, 2 grupy, provisionowane z repo; ops/observability/prometheus.yml — bez rule_files, z opisem dlaczego; ops/observability/grafana/provisioning/datasources/datasources.yml — uid: Prometheus; docker-compose.prod.yml — bez montowania usuniętego alerts.yml; ops/observability/grafana/migracja-regul-do-grafany.py — zapis, jak powstał wynik; apps/api/src/test/routing-alertow.spec.ts (31); docs/ops/GRAFANA_ALERTING.md</t>
+          <t>Dockerfile.api / Dockerfile.panel — ponowna instalacja PO `COPY libs libs`; package.json — pnpm.overrides @prisma/client 6.19.3 (drzewo znów ma jedną wersję); .github/workflows/ci.yml — job `Obraz API (build bez push)`; apps/api/src/test/obrazy-dockera.spec.ts (14). Przyczyna deployu #63: „Could not resolve @prisma/client"</t>
         </is>
       </c>
       <c r="K382" s="11" t="inlineStr">
@@ -28423,14 +28423,14 @@
       </c>
       <c r="N382" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md | DOWÓD D3 DOSTARCZALNOŚCI — 2026-08-23, dostarczony przez awarię, nie przez test. Przy X-30 reguły z execErrState: Alerting zapaliły się na błędzie ewaluacji i DZIESIĘĆ maili dotarło na dominik@hvln.pl z tematami [FIRING:1] &lt;alertname&gt; &lt;severity&gt; (Verris). Droga Grafana → SMTP → Postfix na panelu → mail.hvln.pl → skrzynka jest potwierdzona na całej długości. | TEN PRZYPADEK POTWIERDZIŁ TRZY RZECZY, KTÓRYCH PLANOWANY TEST JEDNEGO ALERTU BY NIE POTWIERDZIŁ: (1) droga do skrzynki działa; (2) migracja nie pogubiła nazw ani wag — tematy pokazały critical przy VerrisRuntimeErrorsHigh, VerrisOpenMajorIncident, VerrisSecurityWatchFindings i VerrisProvisioningQueueFailed oraz warning przy pozostałych, dokładnie jak w usuniętym alerts.yml; (3) progi `for:` przetrwały migrację — zapaliło się DZIESIĘĆ z trzynastu, a nie zapaliły się dokładnie te trzy z najdłuższym for: VerrisPostgresBackupStale (30 m), VerrisStatusWebhookFailed (30 m) i VerrisSecurityWatchStale (20 m), bo od restartu nie minęło tyle czasu. Skrypt migracyjny mógł te wartości po cichu przekręcić i żaden test w CI by tego nie zobaczył — zobaczyła to skrzynka.</t>
+          <t>Zamknięte 2026-08-22, wykryte przez wdrożenie #63 — pierwsze po scaleniu sprintu 2. Wysypał się build obrazu verris-api, czyli krok PRZED dotknięciem serwera: produkcja została nietknięta, migracje nie poszły. | DWIE PRZYCZYNY, NIE JEDNA. (1) `COPY libs libs` w etapie budowania kładzie katalogi pakietów na te, które zostawił etap `deps`, i pakiet traci WŁASNE node_modules. Dopóki każda zależność lądowała w node_modules katalogu głównego (linker hoisted), nie było tego widać — założenie trzymało się PRZYPADKIEM. (2) Przestało być prawdą przy X-18: apps/www podniosło Payloada, jego adapter postgresowy ciągnie drizzle-orm, a to ma @prisma/client jako peer OPCJONALNY; pnpm dociąga takie peery samo (autoInstallPeers), więc w drzewie stanęły DWIE wersje — 7.9.1 na górze i nasza 6.19.3 w libs/database. Po COPY zostawała tylko ta z góry, a `prisma generate` z CLI 6.19.3 nie umie pracować z klientem 7.x. | Poprawki są dwie, bo błędy są dwa: pnpm.overrides sprowadza drzewo do jednej wersji klienta (to naprawia TEN przypadek i chroni też obraz runtime, który kopiuje node_modules katalogu głównego), a ponowna instalacja w obrazach znosi założenie o hoistowaniu (to chroni przed następnym pakietem w dwóch wersjach). Dockerfile.panel dostał tę samą poprawkę mimo że jeszcze nie wybuchł — naprawiona jedna kopia i zostawiona druga to wzorzec, który dał Z-12, Z-16 i X-24. | NAJWAŻNIEJSZE ZNALEZISKO STRUKTURALNE: obraz, który JAKO JEDYNY trafia na serwer, powstawał wyłącznie w workflow wdrożeniowym — czyli PO scaleniu do main. Bramka scalenia sprawdzała lint, typy, 605 testów, migracje i asercje bazy, i nie sprawdzała tej jednej rzeczy. `pnpm build` w repozytorium przechodzi, bo tam node_modules są kompletne; rozjeżdżało się wyłącznie w układzie plików wewnątrz obrazu. Dlatego CI dostało job budujący Dockerfile.api bez pushowania. | DWA RAZY UWIERZYŁEM W WYNIK, KTÓRY NICZEGO NIE DOWODZIŁ: raz pnpm nie przeliczył lockfile'a i override wyglądał na nieskuteczny; raz uproszczone repozytorium testowe nie zawierało package.json apps/www, czyli pakietu ciągnącego 7.9.1 — więc wynik wyglądał dobrze z niewłaściwego powodu. Rozstrzygnięte dopiero na pełnym drzewie zależności. Ta sama rodzina co Z-01 i H-20. | Czerwieni się na starym kodzie: 7 z 14. | CZEGO NIE ROBI: CI nie buduje obrazów paneli (własny Dockerfile, ~2,5 min każdy, bez Prismy) — jeżeli kiedyś wywali się panel, job dostanie drugą pozycję w macierzy, a nie listę wyjątków. Dokumentacja: docs/zadania/X-27-obraz-api-w-ci.md</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="11" t="inlineStr">
         <is>
-          <t>X-29</t>
+          <t>X-28</t>
         </is>
       </c>
       <c r="B383" s="12" t="inlineStr">
@@ -28440,7 +28440,7 @@
       </c>
       <c r="C383" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie dowozi konfigurację obserwowalności na serwer</t>
+          <t>Reguła alertowa ma odbiorcę, a nie tylko próg</t>
         </is>
       </c>
       <c r="D383" s="11" t="inlineStr">
@@ -28475,7 +28475,7 @@
       </c>
       <c r="J383" s="12" t="inlineStr">
         <is>
-          <t>ops/scripts/prod-deploy-ghcr.sh — krok 4.5: OBS_SERVICES, promtool check config przed restartem, compose up -d + compose restart, sprawdzenie /api/health i /-/healthy po restarcie, exit 1 gdy nie wrócą; apps/api/src/test/wdrozenie-obserwowalnosci.spec.ts (8)</t>
+          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — 13 reguł, 2 grupy, provisionowane z repo; ops/observability/prometheus.yml — bez rule_files, z opisem dlaczego; ops/observability/grafana/provisioning/datasources/datasources.yml — uid: Prometheus; docker-compose.prod.yml — bez montowania usuniętego alerts.yml; ops/observability/grafana/migracja-regul-do-grafany.py — zapis, jak powstał wynik; apps/api/src/test/routing-alertow.spec.ts (31); docs/ops/GRAFANA_ALERTING.md</t>
         </is>
       </c>
       <c r="K383" s="11" t="inlineStr">
@@ -28495,14 +28495,14 @@
       </c>
       <c r="N383" s="12" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-23. Wykryte przy X-28, pytaniem kontrolnym: co się właściwie stanie po wdrożeniu poprawki, która przenosi reguły alertowe do Grafany? Odpowiedź: NIC. | MECHANIZM: prod-deploy-ghcr.sh robi na serwerze checkout repozytorium do wdrażanego SHA, więc nowe pliki lądują na dysku — po czym restartuje wyłącznie APP_SERVICES="api client-panel staff-panel admin-panel status-page www". Prometheusa i Grafany na tej liście nie ma, a oba czytają konfigurację TYLKO przy starcie kontenera i oba mają ją podmontowaną z repozytorium. | ZASIĘG SZERSZY NIŻ ALERTY: tą samą drogą nie docierało na produkcję wszystko pod ops/observability/ — cele scrapowania i retencja w prometheus.yml, źródła danych, dwadzieścia kilka dashboardów Grafany, punkty kontaktowe i polityki. Każda zmiana w tych plikach od ostatniego RĘCZNEGO restartu Grafany istniała wyłącznie w repozytorium. | RODZINA: ten sam kształt co X-28 (alarm bez odbiorcy), X-14 i X-23 (kontrola, która melduje zamiast zatrzymywać) i H-20 (procedura bez dowodu wykonania) — COŚ WYGLĄDA NA ZROBIONE, BO ISTNIEJE. Zielone CI, zielony deploy, plik na dysku, pozycja zamknięta — i zero zmiany w działającym systemie. Różnica: tu zawodziło ostatnie ogniwo, nie budowa ani test, tylko DOSTARCZENIE. | POPRAWKA: krok 4.5, dwa polecenia zamiast jednego. `up -d` odtwarza kontener, gdy zmieniła się DEFINICJA usługi (X-28 usunęło montowanie alerts.yml); `restart` wymusza ponowne wczytanie, gdy zmieniła się tylko TREŚĆ podmontowanego pliku — tego compose nie widzi. | BEZWARUNKOWO, nie „gdy się zmieniło": porównanie z poprzednim SHA wymagałoby obu wersji w repozytorium na serwerze, a fetch jest tam płytki (--depth 1); nieudane porównanie skończyłoby się cichym „brak zmian → nie restartuj", czyli dokładnie tym błędem, który ta pozycja naprawia. Kilkanaście sekund przerwy w metrykach kontra miesiąc bez kopii bazy. | SPRAWDZENIE PRZED: promtool check config przez `compose run --rm --no-deps --entrypoint promtool`, a nie `exec` — świeży kontener z tą samą definicją, więc sprawdzenie działa także wtedy, gdy Prometheus akurat leży; przy `exec` padałoby w jedynym momencie, w którym naprawdę zależy nam na restarcie. Restart na zepsutej konfiguracji zdejmuje monitoring, a zauważyć to miał właśnie monitoring. | SPRAWDZENIE PO: „wydałem polecenie restartu" to nie to samo co „wróciły" — /api/health Grafany i /-/healthy Prometheusa (pytany Z KONTENERA Grafany, bo obraz Prometheusa nie ma czym wykonać zapytania HTTP), 20 prób co 3 s, potem exit 1. | KOLEJNOŚĆ W DWIE STRONY: krok jest PO bramce zdrowia i PO zapisaniu .last-good-image-tag, żeby awaria monitoringu nie wywróciła sprawnego wdrożenia; kończy się exit 1, a nie ostrzeżeniem, żeby wdrożenie nie uchodziło za skończone, zanim monitoring dostanie nową konfigurację. | Czerwieni się na starym kodzie: 6 z 8. Dwie przechodziły i przedtem — w tym ta o APP_SERVICES, bo Prometheusa i Grafany naprawdę tam nie było (tyle że nie było ich też nigdzie indziej). | CZEGO NIE DOWODZI: że po najbliższym wdrożeniu Grafana MA reguły — to obserwacja na produkcji (D3): Alerting → Alert rules powinno pokazać trzynaście reguł w folderze Verris. | Deploy #66 (scalenie X-28) poszedł jeszcze STARYM skryptem, więc pliki wjechały na serwer, a monitoring został z poprzednią konfiguracją; naprawia się to samo przy pierwszym wdrożeniu z tą zmianą. Dokumentacja: docs/zadania/X-29-obserwowalnosc-nie-docierala-na-produkcje.md</t>
+          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md | DOWÓD D3 DOSTARCZALNOŚCI — 2026-08-23, dostarczony przez awarię, nie przez test. Przy X-30 reguły z execErrState: Alerting zapaliły się na błędzie ewaluacji i DZIESIĘĆ maili dotarło na dominik@hvln.pl z tematami [FIRING:1] &lt;alertname&gt; &lt;severity&gt; (Verris). Droga Grafana → SMTP → Postfix na panelu → mail.hvln.pl → skrzynka jest potwierdzona na całej długości. | TEN PRZYPADEK POTWIERDZIŁ TRZY RZECZY, KTÓRYCH PLANOWANY TEST JEDNEGO ALERTU BY NIE POTWIERDZIŁ: (1) droga do skrzynki działa; (2) migracja nie pogubiła nazw ani wag — tematy pokazały critical przy VerrisRuntimeErrorsHigh, VerrisOpenMajorIncident, VerrisSecurityWatchFindings i VerrisProvisioningQueueFailed oraz warning przy pozostałych, dokładnie jak w usuniętym alerts.yml; (3) progi `for:` przetrwały migrację — zapaliło się DZIESIĘĆ z trzynastu, a nie zapaliły się dokładnie te trzy z najdłuższym for: VerrisPostgresBackupStale (30 m), VerrisStatusWebhookFailed (30 m) i VerrisSecurityWatchStale (20 m), bo od restartu nie minęło tyle czasu. Skrypt migracyjny mógł te wartości po cichu przekręcić i żaden test w CI by tego nie zobaczył — zobaczyła to skrzynka.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="11" t="inlineStr">
         <is>
-          <t>X-30</t>
+          <t>X-29</t>
         </is>
       </c>
       <c r="B384" s="12" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="C384" s="11" t="inlineStr">
         <is>
-          <t>Reguły alertowe nie tylko są wczytane, ale się liczą</t>
+          <t>Wdrożenie dowozi konfigurację obserwowalności na serwer</t>
         </is>
       </c>
       <c r="D384" s="11" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="J384" s="12" t="inlineStr">
         <is>
-          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). DOWÓD D3: wdrożenie #68 zielone przez krok 4.6; log Grafany po restarcie 11:01:46 bez „Failed to build rule evaluator" (wszystkie wystąpienia 10:58–11:01:39, czyli sprzed restartu); „inserting datasource from configuration" name=Prometheus uid=Prometheus.</t>
+          <t>ops/scripts/prod-deploy-ghcr.sh — krok 4.5: OBS_SERVICES, promtool check config przed restartem, compose up -d + compose restart, sprawdzenie /api/health i /-/healthy po restarcie, exit 1 gdy nie wrócą; apps/api/src/test/wdrozenie-obserwowalnosci.spec.ts (8)</t>
         </is>
       </c>
       <c r="K384" s="11" t="inlineStr">
@@ -28567,85 +28567,157 @@
       </c>
       <c r="N384" s="12" t="inlineStr">
         <is>
-          <t>ZAMKNIĘTE 2026-08-23. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md | ZAMKNIĘTE 2026-08-23 — DOWÓD D3 Z LOGU PRODUKCYJNEJ GRAFANY. Wdrożenie #68 (2788011) przeszło przez nowy krok 4.6 i trwało 9m54s, czyli o te 75 sekund dłużej — krok przechodzi tylko wtedy, gdy Grafana ma reguły I licznik nieudanych ewaluacji nie urósł. W logu: 11:01:46 „deleted datasource based on configuration" name=Prometheus, zaraz po tym „inserting datasource from configuration" name=Prometheus uid=Prometheus. Wszystkie wpisy „Failed to build rule evaluator" mają znacznik 10:58–11:01:39, czyli SPRZED restartu; po 11:01:46 nie ma ANI JEDNEGO. Wpisy „Detected stale state entry ... reason=Error" o 11:02–11:03 to Grafana sprzątająca stare wpisy w stanie Alerting-z-powodu-błędu, stąd wiadomości [RESOLVED]. | POTWIERDZENIE UBOCZNE, MOCNIEJSZE OD SAMEGO LOGU: reguła VerrisProvisioningQueueFailed NIE ucichła po naprawie — wysyła alarm co minutę od 11:12, a ma for: 10m przy restarcie 11:01:46, więc pierwsze zapalenie o 11:12 zgadza się co do sekundy. To znaczy, że warunek verris_provisioning_queue_depth{state="failed"} &gt; 0 jest PRAWDZIWIE spełniony: alerting zaczął działać i w ciągu dziesięciu minut znalazł na produkcji coś realnego. Reguła, która zapala się z właściwego powodu, dowodzi więcej niż cisza. Osobna pozycja.</t>
+          <t>Zamknięte 2026-08-23. Wykryte przy X-28, pytaniem kontrolnym: co się właściwie stanie po wdrożeniu poprawki, która przenosi reguły alertowe do Grafany? Odpowiedź: NIC. | MECHANIZM: prod-deploy-ghcr.sh robi na serwerze checkout repozytorium do wdrażanego SHA, więc nowe pliki lądują na dysku — po czym restartuje wyłącznie APP_SERVICES="api client-panel staff-panel admin-panel status-page www". Prometheusa i Grafany na tej liście nie ma, a oba czytają konfigurację TYLKO przy starcie kontenera i oba mają ją podmontowaną z repozytorium. | ZASIĘG SZERSZY NIŻ ALERTY: tą samą drogą nie docierało na produkcję wszystko pod ops/observability/ — cele scrapowania i retencja w prometheus.yml, źródła danych, dwadzieścia kilka dashboardów Grafany, punkty kontaktowe i polityki. Każda zmiana w tych plikach od ostatniego RĘCZNEGO restartu Grafany istniała wyłącznie w repozytorium. | RODZINA: ten sam kształt co X-28 (alarm bez odbiorcy), X-14 i X-23 (kontrola, która melduje zamiast zatrzymywać) i H-20 (procedura bez dowodu wykonania) — COŚ WYGLĄDA NA ZROBIONE, BO ISTNIEJE. Zielone CI, zielony deploy, plik na dysku, pozycja zamknięta — i zero zmiany w działającym systemie. Różnica: tu zawodziło ostatnie ogniwo, nie budowa ani test, tylko DOSTARCZENIE. | POPRAWKA: krok 4.5, dwa polecenia zamiast jednego. `up -d` odtwarza kontener, gdy zmieniła się DEFINICJA usługi (X-28 usunęło montowanie alerts.yml); `restart` wymusza ponowne wczytanie, gdy zmieniła się tylko TREŚĆ podmontowanego pliku — tego compose nie widzi. | BEZWARUNKOWO, nie „gdy się zmieniło": porównanie z poprzednim SHA wymagałoby obu wersji w repozytorium na serwerze, a fetch jest tam płytki (--depth 1); nieudane porównanie skończyłoby się cichym „brak zmian → nie restartuj", czyli dokładnie tym błędem, który ta pozycja naprawia. Kilkanaście sekund przerwy w metrykach kontra miesiąc bez kopii bazy. | SPRAWDZENIE PRZED: promtool check config przez `compose run --rm --no-deps --entrypoint promtool`, a nie `exec` — świeży kontener z tą samą definicją, więc sprawdzenie działa także wtedy, gdy Prometheus akurat leży; przy `exec` padałoby w jedynym momencie, w którym naprawdę zależy nam na restarcie. Restart na zepsutej konfiguracji zdejmuje monitoring, a zauważyć to miał właśnie monitoring. | SPRAWDZENIE PO: „wydałem polecenie restartu" to nie to samo co „wróciły" — /api/health Grafany i /-/healthy Prometheusa (pytany Z KONTENERA Grafany, bo obraz Prometheusa nie ma czym wykonać zapytania HTTP), 20 prób co 3 s, potem exit 1. | KOLEJNOŚĆ W DWIE STRONY: krok jest PO bramce zdrowia i PO zapisaniu .last-good-image-tag, żeby awaria monitoringu nie wywróciła sprawnego wdrożenia; kończy się exit 1, a nie ostrzeżeniem, żeby wdrożenie nie uchodziło za skończone, zanim monitoring dostanie nową konfigurację. | Czerwieni się na starym kodzie: 6 z 8. Dwie przechodziły i przedtem — w tym ta o APP_SERVICES, bo Prometheusa i Grafany naprawdę tam nie było (tyle że nie było ich też nigdzie indziej). | CZEGO NIE DOWODZI: że po najbliższym wdrożeniu Grafana MA reguły — to obserwacja na produkcji (D3): Alerting → Alert rules powinno pokazać trzynaście reguł w folderze Verris. | Deploy #66 (scalenie X-28) poszedł jeszcze STARYM skryptem, więc pliki wjechały na serwer, a monitoring został z poprzednią konfiguracją; naprawia się to samo przy pierwszym wdrożeniu z tą zmianą. Dokumentacja: docs/zadania/X-29-obserwowalnosc-nie-docierala-na-produkcje.md</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="11" t="inlineStr">
         <is>
+          <t>X-30</t>
+        </is>
+      </c>
+      <c r="B385" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C385" s="11" t="inlineStr">
+        <is>
+          <t>Reguły alertowe nie tylko są wczytane, ale się liczą</t>
+        </is>
+      </c>
+      <c r="D385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I385" s="11" t="inlineStr">
+        <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="J385" s="12" t="inlineStr">
+        <is>
+          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). DOWÓD D3: wdrożenie #68 zielone przez krok 4.6; log Grafany po restarcie 11:01:46 bez „Failed to build rule evaluator" (wszystkie wystąpienia 10:58–11:01:39, czyli sprzed restartu); „inserting datasource from configuration" name=Prometheus uid=Prometheus.</t>
+        </is>
+      </c>
+      <c r="K385" s="11" t="inlineStr">
+        <is>
+          <t>PARYTET</t>
+        </is>
+      </c>
+      <c r="L385" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M385" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N385" s="12" t="inlineStr">
+        <is>
+          <t>ZAMKNIĘTE 2026-08-23. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md | ZAMKNIĘTE 2026-08-23 — DOWÓD D3 Z LOGU PRODUKCYJNEJ GRAFANY. Wdrożenie #68 (2788011) przeszło przez nowy krok 4.6 i trwało 9m54s, czyli o te 75 sekund dłużej — krok przechodzi tylko wtedy, gdy Grafana ma reguły I licznik nieudanych ewaluacji nie urósł. W logu: 11:01:46 „deleted datasource based on configuration" name=Prometheus, zaraz po tym „inserting datasource from configuration" name=Prometheus uid=Prometheus. Wszystkie wpisy „Failed to build rule evaluator" mają znacznik 10:58–11:01:39, czyli SPRZED restartu; po 11:01:46 nie ma ANI JEDNEGO. Wpisy „Detected stale state entry ... reason=Error" o 11:02–11:03 to Grafana sprzątająca stare wpisy w stanie Alerting-z-powodu-błędu, stąd wiadomości [RESOLVED]. | POTWIERDZENIE UBOCZNE, MOCNIEJSZE OD SAMEGO LOGU: reguła VerrisProvisioningQueueFailed NIE ucichła po naprawie — wysyła alarm co minutę od 11:12, a ma for: 10m przy restarcie 11:01:46, więc pierwsze zapalenie o 11:12 zgadza się co do sekundy. To znaczy, że warunek verris_provisioning_queue_depth{state="failed"} &gt; 0 jest PRAWDZIWIE spełniony: alerting zaczął działać i w ciągu dziesięciu minut znalazł na produkcji coś realnego. Reguła, która zapala się z właściwego powodu, dowodzi więcej niż cisza. Osobna pozycja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="11" t="inlineStr">
+        <is>
           <t>X-31</t>
         </is>
       </c>
-      <c r="B385" s="12" t="inlineStr">
+      <c r="B386" s="12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C385" s="11" t="inlineStr">
+      <c r="C386" s="11" t="inlineStr">
         <is>
           <t>Kanał alertów daje znak życia (dead man's switch)</t>
         </is>
       </c>
-      <c r="D385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I385" s="11" t="inlineStr">
+      <c r="D386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I386" s="11" t="inlineStr">
         <is>
           <t>CZĘŚCIOWE</t>
         </is>
       </c>
-      <c r="J385" s="12" t="inlineStr">
+      <c r="J386" s="12" t="inlineStr">
         <is>
           <t>ops/observability/grafana/provisioning/alerting/rules.yaml — grupa verris_kanal_alertow, reguła VerrisKanalAlertowZyje (vector(1), for: 0s, oba stany awaryjne na Alerting, etykieta kanal: heartbeat); policies.yaml — gałąź object_matchers kanal=heartbeat, repeat_interval 24h; apps/api/src/test/routing-alertow.spec.ts (5 asercji X-31); docs/ops/GRAFANA_ALERTING.md §4. BRAK: pierwszego maila [FIRING:1] VerrisKanalAlertowZyje — dowód D3 jeszcze nie powstał.</t>
         </is>
       </c>
-      <c r="K385" s="11" t="inlineStr">
+      <c r="K386" s="11" t="inlineStr">
         <is>
           <t>CZĘŚCIOWY</t>
         </is>
       </c>
-      <c r="L385" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M385" s="11" t="inlineStr">
+      <c r="L386" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M386" s="11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N385" s="12" t="inlineStr">
+      <c r="N386" s="12" t="inlineStr">
         <is>
           <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 powstanie przy pierwszym mailu. Decyzja właściciela produktu: wariant „jeden mail na dobę". | PROBLEM: po naprawie X-30 alerty ucichną, a cisza będzie znaczyła „nic się nie pali" — i będzie wyglądała IDENTYCZNIE jak: Grafana padła, Postfix przestał przyjmować, mail.hvln.pl zaczął odrzucać albo wrzucać do spamu, ktoś zmienił adres w punkcie kontaktowym, polityka przestała pasować do etykiet. To dokładnie ta sama cisza, która przez miesiąc znaczyła „kopia bazy jest w porządku" (H-23) i kosztowała wszystkie kopie zapasowe. | ROZWIĄZANIE: VerrisKanalAlertowZyje — reguła vector(1), pali się ZAWSZE, jej BRAK jest sygnałem. for: 0s, noDataState: Alerting, execErrState: Alerting — nie da się jej „nie zapalić": normalnie warunek jest spełniony, a gdyby źródło danych przestało odpowiadać, oba stany awaryjne też prowadzą do Alerting. Milczenie ma znaczyć awarię, nigdy spokój. | JEDEN MAIL NA DOBĘ, NIE SZEŚĆ: osobna gałąź polityki na etykiecie kanal: heartbeat z repeat_interval 24h. Na domyślnej (4h) byłoby sześć dziennie, a alert przychodzący sześć razy dziennie przestaje być czytany po tygodniu — wtedy przestaje cokolwiek dawać, bo jego BRAK jest jedyną informacją, jaką niesie. Strażnik pilnuje osobno, że polityka domyślna NIE została przy okazji przestawiona na dobę: prawdziwy alarm ma się przypominać co cztery godziny. | HACZYK, KTÓRY TRZEBA NAZWAĆ: mail, którego się nie czyta, wraca do punktu wyjścia. Jeśli po tygodniu przestanie być zauważany, reguła przestaje działać — nie dlatego, że jest zepsuta, tylko dlatego, że przestała być czytana. Tego nie da się naprawić kodem. | CZEGO NIE OBEJMUJE: awarii całego serwera (heartbeat mieszka na tej samej maszynie co Grafana i milczy razem z nią — odporny byłby watchdog SPOZA naszej infrastruktury, pukany cronem; nie ma go i to świadoma decyzja, nie przeoczenie) ani poprawności pozostałych reguł (tego pilnuje bramka z X-30). | Czerwieni się na starym kodzie: 5 z 36. | Doszła lista DOPISANE_POZNIEJ, trzymana osobno od ALERTY: tamta odpowiada na pytanie „czy migracja czegoś nie zgubiła" i ma zostać zamrożona, ta na „czy ktoś czegoś po cichu nie dołożył". Dokumentacja: docs/zadania/X-31-znak-zycia-kanalu-alertow.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N385"/>
-  <conditionalFormatting sqref="D2:D385">
+  <autoFilter ref="A1:N386"/>
+  <conditionalFormatting sqref="D2:D386">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28662,7 +28734,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E385">
+  <conditionalFormatting sqref="E2:E386">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28679,7 +28751,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F385">
+  <conditionalFormatting sqref="F2:F386">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28696,7 +28768,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G385">
+  <conditionalFormatting sqref="G2:G386">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28713,7 +28785,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H385">
+  <conditionalFormatting sqref="H2:H386">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28730,7 +28802,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I385">
+  <conditionalFormatting sqref="I2:I386">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28750,7 +28822,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K385">
+  <conditionalFormatting sqref="K2:K386">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28767,7 +28839,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L385">
+  <conditionalFormatting sqref="L2:L386">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$387</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$386,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$387,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$386,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$387,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$386,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$387,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$386,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$387,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$386,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$387,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$386,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$387,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$386,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$387,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$386,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$387,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$386,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$387,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$386,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$387,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"A",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"B",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"C",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"D",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"E",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"F",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"G",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"H",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"I",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"J",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"K",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"L",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"M",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"N",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"O",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"P",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Q",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"X",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$386,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$387,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$K$2:$K$386,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$386,"Z",Macierz!$L$2:$L$386,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N386"/>
+  <dimension ref="A1:N387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28715,9 +28715,81 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="11" t="inlineStr">
+        <is>
+          <t>X-32</t>
+        </is>
+      </c>
+      <c r="B387" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C387" s="11" t="inlineStr">
+        <is>
+          <t>Martwy job da się odrzucić z panelu, ze śladem w audycie</t>
+        </is>
+      </c>
+      <c r="D387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I387" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J387" s="12" t="inlineStr">
+        <is>
+          <t>apps/api/src/common/audit/audit.actions.ts — PROVISIONING_JOB_DISCARDED_BY_ADMIN; provisioning-queue.service.ts — odrzucJob (getState() === failed, ślad przed job.remove(), audyt z subskrypcją, typem, liczbą prób, failedReason i powodem); provisioning-queue.admin.controller.ts — POST :id/odrzuc za @StaffPerm('PROVISIONING_MANAGE'); apps/admin-panel/.../provisioning-queue/ — actions.ts, odrzuc-button.tsx (dwa kliknięcia, powód ≥5 znaków, zdanie o nietkniętej subskrypcji), page.tsx; apps/api/src/test/odrzucenie-martwego-joba.spec.ts (13). BRAK: pierwszego odrzucenia na produkcji — dowód D3 jeszcze nie powstał.</t>
+        </is>
+      </c>
+      <c r="K387" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L387" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M387" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N387" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym odrzuceniu na produkcji — a to da się zrobić od razu po wdrożeniu, w odróżnieniu od Z-18, który czeka na węzeł. Decyzja właściciela produktu: dorobić akcję w panelu zamiast jednorazowego czyszczenia Redisa. | JAK TO WYSZŁO: X-30 naprawiło alerting, VerrisProvisioningQueueFailed zapalił się z prawdziwego powodu i wskazał cztery martwe joby (to z nich wyszło Z-18). Naturalny następny ruch — usunąć je — okazał się NIEWYKONALNY: panel ma przy nich wyłącznie „Retry", a kontroler administracyjny dokładnie dwa endpointy, listowanie i ponowienie. Retry nic nie daje, bo węzła nie ma: job padnie ponownie, podbije licznik prób i dołoży wpisy do audytu — cztery martwe joby zamieniają się w cztery martwe joby z dłuższą historią. Zostawało grzebanie w Redisie ręcznie, czyli zmiana stanu produkcyjnego dotyczącego subskrypcji klientów BEZ ŚLADU W AUDYCIE. | TO NIE JEST USTERKA TYCH CZTERECH JOBÓW, tylko luka w warstwie operatorskiej, która ujawni się ponownie przy pierwszym prawdziwym niepowodzeniu provisioningu — z tą różnicą, że wtedy po drugiej stronie będzie klient. | ROZWIĄZANIE: POST /admin/provisioning-queue/:id/odrzuc + przycisk „Odrzuć" obok Retry. TRZY REGUŁY: (1) TYLKO STAN failed — usunięcie joba aktywnego albo czekającego osierociłoby provisioning w trakcie, konto na węźle mogłoby powstać, a system przestałby o nim wiedzieć; ograniczenie siedzi w usłudze, nie w kontrolerze, bo to reguła o kolejce, nie o HTTP; (2) POWÓD WYMAGANY, tak samo jak przy retry — operacja bez powodu to operacja, której za pół roku nikt nie wyjaśni; (3) NAJPIERW ODCZYT, POTEM USUNIĘCIE — ślad zbierany PRZED job.remove(), bo po usunięciu nie ma już czego odczytać; zapisujemy subskrypcję, joba, typ, liczbę prób, ostatni błąd i powód. Po Z-18 ten ostatni błąd niesie PRAWDZIWĄ przyczynę, więc wpis ma realną wartość dowodową — jeszcze wczoraj zapisałby zdanie o brakującym pakiecie DirectAdmina, którego nigdy nie brakowało. | OSOBNA AKCJA AUDYTU (PROVISIONING_JOB_DISCARDED_BY_ADMIN), nie wariant retry: w raportach odrzucenie i ponowienie to dwie różne decyzje i nie wolno im się zlewać. | DWA KLIKNIĘCIA, NIE JEDNO: retry można cofnąć następnym retry, odrzucenia nie da się cofnąć wcale. Potwierdzenie jest po to, żeby ta różnica była wyczuwalna w palcach. | ZDANIE PRZY PRZYCISKU: „Usuwa wpis z kolejki bez możliwości cofnięcia. Subskrypcja zostaje nietknięta." Operator ma prawo założyć, że „odrzuć" anuluje zamówienie — nie anuluje. Musi to być napisane tam, gdzie się klika, a nie w dokumentacji, której nikt nie otworzy w trakcie incydentu. | Czerwieni się na starym kodzie: 11 z 13. | DWIE UWAGI O SAMYCH TESTACH: odczyty plików panelu są LENIWE, bo odczyt na poziomie describe wywalał cały plik testowy, zanim cokolwiek się policzyło — a wtedy nie wiadomo, ILE asercji się czerwieni, tylko że „nie skompilowało się"; asercja o warunku row.failedReason nie mierzy odległości w znakach, tylko relację między warunkiem a przyciskiem, bo wersja licząca znaki zepsuła się od dopisania komentarza i kusiło, żeby poszerzyć okno zamiast poprawić asercję — to byłoby naprawianie testu zamiast kodu. | CZEGO NIE OBEJMUJE: losu czterech subskrypcji, które dostały zwrot i status PENDING_PAYMENT (odrzucenie joba ich nie dotyka — osobne sprzątanie po stronie bazy); odrzucania hurtem — świadomie, bo przycisk „odrzuć wszystkie" jest wygodny dokładnie do momentu, w którym ktoś kliknie go na kolejce z prawdziwym zamówieniem. | JAK ZAMKNĄĆ: odrzucić jeden z czterech martwych jobów, obejrzeć wpis PROVISIONING_JOB_DISCARDED_BY_ADMIN w audycie i sprawdzić, że verris_provisioning_queue_depth{state="failed"} spadło o jeden. Dokumentacja: docs/zadania/X-32-odrzucenie-martwego-joba.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N386"/>
-  <conditionalFormatting sqref="D2:D386">
+  <autoFilter ref="A1:N387"/>
+  <conditionalFormatting sqref="D2:D387">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28734,7 +28806,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E386">
+  <conditionalFormatting sqref="E2:E387">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28751,7 +28823,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F386">
+  <conditionalFormatting sqref="F2:F387">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28768,7 +28840,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G386">
+  <conditionalFormatting sqref="G2:G387">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28785,7 +28857,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H386">
+  <conditionalFormatting sqref="H2:H387">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28802,7 +28874,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I386">
+  <conditionalFormatting sqref="I2:I387">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28822,7 +28894,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K386">
+  <conditionalFormatting sqref="K2:K387">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28839,7 +28911,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L386">
+  <conditionalFormatting sqref="L2:L387">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$388</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$387,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$388,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$387,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$388,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$387,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$388,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$387,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$388,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$387,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$388,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$387,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$388,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$387,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$388,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$387,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$388,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$387,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$388,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$387,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$388,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"A",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"B",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"C",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"D",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"E",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"F",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"G",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"H",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"I",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"J",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"K",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"L",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"M",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"N",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"O",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"P",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Q",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"X",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$387,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$388,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$K$2:$K$387,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$387,"Z",Macierz!$L$2:$L$387,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N387"/>
+  <dimension ref="A1:N388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28787,9 +28787,81 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" s="11" t="inlineStr">
+        <is>
+          <t>X-33</t>
+        </is>
+      </c>
+      <c r="B388" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C388" s="11" t="inlineStr">
+        <is>
+          <t>Bramka alertów odróżnia „nie ma" od „jeszcze nie ma"</t>
+        </is>
+      </c>
+      <c r="D388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I388" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J388" s="12" t="inlineStr">
+        <is>
+          <t>ops/scripts/lib/bramka-regul-alertowych.sh — czekaj_na_reguly (do 20 prób co 3 s, warunek: aktywne == oczekiwane i paused == 0), policz_reguly_w_pliku (liczba odniesienia z rules.yaml), regul_w_stanie, metryka_istnieje (rozróżnienie braku linii od linii z zerem); ops/scripts/prod-deploy-ghcr.sh — krok 4.6a; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (9 asercji, uruchamia prawdziwą funkcję bashową z atrapą Grafany); apps/api/src/test/reguly-alertowe-licza-sie.spec.ts — kodZBibliotekami(). BRAK: zielonego wdrożenia — dowód D3 jeszcze nie powstał.</t>
+        </is>
+      </c>
+      <c r="K388" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L388" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M388" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N388" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N387"/>
-  <conditionalFormatting sqref="D2:D387">
+  <autoFilter ref="A1:N388"/>
+  <conditionalFormatting sqref="D2:D388">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28806,7 +28878,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E387">
+  <conditionalFormatting sqref="E2:E388">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28823,7 +28895,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F387">
+  <conditionalFormatting sqref="F2:F388">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28840,7 +28912,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G387">
+  <conditionalFormatting sqref="G2:G388">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28857,7 +28929,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H387">
+  <conditionalFormatting sqref="H2:H388">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28874,7 +28946,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I387">
+  <conditionalFormatting sqref="I2:I388">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28894,7 +28966,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K387">
+  <conditionalFormatting sqref="K2:K388">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28911,7 +28983,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L387">
+  <conditionalFormatting sqref="L2:L388">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wygenerowane 2026-08-23 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
+          <t>Wygenerowane 2026-08-24 z audyt/dane/macierz.csv · nie edytuj tego pliku ręcznie</t>
         </is>
       </c>
     </row>
@@ -28830,17 +28830,17 @@
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J388" s="12" t="inlineStr">
         <is>
-          <t>ops/scripts/lib/bramka-regul-alertowych.sh — czekaj_na_reguly (do 20 prób co 3 s, warunek: aktywne == oczekiwane i paused == 0), policz_reguly_w_pliku (liczba odniesienia z rules.yaml), regul_w_stanie, metryka_istnieje (rozróżnienie braku linii od linii z zerem); ops/scripts/prod-deploy-ghcr.sh — krok 4.6a; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (9 asercji, uruchamia prawdziwą funkcję bashową z atrapą Grafany); apps/api/src/test/reguly-alertowe-licza-sie.spec.ts — kodZBibliotekami(). BRAK: zielonego wdrożenia — dowód D3 jeszcze nie powstał.</t>
+          <t>ops/scripts/lib/bramka-regul-alertowych.sh — czekaj_na_reguly (do 20 prób co 3 s, warunek: aktywne == oczekiwane i paused == 0), policz_reguly_w_pliku (liczba odniesienia z rules.yaml), regul_w_stanie, metryka_istnieje (rozróżnienie braku linii od linii z zerem); ops/scripts/prod-deploy-ghcr.sh — krok 4.6a; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (9 asercji, uruchamia prawdziwą funkcję bashową z atrapą Grafany); apps/api/src/test/reguly-alertowe-licza-sie.spec.ts — kodZBibliotekami(). D3: wdrożenie #71 (2026-08-24) — „OK: 14/14 reguł aktywnych (próba 17)", metryka po 54 s. ops/scripts/lib/bramka-regul-alertowych.sh — okno_bramki_sekundy (jedno źródło okna, 180 s).</t>
         </is>
       </c>
       <c r="K388" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L388" s="11" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="N388" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. | DOWÓD D3 — WDROŻENIE #71 (2026-08-24, zielone, wszystkie 8 zadań): „09:30:43 czekam na scheduler alertów (oczekuję 14 reguł); 09:31:37 OK: 14/14 reguł aktywnych (PRÓBA 17); 09:32:52 reguły liczą się bez błędów (0 → 0)". PRÓBA SIEDEMNASTA, nie pierwsza: metryka pojawiła się 54 SEKUNDY po restarcie, nie siedem i nie dziesięć. To nie jest dowód „bramka przeszła", tylko dowód, że w tym samym miejscu poprzednia wersja padłaby PO RAZ DRUGI na zdrowym systemie. Wdrożenie trwało 3 m 58 s zamiast ~3 m — cała różnica to te 54 sekundy czekania. | TEN SAM LOG WYKRYŁ BŁĄD W MOJEJ WŁASNEJ LICZBIE: zakładałem takt schedulera ~10 s i ustawiłem okno na 60 s (20 prób); zużyliśmy 17, czyli zapas wynosił TRZY PRÓBY — dziewięć sekund. Przy odrobinę wolniejszym starcie Grafany kolejne wdrożenie padłoby dokładnie tak jak #70 i z dokładnie tego samego nie-powodu. Mechanizm był dobry, liczba dobrana na wyczucie, a wyczucie o 80% za optymistyczne. OKNO PODNIESIONE DO 180 s (60 prób co 3 s) — decyzja właściciela produktu: trzykrotny zapas, nie dwukrotny, bo 54 s to JEDNA OBSERWACJA, nie rozkład. Dłuższe okno NIE SPOWALNIA zdrowego wdrożenia ani o sekundę: pętla kończy się w chwili, w której reguły się zgadzają; płacimy wyłącznie przy prawdziwej awarii prowizjonowania — błąd po trzech minutach zamiast po jednej. Dobry kurs wymiany: fałszywy alarm uczy klikać „re-run", a dwie minuty dłuższego czekania na prawdziwą awarię nie uczą niczego. | I OD RAZU BLIŹNIACZE MIEJSCE, KTÓREGO OMAL NIE ZROBIŁEM: pierwsza wersja poprawki wpisywała 180 do komunikatu w skrypcie, a 60 prób do biblioteki — log mówiłby „do 180 s" niezależnie od tego, ile bramka naprawdę czeka, i okłamałby pierwszą osobę czytającą go w trakcie awarii. Okno podaje teraz okno_bramki_sekundy i tylko ona. Dwie dodatkowe asercje (razem 11), obie czerwone na kodzie sprzed #71. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
         </is>
       </c>
     </row>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$1:$N$389</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$388,A6)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$389,A6)</f>
         <v/>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$388,A7)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$389,A7)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$388,A8)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$389,A8)</f>
         <v/>
       </c>
     </row>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$388,A9)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$389,A9)</f>
         <v/>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Macierz!$K$2:$K$388,A10)</f>
+        <f>COUNTIF(Macierz!$K$2:$K$389,A10)</f>
         <v/>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A15)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A15)</f>
         <v/>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A16)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A16)</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A17)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A17)</f>
         <v/>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A18)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A18)</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A19)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A19)</f>
         <v/>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A20)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A20)</f>
         <v/>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF(Macierz!$I$2:$I$388,A21)</f>
+        <f>COUNTIF(Macierz!$I$2:$I$389,A21)</f>
         <v/>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B26" s="6">
-        <f>COUNTIF(Macierz!$L$2:$L$388,A26)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$389,A26)</f>
         <v/>
       </c>
     </row>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$388,A27)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$389,A27)</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$388,A28)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$389,A28)</f>
         <v/>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Macierz!$L$2:$L$388,A29)</f>
+        <f>COUNTIF(Macierz!$L$2:$L$389,A29)</f>
         <v/>
       </c>
     </row>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"A")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"A")</f>
         <v/>
       </c>
       <c r="C33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"A",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"A",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"A",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"A",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"A",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F33" s="8">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"B")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"B")</f>
         <v/>
       </c>
       <c r="C34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"B",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"B",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"B",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"B",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"B",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F34" s="8">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"C")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"C")</f>
         <v/>
       </c>
       <c r="C35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"C",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"C",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"C",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"C",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"C",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F35" s="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"D")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"D")</f>
         <v/>
       </c>
       <c r="C36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"D",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"D",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"D",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"D",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"D",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F36" s="8">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"E")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"E")</f>
         <v/>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"E",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"E",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"E",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"E",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"E",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F37" s="8">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"F")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"F")</f>
         <v/>
       </c>
       <c r="C38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"F",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"F",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"F",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E38" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"F",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"F",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F38" s="8">
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"G")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"G")</f>
         <v/>
       </c>
       <c r="C39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"G",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"G",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"G",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E39" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"G",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"G",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F39" s="8">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"H")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"H")</f>
         <v/>
       </c>
       <c r="C40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"H",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"H",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"H",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E40" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"H",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"H",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F40" s="8">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"I")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"I")</f>
         <v/>
       </c>
       <c r="C41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"I",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"I",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"I",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E41" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"I",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"I",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F41" s="8">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"J")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"J")</f>
         <v/>
       </c>
       <c r="C42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"J",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"J",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"J",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E42" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"J",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"J",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F42" s="8">
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B43" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"K")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"K")</f>
         <v/>
       </c>
       <c r="C43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"K",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"K",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"K",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E43" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"K",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"K",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F43" s="8">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B44" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"L")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"L")</f>
         <v/>
       </c>
       <c r="C44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"L",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"L",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"L",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E44" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"L",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"L",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F44" s="8">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="B45" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"M")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"M")</f>
         <v/>
       </c>
       <c r="C45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"M",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"M",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"M",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E45" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"M",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"M",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F45" s="8">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"N")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"N")</f>
         <v/>
       </c>
       <c r="C46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"N",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"N",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"N",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E46" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"N",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"N",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F46" s="8">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"O")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"O")</f>
         <v/>
       </c>
       <c r="C47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"O",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"O",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"O",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E47" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"O",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"O",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F47" s="8">
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B48" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"P")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"P")</f>
         <v/>
       </c>
       <c r="C48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"P",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"P",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"P",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E48" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"P",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"P",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F48" s="8">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"Q")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"Q")</f>
         <v/>
       </c>
       <c r="C49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Q",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"Q",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Q",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E49" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Q",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Q",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F49" s="8">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"X")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"X")</f>
         <v/>
       </c>
       <c r="C50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"X",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"X",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"X",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E50" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"X",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"X",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F50" s="8">
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>COUNTIF(Macierz!$B$2:$B$388,"Z")</f>
+        <f>COUNTIF(Macierz!$B$2:$B$389,"Z")</f>
         <v/>
       </c>
       <c r="C51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"PRZEWAGA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Z",Macierz!$K$2:$K$389,"PARYTET")+COUNTIFS(Macierz!$B$2:$B$389,"Z",Macierz!$K$2:$K$389,"PRZEWAGA")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$K$2:$K$388,"LUKA")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Z",Macierz!$K$2:$K$389,"LUKA")</f>
         <v/>
       </c>
       <c r="E51" s="7">
-        <f>COUNTIFS(Macierz!$B$2:$B$388,"Z",Macierz!$L$2:$L$388,"BLOKER STARTU")</f>
+        <f>COUNTIFS(Macierz!$B$2:$B$389,"Z",Macierz!$L$2:$L$389,"BLOKER STARTU")</f>
         <v/>
       </c>
       <c r="F51" s="8">
@@ -1500,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N388"/>
+  <dimension ref="A1:N389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="J388" s="12" t="inlineStr">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="K388" s="11" t="inlineStr">
         <is>
-          <t>PARYTET</t>
+          <t>CZĘŚCIOWY</t>
         </is>
       </c>
       <c r="L388" s="11" t="inlineStr">
@@ -28855,13 +28855,85 @@
       </c>
       <c r="N388" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. | DOWÓD D3 — WDROŻENIE #71 (2026-08-24, zielone, wszystkie 8 zadań): „09:30:43 czekam na scheduler alertów (oczekuję 14 reguł); 09:31:37 OK: 14/14 reguł aktywnych (PRÓBA 17); 09:32:52 reguły liczą się bez błędów (0 → 0)". PRÓBA SIEDEMNASTA, nie pierwsza: metryka pojawiła się 54 SEKUNDY po restarcie, nie siedem i nie dziesięć. To nie jest dowód „bramka przeszła", tylko dowód, że w tym samym miejscu poprzednia wersja padłaby PO RAZ DRUGI na zdrowym systemie. Wdrożenie trwało 3 m 58 s zamiast ~3 m — cała różnica to te 54 sekundy czekania. | TEN SAM LOG WYKRYŁ BŁĄD W MOJEJ WŁASNEJ LICZBIE: zakładałem takt schedulera ~10 s i ustawiłem okno na 60 s (20 prób); zużyliśmy 17, czyli zapas wynosił TRZY PRÓBY — dziewięć sekund. Przy odrobinę wolniejszym starcie Grafany kolejne wdrożenie padłoby dokładnie tak jak #70 i z dokładnie tego samego nie-powodu. Mechanizm był dobry, liczba dobrana na wyczucie, a wyczucie o 80% za optymistyczne. OKNO PODNIESIONE DO 180 s (60 prób co 3 s) — decyzja właściciela produktu: trzykrotny zapas, nie dwukrotny, bo 54 s to JEDNA OBSERWACJA, nie rozkład. Dłuższe okno NIE SPOWALNIA zdrowego wdrożenia ani o sekundę: pętla kończy się w chwili, w której reguły się zgadzają; płacimy wyłącznie przy prawdziwej awarii prowizjonowania — błąd po trzech minutach zamiast po jednej. Dobry kurs wymiany: fałszywy alarm uczy klikać „re-run", a dwie minuty dłuższego czekania na prawdziwą awarię nie uczą niczego. | I OD RAZU BLIŹNIACZE MIEJSCE, KTÓREGO OMAL NIE ZROBIŁEM: pierwsza wersja poprawki wpisywała 180 do komunikatu w skrypcie, a 60 prób do biblioteki — log mówiłby „do 180 s" niezależnie od tego, ile bramka naprawdę czeka, i okłamałby pierwszą osobę czytającą go w trakcie awarii. Okno podaje teraz okno_bramki_sekundy i tylko ona. Dwie dodatkowe asercje (razem 11), obie czerwone na kodzie sprzed #71. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. | DOWÓD D3 — WDROŻENIE #71 (2026-08-24, zielone, wszystkie 8 zadań): „09:30:43 czekam na scheduler alertów (oczekuję 14 reguł); 09:31:37 OK: 14/14 reguł aktywnych (PRÓBA 17); 09:32:52 reguły liczą się bez błędów (0 → 0)". PRÓBA SIEDEMNASTA, nie pierwsza: metryka pojawiła się 54 SEKUNDY po restarcie, nie siedem i nie dziesięć. To nie jest dowód „bramka przeszła", tylko dowód, że w tym samym miejscu poprzednia wersja padłaby PO RAZ DRUGI na zdrowym systemie. Wdrożenie trwało 3 m 58 s zamiast ~3 m — cała różnica to te 54 sekundy czekania. | TEN SAM LOG WYKRYŁ BŁĄD W MOJEJ WŁASNEJ LICZBIE: zakładałem takt schedulera ~10 s i ustawiłem okno na 60 s (20 prób); zużyliśmy 17, czyli zapas wynosił TRZY PRÓBY — dziewięć sekund. Przy odrobinę wolniejszym starcie Grafany kolejne wdrożenie padłoby dokładnie tak jak #70 i z dokładnie tego samego nie-powodu. Mechanizm był dobry, liczba dobrana na wyczucie, a wyczucie o 80% za optymistyczne. OKNO PODNIESIONE DO 180 s (60 prób co 3 s) — decyzja właściciela produktu: trzykrotny zapas, nie dwukrotny, bo 54 s to JEDNA OBSERWACJA, nie rozkład. Dłuższe okno NIE SPOWALNIA zdrowego wdrożenia ani o sekundę: pętla kończy się w chwili, w której reguły się zgadzają; płacimy wyłącznie przy prawdziwej awarii prowizjonowania — błąd po trzech minutach zamiast po jednej. Dobry kurs wymiany: fałszywy alarm uczy klikać „re-run", a dwie minuty dłuższego czekania na prawdziwą awarię nie uczą niczego. | I OD RAZU BLIŹNIACZE MIEJSCE, KTÓREGO OMAL NIE ZROBIŁEM: pierwsza wersja poprawki wpisywała 180 do komunikatu w skrypcie, a 60 prób do biblioteki — log mówiłby „do 180 s" niezależnie od tego, ile bramka naprawdę czeka, i okłamałby pierwszą osobę czytającą go w trakcie awarii. Okno podaje teraz okno_bramki_sekundy i tylko ona. Dwie dodatkowe asercje (razem 11), obie czerwone na kodzie sprzed #71. | DOWÓD D3 COFNIĘTY 2026-08-24: wdrożenie #71 przeszło PRZYPADKIEM, nie dlatego, że bramka działała. „Próba 17" nie była czasem startu Grafany, tylko czasem, przez który kłamał odczyt (X-34: SIGPIPE + pipefail; metryka zdążyła się pojawić, zanim odpowiedź /metrics przekroczyła 64 KB). Uzasadnienie okna 180 s oparte na tych 54 sekundach było fałszywe. D3 wróci przy zielonym wdrożeniu z biblioteką po X-34. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="11" t="inlineStr">
+        <is>
+          <t>X-34</t>
+        </is>
+      </c>
+      <c r="B389" s="12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C389" s="11" t="inlineStr">
+        <is>
+          <t>Bramka alertów czyta metryki bez potoku (SIGPIPE + pipefail)</t>
+        </is>
+      </c>
+      <c r="D389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I389" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="J389" s="12" t="inlineStr">
+        <is>
+          <t>ops/scripts/lib/bramka-regul-alertowych.sh — metryka_istnieje bez potoku (dopasowanie wzorcem w powłoce), regul_w_stanie przez &lt;&lt;&lt; zamiast |; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (13 asercji, atrapa &gt; 64 KB, harness z set -Eeuo pipefail). BRAK: zielonego wdrożenia z tą biblioteką — dowód D3 jeszcze nie powstał.</t>
+        </is>
+      </c>
+      <c r="K389" s="11" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWY</t>
+        </is>
+      </c>
+      <c r="L389" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M389" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N389" s="12" t="inlineStr">
+        <is>
+          <t>Stan 2026-08-24: ZROBIONE W KODZIE (D2), D3 przy pierwszym zielonym wdrożeniu. | CO SIĘ STAŁO: wdrożenie #72 padło z komunikatem „Grafana nie opublikowała metryki grafana_alerting_rule_group_rules w ciągu 60 prób co 3s. Scheduler alertów nie wystartował" — 193 sekundy bez ani jednej linii. Log SAMEJ GRAFANY z tej samej minuty mówi coś przeciwnego: 09:53:15.845 ngalert.scheduler „Starting scheduler" tickInterval=10s; 09:53:15.845 ngalert.state.manager „State cache has been initialized" states=14; 09:53:31.549 pierwsze alerty. Scheduler wystartował CZTERY SEKUNDY po restarcie. GRAFANA BYŁA ZDROWA — KŁAMAŁ MÓJ ODCZYT. | PRZYCZYNA, jedna linijka: printf '%s\n' "$metryki" | grep -q '^grafana_alerting_rule_group_rules{' przy set -Eeuo pipefail. grep -q kończy się NATYCHMIAST po dopasowaniu, printf wciąż pisze resztę; gdy odpowiedź nie mieści się w buforze potoku, printf dostaje SIGPIPE (141), a pipefail przepisuje ten status na cały potok — sprawdzenie zwraca BŁĄD DOKŁADNIE WTEDY, GDY METRYKA JEST. Zmierzone, deterministyczne, próg na buforze potoku: 16 KB → znaleziono, 32 KB → znaleziono, 63 KB → znaleziono, 64 KB → BRAK, 80 KB → BRAK, 128 KB → BRAK. | TO WYJAŚNIA WSZYSTKO, CZEGO NIE UMIAŁEM WYJAŚNIĆ: /metrics Grafany ROŚNIE w miarę rejestrowania kolektorów, więc wyścig toczył się nie między bramką a schedulerem, tylko między POJAWIENIEM SIĘ METRYKI a PRZEKROCZENIEM 64 KB. #71: metryka zdążyła, gdy odpowiedź była jeszcze &lt; 64 KB → odczyt udał się na 17. próbie, a ja odczytałem to jako „scheduler potrzebuje 54 sekund". #72: odpowiedź przekroczyła 64 KB pierwsza → 60 odczytów z rzędu skłamało, a ja odczytałem to jako „scheduler nie wystartował". OBIE INTERPRETACJE BYŁY FAŁSZYWE, a na podstawie pierwszej zdążyłem podnieść okno i napisać uzasadnienie, które brzmiało solidnie. Ten sam mechanizm prawdopodobnie stoi za #70. | DLACZEGO STARA BRAMKA TEGO NIE MIAŁA: czytała przez „| awk", a AWK CZYTA WEJŚCIE DO KOŃCA — nie zamyka potoku wcześniej, więc SIGPIPE nie powstaje. Wdrożenia #68 i #69 działały nie ze szczęścia, tylko dlatego, że nie miały tej usterki. TEN BŁĄD WPROWADZIŁEM JA, RAZEM Z grep -q. | ROZWIĄZANIE: w bibliotece NIE MA JUŻ ANI JEDNEGO POTOKU — obecność metryki dopasowuje sama powłoka wzorcem na zmiennej (case), a awk dostaje wejście przez &lt;&lt;&lt; (here-string to przekierowanie, nie potok, więc pipefail nie ma czego zepsuć). | OKNO ZOSTAJE 180 s, ALE Z INNEGO POWODU: stare uzasadnienie („zmierzone 54 s × 3") było nieprawdziwe i zostało w komentarzu przekreślone, żeby nikt go nie odtworzył. Prawdziwy pomiar z logu Grafany: scheduler startuje ~4 s po restarcie. 60 s by wystarczyło; 180 s zostaje, bo CZEKANIE JEST DARMOWE (pętla kończy się w chwili zgodności), a nie dlatego, że tyle zmierzono. Ta liczba NIE MA maskować usterki odczytu — gdyby bramka znów czekała minutami, odpowiedzią jest diagnoza, nie 300 s. | DLACZEGO STRAŻNIK Z X-33 TEGO NIE ZŁAPAŁ — NAJWAŻNIEJSZA CZĘŚĆ: test był ZIELONY, a kod kłamał 60 razy z rzędu. Nie dlatego, że sprawdzał złą rzecz — dlatego, że JEGO ŚRODOWISKO RÓŻNIŁO SIĘ OD PRODUKCYJNEGO W DWÓCH WYMIARACH, KTÓRE DECYDOWAŁY O WYNIKU: (1) atrapa ważyła 200 bajtów, a prawdziwe /metrics setki kilobajtów — przy 200 bajtach printf zdąży zapisać wszystko do bufora, zanim grep się zamknie, więc SIGPIPE nigdy nie powstanie; (2) harness ustawiał set -u, a produkcja set -Eeuo pipefail — BEZ PIPEFAIL TA USTERKA NIE ISTNIEJE. Testowałem inną powłokę niż ta, która to uruchamia. To NOWA ODMIANA rodziny „test, który niczego nie dowodzi" (Z-01, H-20, M-06, X-28): nie fałszywa asercja, tylko FAŁSZYWE ŚRODOWISKO. Asercje były dobre, kłamały dane wejściowe. PYTANIE DO KAŻDEGO PRZYSZŁEGO HARNESSU: czym moja atrapa różni się od produkcji i czy któraś z tych różnic może decydować o wyniku? Rozmiar wejścia i flagi powłoki to nie szczegóły techniczne, tylko warunki, w których kod działa albo nie. | STRAŻNIK (13 asercji, było 11): atrapa waży ponad 64 KB i test to ASERTUJE, żeby nikt jej nie „uprościł"; harness ustawia dokładnie te flagi co skrypt wdrożeniowy; osobna asercja, że odpowiedź większa niż bufor potoku nie zamienia się w „brak metryki"; asercja o treści biblioteki (żadnego | grep, żadnego printf |) stojąca OBOK zachowaniowej, nie zamiast niej — tamta łapie usterkę, ta pilnuje, żeby nie wróciła tą samą drogą. | Czerwieni się na kodzie sprzed X-34: 7 z 13. | JAK ZAMKNĄĆ: zielone wdrożenie z tą biblioteką, z NISKIM numerem próby (kilkanaście sekund, nie pięćdziesiąt cztery). Dwucyfrowy numer oznaczałby, że nadal czegoś nie rozumiem. Dokumentacja: docs/zadania/X-34-bramka-klamala-o-wlasnym-odczycie.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N388"/>
-  <conditionalFormatting sqref="D2:D388">
+  <autoFilter ref="A1:N389"/>
+  <conditionalFormatting sqref="D2:D389">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28878,7 +28950,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E388">
+  <conditionalFormatting sqref="E2:E389">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28895,7 +28967,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F388">
+  <conditionalFormatting sqref="F2:F389">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28912,7 +28984,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G388">
+  <conditionalFormatting sqref="G2:G389">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28929,7 +29001,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H388">
+  <conditionalFormatting sqref="H2:H389">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"TAK"</formula>
     </cfRule>
@@ -28946,7 +29018,7 @@
       <formula>"b.d."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I388">
+  <conditionalFormatting sqref="I2:I389">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
       <formula>"DZIAŁA"</formula>
     </cfRule>
@@ -28966,7 +29038,7 @@
       <formula>"BRAK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K388">
+  <conditionalFormatting sqref="K2:K389">
     <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
       <formula>"PARYTET"</formula>
     </cfRule>
@@ -28983,7 +29055,7 @@
       <formula>"POZA ZAKRESEM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L388">
+  <conditionalFormatting sqref="L2:L389">
     <cfRule type="cellIs" priority="37" operator="equal" dxfId="9">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>

--- a/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
+++ b/audyt-parytetu-2026-08/VERRIS_PARYTET_FUNKCJI_2026-08.xlsx
@@ -28830,17 +28830,17 @@
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J388" s="12" t="inlineStr">
         <is>
-          <t>ops/scripts/lib/bramka-regul-alertowych.sh — czekaj_na_reguly (do 20 prób co 3 s, warunek: aktywne == oczekiwane i paused == 0), policz_reguly_w_pliku (liczba odniesienia z rules.yaml), regul_w_stanie, metryka_istnieje (rozróżnienie braku linii od linii z zerem); ops/scripts/prod-deploy-ghcr.sh — krok 4.6a; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (9 asercji, uruchamia prawdziwą funkcję bashową z atrapą Grafany); apps/api/src/test/reguly-alertowe-licza-sie.spec.ts — kodZBibliotekami(). D3: wdrożenie #71 (2026-08-24) — „OK: 14/14 reguł aktywnych (próba 17)", metryka po 54 s. ops/scripts/lib/bramka-regul-alertowych.sh — okno_bramki_sekundy (jedno źródło okna, 180 s).</t>
+          <t>ops/scripts/lib/bramka-regul-alertowych.sh — czekaj_na_reguly (do 20 prób co 3 s, warunek: aktywne == oczekiwane i paused == 0), policz_reguly_w_pliku (liczba odniesienia z rules.yaml), regul_w_stanie, metryka_istnieje (rozróżnienie braku linii od linii z zerem); ops/scripts/prod-deploy-ghcr.sh — krok 4.6a; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (9 asercji, uruchamia prawdziwą funkcję bashową z atrapą Grafany); apps/api/src/test/reguly-alertowe-licza-sie.spec.ts — kodZBibliotekami(). D3: wdrożenie #73 (2026-08-24) — „OK: 14/14 reguł aktywnych (próba 4)" (dowód z #71 unieważniony przez X-34). ops/scripts/lib/bramka-regul-alertowych.sh — okno_bramki_sekundy (jedno źródło okna, 180 s).</t>
         </is>
       </c>
       <c r="K388" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L388" s="11" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="N388" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. | DOWÓD D3 — WDROŻENIE #71 (2026-08-24, zielone, wszystkie 8 zadań): „09:30:43 czekam na scheduler alertów (oczekuję 14 reguł); 09:31:37 OK: 14/14 reguł aktywnych (PRÓBA 17); 09:32:52 reguły liczą się bez błędów (0 → 0)". PRÓBA SIEDEMNASTA, nie pierwsza: metryka pojawiła się 54 SEKUNDY po restarcie, nie siedem i nie dziesięć. To nie jest dowód „bramka przeszła", tylko dowód, że w tym samym miejscu poprzednia wersja padłaby PO RAZ DRUGI na zdrowym systemie. Wdrożenie trwało 3 m 58 s zamiast ~3 m — cała różnica to te 54 sekundy czekania. | TEN SAM LOG WYKRYŁ BŁĄD W MOJEJ WŁASNEJ LICZBIE: zakładałem takt schedulera ~10 s i ustawiłem okno na 60 s (20 prób); zużyliśmy 17, czyli zapas wynosił TRZY PRÓBY — dziewięć sekund. Przy odrobinę wolniejszym starcie Grafany kolejne wdrożenie padłoby dokładnie tak jak #70 i z dokładnie tego samego nie-powodu. Mechanizm był dobry, liczba dobrana na wyczucie, a wyczucie o 80% za optymistyczne. OKNO PODNIESIONE DO 180 s (60 prób co 3 s) — decyzja właściciela produktu: trzykrotny zapas, nie dwukrotny, bo 54 s to JEDNA OBSERWACJA, nie rozkład. Dłuższe okno NIE SPOWALNIA zdrowego wdrożenia ani o sekundę: pętla kończy się w chwili, w której reguły się zgadzają; płacimy wyłącznie przy prawdziwej awarii prowizjonowania — błąd po trzech minutach zamiast po jednej. Dobry kurs wymiany: fałszywy alarm uczy klikać „re-run", a dwie minuty dłuższego czekania na prawdziwą awarię nie uczą niczego. | I OD RAZU BLIŹNIACZE MIEJSCE, KTÓREGO OMAL NIE ZROBIŁEM: pierwsza wersja poprawki wpisywała 180 do komunikatu w skrypcie, a 60 prób do biblioteki — log mówiłby „do 180 s" niezależnie od tego, ile bramka naprawdę czeka, i okłamałby pierwszą osobę czytającą go w trakcie awarii. Okno podaje teraz okno_bramki_sekundy i tylko ona. Dwie dodatkowe asercje (razem 11), obie czerwone na kodzie sprzed #71. | DOWÓD D3 COFNIĘTY 2026-08-24: wdrożenie #71 przeszło PRZYPADKIEM, nie dlatego, że bramka działała. „Próba 17" nie była czasem startu Grafany, tylko czasem, przez który kłamał odczyt (X-34: SIGPIPE + pipefail; metryka zdążyła się pojawić, zanim odpowiedź /metrics przekroczyła 64 KB). Uzasadnienie okna 180 s oparte na tych 54 sekundach było fałszywe. D3 wróci przy zielonym wdrożeniu z biblioteką po X-34. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 przy pierwszym ZIELONYM wdrożeniu. | CO SIĘ STAŁO: wdrożenie #70 (b64db02, scalenie X-32) padło na bramce X-30 z komunikatem „Grafana nie ma ANI JEDNEJ reguły alertowej", podczas gdy Grafana miała w tej samej chwili CZTERNAŚCIE aktywnych reguł (grafana_alerting_rule_group_rules{state="active"}=14, paused=0). Oś czasu z logu: 15:43:09 restart, 15:43:15 /api/health OK, 15:43:16 odczyt metryki → zero → FAIL. Siedem sekund od restartu. | DLACZEGO ZERO NIE ZNACZYŁO ZERA: w Grafanie 10.4.2 grafana_alerting_rule_group_rules to GaugeVec z etykietami org i state, ustawiany w processTick() — na pierwszym takcie schedulera alertów (domyślnie 10 s), nie przy starcie procesu. Do tego momentu metryka NIE MA W /metrics ANI JEDNEJ LINII; suma z pustki przez awk daje zero i wygląda identycznie jak katastrofa. /api/health odpowiada dużo wcześniej. Wdrożenia #68 i #69 wygrały ten wyścig, #70 przegrało — o werdykcie bramki decydowała szybkość startu, nie stan systemu. | DLACZEGO TO POWAŻNIEJSZE NIŻ JEDEN CZERWONY DEPLOY: bramka, która potrafi zapalić się na zdrowym systemie, uczy człowieka klikać „re-run" — od tej chwili nie chroni już niczego, a nadal figuruje w audycie jako dowód D2. | NOWY TYP W KOLEKCJI: „kontrola, która nie odróżnia NIE MA od JESZCZE NIE MA". Mieliśmy bramki meldujące zamiast bramkować (X-14, X-23, H-19, H-20, X-27, X-28), testy niczego niedowodzące (Z-01, H-20, M-06, X-28) i poprawną kontrolę, której się kłamie (Z-18). Pytanie do każdej przyszłej bramki: CZY BRAK DANYCH I ZŁA WARTOŚĆ DAJĄ W NIEJ TEN SAM WYNIK? Jeśli tak — bramka mierzy czas, a nie stan. | ROZWIĄZANIE: logika w osobnym pliku ops/scripts/lib/bramka-regul-alertowych.sh, wczytywanym przez skrypt wdrożeniowy. czekaj_na_reguly odpytuje Grafanę do 20 razy co 3 s i przechodzi dopiero, gdy liczba reguł aktywnych zgadza się z oczekiwaną i żadna nie wisi w stanie paused. TO NIE JEST POLUZOWANIE: stara wersja przepuszczała 9 reguł z 14 (bo 9 &gt; 0) i odrzucała 14 z 14 (bo mierzyła za wcześnie) — nowa robi odwrotnie w obu przypadkach. | TRZY RÓŻNE NIEPOWODZENIA, TRZY RÓŻNE KOMUNIKATY: brak metryki → „scheduler nie wystartował" (naprawiaj Grafanę); za mało reguł → „prowizjonowanie CZĘŚCIOWE: 9 z 14" (naprawiaj rules.yaml); reguły paused → „wczytane, ale NIE LICZĄ SIĘ". Bramka mówiąca jedno zdanie na trzy awarie każe diagnozować od zera — ta sama lekcja co Z-18. | LICZBA ODNIESIENIA Z PLIKU: policz_reguly_w_pliku liczy wpisy „- uid:" w rules.yaml w chwili wdrożenia. Wpisanie „14" do skryptu byłoby SZÓSTYM BLIŹNIACZYM MIEJSCEM (Z-12, Z-16, M-06, X-24, H-24). | CZEGO ŚWIADOMIE NIE ZROBILIŚMY: nie skróciliśmy taktu schedulera Grafany — zmiana ustawienia produkcyjnego po to, żeby zadowolić bramkę, odwraca zależność. | STRAŻNIK WYGLĄDA INACZEJ NIŻ POPRZEDNIE i to jest jego sedno: ani jednej asercji typu „w skrypcie występuje słowo sleep". Test URUCHAMIA PRAWDZIWĄ FUNKCJĘ BASHOWĄ i podstawia jej atrapę Grafany zachowującą się dokładnie tak, jak Grafana o 15:43:16 (trzy odpowiedzi bez metryki, potem czternaście reguł). Właśnie po to logika trafiła do osobnego pliku — dopóki siedziała w skrypcie, jedyną możliwą asercją było czytanie tekstu skryptu, czyli błąd X-28. | Czerwieni się na starym kodzie: 9 z 9 — ale ta liczba jest mało pouczająca, bo na starym stanie repozytorium biblioteki nie ma wcale i wszystko wysypuje się na braku pliku. Zmierzone drugi raz, ze STARĄ SEMANTYKĄ podstawioną pod ten sam interfejs (jeden odczyt, warunek „&gt; 0"): 7 z 9. To uczciwsza liczba — oddziela zmianę zachowania od zniknięcia pliku. | CO ZŁAPALI STRAŻNICY, KTÓRZY JUŻ BYLI (oba miały rację): (1) skrypty-wykonywalne.spec.ts — nowa biblioteka nie miała bitu wykonywalności; kusiło dopisać wyjątek „to plik wczytywany", ale komentarz tego strażnika mówi wprost, że reguła jest bezwyjątkowa właśnie dlatego, że lista wyjątków byłaby kolejnym bliźniaczym miejscem — chmod +x, strażnik bez zmian; poluzowanie go byłoby JEDENASTYM wystąpieniem rodziny „strażnik dopasowuje własną prozę"; (2) reguly-alertowe-licza-sie.spec.ts (strażnik X-30) — sprawdzał treść prod-deploy-ghcr.sh, a logika przeniosła się do biblioteki; samo usunięcie asercji sprawiłoby, że X-30 pilnuje mniej niż wcześniej nie mówiąc o tym ani słowem, więc strażnik czyta teraz skrypt RAZEM Z BIBLIOTEKAMI, które sam wczytuje, a asercja o pustym provisioningu została WZMOCNIONA z „więcej niż zero" do „komplet reguł". | STAN PRODUKCJI PO #70: exit 1 w tym miejscu kończy skrypt PRZED sekcją rollbacku, więc nic się nie cofnęło — na produkcji stoi b64db02, /healthz przeszedł, .last-good-image-tag zapisany, przycisk „Odrzuć" z X-32 jest live, czternaście reguł się liczy. Wdrożenie było UDANE; nieudana była bramka. | JAK ZAMKNĄĆ: pierwsze zielone wdrożenie z linią „[deploy] OK: 14/14 reguł aktywnych (próba N)" w logu. Jeżeli N &gt; 1, mamy w logu bezpośredni dowód, że wyścig był prawdziwy. | DOWÓD D3 — WDROŻENIE #71 (2026-08-24, zielone, wszystkie 8 zadań): „09:30:43 czekam na scheduler alertów (oczekuję 14 reguł); 09:31:37 OK: 14/14 reguł aktywnych (PRÓBA 17); 09:32:52 reguły liczą się bez błędów (0 → 0)". PRÓBA SIEDEMNASTA, nie pierwsza: metryka pojawiła się 54 SEKUNDY po restarcie, nie siedem i nie dziesięć. To nie jest dowód „bramka przeszła", tylko dowód, że w tym samym miejscu poprzednia wersja padłaby PO RAZ DRUGI na zdrowym systemie. Wdrożenie trwało 3 m 58 s zamiast ~3 m — cała różnica to te 54 sekundy czekania. | TEN SAM LOG WYKRYŁ BŁĄD W MOJEJ WŁASNEJ LICZBIE: zakładałem takt schedulera ~10 s i ustawiłem okno na 60 s (20 prób); zużyliśmy 17, czyli zapas wynosił TRZY PRÓBY — dziewięć sekund. Przy odrobinę wolniejszym starcie Grafany kolejne wdrożenie padłoby dokładnie tak jak #70 i z dokładnie tego samego nie-powodu. Mechanizm był dobry, liczba dobrana na wyczucie, a wyczucie o 80% za optymistyczne. OKNO PODNIESIONE DO 180 s (60 prób co 3 s) — decyzja właściciela produktu: trzykrotny zapas, nie dwukrotny, bo 54 s to JEDNA OBSERWACJA, nie rozkład. Dłuższe okno NIE SPOWALNIA zdrowego wdrożenia ani o sekundę: pętla kończy się w chwili, w której reguły się zgadzają; płacimy wyłącznie przy prawdziwej awarii prowizjonowania — błąd po trzech minutach zamiast po jednej. Dobry kurs wymiany: fałszywy alarm uczy klikać „re-run", a dwie minuty dłuższego czekania na prawdziwą awarię nie uczą niczego. | I OD RAZU BLIŹNIACZE MIEJSCE, KTÓREGO OMAL NIE ZROBIŁEM: pierwsza wersja poprawki wpisywała 180 do komunikatu w skrypcie, a 60 prób do biblioteki — log mówiłby „do 180 s" niezależnie od tego, ile bramka naprawdę czeka, i okłamałby pierwszą osobę czytającą go w trakcie awarii. Okno podaje teraz okno_bramki_sekundy i tylko ona. Dwie dodatkowe asercje (razem 11), obie czerwone na kodzie sprzed #71. | DOWÓD D3 COFNIĘTY 2026-08-24: wdrożenie #71 przeszło PRZYPADKIEM, nie dlatego, że bramka działała. „Próba 17" nie była czasem startu Grafany, tylko czasem, przez który kłamał odczyt (X-34: SIGPIPE + pipefail; metryka zdążyła się pojawić, zanim odpowiedź /metrics przekroczyła 64 KB). Uzasadnienie okna 180 s oparte na tych 54 sekundach było fałszywe. D3 wróci przy zielonym wdrożeniu z biblioteką po X-34. | D3 PRZYWRÓCONE 2026-08-24 na wdrożeniu #73 („próba 4", 10 s) — tym razem na ZROZUMIANYM mechanizmie, po naprawie X-34. Bramka przeszła dlatego, że działa, a nie dlatego, że miała szczęście. Dokumentacja: docs/zadania/X-33-bramka-mierzyla-szybkosc-startu.md</t>
         </is>
       </c>
     </row>
@@ -28902,17 +28902,17 @@
       </c>
       <c r="I389" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="J389" s="12" t="inlineStr">
         <is>
-          <t>ops/scripts/lib/bramka-regul-alertowych.sh — metryka_istnieje bez potoku (dopasowanie wzorcem w powłoce), regul_w_stanie przez &lt;&lt;&lt; zamiast |; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (13 asercji, atrapa &gt; 64 KB, harness z set -Eeuo pipefail). BRAK: zielonego wdrożenia z tą biblioteką — dowód D3 jeszcze nie powstał.</t>
+          <t>ops/scripts/lib/bramka-regul-alertowych.sh — metryka_istnieje bez potoku (dopasowanie wzorcem w powłoce), regul_w_stanie przez &lt;&lt;&lt; zamiast |; apps/api/src/test/bramka-regul-nie-myli-braku-z-oczekiwaniem.spec.ts (13 asercji, atrapa &gt; 64 KB, harness z set -Eeuo pipefail). D3: wdrożenie #73 (2026-08-24) — „OK: 14/14 reguł aktywnych (próba 4)", 10 sekund.</t>
         </is>
       </c>
       <c r="K389" s="11" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWY</t>
+          <t>PARYTET</t>
         </is>
       </c>
       <c r="L389" s="11" t="inlineStr">
@@ -28927,7 +28927,7 @@
       </c>
       <c r="N389" s="12" t="inlineStr">
         <is>
-          <t>Stan 2026-08-24: ZROBIONE W KODZIE (D2), D3 przy pierwszym zielonym wdrożeniu. | CO SIĘ STAŁO: wdrożenie #72 padło z komunikatem „Grafana nie opublikowała metryki grafana_alerting_rule_group_rules w ciągu 60 prób co 3s. Scheduler alertów nie wystartował" — 193 sekundy bez ani jednej linii. Log SAMEJ GRAFANY z tej samej minuty mówi coś przeciwnego: 09:53:15.845 ngalert.scheduler „Starting scheduler" tickInterval=10s; 09:53:15.845 ngalert.state.manager „State cache has been initialized" states=14; 09:53:31.549 pierwsze alerty. Scheduler wystartował CZTERY SEKUNDY po restarcie. GRAFANA BYŁA ZDROWA — KŁAMAŁ MÓJ ODCZYT. | PRZYCZYNA, jedna linijka: printf '%s\n' "$metryki" | grep -q '^grafana_alerting_rule_group_rules{' przy set -Eeuo pipefail. grep -q kończy się NATYCHMIAST po dopasowaniu, printf wciąż pisze resztę; gdy odpowiedź nie mieści się w buforze potoku, printf dostaje SIGPIPE (141), a pipefail przepisuje ten status na cały potok — sprawdzenie zwraca BŁĄD DOKŁADNIE WTEDY, GDY METRYKA JEST. Zmierzone, deterministyczne, próg na buforze potoku: 16 KB → znaleziono, 32 KB → znaleziono, 63 KB → znaleziono, 64 KB → BRAK, 80 KB → BRAK, 128 KB → BRAK. | TO WYJAŚNIA WSZYSTKO, CZEGO NIE UMIAŁEM WYJAŚNIĆ: /metrics Grafany ROŚNIE w miarę rejestrowania kolektorów, więc wyścig toczył się nie między bramką a schedulerem, tylko między POJAWIENIEM SIĘ METRYKI a PRZEKROCZENIEM 64 KB. #71: metryka zdążyła, gdy odpowiedź była jeszcze &lt; 64 KB → odczyt udał się na 17. próbie, a ja odczytałem to jako „scheduler potrzebuje 54 sekund". #72: odpowiedź przekroczyła 64 KB pierwsza → 60 odczytów z rzędu skłamało, a ja odczytałem to jako „scheduler nie wystartował". OBIE INTERPRETACJE BYŁY FAŁSZYWE, a na podstawie pierwszej zdążyłem podnieść okno i napisać uzasadnienie, które brzmiało solidnie. Ten sam mechanizm prawdopodobnie stoi za #70. | DLACZEGO STARA BRAMKA TEGO NIE MIAŁA: czytała przez „| awk", a AWK CZYTA WEJŚCIE DO KOŃCA — nie zamyka potoku wcześniej, więc SIGPIPE nie powstaje. Wdrożenia #68 i #69 działały nie ze szczęścia, tylko dlatego, że nie miały tej usterki. TEN BŁĄD WPROWADZIŁEM JA, RAZEM Z grep -q. | ROZWIĄZANIE: w bibliotece NIE MA JUŻ ANI JEDNEGO POTOKU — obecność metryki dopasowuje sama powłoka wzorcem na zmiennej (case), a awk dostaje wejście przez &lt;&lt;&lt; (here-string to przekierowanie, nie potok, więc pipefail nie ma czego zepsuć). | OKNO ZOSTAJE 180 s, ALE Z INNEGO POWODU: stare uzasadnienie („zmierzone 54 s × 3") było nieprawdziwe i zostało w komentarzu przekreślone, żeby nikt go nie odtworzył. Prawdziwy pomiar z logu Grafany: scheduler startuje ~4 s po restarcie. 60 s by wystarczyło; 180 s zostaje, bo CZEKANIE JEST DARMOWE (pętla kończy się w chwili zgodności), a nie dlatego, że tyle zmierzono. Ta liczba NIE MA maskować usterki odczytu — gdyby bramka znów czekała minutami, odpowiedzią jest diagnoza, nie 300 s. | DLACZEGO STRAŻNIK Z X-33 TEGO NIE ZŁAPAŁ — NAJWAŻNIEJSZA CZĘŚĆ: test był ZIELONY, a kod kłamał 60 razy z rzędu. Nie dlatego, że sprawdzał złą rzecz — dlatego, że JEGO ŚRODOWISKO RÓŻNIŁO SIĘ OD PRODUKCYJNEGO W DWÓCH WYMIARACH, KTÓRE DECYDOWAŁY O WYNIKU: (1) atrapa ważyła 200 bajtów, a prawdziwe /metrics setki kilobajtów — przy 200 bajtach printf zdąży zapisać wszystko do bufora, zanim grep się zamknie, więc SIGPIPE nigdy nie powstanie; (2) harness ustawiał set -u, a produkcja set -Eeuo pipefail — BEZ PIPEFAIL TA USTERKA NIE ISTNIEJE. Testowałem inną powłokę niż ta, która to uruchamia. To NOWA ODMIANA rodziny „test, który niczego nie dowodzi" (Z-01, H-20, M-06, X-28): nie fałszywa asercja, tylko FAŁSZYWE ŚRODOWISKO. Asercje były dobre, kłamały dane wejściowe. PYTANIE DO KAŻDEGO PRZYSZŁEGO HARNESSU: czym moja atrapa różni się od produkcji i czy któraś z tych różnic może decydować o wyniku? Rozmiar wejścia i flagi powłoki to nie szczegóły techniczne, tylko warunki, w których kod działa albo nie. | STRAŻNIK (13 asercji, było 11): atrapa waży ponad 64 KB i test to ASERTUJE, żeby nikt jej nie „uprościł"; harness ustawia dokładnie te flagi co skrypt wdrożeniowy; osobna asercja, że odpowiedź większa niż bufor potoku nie zamienia się w „brak metryki"; asercja o treści biblioteki (żadnego | grep, żadnego printf |) stojąca OBOK zachowaniowej, nie zamiast niej — tamta łapie usterkę, ta pilnuje, żeby nie wróciła tą samą drogą. | Czerwieni się na kodzie sprzed X-34: 7 z 13. | JAK ZAMKNĄĆ: zielone wdrożenie z tą biblioteką, z NISKIM numerem próby (kilkanaście sekund, nie pięćdziesiąt cztery). Dwucyfrowy numer oznaczałby, że nadal czegoś nie rozumiem. Dokumentacja: docs/zadania/X-34-bramka-klamala-o-wlasnym-odczycie.md</t>
+          <t>Stan 2026-08-24: ZROBIONE W KODZIE (D2), D3 przy pierwszym zielonym wdrożeniu. | CO SIĘ STAŁO: wdrożenie #72 padło z komunikatem „Grafana nie opublikowała metryki grafana_alerting_rule_group_rules w ciągu 60 prób co 3s. Scheduler alertów nie wystartował" — 193 sekundy bez ani jednej linii. Log SAMEJ GRAFANY z tej samej minuty mówi coś przeciwnego: 09:53:15.845 ngalert.scheduler „Starting scheduler" tickInterval=10s; 09:53:15.845 ngalert.state.manager „State cache has been initialized" states=14; 09:53:31.549 pierwsze alerty. Scheduler wystartował CZTERY SEKUNDY po restarcie. GRAFANA BYŁA ZDROWA — KŁAMAŁ MÓJ ODCZYT. | PRZYCZYNA, jedna linijka: printf '%s\n' "$metryki" | grep -q '^grafana_alerting_rule_group_rules{' przy set -Eeuo pipefail. grep -q kończy się NATYCHMIAST po dopasowaniu, printf wciąż pisze resztę; gdy odpowiedź nie mieści się w buforze potoku, printf dostaje SIGPIPE (141), a pipefail przepisuje ten status na cały potok — sprawdzenie zwraca BŁĄD DOKŁADNIE WTEDY, GDY METRYKA JEST. Zmierzone, deterministyczne, próg na buforze potoku: 16 KB → znaleziono, 32 KB → znaleziono, 63 KB → znaleziono, 64 KB → BRAK, 80 KB → BRAK, 128 KB → BRAK. | TO WYJAŚNIA WSZYSTKO, CZEGO NIE UMIAŁEM WYJAŚNIĆ: /metrics Grafany ROŚNIE w miarę rejestrowania kolektorów, więc wyścig toczył się nie między bramką a schedulerem, tylko między POJAWIENIEM SIĘ METRYKI a PRZEKROCZENIEM 64 KB. #71: metryka zdążyła, gdy odpowiedź była jeszcze &lt; 64 KB → odczyt udał się na 17. próbie, a ja odczytałem to jako „scheduler potrzebuje 54 sekund". #72: odpowiedź przekroczyła 64 KB pierwsza → 60 odczytów z rzędu skłamało, a ja odczytałem to jako „scheduler nie wystartował". OBIE INTERPRETACJE BYŁY FAŁSZYWE, a na podstawie pierwszej zdążyłem podnieść okno i napisać uzasadnienie, które brzmiało solidnie. Ten sam mechanizm prawdopodobnie stoi za #70. | DLACZEGO STARA BRAMKA TEGO NIE MIAŁA: czytała przez „| awk", a AWK CZYTA WEJŚCIE DO KOŃCA — nie zamyka potoku wcześniej, więc SIGPIPE nie powstaje. Wdrożenia #68 i #69 działały nie ze szczęścia, tylko dlatego, że nie miały tej usterki. TEN BŁĄD WPROWADZIŁEM JA, RAZEM Z grep -q. | ROZWIĄZANIE: w bibliotece NIE MA JUŻ ANI JEDNEGO POTOKU — obecność metryki dopasowuje sama powłoka wzorcem na zmiennej (case), a awk dostaje wejście przez &lt;&lt;&lt; (here-string to przekierowanie, nie potok, więc pipefail nie ma czego zepsuć). | OKNO ZOSTAJE 180 s, ALE Z INNEGO POWODU: stare uzasadnienie („zmierzone 54 s × 3") było nieprawdziwe i zostało w komentarzu przekreślone, żeby nikt go nie odtworzył. Prawdziwy pomiar z logu Grafany: scheduler startuje ~4 s po restarcie. 60 s by wystarczyło; 180 s zostaje, bo CZEKANIE JEST DARMOWE (pętla kończy się w chwili zgodności), a nie dlatego, że tyle zmierzono. Ta liczba NIE MA maskować usterki odczytu — gdyby bramka znów czekała minutami, odpowiedzią jest diagnoza, nie 300 s. | DLACZEGO STRAŻNIK Z X-33 TEGO NIE ZŁAPAŁ — NAJWAŻNIEJSZA CZĘŚĆ: test był ZIELONY, a kod kłamał 60 razy z rzędu. Nie dlatego, że sprawdzał złą rzecz — dlatego, że JEGO ŚRODOWISKO RÓŻNIŁO SIĘ OD PRODUKCYJNEGO W DWÓCH WYMIARACH, KTÓRE DECYDOWAŁY O WYNIKU: (1) atrapa ważyła 200 bajtów, a prawdziwe /metrics setki kilobajtów — przy 200 bajtach printf zdąży zapisać wszystko do bufora, zanim grep się zamknie, więc SIGPIPE nigdy nie powstanie; (2) harness ustawiał set -u, a produkcja set -Eeuo pipefail — BEZ PIPEFAIL TA USTERKA NIE ISTNIEJE. Testowałem inną powłokę niż ta, która to uruchamia. To NOWA ODMIANA rodziny „test, który niczego nie dowodzi" (Z-01, H-20, M-06, X-28): nie fałszywa asercja, tylko FAŁSZYWE ŚRODOWISKO. Asercje były dobre, kłamały dane wejściowe. PYTANIE DO KAŻDEGO PRZYSZŁEGO HARNESSU: czym moja atrapa różni się od produkcji i czy któraś z tych różnic może decydować o wyniku? Rozmiar wejścia i flagi powłoki to nie szczegóły techniczne, tylko warunki, w których kod działa albo nie. | STRAŻNIK (13 asercji, było 11): atrapa waży ponad 64 KB i test to ASERTUJE, żeby nikt jej nie „uprościł"; harness ustawia dokładnie te flagi co skrypt wdrożeniowy; osobna asercja, że odpowiedź większa niż bufor potoku nie zamienia się w „brak metryki"; asercja o treści biblioteki (żadnego | grep, żadnego printf |) stojąca OBOK zachowaniowej, nie zamiast niej — tamta łapie usterkę, ta pilnuje, żeby nie wróciła tą samą drogą. | Czerwieni się na kodzie sprzed X-34: 7 z 13. | JAK ZAMKNĄĆ: zielone wdrożenie z tą biblioteką, z NISKIM numerem próby (kilkanaście sekund, nie pięćdziesiąt cztery). Dwucyfrowy numer oznaczałby, że nadal czegoś nie rozumiem. | DOWÓD D3 — WDROŻENIE #73 (2026-08-24, zielone, 3 m 08 s): „10:45:36 restart obserwowalności; 10:45:43 czekam na scheduler alertów (oczekuję 14 reguł, do 180 s); 10:45:53 OK: 14/14 reguł aktywnych (PRÓBA 4); 10:47:08 reguły liczą się bez błędów (0 → 0)". PRÓBA 4 — DZIESIĘĆ SEKUND. Przed wdrożeniem zapisałem FALSYFIKOWALNĄ PRZEPOWIEDNIĘ: jeśli diagnoza jest trafna, numer próby będzie NISKI, a dwucyfrowy oznaczałby, że nadal czegoś nie rozumiem. Wyszła czwarta próba i zgadza się co do rzędu wielkości z logiem samej Grafany (scheduler ~4 s po restarcie, takt 10 s) — czyli z jedynym pomiarem w całej tej historii, który nie pochodził z zepsutego odczytu. Porównanie czasów: #71 — 3 m 58 s (54 s czekania na własne kłamstwo), #72 — 4 m 54 s zakończone błędem, #73 — 3 m 08 s. Dokumentacja: docs/zadania/X-34-bramka-klamala-o-wlasnym-odczycie.md</t>
         </is>
       </c>
     </row>
